--- a/forecast-results/河北电网披露及电价预估数据-20261003.xlsx
+++ b/forecast-results/河北电网披露及电价预估数据-20261003.xlsx
@@ -3764,25 +3764,25 @@
         <v>1</v>
       </c>
       <c r="D2" s="21" t="n">
-        <v>13823</v>
+        <v>13236</v>
       </c>
       <c r="E2" s="22" t="n">
-        <v>14868</v>
+        <v>12015</v>
       </c>
       <c r="F2" s="21" t="n">
-        <v>13692</v>
+        <v>13746</v>
       </c>
       <c r="G2" s="21" t="n">
-        <v>12948</v>
+        <v>13176</v>
       </c>
       <c r="H2" s="22" t="n">
-        <v>13932</v>
+        <v>13662</v>
       </c>
       <c r="I2" s="21" t="n">
-        <v>13689</v>
+        <v>13464</v>
       </c>
       <c r="J2" s="22" t="n">
-        <v>13684</v>
+        <v>13435</v>
       </c>
     </row>
     <row r="3">
@@ -3796,25 +3796,25 @@
         <v>1</v>
       </c>
       <c r="D3" s="21" t="n">
-        <v>13787</v>
+        <v>13210</v>
       </c>
       <c r="E3" s="22" t="n">
-        <v>14814</v>
+        <v>11960</v>
       </c>
       <c r="F3" s="21" t="n">
-        <v>13647</v>
+        <v>13713</v>
       </c>
       <c r="G3" s="21" t="n">
-        <v>12912</v>
+        <v>13172</v>
       </c>
       <c r="H3" s="22" t="n">
-        <v>13954</v>
+        <v>13634</v>
       </c>
       <c r="I3" s="21" t="n">
-        <v>13621</v>
+        <v>13458</v>
       </c>
       <c r="J3" s="22" t="n">
-        <v>13651</v>
+        <v>13403</v>
       </c>
     </row>
     <row r="4">
@@ -3828,25 +3828,25 @@
         <v>1</v>
       </c>
       <c r="D4" s="21" t="n">
-        <v>13637</v>
+        <v>13123</v>
       </c>
       <c r="E4" s="22" t="n">
-        <v>14737</v>
+        <v>11884</v>
       </c>
       <c r="F4" s="21" t="n">
-        <v>13504</v>
+        <v>13578</v>
       </c>
       <c r="G4" s="21" t="n">
-        <v>12766</v>
+        <v>13234</v>
       </c>
       <c r="H4" s="22" t="n">
-        <v>13743</v>
+        <v>13427</v>
       </c>
       <c r="I4" s="21" t="n">
-        <v>13450</v>
+        <v>13308</v>
       </c>
       <c r="J4" s="22" t="n">
-        <v>13492</v>
+        <v>13396</v>
       </c>
     </row>
     <row r="5">
@@ -3860,25 +3860,25 @@
         <v>1</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>13384</v>
+        <v>12961</v>
       </c>
       <c r="E5" s="22" t="n">
-        <v>14629</v>
+        <v>11776</v>
       </c>
       <c r="F5" s="21" t="n">
-        <v>13410</v>
+        <v>13364</v>
       </c>
       <c r="G5" s="21" t="n">
-        <v>12078</v>
+        <v>13152</v>
       </c>
       <c r="H5" s="22" t="n">
-        <v>13523</v>
+        <v>13158</v>
       </c>
       <c r="I5" s="21" t="n">
-        <v>13199</v>
+        <v>13183</v>
       </c>
       <c r="J5" s="22" t="n">
-        <v>13293</v>
+        <v>13222</v>
       </c>
     </row>
     <row r="6">
@@ -3892,25 +3892,25 @@
         <v>2</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>13345</v>
+        <v>12901</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>14605</v>
+        <v>11751</v>
       </c>
       <c r="F6" s="21" t="n">
-        <v>13346</v>
+        <v>13295</v>
       </c>
       <c r="G6" s="21" t="n">
-        <v>12029</v>
+        <v>13134</v>
       </c>
       <c r="H6" s="22" t="n">
-        <v>13464</v>
+        <v>13056</v>
       </c>
       <c r="I6" s="21" t="n">
-        <v>13197</v>
+        <v>13100</v>
       </c>
       <c r="J6" s="22" t="n">
-        <v>13254</v>
+        <v>13159</v>
       </c>
     </row>
     <row r="7">
@@ -3924,25 +3924,25 @@
         <v>2</v>
       </c>
       <c r="D7" s="21" t="n">
-        <v>13310</v>
+        <v>12853</v>
       </c>
       <c r="E7" s="22" t="n">
-        <v>14557</v>
+        <v>11704</v>
       </c>
       <c r="F7" s="21" t="n">
-        <v>13316</v>
+        <v>13192</v>
       </c>
       <c r="G7" s="21" t="n">
-        <v>12029</v>
+        <v>13126</v>
       </c>
       <c r="H7" s="22" t="n">
-        <v>13399</v>
+        <v>12972</v>
       </c>
       <c r="I7" s="21" t="n">
-        <v>13191</v>
+        <v>13087</v>
       </c>
       <c r="J7" s="22" t="n">
-        <v>13195</v>
+        <v>13129</v>
       </c>
     </row>
     <row r="8">
@@ -3956,25 +3956,25 @@
         <v>2</v>
       </c>
       <c r="D8" s="21" t="n">
-        <v>13226</v>
+        <v>12687</v>
       </c>
       <c r="E8" s="22" t="n">
-        <v>14444</v>
+        <v>11591</v>
       </c>
       <c r="F8" s="21" t="n">
-        <v>13177</v>
+        <v>13207</v>
       </c>
       <c r="G8" s="21" t="n">
-        <v>11951</v>
+        <v>12931</v>
       </c>
       <c r="H8" s="22" t="n">
-        <v>13197</v>
+        <v>12540</v>
       </c>
       <c r="I8" s="21" t="n">
-        <v>13202</v>
+        <v>12989</v>
       </c>
       <c r="J8" s="22" t="n">
-        <v>13218</v>
+        <v>12944</v>
       </c>
     </row>
     <row r="9">
@@ -3988,25 +3988,25 @@
         <v>2</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>13137</v>
+        <v>12516</v>
       </c>
       <c r="E9" s="22" t="n">
-        <v>14303</v>
+        <v>11450</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>13225</v>
+        <v>13198</v>
       </c>
       <c r="G9" s="21" t="n">
-        <v>11951</v>
+        <v>12931</v>
       </c>
       <c r="H9" s="22" t="n">
-        <v>13057</v>
+        <v>12248</v>
       </c>
       <c r="I9" s="21" t="n">
-        <v>13083</v>
+        <v>12778</v>
       </c>
       <c r="J9" s="22" t="n">
-        <v>13037</v>
+        <v>12573</v>
       </c>
     </row>
     <row r="10">
@@ -4020,25 +4020,25 @@
         <v>3</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>14141</v>
+        <v>13215</v>
       </c>
       <c r="E10" s="22" t="n">
-        <v>15260</v>
+        <v>12407</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>14172</v>
+        <v>14033</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>13153</v>
+        <v>13310</v>
       </c>
       <c r="H10" s="22" t="n">
-        <v>14052</v>
+        <v>13492</v>
       </c>
       <c r="I10" s="21" t="n">
-        <v>13994</v>
+        <v>13180</v>
       </c>
       <c r="J10" s="22" t="n">
-        <v>14065</v>
+        <v>12914</v>
       </c>
     </row>
     <row r="11">
@@ -4052,25 +4052,25 @@
         <v>3</v>
       </c>
       <c r="D11" s="21" t="n">
-        <v>14075</v>
+        <v>13200</v>
       </c>
       <c r="E11" s="22" t="n">
-        <v>15388</v>
+        <v>12535</v>
       </c>
       <c r="F11" s="21" t="n">
-        <v>14109</v>
+        <v>13937</v>
       </c>
       <c r="G11" s="21" t="n">
-        <v>12991</v>
+        <v>13243</v>
       </c>
       <c r="H11" s="22" t="n">
-        <v>13942</v>
+        <v>13327</v>
       </c>
       <c r="I11" s="21" t="n">
-        <v>13918</v>
+        <v>13251</v>
       </c>
       <c r="J11" s="22" t="n">
-        <v>13932</v>
+        <v>12941</v>
       </c>
     </row>
     <row r="12">
@@ -4084,25 +4084,25 @@
         <v>3</v>
       </c>
       <c r="D12" s="21" t="n">
-        <v>13988</v>
+        <v>13114</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>15297</v>
+        <v>12444</v>
       </c>
       <c r="F12" s="21" t="n">
-        <v>14044</v>
+        <v>13860</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>12970</v>
+        <v>13222</v>
       </c>
       <c r="H12" s="22" t="n">
-        <v>13812</v>
+        <v>13190</v>
       </c>
       <c r="I12" s="21" t="n">
-        <v>13774</v>
+        <v>13138</v>
       </c>
       <c r="J12" s="22" t="n">
-        <v>13862</v>
+        <v>12867</v>
       </c>
     </row>
     <row r="13">
@@ -4116,25 +4116,25 @@
         <v>3</v>
       </c>
       <c r="D13" s="21" t="n">
-        <v>13904</v>
+        <v>13033</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>15207</v>
+        <v>12354</v>
       </c>
       <c r="F13" s="21" t="n">
-        <v>13666</v>
+        <v>13617</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>12989</v>
+        <v>13182</v>
       </c>
       <c r="H13" s="22" t="n">
-        <v>13797</v>
+        <v>13167</v>
       </c>
       <c r="I13" s="21" t="n">
-        <v>13745</v>
+        <v>13059</v>
       </c>
       <c r="J13" s="22" t="n">
-        <v>13874</v>
+        <v>12864</v>
       </c>
     </row>
     <row r="14">
@@ -4148,25 +4148,25 @@
         <v>4</v>
       </c>
       <c r="D14" s="21" t="n">
-        <v>13888</v>
+        <v>13043</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>15222</v>
+        <v>12368</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>13560</v>
+        <v>13455</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>12989</v>
+        <v>13182</v>
       </c>
       <c r="H14" s="22" t="n">
-        <v>13694</v>
+        <v>13124</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>13710</v>
+        <v>13079</v>
       </c>
       <c r="J14" s="22" t="n">
-        <v>14004</v>
+        <v>13096</v>
       </c>
     </row>
     <row r="15">
@@ -4180,25 +4180,25 @@
         <v>4</v>
       </c>
       <c r="D15" s="21" t="n">
-        <v>13880</v>
+        <v>13102</v>
       </c>
       <c r="E15" s="22" t="n">
-        <v>15199</v>
+        <v>12346</v>
       </c>
       <c r="F15" s="21" t="n">
-        <v>13570</v>
+        <v>13601</v>
       </c>
       <c r="G15" s="21" t="n">
-        <v>12907</v>
+        <v>13133</v>
       </c>
       <c r="H15" s="22" t="n">
-        <v>13699</v>
+        <v>13202</v>
       </c>
       <c r="I15" s="21" t="n">
-        <v>13766</v>
+        <v>13221</v>
       </c>
       <c r="J15" s="22" t="n">
-        <v>13983</v>
+        <v>13153</v>
       </c>
     </row>
     <row r="16">
@@ -4212,25 +4212,25 @@
         <v>4</v>
       </c>
       <c r="D16" s="21" t="n">
-        <v>13840</v>
+        <v>13121</v>
       </c>
       <c r="E16" s="22" t="n">
-        <v>15128</v>
+        <v>12275</v>
       </c>
       <c r="F16" s="21" t="n">
-        <v>13626</v>
+        <v>13652</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>12861</v>
+        <v>13313</v>
       </c>
       <c r="H16" s="22" t="n">
-        <v>13634</v>
+        <v>13139</v>
       </c>
       <c r="I16" s="21" t="n">
-        <v>13690</v>
+        <v>13274</v>
       </c>
       <c r="J16" s="22" t="n">
-        <v>13945</v>
+        <v>13133</v>
       </c>
     </row>
     <row r="17">
@@ -4244,25 +4244,25 @@
         <v>4</v>
       </c>
       <c r="D17" s="21" t="n">
-        <v>13600</v>
+        <v>12979</v>
       </c>
       <c r="E17" s="22" t="n">
-        <v>15032</v>
+        <v>12179</v>
       </c>
       <c r="F17" s="21" t="n">
-        <v>13531</v>
+        <v>13441</v>
       </c>
       <c r="G17" s="21" t="n">
-        <v>12061</v>
+        <v>13111</v>
       </c>
       <c r="H17" s="22" t="n">
-        <v>13507</v>
+        <v>12955</v>
       </c>
       <c r="I17" s="21" t="n">
-        <v>13511</v>
+        <v>13202</v>
       </c>
       <c r="J17" s="22" t="n">
-        <v>13753</v>
+        <v>13038</v>
       </c>
     </row>
     <row r="18">
@@ -4276,25 +4276,25 @@
         <v>5</v>
       </c>
       <c r="D18" s="21" t="n">
-        <v>13556</v>
+        <v>12931</v>
       </c>
       <c r="E18" s="22" t="n">
-        <v>15005</v>
+        <v>12151</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>13498</v>
+        <v>13469</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>12011</v>
+        <v>13093</v>
       </c>
       <c r="H18" s="22" t="n">
-        <v>13406</v>
+        <v>12794</v>
       </c>
       <c r="I18" s="21" t="n">
-        <v>13503</v>
+        <v>13102</v>
       </c>
       <c r="J18" s="22" t="n">
-        <v>13706</v>
+        <v>13027</v>
       </c>
     </row>
     <row r="19">
@@ -4308,25 +4308,25 @@
         <v>5</v>
       </c>
       <c r="D19" s="21" t="n">
-        <v>13547</v>
+        <v>12866</v>
       </c>
       <c r="E19" s="22" t="n">
-        <v>14929</v>
+        <v>12076</v>
       </c>
       <c r="F19" s="21" t="n">
-        <v>13533</v>
+        <v>13461</v>
       </c>
       <c r="G19" s="21" t="n">
-        <v>12026</v>
+        <v>12972</v>
       </c>
       <c r="H19" s="22" t="n">
-        <v>13339</v>
+        <v>12715</v>
       </c>
       <c r="I19" s="21" t="n">
-        <v>13524</v>
+        <v>13042</v>
       </c>
       <c r="J19" s="22" t="n">
-        <v>13730</v>
+        <v>12975</v>
       </c>
     </row>
     <row r="20">
@@ -4340,25 +4340,25 @@
         <v>5</v>
       </c>
       <c r="D20" s="21" t="n">
-        <v>13498</v>
+        <v>12824</v>
       </c>
       <c r="E20" s="22" t="n">
-        <v>14880</v>
+        <v>12027</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>13479</v>
+        <v>13389</v>
       </c>
       <c r="G20" s="21" t="n">
-        <v>12017</v>
+        <v>12972</v>
       </c>
       <c r="H20" s="22" t="n">
-        <v>13245</v>
+        <v>12622</v>
       </c>
       <c r="I20" s="21" t="n">
-        <v>13475</v>
+        <v>13013</v>
       </c>
       <c r="J20" s="22" t="n">
-        <v>13693</v>
+        <v>12969</v>
       </c>
     </row>
     <row r="21">
@@ -4372,25 +4372,25 @@
         <v>5</v>
       </c>
       <c r="D21" s="21" t="n">
-        <v>13432</v>
+        <v>12777</v>
       </c>
       <c r="E21" s="22" t="n">
-        <v>14837</v>
+        <v>11983</v>
       </c>
       <c r="F21" s="21" t="n">
-        <v>13448</v>
+        <v>13384</v>
       </c>
       <c r="G21" s="21" t="n">
-        <v>11916</v>
+        <v>12891</v>
       </c>
       <c r="H21" s="22" t="n">
-        <v>13194</v>
+        <v>12549</v>
       </c>
       <c r="I21" s="21" t="n">
-        <v>13374</v>
+        <v>12978</v>
       </c>
       <c r="J21" s="22" t="n">
-        <v>13617</v>
+        <v>12919</v>
       </c>
     </row>
     <row r="22">
@@ -4404,25 +4404,25 @@
         <v>6</v>
       </c>
       <c r="D22" s="21" t="n">
-        <v>13437</v>
+        <v>12752</v>
       </c>
       <c r="E22" s="22" t="n">
-        <v>14867</v>
+        <v>12014</v>
       </c>
       <c r="F22" s="21" t="n">
-        <v>13450</v>
+        <v>13314</v>
       </c>
       <c r="G22" s="21" t="n">
-        <v>11929</v>
+        <v>12891</v>
       </c>
       <c r="H22" s="22" t="n">
-        <v>13170</v>
+        <v>12484</v>
       </c>
       <c r="I22" s="21" t="n">
-        <v>13396</v>
+        <v>12957</v>
       </c>
       <c r="J22" s="22" t="n">
-        <v>13606</v>
+        <v>12893</v>
       </c>
     </row>
     <row r="23">
@@ -4436,25 +4436,25 @@
         <v>6</v>
       </c>
       <c r="D23" s="21" t="n">
-        <v>13429</v>
+        <v>12727</v>
       </c>
       <c r="E23" s="22" t="n">
-        <v>14837</v>
+        <v>11984</v>
       </c>
       <c r="F23" s="21" t="n">
-        <v>13470</v>
+        <v>13319</v>
       </c>
       <c r="G23" s="21" t="n">
-        <v>11897</v>
+        <v>12859</v>
       </c>
       <c r="H23" s="22" t="n">
-        <v>13131</v>
+        <v>12335</v>
       </c>
       <c r="I23" s="21" t="n">
-        <v>13416</v>
+        <v>12986</v>
       </c>
       <c r="J23" s="22" t="n">
-        <v>13618</v>
+        <v>12918</v>
       </c>
     </row>
     <row r="24">
@@ -4468,25 +4468,25 @@
         <v>6</v>
       </c>
       <c r="D24" s="21" t="n">
-        <v>13438</v>
+        <v>12718</v>
       </c>
       <c r="E24" s="22" t="n">
-        <v>14819</v>
+        <v>11966</v>
       </c>
       <c r="F24" s="21" t="n">
-        <v>13460</v>
+        <v>13311</v>
       </c>
       <c r="G24" s="21" t="n">
-        <v>11897</v>
+        <v>12859</v>
       </c>
       <c r="H24" s="22" t="n">
-        <v>13230</v>
+        <v>12464</v>
       </c>
       <c r="I24" s="21" t="n">
-        <v>13403</v>
+        <v>12931</v>
       </c>
       <c r="J24" s="22" t="n">
-        <v>13615</v>
+        <v>12822</v>
       </c>
     </row>
     <row r="25">
@@ -4500,25 +4500,25 @@
         <v>6</v>
       </c>
       <c r="D25" s="21" t="n">
-        <v>13439</v>
+        <v>12721</v>
       </c>
       <c r="E25" s="22" t="n">
-        <v>14804</v>
+        <v>11950</v>
       </c>
       <c r="F25" s="21" t="n">
-        <v>13498</v>
+        <v>13316</v>
       </c>
       <c r="G25" s="21" t="n">
-        <v>11897</v>
+        <v>12859</v>
       </c>
       <c r="H25" s="22" t="n">
-        <v>13218</v>
+        <v>12470</v>
       </c>
       <c r="I25" s="21" t="n">
-        <v>13398</v>
+        <v>12930</v>
       </c>
       <c r="J25" s="22" t="n">
-        <v>13614</v>
+        <v>12844</v>
       </c>
     </row>
     <row r="26">
@@ -4532,25 +4532,25 @@
         <v>7</v>
       </c>
       <c r="D26" s="21" t="n">
-        <v>13365</v>
+        <v>12758</v>
       </c>
       <c r="E26" s="22" t="n">
-        <v>14384</v>
+        <v>11531</v>
       </c>
       <c r="F26" s="21" t="n">
-        <v>13387</v>
+        <v>13313</v>
       </c>
       <c r="G26" s="21" t="n">
-        <v>11978</v>
+        <v>12987</v>
       </c>
       <c r="H26" s="22" t="n">
-        <v>13351</v>
+        <v>12765</v>
       </c>
       <c r="I26" s="21" t="n">
-        <v>13417</v>
+        <v>13085</v>
       </c>
       <c r="J26" s="22" t="n">
-        <v>13511</v>
+        <v>12958</v>
       </c>
     </row>
     <row r="27">
@@ -4564,25 +4564,25 @@
         <v>7</v>
       </c>
       <c r="D27" s="21" t="n">
-        <v>13331</v>
+        <v>12660</v>
       </c>
       <c r="E27" s="22" t="n">
-        <v>14347</v>
+        <v>11493</v>
       </c>
       <c r="F27" s="21" t="n">
-        <v>13233</v>
+        <v>13209</v>
       </c>
       <c r="G27" s="21" t="n">
-        <v>12238</v>
+        <v>12624</v>
       </c>
       <c r="H27" s="22" t="n">
-        <v>13387</v>
+        <v>12782</v>
       </c>
       <c r="I27" s="21" t="n">
-        <v>13222</v>
+        <v>12913</v>
       </c>
       <c r="J27" s="22" t="n">
-        <v>13418</v>
+        <v>13007</v>
       </c>
     </row>
     <row r="28">
@@ -4596,25 +4596,25 @@
         <v>7</v>
       </c>
       <c r="D28" s="21" t="n">
-        <v>13155</v>
+        <v>12419</v>
       </c>
       <c r="E28" s="22" t="n">
-        <v>14186</v>
+        <v>11333</v>
       </c>
       <c r="F28" s="21" t="n">
-        <v>13108</v>
+        <v>12718</v>
       </c>
       <c r="G28" s="21" t="n">
-        <v>11881</v>
+        <v>12663</v>
       </c>
       <c r="H28" s="22" t="n">
-        <v>13156</v>
+        <v>12516</v>
       </c>
       <c r="I28" s="21" t="n">
-        <v>13117</v>
+        <v>12856</v>
       </c>
       <c r="J28" s="22" t="n">
-        <v>13324</v>
+        <v>12521</v>
       </c>
     </row>
     <row r="29">
@@ -4628,25 +4628,25 @@
         <v>7</v>
       </c>
       <c r="D29" s="21" t="n">
-        <v>12884</v>
+        <v>11883</v>
       </c>
       <c r="E29" s="22" t="n">
-        <v>13858</v>
+        <v>11005</v>
       </c>
       <c r="F29" s="21" t="n">
-        <v>12964</v>
+        <v>12254</v>
       </c>
       <c r="G29" s="21" t="n">
-        <v>11871</v>
+        <v>12009</v>
       </c>
       <c r="H29" s="22" t="n">
-        <v>12816</v>
+        <v>12054</v>
       </c>
       <c r="I29" s="21" t="n">
-        <v>12632</v>
+        <v>12111</v>
       </c>
       <c r="J29" s="22" t="n">
-        <v>13024</v>
+        <v>11931</v>
       </c>
     </row>
     <row r="30">
@@ -4660,25 +4660,25 @@
         <v>8</v>
       </c>
       <c r="D30" s="21" t="n">
-        <v>12593</v>
+        <v>11453</v>
       </c>
       <c r="E30" s="22" t="n">
-        <v>13471</v>
+        <v>10617</v>
       </c>
       <c r="F30" s="21" t="n">
-        <v>12621</v>
+        <v>11713</v>
       </c>
       <c r="G30" s="21" t="n">
-        <v>11791</v>
+        <v>11702</v>
       </c>
       <c r="H30" s="22" t="n">
-        <v>12406</v>
+        <v>11324</v>
       </c>
       <c r="I30" s="21" t="n">
-        <v>12436</v>
+        <v>11879</v>
       </c>
       <c r="J30" s="22" t="n">
-        <v>12714</v>
+        <v>11555</v>
       </c>
     </row>
     <row r="31">
@@ -4692,25 +4692,25 @@
         <v>8</v>
       </c>
       <c r="D31" s="21" t="n">
-        <v>12036</v>
+        <v>10635</v>
       </c>
       <c r="E31" s="22" t="n">
-        <v>12929</v>
+        <v>10075</v>
       </c>
       <c r="F31" s="21" t="n">
-        <v>11813</v>
+        <v>10883</v>
       </c>
       <c r="G31" s="21" t="n">
-        <v>11525</v>
+        <v>11273</v>
       </c>
       <c r="H31" s="22" t="n">
-        <v>11883</v>
+        <v>10334</v>
       </c>
       <c r="I31" s="21" t="n">
-        <v>11794</v>
+        <v>10688</v>
       </c>
       <c r="J31" s="22" t="n">
-        <v>12178</v>
+        <v>10621</v>
       </c>
     </row>
     <row r="32">
@@ -4724,25 +4724,25 @@
         <v>8</v>
       </c>
       <c r="D32" s="21" t="n">
-        <v>11204</v>
+        <v>9345</v>
       </c>
       <c r="E32" s="22" t="n">
-        <v>12263</v>
+        <v>9410</v>
       </c>
       <c r="F32" s="21" t="n">
-        <v>10932</v>
+        <v>9636</v>
       </c>
       <c r="G32" s="21" t="n">
-        <v>10903</v>
+        <v>9642</v>
       </c>
       <c r="H32" s="22" t="n">
-        <v>11164</v>
+        <v>9103</v>
       </c>
       <c r="I32" s="21" t="n">
-        <v>10793</v>
+        <v>9203</v>
       </c>
       <c r="J32" s="22" t="n">
-        <v>11076</v>
+        <v>9078</v>
       </c>
     </row>
     <row r="33">
@@ -4756,25 +4756,25 @@
         <v>8</v>
       </c>
       <c r="D33" s="21" t="n">
-        <v>10749</v>
+        <v>8569</v>
       </c>
       <c r="E33" s="22" t="n">
-        <v>11503</v>
+        <v>8650</v>
       </c>
       <c r="F33" s="21" t="n">
-        <v>10829</v>
+        <v>8767</v>
       </c>
       <c r="G33" s="21" t="n">
-        <v>10424</v>
+        <v>8997</v>
       </c>
       <c r="H33" s="22" t="n">
-        <v>10586</v>
+        <v>8242</v>
       </c>
       <c r="I33" s="21" t="n">
-        <v>10424</v>
+        <v>8346</v>
       </c>
       <c r="J33" s="22" t="n">
-        <v>10644</v>
+        <v>8420</v>
       </c>
     </row>
     <row r="34">
@@ -4788,25 +4788,25 @@
         <v>9</v>
       </c>
       <c r="D34" s="21" t="n">
-        <v>10377</v>
+        <v>7753</v>
       </c>
       <c r="E34" s="22" t="n">
-        <v>10853</v>
+        <v>8000</v>
       </c>
       <c r="F34" s="21" t="n">
-        <v>10933</v>
+        <v>8113</v>
       </c>
       <c r="G34" s="21" t="n">
-        <v>9828</v>
+        <v>7780</v>
       </c>
       <c r="H34" s="22" t="n">
-        <v>10463</v>
+        <v>7785</v>
       </c>
       <c r="I34" s="21" t="n">
-        <v>9921</v>
+        <v>7389</v>
       </c>
       <c r="J34" s="22" t="n">
-        <v>10176</v>
+        <v>7420</v>
       </c>
     </row>
     <row r="35">
@@ -4820,25 +4820,25 @@
         <v>9</v>
       </c>
       <c r="D35" s="21" t="n">
-        <v>10067</v>
+        <v>7418</v>
       </c>
       <c r="E35" s="22" t="n">
-        <v>10212</v>
+        <v>7359</v>
       </c>
       <c r="F35" s="21" t="n">
-        <v>10418</v>
+        <v>7860</v>
       </c>
       <c r="G35" s="21" t="n">
-        <v>9541</v>
+        <v>7754</v>
       </c>
       <c r="H35" s="22" t="n">
-        <v>10421</v>
+        <v>7401</v>
       </c>
       <c r="I35" s="21" t="n">
-        <v>9801</v>
+        <v>7062</v>
       </c>
       <c r="J35" s="22" t="n">
-        <v>9961</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="36">
@@ -4852,25 +4852,25 @@
         <v>9</v>
       </c>
       <c r="D36" s="21" t="n">
-        <v>9936</v>
+        <v>7311</v>
       </c>
       <c r="E36" s="22" t="n">
-        <v>9581</v>
+        <v>6727</v>
       </c>
       <c r="F36" s="21" t="n">
-        <v>10310</v>
+        <v>7799</v>
       </c>
       <c r="G36" s="21" t="n">
-        <v>9476</v>
+        <v>7733</v>
       </c>
       <c r="H36" s="22" t="n">
-        <v>10485</v>
+        <v>7370</v>
       </c>
       <c r="I36" s="21" t="n">
-        <v>9812</v>
+        <v>7089</v>
       </c>
       <c r="J36" s="22" t="n">
-        <v>9945</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="37">
@@ -4884,25 +4884,25 @@
         <v>9</v>
       </c>
       <c r="D37" s="21" t="n">
-        <v>9790</v>
+        <v>7052</v>
       </c>
       <c r="E37" s="22" t="n">
-        <v>8984</v>
+        <v>6131</v>
       </c>
       <c r="F37" s="21" t="n">
-        <v>10223</v>
+        <v>7730</v>
       </c>
       <c r="G37" s="21" t="n">
-        <v>9476</v>
+        <v>7725</v>
       </c>
       <c r="H37" s="22" t="n">
-        <v>10434</v>
+        <v>6797</v>
       </c>
       <c r="I37" s="21" t="n">
-        <v>9814</v>
+        <v>7031</v>
       </c>
       <c r="J37" s="22" t="n">
-        <v>9849</v>
+        <v>6979</v>
       </c>
     </row>
     <row r="38">
@@ -4916,25 +4916,25 @@
         <v>10</v>
       </c>
       <c r="D38" s="21" t="n">
-        <v>9693</v>
+        <v>6957</v>
       </c>
       <c r="E38" s="22" t="n">
-        <v>8526</v>
+        <v>5672</v>
       </c>
       <c r="F38" s="21" t="n">
-        <v>10078</v>
+        <v>7691</v>
       </c>
       <c r="G38" s="21" t="n">
-        <v>9476</v>
+        <v>7725</v>
       </c>
       <c r="H38" s="22" t="n">
-        <v>10402</v>
+        <v>6600</v>
       </c>
       <c r="I38" s="21" t="n">
-        <v>9844</v>
+        <v>7113</v>
       </c>
       <c r="J38" s="22" t="n">
-        <v>9910</v>
+        <v>7055</v>
       </c>
     </row>
     <row r="39">
@@ -4948,25 +4948,25 @@
         <v>10</v>
       </c>
       <c r="D39" s="21" t="n">
-        <v>9568</v>
+        <v>6840</v>
       </c>
       <c r="E39" s="22" t="n">
-        <v>8062</v>
+        <v>5209</v>
       </c>
       <c r="F39" s="21" t="n">
-        <v>9993</v>
+        <v>7641</v>
       </c>
       <c r="G39" s="21" t="n">
-        <v>9482</v>
+        <v>7718</v>
       </c>
       <c r="H39" s="22" t="n">
-        <v>10415</v>
+        <v>6596</v>
       </c>
       <c r="I39" s="21" t="n">
-        <v>9714</v>
+        <v>7046</v>
       </c>
       <c r="J39" s="22" t="n">
-        <v>9853</v>
+        <v>6974</v>
       </c>
     </row>
     <row r="40">
@@ -4980,25 +4980,25 @@
         <v>10</v>
       </c>
       <c r="D40" s="21" t="n">
-        <v>9455</v>
+        <v>6723</v>
       </c>
       <c r="E40" s="22" t="n">
-        <v>7655</v>
+        <v>4801</v>
       </c>
       <c r="F40" s="21" t="n">
-        <v>9875</v>
+        <v>7579</v>
       </c>
       <c r="G40" s="21" t="n">
-        <v>9510</v>
+        <v>7715</v>
       </c>
       <c r="H40" s="22" t="n">
-        <v>10382</v>
+        <v>6550</v>
       </c>
       <c r="I40" s="21" t="n">
-        <v>9655</v>
+        <v>6950</v>
       </c>
       <c r="J40" s="22" t="n">
-        <v>9795</v>
+        <v>6916</v>
       </c>
     </row>
     <row r="41">
@@ -5012,25 +5012,25 @@
         <v>10</v>
       </c>
       <c r="D41" s="21" t="n">
-        <v>9375</v>
+        <v>6673</v>
       </c>
       <c r="E41" s="22" t="n">
-        <v>7312</v>
+        <v>4459</v>
       </c>
       <c r="F41" s="21" t="n">
-        <v>9852</v>
+        <v>7658</v>
       </c>
       <c r="G41" s="21" t="n">
-        <v>9510</v>
+        <v>7715</v>
       </c>
       <c r="H41" s="22" t="n">
-        <v>10385</v>
+        <v>6555</v>
       </c>
       <c r="I41" s="21" t="n">
-        <v>9619</v>
+        <v>6935</v>
       </c>
       <c r="J41" s="22" t="n">
-        <v>9737</v>
+        <v>6912</v>
       </c>
     </row>
     <row r="42">
@@ -5044,25 +5044,25 @@
         <v>11</v>
       </c>
       <c r="D42" s="21" t="n">
-        <v>9326</v>
+        <v>6652</v>
       </c>
       <c r="E42" s="22" t="n">
-        <v>7079</v>
+        <v>4226</v>
       </c>
       <c r="F42" s="21" t="n">
-        <v>9765</v>
+        <v>7631</v>
       </c>
       <c r="G42" s="21" t="n">
-        <v>9510</v>
+        <v>7715</v>
       </c>
       <c r="H42" s="22" t="n">
-        <v>10382</v>
+        <v>6585</v>
       </c>
       <c r="I42" s="21" t="n">
-        <v>9693</v>
+        <v>7047</v>
       </c>
       <c r="J42" s="22" t="n">
-        <v>9713</v>
+        <v>6926</v>
       </c>
     </row>
     <row r="43">
@@ -5076,25 +5076,25 @@
         <v>11</v>
       </c>
       <c r="D43" s="21" t="n">
-        <v>9267</v>
+        <v>6605</v>
       </c>
       <c r="E43" s="22" t="n">
-        <v>6785</v>
+        <v>3931</v>
       </c>
       <c r="F43" s="21" t="n">
-        <v>9779</v>
+        <v>7640</v>
       </c>
       <c r="G43" s="21" t="n">
-        <v>9510</v>
+        <v>7716</v>
       </c>
       <c r="H43" s="22" t="n">
-        <v>10349</v>
+        <v>6590</v>
       </c>
       <c r="I43" s="21" t="n">
-        <v>9681</v>
+        <v>7050</v>
       </c>
       <c r="J43" s="22" t="n">
-        <v>9702</v>
+        <v>6939</v>
       </c>
     </row>
     <row r="44">
@@ -5108,25 +5108,25 @@
         <v>11</v>
       </c>
       <c r="D44" s="21" t="n">
-        <v>9232</v>
+        <v>6585</v>
       </c>
       <c r="E44" s="22" t="n">
-        <v>6578</v>
+        <v>3725</v>
       </c>
       <c r="F44" s="21" t="n">
-        <v>9782</v>
+        <v>7649</v>
       </c>
       <c r="G44" s="21" t="n">
-        <v>9510</v>
+        <v>7716</v>
       </c>
       <c r="H44" s="22" t="n">
-        <v>10370</v>
+        <v>6637</v>
       </c>
       <c r="I44" s="21" t="n">
-        <v>9684</v>
+        <v>7056</v>
       </c>
       <c r="J44" s="22" t="n">
-        <v>9688</v>
+        <v>6980</v>
       </c>
     </row>
     <row r="45">
@@ -5140,25 +5140,25 @@
         <v>11</v>
       </c>
       <c r="D45" s="21" t="n">
-        <v>9216</v>
+        <v>6560</v>
       </c>
       <c r="E45" s="22" t="n">
-        <v>6547</v>
+        <v>3694</v>
       </c>
       <c r="F45" s="21" t="n">
-        <v>9821</v>
+        <v>7621</v>
       </c>
       <c r="G45" s="21" t="n">
-        <v>9510</v>
+        <v>7716</v>
       </c>
       <c r="H45" s="22" t="n">
-        <v>10325</v>
+        <v>6644</v>
       </c>
       <c r="I45" s="21" t="n">
-        <v>9655</v>
+        <v>7015</v>
       </c>
       <c r="J45" s="22" t="n">
-        <v>9660</v>
+        <v>6925</v>
       </c>
     </row>
     <row r="46">
@@ -5172,25 +5172,25 @@
         <v>12</v>
       </c>
       <c r="D46" s="21" t="n">
-        <v>9298</v>
+        <v>6668</v>
       </c>
       <c r="E46" s="22" t="n">
-        <v>7210</v>
+        <v>4357</v>
       </c>
       <c r="F46" s="21" t="n">
-        <v>9660</v>
+        <v>7609</v>
       </c>
       <c r="G46" s="21" t="n">
-        <v>9517</v>
+        <v>7716</v>
       </c>
       <c r="H46" s="22" t="n">
-        <v>10373</v>
+        <v>6712</v>
       </c>
       <c r="I46" s="21" t="n">
-        <v>9595</v>
+        <v>6945</v>
       </c>
       <c r="J46" s="22" t="n">
-        <v>9610</v>
+        <v>6880</v>
       </c>
     </row>
     <row r="47">
@@ -5204,25 +5204,25 @@
         <v>12</v>
       </c>
       <c r="D47" s="21" t="n">
-        <v>9295</v>
+        <v>6653</v>
       </c>
       <c r="E47" s="22" t="n">
-        <v>7223</v>
+        <v>4369</v>
       </c>
       <c r="F47" s="21" t="n">
-        <v>9696</v>
+        <v>7629</v>
       </c>
       <c r="G47" s="21" t="n">
-        <v>9510</v>
+        <v>7716</v>
       </c>
       <c r="H47" s="22" t="n">
-        <v>10207</v>
+        <v>6524</v>
       </c>
       <c r="I47" s="21" t="n">
-        <v>9663</v>
+        <v>7008</v>
       </c>
       <c r="J47" s="22" t="n">
-        <v>9645</v>
+        <v>6878</v>
       </c>
     </row>
     <row r="48">
@@ -5236,25 +5236,25 @@
         <v>12</v>
       </c>
       <c r="D48" s="21" t="n">
-        <v>9303</v>
+        <v>6637</v>
       </c>
       <c r="E48" s="22" t="n">
-        <v>7114</v>
+        <v>4261</v>
       </c>
       <c r="F48" s="21" t="n">
-        <v>9729</v>
+        <v>7620</v>
       </c>
       <c r="G48" s="21" t="n">
-        <v>9510</v>
+        <v>7716</v>
       </c>
       <c r="H48" s="22" t="n">
-        <v>10255</v>
+        <v>6559</v>
       </c>
       <c r="I48" s="21" t="n">
-        <v>9706</v>
+        <v>7000</v>
       </c>
       <c r="J48" s="22" t="n">
-        <v>9685</v>
+        <v>6876</v>
       </c>
     </row>
     <row r="49">
@@ -5268,25 +5268,25 @@
         <v>12</v>
       </c>
       <c r="D49" s="21" t="n">
-        <v>9248</v>
+        <v>6606</v>
       </c>
       <c r="E49" s="22" t="n">
-        <v>6745</v>
+        <v>3892</v>
       </c>
       <c r="F49" s="21" t="n">
-        <v>9747</v>
+        <v>7613</v>
       </c>
       <c r="G49" s="21" t="n">
-        <v>9493</v>
+        <v>7716</v>
       </c>
       <c r="H49" s="22" t="n">
-        <v>10281</v>
+        <v>6558</v>
       </c>
       <c r="I49" s="21" t="n">
-        <v>9758</v>
+        <v>7158</v>
       </c>
       <c r="J49" s="22" t="n">
-        <v>9670</v>
+        <v>6940</v>
       </c>
     </row>
     <row r="50">
@@ -5300,25 +5300,25 @@
         <v>13</v>
       </c>
       <c r="D50" s="21" t="n">
-        <v>9216</v>
+        <v>6595</v>
       </c>
       <c r="E50" s="22" t="n">
-        <v>6614</v>
+        <v>3761</v>
       </c>
       <c r="F50" s="21" t="n">
-        <v>9769</v>
+        <v>7634</v>
       </c>
       <c r="G50" s="21" t="n">
-        <v>9522</v>
+        <v>7716</v>
       </c>
       <c r="H50" s="22" t="n">
-        <v>10167</v>
+        <v>6479</v>
       </c>
       <c r="I50" s="21" t="n">
-        <v>9735</v>
+        <v>7187</v>
       </c>
       <c r="J50" s="22" t="n">
-        <v>9703</v>
+        <v>7042</v>
       </c>
     </row>
     <row r="51">
@@ -5332,25 +5332,25 @@
         <v>13</v>
       </c>
       <c r="D51" s="21" t="n">
-        <v>9219</v>
+        <v>6602</v>
       </c>
       <c r="E51" s="22" t="n">
-        <v>6552</v>
+        <v>3699</v>
       </c>
       <c r="F51" s="21" t="n">
-        <v>9778</v>
+        <v>7640</v>
       </c>
       <c r="G51" s="21" t="n">
-        <v>9522</v>
+        <v>7716</v>
       </c>
       <c r="H51" s="22" t="n">
-        <v>10247</v>
+        <v>6550</v>
       </c>
       <c r="I51" s="21" t="n">
-        <v>9699</v>
+        <v>7175</v>
       </c>
       <c r="J51" s="22" t="n">
-        <v>9734</v>
+        <v>7085</v>
       </c>
     </row>
     <row r="52">
@@ -5364,25 +5364,25 @@
         <v>13</v>
       </c>
       <c r="D52" s="21" t="n">
-        <v>9195</v>
+        <v>6582</v>
       </c>
       <c r="E52" s="22" t="n">
-        <v>6554</v>
+        <v>3701</v>
       </c>
       <c r="F52" s="21" t="n">
-        <v>9776</v>
+        <v>7633</v>
       </c>
       <c r="G52" s="21" t="n">
-        <v>9522</v>
+        <v>7716</v>
       </c>
       <c r="H52" s="22" t="n">
-        <v>10156</v>
+        <v>6471</v>
       </c>
       <c r="I52" s="21" t="n">
-        <v>9688</v>
+        <v>7179</v>
       </c>
       <c r="J52" s="22" t="n">
-        <v>9690</v>
+        <v>7044</v>
       </c>
     </row>
     <row r="53">
@@ -5396,25 +5396,25 @@
         <v>13</v>
       </c>
       <c r="D53" s="21" t="n">
-        <v>9195</v>
+        <v>6594</v>
       </c>
       <c r="E53" s="22" t="n">
-        <v>6708</v>
+        <v>3854</v>
       </c>
       <c r="F53" s="21" t="n">
-        <v>9764</v>
+        <v>7616</v>
       </c>
       <c r="G53" s="21" t="n">
-        <v>9529</v>
+        <v>7716</v>
       </c>
       <c r="H53" s="22" t="n">
-        <v>10144</v>
+        <v>6459</v>
       </c>
       <c r="I53" s="21" t="n">
-        <v>9602</v>
+        <v>7116</v>
       </c>
       <c r="J53" s="22" t="n">
-        <v>9634</v>
+        <v>7041</v>
       </c>
     </row>
     <row r="54">
@@ -5428,25 +5428,25 @@
         <v>14</v>
       </c>
       <c r="D54" s="21" t="n">
-        <v>9227</v>
+        <v>6625</v>
       </c>
       <c r="E54" s="22" t="n">
-        <v>6929</v>
+        <v>4075</v>
       </c>
       <c r="F54" s="21" t="n">
-        <v>9717</v>
+        <v>7603</v>
       </c>
       <c r="G54" s="21" t="n">
-        <v>9522</v>
+        <v>7716</v>
       </c>
       <c r="H54" s="22" t="n">
-        <v>10135</v>
+        <v>6465</v>
       </c>
       <c r="I54" s="21" t="n">
-        <v>9622</v>
+        <v>7082</v>
       </c>
       <c r="J54" s="22" t="n">
-        <v>9631</v>
+        <v>7036</v>
       </c>
     </row>
     <row r="55">
@@ -5460,25 +5460,25 @@
         <v>14</v>
       </c>
       <c r="D55" s="21" t="n">
-        <v>9257</v>
+        <v>6656</v>
       </c>
       <c r="E55" s="22" t="n">
-        <v>7123</v>
+        <v>4269</v>
       </c>
       <c r="F55" s="21" t="n">
-        <v>9717</v>
+        <v>7584</v>
       </c>
       <c r="G55" s="21" t="n">
-        <v>9529</v>
+        <v>7716</v>
       </c>
       <c r="H55" s="22" t="n">
-        <v>10130</v>
+        <v>6459</v>
       </c>
       <c r="I55" s="21" t="n">
-        <v>9596</v>
+        <v>7062</v>
       </c>
       <c r="J55" s="22" t="n">
-        <v>9628</v>
+        <v>7057</v>
       </c>
     </row>
     <row r="56">
@@ -5492,25 +5492,25 @@
         <v>14</v>
       </c>
       <c r="D56" s="21" t="n">
-        <v>9284</v>
+        <v>6670</v>
       </c>
       <c r="E56" s="22" t="n">
-        <v>7364</v>
+        <v>4510</v>
       </c>
       <c r="F56" s="21" t="n">
-        <v>9728</v>
+        <v>7578</v>
       </c>
       <c r="G56" s="21" t="n">
-        <v>9529</v>
+        <v>7716</v>
       </c>
       <c r="H56" s="22" t="n">
-        <v>10095</v>
+        <v>6417</v>
       </c>
       <c r="I56" s="21" t="n">
-        <v>9573</v>
+        <v>7036</v>
       </c>
       <c r="J56" s="22" t="n">
-        <v>9575</v>
+        <v>6954</v>
       </c>
     </row>
     <row r="57">
@@ -5524,25 +5524,25 @@
         <v>14</v>
       </c>
       <c r="D57" s="21" t="n">
-        <v>9334</v>
+        <v>6720</v>
       </c>
       <c r="E57" s="22" t="n">
-        <v>7639</v>
+        <v>4786</v>
       </c>
       <c r="F57" s="21" t="n">
-        <v>9743</v>
+        <v>7580</v>
       </c>
       <c r="G57" s="21" t="n">
-        <v>9529</v>
+        <v>7716</v>
       </c>
       <c r="H57" s="22" t="n">
-        <v>10095</v>
+        <v>6409</v>
       </c>
       <c r="I57" s="21" t="n">
-        <v>9565</v>
+        <v>7023</v>
       </c>
       <c r="J57" s="22" t="n">
-        <v>9572</v>
+        <v>6981</v>
       </c>
     </row>
     <row r="58">
@@ -5556,25 +5556,25 @@
         <v>15</v>
       </c>
       <c r="D58" s="21" t="n">
-        <v>9379</v>
+        <v>6758</v>
       </c>
       <c r="E58" s="22" t="n">
-        <v>8035</v>
+        <v>5181</v>
       </c>
       <c r="F58" s="21" t="n">
-        <v>9732</v>
+        <v>7596</v>
       </c>
       <c r="G58" s="21" t="n">
-        <v>9495</v>
+        <v>7716</v>
       </c>
       <c r="H58" s="22" t="n">
-        <v>10060</v>
+        <v>6360</v>
       </c>
       <c r="I58" s="21" t="n">
-        <v>9502</v>
+        <v>6888</v>
       </c>
       <c r="J58" s="22" t="n">
-        <v>9557</v>
+        <v>6948</v>
       </c>
     </row>
     <row r="59">
@@ -5588,25 +5588,25 @@
         <v>15</v>
       </c>
       <c r="D59" s="21" t="n">
-        <v>9433</v>
+        <v>6821</v>
       </c>
       <c r="E59" s="22" t="n">
-        <v>8424</v>
+        <v>5571</v>
       </c>
       <c r="F59" s="21" t="n">
-        <v>9692</v>
+        <v>7602</v>
       </c>
       <c r="G59" s="21" t="n">
-        <v>9512</v>
+        <v>7716</v>
       </c>
       <c r="H59" s="22" t="n">
-        <v>10038</v>
+        <v>6372</v>
       </c>
       <c r="I59" s="21" t="n">
-        <v>9501</v>
+        <v>6890</v>
       </c>
       <c r="J59" s="22" t="n">
-        <v>9518</v>
+        <v>6891</v>
       </c>
     </row>
     <row r="60">
@@ -5620,25 +5620,25 @@
         <v>15</v>
       </c>
       <c r="D60" s="21" t="n">
-        <v>9516</v>
+        <v>6902</v>
       </c>
       <c r="E60" s="22" t="n">
-        <v>8845</v>
+        <v>5992</v>
       </c>
       <c r="F60" s="21" t="n">
-        <v>9742</v>
+        <v>7602</v>
       </c>
       <c r="G60" s="21" t="n">
-        <v>9512</v>
+        <v>7713</v>
       </c>
       <c r="H60" s="22" t="n">
-        <v>9971</v>
+        <v>6391</v>
       </c>
       <c r="I60" s="21" t="n">
-        <v>9514</v>
+        <v>6867</v>
       </c>
       <c r="J60" s="22" t="n">
-        <v>9564</v>
+        <v>6932</v>
       </c>
     </row>
     <row r="61">
@@ -5652,25 +5652,25 @@
         <v>15</v>
       </c>
       <c r="D61" s="21" t="n">
-        <v>9594</v>
+        <v>7001</v>
       </c>
       <c r="E61" s="22" t="n">
-        <v>9279</v>
+        <v>6426</v>
       </c>
       <c r="F61" s="21" t="n">
-        <v>9770</v>
+        <v>7653</v>
       </c>
       <c r="G61" s="21" t="n">
-        <v>9512</v>
+        <v>7711</v>
       </c>
       <c r="H61" s="22" t="n">
-        <v>9953</v>
+        <v>6411</v>
       </c>
       <c r="I61" s="21" t="n">
-        <v>9513</v>
+        <v>6897</v>
       </c>
       <c r="J61" s="22" t="n">
-        <v>9558</v>
+        <v>6962</v>
       </c>
     </row>
     <row r="62">
@@ -5684,25 +5684,25 @@
         <v>16</v>
       </c>
       <c r="D62" s="21" t="n">
-        <v>9655</v>
+        <v>7116</v>
       </c>
       <c r="E62" s="22" t="n">
-        <v>9398</v>
+        <v>6545</v>
       </c>
       <c r="F62" s="21" t="n">
-        <v>9896</v>
+        <v>7711</v>
       </c>
       <c r="G62" s="21" t="n">
-        <v>9512</v>
+        <v>7832</v>
       </c>
       <c r="H62" s="22" t="n">
-        <v>9931</v>
+        <v>6491</v>
       </c>
       <c r="I62" s="21" t="n">
-        <v>9606</v>
+        <v>7035</v>
       </c>
       <c r="J62" s="22" t="n">
-        <v>9598</v>
+        <v>7139</v>
       </c>
     </row>
     <row r="63">
@@ -5716,25 +5716,25 @@
         <v>16</v>
       </c>
       <c r="D63" s="21" t="n">
-        <v>9832</v>
+        <v>7392</v>
       </c>
       <c r="E63" s="22" t="n">
-        <v>9951</v>
+        <v>7098</v>
       </c>
       <c r="F63" s="21" t="n">
-        <v>9958</v>
+        <v>7958</v>
       </c>
       <c r="G63" s="21" t="n">
-        <v>9543</v>
+        <v>8014</v>
       </c>
       <c r="H63" s="22" t="n">
-        <v>10007</v>
+        <v>6765</v>
       </c>
       <c r="I63" s="21" t="n">
-        <v>9714</v>
+        <v>7333</v>
       </c>
       <c r="J63" s="22" t="n">
-        <v>9789</v>
+        <v>7215</v>
       </c>
     </row>
     <row r="64">
@@ -5748,25 +5748,25 @@
         <v>16</v>
       </c>
       <c r="D64" s="21" t="n">
-        <v>10030</v>
+        <v>7684</v>
       </c>
       <c r="E64" s="22" t="n">
-        <v>10490</v>
+        <v>7637</v>
       </c>
       <c r="F64" s="21" t="n">
-        <v>10148</v>
+        <v>8119</v>
       </c>
       <c r="G64" s="21" t="n">
-        <v>9874</v>
+        <v>8111</v>
       </c>
       <c r="H64" s="22" t="n">
-        <v>10086</v>
+        <v>7491</v>
       </c>
       <c r="I64" s="21" t="n">
-        <v>9754</v>
+        <v>7435</v>
       </c>
       <c r="J64" s="22" t="n">
-        <v>9778</v>
+        <v>7326</v>
       </c>
     </row>
     <row r="65">
@@ -5780,25 +5780,25 @@
         <v>16</v>
       </c>
       <c r="D65" s="21" t="n">
-        <v>10483</v>
+        <v>8250</v>
       </c>
       <c r="E65" s="22" t="n">
-        <v>11022</v>
+        <v>8169</v>
       </c>
       <c r="F65" s="21" t="n">
-        <v>10553</v>
+        <v>8689</v>
       </c>
       <c r="G65" s="21" t="n">
-        <v>10518</v>
+        <v>8897</v>
       </c>
       <c r="H65" s="22" t="n">
-        <v>10334</v>
+        <v>7963</v>
       </c>
       <c r="I65" s="21" t="n">
-        <v>10332</v>
+        <v>7951</v>
       </c>
       <c r="J65" s="22" t="n">
-        <v>10094</v>
+        <v>7859</v>
       </c>
     </row>
     <row r="66">
@@ -5812,25 +5812,25 @@
         <v>17</v>
       </c>
       <c r="D66" s="21" t="n">
-        <v>11099</v>
+        <v>9072</v>
       </c>
       <c r="E66" s="22" t="n">
-        <v>11394</v>
+        <v>8540</v>
       </c>
       <c r="F66" s="21" t="n">
-        <v>11201</v>
+        <v>9911</v>
       </c>
       <c r="G66" s="21" t="n">
-        <v>10985</v>
+        <v>9502</v>
       </c>
       <c r="H66" s="22" t="n">
-        <v>10929</v>
+        <v>9014</v>
       </c>
       <c r="I66" s="21" t="n">
-        <v>11260</v>
+        <v>8905</v>
       </c>
       <c r="J66" s="22" t="n">
-        <v>10793</v>
+        <v>8601</v>
       </c>
     </row>
     <row r="67">
@@ -5844,25 +5844,25 @@
         <v>17</v>
       </c>
       <c r="D67" s="21" t="n">
-        <v>11556</v>
+        <v>9932</v>
       </c>
       <c r="E67" s="22" t="n">
-        <v>11992</v>
+        <v>9139</v>
       </c>
       <c r="F67" s="21" t="n">
-        <v>11528</v>
+        <v>10738</v>
       </c>
       <c r="G67" s="21" t="n">
-        <v>11116</v>
+        <v>10443</v>
       </c>
       <c r="H67" s="22" t="n">
-        <v>11493</v>
+        <v>9721</v>
       </c>
       <c r="I67" s="21" t="n">
-        <v>11608</v>
+        <v>9900</v>
       </c>
       <c r="J67" s="22" t="n">
-        <v>11538</v>
+        <v>9711</v>
       </c>
     </row>
     <row r="68">
@@ -5876,25 +5876,25 @@
         <v>17</v>
       </c>
       <c r="D68" s="21" t="n">
-        <v>12055</v>
+        <v>10801</v>
       </c>
       <c r="E68" s="22" t="n">
-        <v>12555</v>
+        <v>9702</v>
       </c>
       <c r="F68" s="21" t="n">
-        <v>12241</v>
+        <v>11933</v>
       </c>
       <c r="G68" s="21" t="n">
-        <v>11294</v>
+        <v>11144</v>
       </c>
       <c r="H68" s="22" t="n">
-        <v>12092</v>
+        <v>10609</v>
       </c>
       <c r="I68" s="21" t="n">
-        <v>12108</v>
+        <v>10967</v>
       </c>
       <c r="J68" s="22" t="n">
-        <v>11950</v>
+        <v>10519</v>
       </c>
     </row>
     <row r="69">
@@ -5908,25 +5908,25 @@
         <v>17</v>
       </c>
       <c r="D69" s="21" t="n">
-        <v>12448</v>
+        <v>11376</v>
       </c>
       <c r="E69" s="22" t="n">
-        <v>13072</v>
+        <v>10218</v>
       </c>
       <c r="F69" s="21" t="n">
-        <v>12752</v>
+        <v>12378</v>
       </c>
       <c r="G69" s="21" t="n">
-        <v>11590</v>
+        <v>11337</v>
       </c>
       <c r="H69" s="22" t="n">
-        <v>12466</v>
+        <v>11353</v>
       </c>
       <c r="I69" s="21" t="n">
-        <v>12363</v>
+        <v>11675</v>
       </c>
       <c r="J69" s="22" t="n">
-        <v>12336</v>
+        <v>11351</v>
       </c>
     </row>
     <row r="70">
@@ -5940,25 +5940,25 @@
         <v>18</v>
       </c>
       <c r="D70" s="21" t="n">
-        <v>12650</v>
+        <v>11743</v>
       </c>
       <c r="E70" s="22" t="n">
-        <v>13569</v>
+        <v>10716</v>
       </c>
       <c r="F70" s="21" t="n">
-        <v>12821</v>
+        <v>12587</v>
       </c>
       <c r="G70" s="21" t="n">
-        <v>11746</v>
+        <v>11792</v>
       </c>
       <c r="H70" s="22" t="n">
-        <v>12610</v>
+        <v>11838</v>
       </c>
       <c r="I70" s="21" t="n">
-        <v>12523</v>
+        <v>11926</v>
       </c>
       <c r="J70" s="22" t="n">
-        <v>12503</v>
+        <v>11655</v>
       </c>
     </row>
     <row r="71">
@@ -5972,25 +5972,25 @@
         <v>18</v>
       </c>
       <c r="D71" s="21" t="n">
-        <v>12852</v>
+        <v>11983</v>
       </c>
       <c r="E71" s="22" t="n">
-        <v>13971</v>
+        <v>11117</v>
       </c>
       <c r="F71" s="21" t="n">
-        <v>13094</v>
+        <v>12762</v>
       </c>
       <c r="G71" s="21" t="n">
-        <v>11871</v>
+        <v>11869</v>
       </c>
       <c r="H71" s="22" t="n">
-        <v>12815</v>
+        <v>12323</v>
       </c>
       <c r="I71" s="21" t="n">
-        <v>12534</v>
+        <v>11989</v>
       </c>
       <c r="J71" s="22" t="n">
-        <v>12675</v>
+        <v>11880</v>
       </c>
     </row>
     <row r="72">
@@ -6004,25 +6004,25 @@
         <v>18</v>
       </c>
       <c r="D72" s="21" t="n">
-        <v>12898</v>
+        <v>12232</v>
       </c>
       <c r="E72" s="22" t="n">
-        <v>14300</v>
+        <v>11446</v>
       </c>
       <c r="F72" s="21" t="n">
-        <v>13058</v>
+        <v>13085</v>
       </c>
       <c r="G72" s="21" t="n">
-        <v>11848</v>
+        <v>11910</v>
       </c>
       <c r="H72" s="22" t="n">
-        <v>12814</v>
+        <v>12529</v>
       </c>
       <c r="I72" s="21" t="n">
-        <v>12592</v>
+        <v>12182</v>
       </c>
       <c r="J72" s="22" t="n">
-        <v>12601</v>
+        <v>12259</v>
       </c>
     </row>
     <row r="73">
@@ -6036,25 +6036,25 @@
         <v>18</v>
       </c>
       <c r="D73" s="21" t="n">
-        <v>12884</v>
+        <v>12223</v>
       </c>
       <c r="E73" s="22" t="n">
-        <v>14476</v>
+        <v>11622</v>
       </c>
       <c r="F73" s="21" t="n">
-        <v>13169</v>
+        <v>12968</v>
       </c>
       <c r="G73" s="21" t="n">
-        <v>11832</v>
+        <v>11916</v>
       </c>
       <c r="H73" s="22" t="n">
-        <v>12658</v>
+        <v>12507</v>
       </c>
       <c r="I73" s="21" t="n">
-        <v>12524</v>
+        <v>12214</v>
       </c>
       <c r="J73" s="22" t="n">
-        <v>12448</v>
+        <v>12122</v>
       </c>
     </row>
     <row r="74">
@@ -6068,25 +6068,25 @@
         <v>19</v>
       </c>
       <c r="D74" s="21" t="n">
-        <v>12812</v>
+        <v>12155</v>
       </c>
       <c r="E74" s="22" t="n">
-        <v>14587</v>
+        <v>11733</v>
       </c>
       <c r="F74" s="21" t="n">
-        <v>13233</v>
+        <v>13033</v>
       </c>
       <c r="G74" s="21" t="n">
-        <v>11838</v>
+        <v>11930</v>
       </c>
       <c r="H74" s="22" t="n">
-        <v>12484</v>
+        <v>12306</v>
       </c>
       <c r="I74" s="21" t="n">
-        <v>12299</v>
+        <v>12034</v>
       </c>
       <c r="J74" s="22" t="n">
-        <v>12221</v>
+        <v>11886</v>
       </c>
     </row>
     <row r="75">
@@ -6100,25 +6100,25 @@
         <v>19</v>
       </c>
       <c r="D75" s="21" t="n">
-        <v>12732</v>
+        <v>12167</v>
       </c>
       <c r="E75" s="22" t="n">
-        <v>14565</v>
+        <v>11712</v>
       </c>
       <c r="F75" s="21" t="n">
-        <v>13089</v>
+        <v>13076</v>
       </c>
       <c r="G75" s="21" t="n">
-        <v>11874</v>
+        <v>12125</v>
       </c>
       <c r="H75" s="22" t="n">
-        <v>12378</v>
+        <v>12226</v>
       </c>
       <c r="I75" s="21" t="n">
-        <v>12111</v>
+        <v>11994</v>
       </c>
       <c r="J75" s="22" t="n">
-        <v>12164</v>
+        <v>11873</v>
       </c>
     </row>
     <row r="76">
@@ -6132,25 +6132,25 @@
         <v>19</v>
       </c>
       <c r="D76" s="21" t="n">
-        <v>12584</v>
+        <v>12154</v>
       </c>
       <c r="E76" s="22" t="n">
-        <v>14464</v>
+        <v>11611</v>
       </c>
       <c r="F76" s="21" t="n">
-        <v>13028</v>
+        <v>12956</v>
       </c>
       <c r="G76" s="21" t="n">
-        <v>11633</v>
+        <v>12496</v>
       </c>
       <c r="H76" s="22" t="n">
-        <v>12255</v>
+        <v>12120</v>
       </c>
       <c r="I76" s="21" t="n">
-        <v>11943</v>
+        <v>11963</v>
       </c>
       <c r="J76" s="22" t="n">
-        <v>11958</v>
+        <v>11815</v>
       </c>
     </row>
     <row r="77">
@@ -6164,25 +6164,25 @@
         <v>19</v>
       </c>
       <c r="D77" s="21" t="n">
-        <v>12536</v>
+        <v>12092</v>
       </c>
       <c r="E77" s="22" t="n">
-        <v>14370</v>
+        <v>11517</v>
       </c>
       <c r="F77" s="21" t="n">
-        <v>12940</v>
+        <v>12799</v>
       </c>
       <c r="G77" s="21" t="n">
-        <v>11681</v>
+        <v>12576</v>
       </c>
       <c r="H77" s="22" t="n">
-        <v>12172</v>
+        <v>11977</v>
       </c>
       <c r="I77" s="21" t="n">
-        <v>11977</v>
+        <v>11953</v>
       </c>
       <c r="J77" s="22" t="n">
-        <v>11866</v>
+        <v>11783</v>
       </c>
     </row>
     <row r="78">
@@ -6196,25 +6196,25 @@
         <v>20</v>
       </c>
       <c r="D78" s="21" t="n">
-        <v>12456</v>
+        <v>12059</v>
       </c>
       <c r="E78" s="22" t="n">
-        <v>14329</v>
+        <v>11476</v>
       </c>
       <c r="F78" s="21" t="n">
-        <v>12735</v>
+        <v>12688</v>
       </c>
       <c r="G78" s="21" t="n">
-        <v>11845</v>
+        <v>12744</v>
       </c>
       <c r="H78" s="22" t="n">
-        <v>12032</v>
+        <v>11774</v>
       </c>
       <c r="I78" s="21" t="n">
-        <v>11861</v>
+        <v>11926</v>
       </c>
       <c r="J78" s="22" t="n">
-        <v>11738</v>
+        <v>11809</v>
       </c>
     </row>
     <row r="79">
@@ -6228,25 +6228,25 @@
         <v>20</v>
       </c>
       <c r="D79" s="21" t="n">
-        <v>12413</v>
+        <v>11998</v>
       </c>
       <c r="E79" s="22" t="n">
-        <v>14221</v>
+        <v>11367</v>
       </c>
       <c r="F79" s="21" t="n">
-        <v>12735</v>
+        <v>12672</v>
       </c>
       <c r="G79" s="21" t="n">
-        <v>11798</v>
+        <v>12663</v>
       </c>
       <c r="H79" s="22" t="n">
-        <v>11956</v>
+        <v>11572</v>
       </c>
       <c r="I79" s="21" t="n">
-        <v>11828</v>
+        <v>11931</v>
       </c>
       <c r="J79" s="22" t="n">
-        <v>11751</v>
+        <v>11839</v>
       </c>
     </row>
     <row r="80">
@@ -6260,25 +6260,25 @@
         <v>20</v>
       </c>
       <c r="D80" s="21" t="n">
-        <v>12406</v>
+        <v>11968</v>
       </c>
       <c r="E80" s="22" t="n">
-        <v>14104</v>
+        <v>11251</v>
       </c>
       <c r="F80" s="21" t="n">
-        <v>12689</v>
+        <v>12713</v>
       </c>
       <c r="G80" s="21" t="n">
-        <v>11868</v>
+        <v>12733</v>
       </c>
       <c r="H80" s="22" t="n">
-        <v>11871</v>
+        <v>11383</v>
       </c>
       <c r="I80" s="21" t="n">
-        <v>11872</v>
+        <v>11905</v>
       </c>
       <c r="J80" s="22" t="n">
-        <v>11855</v>
+        <v>11889</v>
       </c>
     </row>
     <row r="81">
@@ -6292,25 +6292,25 @@
         <v>20</v>
       </c>
       <c r="D81" s="21" t="n">
-        <v>12383</v>
+        <v>11940</v>
       </c>
       <c r="E81" s="22" t="n">
-        <v>14036</v>
+        <v>11183</v>
       </c>
       <c r="F81" s="21" t="n">
-        <v>12688</v>
+        <v>12736</v>
       </c>
       <c r="G81" s="21" t="n">
-        <v>11868</v>
+        <v>12733</v>
       </c>
       <c r="H81" s="22" t="n">
-        <v>11807</v>
+        <v>11323</v>
       </c>
       <c r="I81" s="21" t="n">
-        <v>11865</v>
+        <v>11893</v>
       </c>
       <c r="J81" s="22" t="n">
-        <v>11859</v>
+        <v>11839</v>
       </c>
     </row>
     <row r="82">
@@ -6324,25 +6324,25 @@
         <v>21</v>
       </c>
       <c r="D82" s="21" t="n">
-        <v>12364</v>
+        <v>11908</v>
       </c>
       <c r="E82" s="22" t="n">
-        <v>14045</v>
+        <v>11192</v>
       </c>
       <c r="F82" s="21" t="n">
-        <v>12645</v>
+        <v>12708</v>
       </c>
       <c r="G82" s="21" t="n">
-        <v>11822</v>
+        <v>12687</v>
       </c>
       <c r="H82" s="22" t="n">
-        <v>11694</v>
+        <v>11197</v>
       </c>
       <c r="I82" s="21" t="n">
-        <v>11953</v>
+        <v>11946</v>
       </c>
       <c r="J82" s="22" t="n">
-        <v>11842</v>
+        <v>11779</v>
       </c>
     </row>
     <row r="83">
@@ -6356,25 +6356,25 @@
         <v>21</v>
       </c>
       <c r="D83" s="21" t="n">
-        <v>12386</v>
+        <v>11945</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>14035</v>
+        <v>11182</v>
       </c>
       <c r="F83" s="21" t="n">
-        <v>12647</v>
+        <v>12806</v>
       </c>
       <c r="G83" s="21" t="n">
-        <v>11840</v>
+        <v>12706</v>
       </c>
       <c r="H83" s="22" t="n">
-        <v>11731</v>
+        <v>11235</v>
       </c>
       <c r="I83" s="21" t="n">
-        <v>11975</v>
+        <v>11949</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>11910</v>
+        <v>11853</v>
       </c>
     </row>
     <row r="84">
@@ -6388,25 +6388,25 @@
         <v>21</v>
       </c>
       <c r="D84" s="21" t="n">
-        <v>12379</v>
+        <v>11986</v>
       </c>
       <c r="E84" s="22" t="n">
-        <v>14092</v>
+        <v>11239</v>
       </c>
       <c r="F84" s="21" t="n">
-        <v>12667</v>
+        <v>12836</v>
       </c>
       <c r="G84" s="21" t="n">
-        <v>11827</v>
+        <v>12706</v>
       </c>
       <c r="H84" s="22" t="n">
-        <v>11723</v>
+        <v>11429</v>
       </c>
       <c r="I84" s="21" t="n">
-        <v>11874</v>
+        <v>11904</v>
       </c>
       <c r="J84" s="22" t="n">
-        <v>11905</v>
+        <v>11865</v>
       </c>
     </row>
     <row r="85">
@@ -6420,25 +6420,25 @@
         <v>21</v>
       </c>
       <c r="D85" s="21" t="n">
-        <v>12401</v>
+        <v>12033</v>
       </c>
       <c r="E85" s="22" t="n">
-        <v>14142</v>
+        <v>11288</v>
       </c>
       <c r="F85" s="21" t="n">
-        <v>12712</v>
+        <v>12877</v>
       </c>
       <c r="G85" s="21" t="n">
-        <v>11804</v>
+        <v>12716</v>
       </c>
       <c r="H85" s="22" t="n">
-        <v>11786</v>
+        <v>11621</v>
       </c>
       <c r="I85" s="21" t="n">
-        <v>11932</v>
+        <v>11958</v>
       </c>
       <c r="J85" s="22" t="n">
-        <v>11844</v>
+        <v>11799</v>
       </c>
     </row>
     <row r="86">
@@ -6452,25 +6452,25 @@
         <v>22</v>
       </c>
       <c r="D86" s="21" t="n">
-        <v>12482</v>
+        <v>12165</v>
       </c>
       <c r="E86" s="22" t="n">
-        <v>14252</v>
+        <v>11399</v>
       </c>
       <c r="F86" s="21" t="n">
-        <v>12732</v>
+        <v>12976</v>
       </c>
       <c r="G86" s="21" t="n">
-        <v>11756</v>
+        <v>12735</v>
       </c>
       <c r="H86" s="22" t="n">
-        <v>12060</v>
+        <v>12008</v>
       </c>
       <c r="I86" s="21" t="n">
-        <v>11995</v>
+        <v>12047</v>
       </c>
       <c r="J86" s="22" t="n">
-        <v>11905</v>
+        <v>11886</v>
       </c>
     </row>
     <row r="87">
@@ -6484,25 +6484,25 @@
         <v>22</v>
       </c>
       <c r="D87" s="21" t="n">
-        <v>12465</v>
+        <v>12142</v>
       </c>
       <c r="E87" s="22" t="n">
-        <v>14229</v>
+        <v>11375</v>
       </c>
       <c r="F87" s="21" t="n">
-        <v>12636</v>
+        <v>12962</v>
       </c>
       <c r="G87" s="21" t="n">
-        <v>11813</v>
+        <v>12696</v>
       </c>
       <c r="H87" s="22" t="n">
-        <v>12042</v>
+        <v>11962</v>
       </c>
       <c r="I87" s="21" t="n">
-        <v>11999</v>
+        <v>12053</v>
       </c>
       <c r="J87" s="22" t="n">
-        <v>11883</v>
+        <v>11870</v>
       </c>
     </row>
     <row r="88">
@@ -6516,25 +6516,25 @@
         <v>22</v>
       </c>
       <c r="D88" s="21" t="n">
-        <v>12468</v>
+        <v>12166</v>
       </c>
       <c r="E88" s="22" t="n">
-        <v>14191</v>
+        <v>11337</v>
       </c>
       <c r="F88" s="21" t="n">
-        <v>12634</v>
+        <v>12983</v>
       </c>
       <c r="G88" s="21" t="n">
-        <v>11794</v>
+        <v>12773</v>
       </c>
       <c r="H88" s="22" t="n">
-        <v>12079</v>
+        <v>12007</v>
       </c>
       <c r="I88" s="21" t="n">
-        <v>11997</v>
+        <v>12054</v>
       </c>
       <c r="J88" s="22" t="n">
-        <v>11927</v>
+        <v>11912</v>
       </c>
     </row>
     <row r="89">
@@ -6548,22 +6548,22 @@
         <v>22</v>
       </c>
       <c r="D89" s="21" t="n">
-        <v>12449</v>
+        <v>12160</v>
       </c>
       <c r="E89" s="22" t="n">
-        <v>14158</v>
+        <v>11305</v>
       </c>
       <c r="F89" s="21" t="n">
-        <v>12624</v>
+        <v>13038</v>
       </c>
       <c r="G89" s="21" t="n">
-        <v>11812</v>
+        <v>12791</v>
       </c>
       <c r="H89" s="22" t="n">
-        <v>12102</v>
+        <v>12031</v>
       </c>
       <c r="I89" s="21" t="n">
-        <v>11931</v>
+        <v>11979</v>
       </c>
       <c r="J89" s="22" t="n">
         <v>11886</v>
@@ -6580,25 +6580,25 @@
         <v>23</v>
       </c>
       <c r="D90" s="21" t="n">
-        <v>12475</v>
+        <v>12150</v>
       </c>
       <c r="E90" s="22" t="n">
-        <v>14156</v>
+        <v>11303</v>
       </c>
       <c r="F90" s="21" t="n">
-        <v>12625</v>
+        <v>13053</v>
       </c>
       <c r="G90" s="21" t="n">
-        <v>11885</v>
+        <v>12739</v>
       </c>
       <c r="H90" s="22" t="n">
-        <v>12182</v>
+        <v>12049</v>
       </c>
       <c r="I90" s="21" t="n">
-        <v>11893</v>
+        <v>11928</v>
       </c>
       <c r="J90" s="22" t="n">
-        <v>11938</v>
+        <v>11894</v>
       </c>
     </row>
     <row r="91">
@@ -6612,25 +6612,25 @@
         <v>23</v>
       </c>
       <c r="D91" s="21" t="n">
-        <v>12564</v>
+        <v>12250</v>
       </c>
       <c r="E91" s="22" t="n">
-        <v>14139</v>
+        <v>11285</v>
       </c>
       <c r="F91" s="21" t="n">
-        <v>12791</v>
+        <v>13079</v>
       </c>
       <c r="G91" s="21" t="n">
-        <v>11764</v>
+        <v>12723</v>
       </c>
       <c r="H91" s="22" t="n">
-        <v>12379</v>
+        <v>12283</v>
       </c>
       <c r="I91" s="21" t="n">
-        <v>12024</v>
+        <v>12161</v>
       </c>
       <c r="J91" s="22" t="n">
-        <v>12109</v>
+        <v>12045</v>
       </c>
     </row>
     <row r="92">
@@ -6644,25 +6644,25 @@
         <v>23</v>
       </c>
       <c r="D92" s="21" t="n">
-        <v>12712</v>
+        <v>12207</v>
       </c>
       <c r="E92" s="22" t="n">
-        <v>14172</v>
+        <v>11319</v>
       </c>
       <c r="F92" s="21" t="n">
-        <v>13007</v>
+        <v>13227</v>
       </c>
       <c r="G92" s="21" t="n">
-        <v>11327</v>
+        <v>11419</v>
       </c>
       <c r="H92" s="22" t="n">
-        <v>12743</v>
+        <v>12678</v>
       </c>
       <c r="I92" s="21" t="n">
-        <v>12480</v>
+        <v>12414</v>
       </c>
       <c r="J92" s="22" t="n">
-        <v>12343</v>
+        <v>12183</v>
       </c>
     </row>
     <row r="93">
@@ -6676,25 +6676,25 @@
         <v>23</v>
       </c>
       <c r="D93" s="21" t="n">
-        <v>12760</v>
+        <v>12283</v>
       </c>
       <c r="E93" s="22" t="n">
-        <v>14135</v>
+        <v>11282</v>
       </c>
       <c r="F93" s="21" t="n">
-        <v>12949</v>
+        <v>13124</v>
       </c>
       <c r="G93" s="21" t="n">
-        <v>11678</v>
+        <v>11951</v>
       </c>
       <c r="H93" s="22" t="n">
-        <v>12776</v>
+        <v>12675</v>
       </c>
       <c r="I93" s="21" t="n">
-        <v>12469</v>
+        <v>12456</v>
       </c>
       <c r="J93" s="22" t="n">
-        <v>12377</v>
+        <v>12247</v>
       </c>
     </row>
     <row r="94">
@@ -6708,25 +6708,25 @@
         <v>24</v>
       </c>
       <c r="D94" s="21" t="n">
-        <v>12816</v>
+        <v>12535</v>
       </c>
       <c r="E94" s="22" t="n">
-        <v>14123</v>
+        <v>11270</v>
       </c>
       <c r="F94" s="21" t="n">
-        <v>13144</v>
+        <v>13339</v>
       </c>
       <c r="G94" s="21" t="n">
-        <v>11851</v>
+        <v>12798</v>
       </c>
       <c r="H94" s="22" t="n">
-        <v>12605</v>
+        <v>12581</v>
       </c>
       <c r="I94" s="21" t="n">
-        <v>12522</v>
+        <v>12745</v>
       </c>
       <c r="J94" s="22" t="n">
-        <v>12476</v>
+        <v>12565</v>
       </c>
     </row>
     <row r="95">
@@ -6740,25 +6740,25 @@
         <v>24</v>
       </c>
       <c r="D95" s="21" t="n">
-        <v>12793</v>
+        <v>12435</v>
       </c>
       <c r="E95" s="22" t="n">
-        <v>14046</v>
+        <v>11192</v>
       </c>
       <c r="F95" s="21" t="n">
-        <v>13011</v>
+        <v>13194</v>
       </c>
       <c r="G95" s="21" t="n">
-        <v>11929</v>
+        <v>12811</v>
       </c>
       <c r="H95" s="22" t="n">
-        <v>12546</v>
+        <v>12430</v>
       </c>
       <c r="I95" s="21" t="n">
-        <v>12624</v>
+        <v>12610</v>
       </c>
       <c r="J95" s="22" t="n">
-        <v>12445</v>
+        <v>12466</v>
       </c>
     </row>
     <row r="96">
@@ -6772,25 +6772,25 @@
         <v>24</v>
       </c>
       <c r="D96" s="21" t="n">
-        <v>12710</v>
+        <v>12299</v>
       </c>
       <c r="E96" s="22" t="n">
-        <v>13872</v>
+        <v>11018</v>
       </c>
       <c r="F96" s="21" t="n">
-        <v>13013</v>
+        <v>13245</v>
       </c>
       <c r="G96" s="21" t="n">
-        <v>11911</v>
+        <v>12807</v>
       </c>
       <c r="H96" s="22" t="n">
-        <v>12192</v>
+        <v>11791</v>
       </c>
       <c r="I96" s="21" t="n">
-        <v>12641</v>
+        <v>12565</v>
       </c>
       <c r="J96" s="22" t="n">
-        <v>12476</v>
+        <v>12458</v>
       </c>
     </row>
     <row r="97">
@@ -6806,25 +6806,25 @@
         <v>24</v>
       </c>
       <c r="D97" s="21" t="n">
-        <v>12543</v>
+        <v>12004</v>
       </c>
       <c r="E97" s="22" t="n">
-        <v>13727</v>
+        <v>10873</v>
       </c>
       <c r="F97" s="21" t="n">
-        <v>12802</v>
+        <v>12848</v>
       </c>
       <c r="G97" s="21" t="n">
-        <v>11857</v>
+        <v>12544</v>
       </c>
       <c r="H97" s="22" t="n">
-        <v>12068</v>
+        <v>11423</v>
       </c>
       <c r="I97" s="21" t="n">
-        <v>12436</v>
+        <v>12304</v>
       </c>
       <c r="J97" s="22" t="n">
-        <v>12221</v>
+        <v>12115</v>
       </c>
     </row>
   </sheetData>
@@ -6979,35 +6979,29 @@
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="13" t="n">
-        <v>385</v>
-      </c>
-      <c r="E2" s="13" t="n">
-        <v>380</v>
-      </c>
-      <c r="F2" s="13" t="n">
-        <v>385.1</v>
-      </c>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="13" t="n"/>
       <c r="G2" s="23" t="n">
-        <v>315.35</v>
+        <v>398.17</v>
       </c>
       <c r="H2" s="24" t="n">
-        <v>269.44</v>
+        <v>424.99</v>
       </c>
       <c r="I2" s="23" t="n">
-        <v>335.62</v>
+        <v>378.03</v>
       </c>
       <c r="J2" s="23" t="n">
-        <v>357.43</v>
+        <v>430.9</v>
       </c>
       <c r="K2" s="24" t="n">
-        <v>285.48</v>
+        <v>387.42</v>
       </c>
       <c r="L2" s="23" t="n">
-        <v>326.49</v>
+        <v>395.56</v>
       </c>
       <c r="M2" s="24" t="n">
-        <v>309.87</v>
+        <v>375.69</v>
       </c>
     </row>
     <row r="3">
@@ -7020,35 +7014,29 @@
       <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="13" t="n">
-        <v>385</v>
-      </c>
-      <c r="E3" s="13" t="n">
-        <v>380</v>
-      </c>
-      <c r="F3" s="13" t="n">
-        <v>385.1</v>
-      </c>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="13" t="n"/>
       <c r="G3" s="23" t="n">
-        <v>311.7</v>
+        <v>397.68</v>
       </c>
       <c r="H3" s="24" t="n">
-        <v>266.59</v>
+        <v>422.17</v>
       </c>
       <c r="I3" s="23" t="n">
-        <v>334.02</v>
+        <v>376.1</v>
       </c>
       <c r="J3" s="23" t="n">
-        <v>348.75</v>
+        <v>429.3</v>
       </c>
       <c r="K3" s="24" t="n">
-        <v>286.76</v>
+        <v>387.67</v>
       </c>
       <c r="L3" s="23" t="n">
-        <v>318.65</v>
+        <v>395.73</v>
       </c>
       <c r="M3" s="24" t="n">
-        <v>307.75</v>
+        <v>378.47</v>
       </c>
     </row>
     <row r="4">
@@ -7061,35 +7049,29 @@
       <c r="C4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="13" t="n">
-        <v>385</v>
-      </c>
-      <c r="E4" s="13" t="n">
-        <v>380</v>
-      </c>
-      <c r="F4" s="13" t="n">
-        <v>385.1</v>
-      </c>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="13" t="n"/>
       <c r="G4" s="23" t="n">
-        <v>302.39</v>
+        <v>392.36</v>
       </c>
       <c r="H4" s="24" t="n">
-        <v>261.97</v>
+        <v>417.76</v>
       </c>
       <c r="I4" s="23" t="n">
-        <v>334.18</v>
+        <v>373.02</v>
       </c>
       <c r="J4" s="23" t="n">
-        <v>339.12</v>
+        <v>434.37</v>
       </c>
       <c r="K4" s="24" t="n">
-        <v>274.81</v>
+        <v>380.04</v>
       </c>
       <c r="L4" s="23" t="n">
-        <v>296.14</v>
+        <v>381.25</v>
       </c>
       <c r="M4" s="24" t="n">
-        <v>300.56</v>
+        <v>370.77</v>
       </c>
     </row>
     <row r="5">
@@ -7102,35 +7084,29 @@
       <c r="C5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="13" t="n">
-        <v>385</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>380</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>385.1</v>
-      </c>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
       <c r="G5" s="23" t="n">
-        <v>298.2</v>
+        <v>387.37</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>254.66</v>
+        <v>410.75</v>
       </c>
       <c r="I5" s="23" t="n">
-        <v>323.47</v>
+        <v>368.3</v>
       </c>
       <c r="J5" s="23" t="n">
-        <v>348.32</v>
+        <v>437.13</v>
       </c>
       <c r="K5" s="24" t="n">
-        <v>273.81</v>
+        <v>377.67</v>
       </c>
       <c r="L5" s="23" t="n">
-        <v>283.2</v>
+        <v>367.11</v>
       </c>
       <c r="M5" s="24" t="n">
-        <v>297.69</v>
+        <v>365.76</v>
       </c>
     </row>
     <row r="6">
@@ -7143,35 +7119,29 @@
       <c r="C6" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="13" t="n">
-        <v>385</v>
-      </c>
-      <c r="E6" s="13" t="n">
-        <v>380</v>
-      </c>
-      <c r="F6" s="13" t="n">
-        <v>390</v>
-      </c>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
       <c r="G6" s="23" t="n">
-        <v>284.28</v>
+        <v>376.22</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>250.79</v>
+        <v>406.81</v>
       </c>
       <c r="I6" s="23" t="n">
-        <v>310.92</v>
+        <v>347.6</v>
       </c>
       <c r="J6" s="23" t="n">
-        <v>332.8</v>
+        <v>434.58</v>
       </c>
       <c r="K6" s="24" t="n">
-        <v>271.74</v>
+        <v>375.38</v>
       </c>
       <c r="L6" s="23" t="n">
-        <v>248.67</v>
+        <v>344.59</v>
       </c>
       <c r="M6" s="24" t="n">
-        <v>283.78</v>
+        <v>351.92</v>
       </c>
     </row>
     <row r="7">
@@ -7184,35 +7154,29 @@
       <c r="C7" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="13" t="n">
-        <v>385</v>
-      </c>
-      <c r="E7" s="13" t="n">
-        <v>380</v>
-      </c>
-      <c r="F7" s="13" t="n">
-        <v>390</v>
-      </c>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="n"/>
       <c r="G7" s="23" t="n">
-        <v>309.47</v>
+        <v>387.5</v>
       </c>
       <c r="H7" s="24" t="n">
-        <v>249.95</v>
+        <v>405.92</v>
       </c>
       <c r="I7" s="23" t="n">
-        <v>308.62</v>
+        <v>351.15</v>
       </c>
       <c r="J7" s="23" t="n">
-        <v>392.72</v>
+        <v>433.27</v>
       </c>
       <c r="K7" s="24" t="n">
-        <v>274.17</v>
+        <v>378.54</v>
       </c>
       <c r="L7" s="23" t="n">
-        <v>312.83</v>
+        <v>377.91</v>
       </c>
       <c r="M7" s="24" t="n">
-        <v>308.85</v>
+        <v>380.99</v>
       </c>
     </row>
     <row r="8">
@@ -7225,35 +7189,29 @@
       <c r="C8" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="13" t="n">
-        <v>385</v>
-      </c>
-      <c r="E8" s="13" t="n">
-        <v>380</v>
-      </c>
-      <c r="F8" s="13" t="n">
-        <v>390</v>
-      </c>
+      <c r="D8" s="13" t="n"/>
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="13" t="n"/>
       <c r="G8" s="23" t="n">
-        <v>284.92</v>
+        <v>376.6</v>
       </c>
       <c r="H8" s="24" t="n">
-        <v>238.54</v>
+        <v>394.24</v>
       </c>
       <c r="I8" s="23" t="n">
-        <v>304.17</v>
+        <v>345.35</v>
       </c>
       <c r="J8" s="23" t="n">
-        <v>321.61</v>
+        <v>414.38</v>
       </c>
       <c r="K8" s="24" t="n">
-        <v>266.35</v>
+        <v>372.59</v>
       </c>
       <c r="L8" s="23" t="n">
-        <v>276.59</v>
+        <v>364.95</v>
       </c>
       <c r="M8" s="24" t="n">
-        <v>294.44</v>
+        <v>370.76</v>
       </c>
     </row>
     <row r="9">
@@ -7266,35 +7224,29 @@
       <c r="C9" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="13" t="n">
-        <v>385</v>
-      </c>
-      <c r="E9" s="13" t="n">
-        <v>380</v>
-      </c>
-      <c r="F9" s="13" t="n">
-        <v>390</v>
-      </c>
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="13" t="n"/>
       <c r="G9" s="23" t="n">
-        <v>264.77</v>
+        <v>366.91</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>230.74</v>
+        <v>386.18</v>
       </c>
       <c r="I9" s="23" t="n">
-        <v>299.3</v>
+        <v>342.81</v>
       </c>
       <c r="J9" s="23" t="n">
-        <v>274</v>
+        <v>402.96</v>
       </c>
       <c r="K9" s="24" t="n">
-        <v>260.56</v>
+        <v>371.03</v>
       </c>
       <c r="L9" s="23" t="n">
-        <v>253.53</v>
+        <v>348.88</v>
       </c>
       <c r="M9" s="24" t="n">
-        <v>264.24</v>
+        <v>352.14</v>
       </c>
     </row>
     <row r="10">
@@ -7307,35 +7259,29 @@
       <c r="C10" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="13" t="n">
-        <v>390</v>
-      </c>
-      <c r="E10" s="13" t="n">
-        <v>385</v>
-      </c>
-      <c r="F10" s="13" t="n">
-        <v>395</v>
-      </c>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
       <c r="G10" s="23" t="n">
-        <v>303.78</v>
+        <v>393.13</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>280.7</v>
+        <v>435.13</v>
       </c>
       <c r="I10" s="23" t="n">
-        <v>334.06</v>
+        <v>378.17</v>
       </c>
       <c r="J10" s="23" t="n">
-        <v>301.23</v>
+        <v>421.02</v>
       </c>
       <c r="K10" s="24" t="n">
-        <v>279.34</v>
+        <v>376.37</v>
       </c>
       <c r="L10" s="23" t="n">
-        <v>308.36</v>
+        <v>387.01</v>
       </c>
       <c r="M10" s="24" t="n">
-        <v>314.82</v>
+        <v>366.49</v>
       </c>
     </row>
     <row r="11">
@@ -7348,35 +7294,29 @@
       <c r="C11" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="13" t="n">
-        <v>390</v>
-      </c>
-      <c r="E11" s="13" t="n">
-        <v>385</v>
-      </c>
-      <c r="F11" s="13" t="n">
-        <v>395</v>
-      </c>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
       <c r="G11" s="23" t="n">
-        <v>315.9</v>
+        <v>401.21</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>264.87</v>
+        <v>419.46</v>
       </c>
       <c r="I11" s="23" t="n">
-        <v>339.42</v>
+        <v>388.67</v>
       </c>
       <c r="J11" s="23" t="n">
-        <v>329.14</v>
+        <v>419.71</v>
       </c>
       <c r="K11" s="24" t="n">
-        <v>284.11</v>
+        <v>385.51</v>
       </c>
       <c r="L11" s="23" t="n">
-        <v>336.99</v>
+        <v>406.51</v>
       </c>
       <c r="M11" s="24" t="n">
-        <v>333.11</v>
+        <v>389.92</v>
       </c>
     </row>
     <row r="12">
@@ -7389,35 +7329,29 @@
       <c r="C12" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D12" s="13" t="n">
-        <v>390</v>
-      </c>
-      <c r="E12" s="13" t="n">
-        <v>385</v>
-      </c>
-      <c r="F12" s="13" t="n">
-        <v>395</v>
-      </c>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
       <c r="G12" s="23" t="n">
-        <v>316.46</v>
+        <v>395.02</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>264.83</v>
+        <v>419.43</v>
       </c>
       <c r="I12" s="23" t="n">
-        <v>336.75</v>
+        <v>378.94</v>
       </c>
       <c r="J12" s="23" t="n">
-        <v>331.34</v>
+        <v>421.42</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>279.21</v>
+        <v>382.88</v>
       </c>
       <c r="L12" s="23" t="n">
-        <v>339.24</v>
+        <v>388.72</v>
       </c>
       <c r="M12" s="24" t="n">
-        <v>339.67</v>
+        <v>381.95</v>
       </c>
     </row>
     <row r="13">
@@ -7430,35 +7364,29 @@
       <c r="C13" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="13" t="n">
-        <v>390</v>
-      </c>
-      <c r="E13" s="13" t="n">
-        <v>385</v>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>395</v>
-      </c>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
       <c r="G13" s="23" t="n">
-        <v>304.19</v>
+        <v>391.17</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>259.55</v>
+        <v>414.16</v>
       </c>
       <c r="I13" s="23" t="n">
-        <v>329.72</v>
+        <v>373.94</v>
       </c>
       <c r="J13" s="23" t="n">
-        <v>296.6</v>
+        <v>413.9</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>273.49</v>
+        <v>378.03</v>
       </c>
       <c r="L13" s="23" t="n">
-        <v>330.93</v>
+        <v>397.01</v>
       </c>
       <c r="M13" s="24" t="n">
-        <v>328.37</v>
+        <v>373.24</v>
       </c>
     </row>
     <row r="14">
@@ -7471,35 +7399,29 @@
       <c r="C14" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D14" s="13" t="n">
-        <v>384.82</v>
-      </c>
-      <c r="E14" s="13" t="n">
-        <v>381</v>
-      </c>
-      <c r="F14" s="13" t="n">
-        <v>385</v>
-      </c>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
       <c r="G14" s="23" t="n">
-        <v>292.48</v>
+        <v>386.08</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>260.17</v>
+        <v>414.87</v>
       </c>
       <c r="I14" s="23" t="n">
-        <v>319.03</v>
+        <v>376.76</v>
       </c>
       <c r="J14" s="23" t="n">
-        <v>282.4</v>
+        <v>413.95</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>265.19</v>
+        <v>373.41</v>
       </c>
       <c r="L14" s="23" t="n">
-        <v>308.91</v>
+        <v>379.78</v>
       </c>
       <c r="M14" s="24" t="n">
-        <v>314.26</v>
+        <v>361.14</v>
       </c>
     </row>
     <row r="15">
@@ -7512,35 +7434,29 @@
       <c r="C15" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D15" s="13" t="n">
-        <v>384.82</v>
-      </c>
-      <c r="E15" s="13" t="n">
-        <v>381</v>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>385</v>
-      </c>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
       <c r="G15" s="23" t="n">
-        <v>288.7</v>
+        <v>388.34</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>261.02</v>
+        <v>415.94</v>
       </c>
       <c r="I15" s="23" t="n">
-        <v>322.98</v>
+        <v>377.54</v>
       </c>
       <c r="J15" s="23" t="n">
-        <v>270.98</v>
+        <v>413.95</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>277.2</v>
+        <v>382.66</v>
       </c>
       <c r="L15" s="23" t="n">
-        <v>288.45</v>
+        <v>376.07</v>
       </c>
       <c r="M15" s="24" t="n">
-        <v>306.94</v>
+        <v>367.25</v>
       </c>
     </row>
     <row r="16">
@@ -7553,35 +7469,29 @@
       <c r="C16" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D16" s="13" t="n">
-        <v>384.82</v>
-      </c>
-      <c r="E16" s="13" t="n">
-        <v>381</v>
-      </c>
-      <c r="F16" s="13" t="n">
-        <v>385</v>
-      </c>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
       <c r="G16" s="23" t="n">
-        <v>293.96</v>
+        <v>391.46</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>254.78</v>
+        <v>409.89</v>
       </c>
       <c r="I16" s="23" t="n">
-        <v>325.42</v>
+        <v>369.7</v>
       </c>
       <c r="J16" s="23" t="n">
-        <v>270.35</v>
+        <v>414.73</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>283.68</v>
+        <v>385.3</v>
       </c>
       <c r="L16" s="23" t="n">
-        <v>305.01</v>
+        <v>391.54</v>
       </c>
       <c r="M16" s="24" t="n">
-        <v>318.72</v>
+        <v>380.39</v>
       </c>
     </row>
     <row r="17">
@@ -7594,35 +7504,29 @@
       <c r="C17" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D17" s="13" t="n">
-        <v>384.82</v>
-      </c>
-      <c r="E17" s="13" t="n">
-        <v>381</v>
-      </c>
-      <c r="F17" s="13" t="n">
-        <v>385</v>
-      </c>
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="13" t="n"/>
       <c r="G17" s="23" t="n">
-        <v>289.68</v>
+        <v>388.11</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>249.73</v>
+        <v>405.16</v>
       </c>
       <c r="I17" s="23" t="n">
-        <v>319.66</v>
+        <v>363.38</v>
       </c>
       <c r="J17" s="23" t="n">
-        <v>270.35</v>
+        <v>416.54</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>281.63</v>
+        <v>384.78</v>
       </c>
       <c r="L17" s="23" t="n">
-        <v>284.28</v>
+        <v>375.98</v>
       </c>
       <c r="M17" s="24" t="n">
-        <v>326.38</v>
+        <v>385.34</v>
       </c>
     </row>
     <row r="18">
@@ -7635,35 +7539,29 @@
       <c r="C18" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="D18" s="13" t="n">
-        <v>385</v>
-      </c>
-      <c r="E18" s="13" t="n">
-        <v>380</v>
-      </c>
-      <c r="F18" s="13" t="n">
-        <v>600</v>
-      </c>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
       <c r="G18" s="23" t="n">
-        <v>282.95</v>
+        <v>390.98</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>243.6</v>
+        <v>399.03</v>
       </c>
       <c r="I18" s="23" t="n">
-        <v>316.4</v>
+        <v>358.96</v>
       </c>
       <c r="J18" s="23" t="n">
-        <v>240.54</v>
+        <v>427.63</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>275.79</v>
+        <v>378.37</v>
       </c>
       <c r="L18" s="23" t="n">
-        <v>294.08</v>
+        <v>393.84</v>
       </c>
       <c r="M18" s="24" t="n">
-        <v>321.87</v>
+        <v>389.69</v>
       </c>
     </row>
     <row r="19">
@@ -7676,35 +7574,29 @@
       <c r="C19" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="13" t="n">
-        <v>385</v>
-      </c>
-      <c r="E19" s="13" t="n">
-        <v>380</v>
-      </c>
-      <c r="F19" s="13" t="n">
-        <v>600</v>
-      </c>
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
       <c r="G19" s="23" t="n">
-        <v>271.82</v>
+        <v>382.41</v>
       </c>
       <c r="H19" s="24" t="n">
-        <v>241.29</v>
+        <v>396.53</v>
       </c>
       <c r="I19" s="23" t="n">
-        <v>312.94</v>
+        <v>356.76</v>
       </c>
       <c r="J19" s="23" t="n">
-        <v>227.77</v>
+        <v>426.03</v>
       </c>
       <c r="K19" s="24" t="n">
-        <v>272.24</v>
+        <v>374.74</v>
       </c>
       <c r="L19" s="23" t="n">
-        <v>263.5</v>
+        <v>365.97</v>
       </c>
       <c r="M19" s="24" t="n">
-        <v>308.41</v>
+        <v>376.24</v>
       </c>
     </row>
     <row r="20">
@@ -7717,35 +7609,29 @@
       <c r="C20" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="13" t="n">
-        <v>385</v>
-      </c>
-      <c r="E20" s="13" t="n">
-        <v>380</v>
-      </c>
-      <c r="F20" s="13" t="n">
-        <v>600</v>
-      </c>
+      <c r="D20" s="13" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="13" t="n"/>
       <c r="G20" s="23" t="n">
-        <v>269.13</v>
+        <v>380.97</v>
       </c>
       <c r="H20" s="24" t="n">
-        <v>240.16</v>
+        <v>395.42</v>
       </c>
       <c r="I20" s="23" t="n">
-        <v>305.81</v>
+        <v>361.13</v>
       </c>
       <c r="J20" s="23" t="n">
-        <v>227.77</v>
+        <v>421.28</v>
       </c>
       <c r="K20" s="24" t="n">
-        <v>272.8</v>
+        <v>374.44</v>
       </c>
       <c r="L20" s="23" t="n">
-        <v>260.61</v>
+        <v>363.47</v>
       </c>
       <c r="M20" s="24" t="n">
-        <v>303.2</v>
+        <v>371.71</v>
       </c>
     </row>
     <row r="21">
@@ -7758,35 +7644,29 @@
       <c r="C21" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="13" t="n">
-        <v>385</v>
-      </c>
-      <c r="E21" s="13" t="n">
-        <v>380</v>
-      </c>
-      <c r="F21" s="13" t="n">
-        <v>600</v>
-      </c>
+      <c r="D21" s="13" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="13" t="n"/>
       <c r="G21" s="23" t="n">
-        <v>269.95</v>
+        <v>381.2</v>
       </c>
       <c r="H21" s="24" t="n">
-        <v>238.6</v>
+        <v>393.93</v>
       </c>
       <c r="I21" s="23" t="n">
-        <v>306.07</v>
+        <v>358.8</v>
       </c>
       <c r="J21" s="23" t="n">
-        <v>227.37</v>
+        <v>420.16</v>
       </c>
       <c r="K21" s="24" t="n">
-        <v>272.14</v>
+        <v>375.57</v>
       </c>
       <c r="L21" s="23" t="n">
-        <v>267.18</v>
+        <v>368.68</v>
       </c>
       <c r="M21" s="24" t="n">
-        <v>303.71</v>
+        <v>371.66</v>
       </c>
     </row>
     <row r="22">
@@ -7799,35 +7679,29 @@
       <c r="C22" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D22" s="13" t="n">
-        <v>385</v>
-      </c>
-      <c r="E22" s="13" t="n">
-        <v>380</v>
-      </c>
-      <c r="F22" s="13" t="n">
-        <v>600</v>
-      </c>
+      <c r="D22" s="13" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
       <c r="G22" s="23" t="n">
-        <v>270.53</v>
+        <v>386.28</v>
       </c>
       <c r="H22" s="24" t="n">
-        <v>237.29</v>
+        <v>392.51</v>
       </c>
       <c r="I22" s="23" t="n">
-        <v>288.69</v>
+        <v>363.51</v>
       </c>
       <c r="J22" s="23" t="n">
-        <v>228.93</v>
+        <v>424.87</v>
       </c>
       <c r="K22" s="24" t="n">
-        <v>272.54</v>
+        <v>373.54</v>
       </c>
       <c r="L22" s="23" t="n">
-        <v>278.04</v>
+        <v>381.84</v>
       </c>
       <c r="M22" s="24" t="n">
-        <v>313.61</v>
+        <v>382.23</v>
       </c>
     </row>
     <row r="23">
@@ -7840,35 +7714,29 @@
       <c r="C23" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D23" s="13" t="n">
-        <v>385</v>
-      </c>
-      <c r="E23" s="13" t="n">
-        <v>380</v>
-      </c>
-      <c r="F23" s="13" t="n">
-        <v>600</v>
-      </c>
+      <c r="D23" s="13" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="13" t="n"/>
       <c r="G23" s="23" t="n">
-        <v>265.85</v>
+        <v>385.23</v>
       </c>
       <c r="H23" s="24" t="n">
-        <v>236.68</v>
+        <v>391.85</v>
       </c>
       <c r="I23" s="23" t="n">
-        <v>290.32</v>
+        <v>364.78</v>
       </c>
       <c r="J23" s="23" t="n">
-        <v>213.03</v>
+        <v>420</v>
       </c>
       <c r="K23" s="24" t="n">
-        <v>269.52</v>
+        <v>372.5</v>
       </c>
       <c r="L23" s="23" t="n">
-        <v>270.27</v>
+        <v>381.69</v>
       </c>
       <c r="M23" s="24" t="n">
-        <v>311.76</v>
+        <v>381.49</v>
       </c>
     </row>
     <row r="24">
@@ -7881,35 +7749,29 @@
       <c r="C24" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D24" s="13" t="n">
-        <v>385</v>
-      </c>
-      <c r="E24" s="13" t="n">
-        <v>380</v>
-      </c>
-      <c r="F24" s="13" t="n">
-        <v>600</v>
-      </c>
+      <c r="D24" s="13" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="13" t="n"/>
       <c r="G24" s="23" t="n">
-        <v>249.39</v>
+        <v>379.08</v>
       </c>
       <c r="H24" s="24" t="n">
-        <v>237.45</v>
+        <v>392.56</v>
       </c>
       <c r="I24" s="23" t="n">
-        <v>286.44</v>
+        <v>362.46</v>
       </c>
       <c r="J24" s="23" t="n">
-        <v>211.98</v>
+        <v>419.94</v>
       </c>
       <c r="K24" s="24" t="n">
-        <v>262.1</v>
+        <v>370.51</v>
       </c>
       <c r="L24" s="23" t="n">
-        <v>231.18</v>
+        <v>365.49</v>
       </c>
       <c r="M24" s="24" t="n">
-        <v>264.8</v>
+        <v>364.9</v>
       </c>
     </row>
     <row r="25">
@@ -7922,35 +7784,29 @@
       <c r="C25" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D25" s="13" t="n">
-        <v>385</v>
-      </c>
-      <c r="E25" s="13" t="n">
-        <v>380</v>
-      </c>
-      <c r="F25" s="13" t="n">
-        <v>600</v>
-      </c>
+      <c r="D25" s="13" t="n"/>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="13" t="n"/>
       <c r="G25" s="23" t="n">
-        <v>241.08</v>
+        <v>372.45</v>
       </c>
       <c r="H25" s="24" t="n">
-        <v>237.73</v>
+        <v>392.85</v>
       </c>
       <c r="I25" s="23" t="n">
-        <v>281.08</v>
+        <v>362.3</v>
       </c>
       <c r="J25" s="23" t="n">
-        <v>211.98</v>
+        <v>418.77</v>
       </c>
       <c r="K25" s="24" t="n">
-        <v>258.37</v>
+        <v>366.01</v>
       </c>
       <c r="L25" s="23" t="n">
-        <v>210.58</v>
+        <v>350.48</v>
       </c>
       <c r="M25" s="24" t="n">
-        <v>245</v>
+        <v>346.1</v>
       </c>
     </row>
     <row r="26">
@@ -7963,35 +7819,29 @@
       <c r="C26" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="D26" s="13" t="n">
-        <v>384.26</v>
-      </c>
-      <c r="E26" s="13" t="n">
-        <v>380</v>
-      </c>
-      <c r="F26" s="13" t="n">
-        <v>385</v>
-      </c>
+      <c r="D26" s="13" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="13" t="n"/>
       <c r="G26" s="23" t="n">
-        <v>227.33</v>
+        <v>369.03</v>
       </c>
       <c r="H26" s="24" t="n">
-        <v>246.84</v>
+        <v>402.32</v>
       </c>
       <c r="I26" s="23" t="n">
-        <v>253.69</v>
+        <v>351.51</v>
       </c>
       <c r="J26" s="23" t="n">
-        <v>209.39</v>
+        <v>418.22</v>
       </c>
       <c r="K26" s="24" t="n">
-        <v>243.67</v>
+        <v>355.62</v>
       </c>
       <c r="L26" s="23" t="n">
-        <v>201.46</v>
+        <v>358.85</v>
       </c>
       <c r="M26" s="24" t="n">
-        <v>210.49</v>
+        <v>331.52</v>
       </c>
     </row>
     <row r="27">
@@ -8004,35 +7854,29 @@
       <c r="C27" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="D27" s="13" t="n">
-        <v>384.26</v>
-      </c>
-      <c r="E27" s="13" t="n">
-        <v>380</v>
-      </c>
-      <c r="F27" s="13" t="n">
-        <v>385</v>
-      </c>
+      <c r="D27" s="13" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="13" t="n"/>
       <c r="G27" s="23" t="n">
-        <v>205.29</v>
+        <v>354.53</v>
       </c>
       <c r="H27" s="24" t="n">
-        <v>253.96</v>
+        <v>409.23</v>
       </c>
       <c r="I27" s="23" t="n">
-        <v>239.29</v>
+        <v>345.91</v>
       </c>
       <c r="J27" s="23" t="n">
-        <v>200.75</v>
+        <v>408.67</v>
       </c>
       <c r="K27" s="24" t="n">
-        <v>228.09</v>
+        <v>341.98</v>
       </c>
       <c r="L27" s="23" t="n">
-        <v>133.04</v>
+        <v>313.1</v>
       </c>
       <c r="M27" s="24" t="n">
-        <v>180.96</v>
+        <v>314.16</v>
       </c>
     </row>
     <row r="28">
@@ -8045,35 +7889,29 @@
       <c r="C28" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="D28" s="13" t="n">
-        <v>384.26</v>
-      </c>
-      <c r="E28" s="13" t="n">
-        <v>380</v>
-      </c>
-      <c r="F28" s="13" t="n">
-        <v>385</v>
-      </c>
+      <c r="D28" s="13" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="13" t="n"/>
       <c r="G28" s="23" t="n">
-        <v>180.28</v>
+        <v>337.93</v>
       </c>
       <c r="H28" s="24" t="n">
-        <v>246.72</v>
+        <v>401.77</v>
       </c>
       <c r="I28" s="23" t="n">
-        <v>225.74</v>
+        <v>328.77</v>
       </c>
       <c r="J28" s="23" t="n">
-        <v>191.29</v>
+        <v>416.13</v>
       </c>
       <c r="K28" s="24" t="n">
-        <v>206.74</v>
+        <v>316.56</v>
       </c>
       <c r="L28" s="23" t="n">
-        <v>110.02</v>
+        <v>317.46</v>
       </c>
       <c r="M28" s="24" t="n">
-        <v>106.93</v>
+        <v>253.52</v>
       </c>
     </row>
     <row r="29">
@@ -8086,35 +7924,29 @@
       <c r="C29" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="D29" s="13" t="n">
-        <v>384.26</v>
-      </c>
-      <c r="E29" s="13" t="n">
-        <v>380</v>
-      </c>
-      <c r="F29" s="13" t="n">
-        <v>385</v>
-      </c>
+      <c r="D29" s="13" t="n"/>
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="13" t="n"/>
       <c r="G29" s="23" t="n">
-        <v>160.02</v>
+        <v>319.1</v>
       </c>
       <c r="H29" s="24" t="n">
-        <v>240.54</v>
+        <v>394.72</v>
       </c>
       <c r="I29" s="23" t="n">
-        <v>166.8</v>
+        <v>292.85</v>
       </c>
       <c r="J29" s="23" t="n">
-        <v>191.04</v>
+        <v>399.9</v>
       </c>
       <c r="K29" s="24" t="n">
-        <v>200.16</v>
+        <v>322.44</v>
       </c>
       <c r="L29" s="23" t="n">
-        <v>77.34999999999999</v>
+        <v>270.57</v>
       </c>
       <c r="M29" s="24" t="n">
-        <v>92.93000000000001</v>
+        <v>242.75</v>
       </c>
     </row>
     <row r="30">
@@ -8127,35 +7959,29 @@
       <c r="C30" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="D30" s="13" t="n">
-        <v>370</v>
-      </c>
-      <c r="E30" s="13" t="n">
-        <v>354.36</v>
-      </c>
-      <c r="F30" s="13" t="n">
-        <v>370</v>
-      </c>
+      <c r="D30" s="13" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="13" t="n"/>
       <c r="G30" s="23" t="n">
-        <v>184.04</v>
+        <v>333.25</v>
       </c>
       <c r="H30" s="24" t="n">
-        <v>219.91</v>
+        <v>373.64</v>
       </c>
       <c r="I30" s="23" t="n">
-        <v>190.11</v>
+        <v>289.76</v>
       </c>
       <c r="J30" s="23" t="n">
-        <v>199.9</v>
+        <v>398</v>
       </c>
       <c r="K30" s="24" t="n">
-        <v>223.9</v>
+        <v>323.06</v>
       </c>
       <c r="L30" s="23" t="n">
-        <v>129.48</v>
+        <v>329.54</v>
       </c>
       <c r="M30" s="24" t="n">
-        <v>144.42</v>
+        <v>291.02</v>
       </c>
     </row>
     <row r="31">
@@ -8168,35 +7994,29 @@
       <c r="C31" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="D31" s="13" t="n">
-        <v>370</v>
-      </c>
-      <c r="E31" s="13" t="n">
-        <v>354.36</v>
-      </c>
-      <c r="F31" s="13" t="n">
-        <v>370</v>
-      </c>
+      <c r="D31" s="13" t="n"/>
+      <c r="E31" s="13" t="n"/>
+      <c r="F31" s="13" t="n"/>
       <c r="G31" s="23" t="n">
-        <v>106.74</v>
+        <v>285.69</v>
       </c>
       <c r="H31" s="24" t="n">
-        <v>185.6</v>
+        <v>338.46</v>
       </c>
       <c r="I31" s="23" t="n">
-        <v>155.86</v>
+        <v>267.79</v>
       </c>
       <c r="J31" s="23" t="n">
-        <v>85.02</v>
+        <v>296.5</v>
       </c>
       <c r="K31" s="24" t="n">
-        <v>169.85</v>
+        <v>278.54</v>
       </c>
       <c r="L31" s="23" t="n">
-        <v>48.18</v>
+        <v>308.72</v>
       </c>
       <c r="M31" s="24" t="n">
-        <v>3.97</v>
+        <v>231.72</v>
       </c>
     </row>
     <row r="32">
@@ -8209,35 +8029,29 @@
       <c r="C32" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="D32" s="13" t="n">
-        <v>370</v>
-      </c>
-      <c r="E32" s="13" t="n">
-        <v>354.36</v>
-      </c>
-      <c r="F32" s="13" t="n">
-        <v>370</v>
-      </c>
+      <c r="D32" s="13" t="n"/>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="13" t="n"/>
       <c r="G32" s="23" t="n">
-        <v>93.26000000000001</v>
+        <v>203.33</v>
       </c>
       <c r="H32" s="24" t="n">
-        <v>146.47</v>
+        <v>297.83</v>
       </c>
       <c r="I32" s="23" t="n">
-        <v>147.12</v>
+        <v>174.53</v>
       </c>
       <c r="J32" s="23" t="n">
-        <v>64.06</v>
+        <v>241.69</v>
       </c>
       <c r="K32" s="24" t="n">
-        <v>131.77</v>
+        <v>188.88</v>
       </c>
       <c r="L32" s="23" t="n">
-        <v>66.06</v>
+        <v>176.88</v>
       </c>
       <c r="M32" s="24" t="n">
-        <v>9.029999999999999</v>
+        <v>152.6</v>
       </c>
     </row>
     <row r="33">
@@ -8250,35 +8064,29 @@
       <c r="C33" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="D33" s="13" t="n">
-        <v>370</v>
-      </c>
-      <c r="E33" s="13" t="n">
-        <v>354.36</v>
-      </c>
-      <c r="F33" s="13" t="n">
-        <v>370</v>
-      </c>
+      <c r="D33" s="13" t="n"/>
+      <c r="E33" s="13" t="n"/>
+      <c r="F33" s="13" t="n"/>
       <c r="G33" s="23" t="n">
-        <v>73.67</v>
+        <v>93.33</v>
       </c>
       <c r="H33" s="24" t="n">
-        <v>101.86</v>
+        <v>252.16</v>
       </c>
       <c r="I33" s="23" t="n">
-        <v>116.88</v>
+        <v>106.02</v>
       </c>
       <c r="J33" s="23" t="n">
-        <v>93.73999999999999</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="K33" s="24" t="n">
-        <v>76.31999999999999</v>
+        <v>82.97</v>
       </c>
       <c r="L33" s="23" t="n">
-        <v>21.04</v>
+        <v>5.63</v>
       </c>
       <c r="M33" s="24" t="n">
-        <v>33.03</v>
+        <v>44.48</v>
       </c>
     </row>
     <row r="34">
@@ -8291,35 +8099,29 @@
       <c r="C34" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="D34" s="13" t="n">
-        <v>195</v>
-      </c>
-      <c r="E34" s="13" t="n">
-        <v>190</v>
-      </c>
-      <c r="F34" s="13" t="n">
-        <v>197</v>
-      </c>
+      <c r="D34" s="13" t="n"/>
+      <c r="E34" s="13" t="n"/>
+      <c r="F34" s="13" t="n"/>
       <c r="G34" s="23" t="n">
-        <v>42.85</v>
+        <v>59.63</v>
       </c>
       <c r="H34" s="24" t="n">
-        <v>63.96</v>
+        <v>212.8</v>
       </c>
       <c r="I34" s="23" t="n">
-        <v>44.03</v>
+        <v>30.38</v>
       </c>
       <c r="J34" s="23" t="n">
-        <v>55.96</v>
+        <v>62.26</v>
       </c>
       <c r="K34" s="24" t="n">
-        <v>52.41</v>
+        <v>38.03</v>
       </c>
       <c r="L34" s="23" t="n">
-        <v>27.79</v>
+        <v>23.49</v>
       </c>
       <c r="M34" s="24" t="n">
-        <v>15.21</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="35">
@@ -8332,35 +8134,29 @@
       <c r="C35" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="D35" s="13" t="n">
-        <v>195</v>
-      </c>
-      <c r="E35" s="13" t="n">
-        <v>190</v>
-      </c>
-      <c r="F35" s="13" t="n">
-        <v>197</v>
-      </c>
+      <c r="D35" s="13" t="n"/>
+      <c r="E35" s="13" t="n"/>
+      <c r="F35" s="13" t="n"/>
       <c r="G35" s="23" t="n">
-        <v>21.84</v>
+        <v>46.15</v>
       </c>
       <c r="H35" s="24" t="n">
-        <v>28.3</v>
+        <v>177.06</v>
       </c>
       <c r="I35" s="23" t="n">
-        <v>27.34</v>
+        <v>35.89</v>
       </c>
       <c r="J35" s="23" t="n">
-        <v>30</v>
+        <v>40.9</v>
       </c>
       <c r="K35" s="24" t="n">
-        <v>29.44</v>
+        <v>-3.68</v>
       </c>
       <c r="L35" s="23" t="n">
-        <v>16.05</v>
+        <v>28.63</v>
       </c>
       <c r="M35" s="24" t="n">
-        <v>0.23</v>
+        <v>15.72</v>
       </c>
     </row>
     <row r="36">
@@ -8373,35 +8169,29 @@
       <c r="C36" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="D36" s="13" t="n">
-        <v>195</v>
-      </c>
-      <c r="E36" s="13" t="n">
-        <v>190</v>
-      </c>
-      <c r="F36" s="13" t="n">
-        <v>197</v>
-      </c>
+      <c r="D36" s="13" t="n"/>
+      <c r="E36" s="13" t="n"/>
+      <c r="F36" s="13" t="n"/>
       <c r="G36" s="23" t="n">
-        <v>5.9</v>
+        <v>23.04</v>
       </c>
       <c r="H36" s="24" t="n">
-        <v>-7.7</v>
+        <v>141.14</v>
       </c>
       <c r="I36" s="23" t="n">
-        <v>23.45</v>
+        <v>19.22</v>
       </c>
       <c r="J36" s="23" t="n">
-        <v>13.63</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="K36" s="24" t="n">
-        <v>25.8</v>
+        <v>-6.93</v>
       </c>
       <c r="L36" s="23" t="n">
-        <v>-10.01</v>
+        <v>-2.21</v>
       </c>
       <c r="M36" s="24" t="n">
-        <v>-12.7</v>
+        <v>-6.85</v>
       </c>
     </row>
     <row r="37">
@@ -8414,35 +8204,29 @@
       <c r="C37" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="D37" s="13" t="n">
-        <v>195</v>
-      </c>
-      <c r="E37" s="13" t="n">
-        <v>190</v>
-      </c>
-      <c r="F37" s="13" t="n">
-        <v>197</v>
-      </c>
+      <c r="D37" s="13" t="n"/>
+      <c r="E37" s="13" t="n"/>
+      <c r="F37" s="13" t="n"/>
       <c r="G37" s="23" t="n">
-        <v>-0.5600000000000001</v>
+        <v>10.13</v>
       </c>
       <c r="H37" s="24" t="n">
-        <v>-39.52</v>
+        <v>108.95</v>
       </c>
       <c r="I37" s="23" t="n">
-        <v>13.48</v>
+        <v>5.55</v>
       </c>
       <c r="J37" s="23" t="n">
-        <v>11.62</v>
+        <v>6.4</v>
       </c>
       <c r="K37" s="24" t="n">
-        <v>25.49</v>
+        <v>-9.18</v>
       </c>
       <c r="L37" s="23" t="n">
-        <v>-5.57</v>
+        <v>-17.67</v>
       </c>
       <c r="M37" s="24" t="n">
-        <v>-14.97</v>
+        <v>-20.27</v>
       </c>
     </row>
     <row r="38">
@@ -8455,35 +8239,29 @@
       <c r="C38" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="D38" s="13" t="n">
-        <v>48</v>
-      </c>
-      <c r="E38" s="13" t="n">
-        <v>35</v>
-      </c>
-      <c r="F38" s="13" t="n">
-        <v>50</v>
-      </c>
+      <c r="D38" s="13" t="n"/>
+      <c r="E38" s="13" t="n"/>
+      <c r="F38" s="13" t="n"/>
       <c r="G38" s="23" t="n">
-        <v>-11.1</v>
+        <v>5.79</v>
       </c>
       <c r="H38" s="24" t="n">
-        <v>-67.67</v>
+        <v>80.8</v>
       </c>
       <c r="I38" s="23" t="n">
-        <v>2.52</v>
+        <v>1.87</v>
       </c>
       <c r="J38" s="23" t="n">
-        <v>0.37</v>
+        <v>0.99</v>
       </c>
       <c r="K38" s="24" t="n">
-        <v>19.52</v>
+        <v>-9.52</v>
       </c>
       <c r="L38" s="23" t="n">
-        <v>-12.13</v>
+        <v>-11.73</v>
       </c>
       <c r="M38" s="24" t="n">
-        <v>-17.52</v>
+        <v>-17.71</v>
       </c>
     </row>
     <row r="39">
@@ -8496,35 +8274,29 @@
       <c r="C39" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="D39" s="13" t="n">
-        <v>48</v>
-      </c>
-      <c r="E39" s="13" t="n">
-        <v>35</v>
-      </c>
-      <c r="F39" s="13" t="n">
-        <v>50</v>
-      </c>
+      <c r="D39" s="13" t="n"/>
+      <c r="E39" s="13" t="n"/>
+      <c r="F39" s="13" t="n"/>
       <c r="G39" s="23" t="n">
-        <v>-13.82</v>
+        <v>4.53</v>
       </c>
       <c r="H39" s="24" t="n">
-        <v>-89.23</v>
+        <v>59.26</v>
       </c>
       <c r="I39" s="23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="J39" s="23" t="n">
-        <v>0.37</v>
+        <v>0.99</v>
       </c>
       <c r="K39" s="24" t="n">
-        <v>20.45</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="L39" s="23" t="n">
-        <v>-10.96</v>
+        <v>-1.42</v>
       </c>
       <c r="M39" s="24" t="n">
-        <v>-14.38</v>
+        <v>-17.19</v>
       </c>
     </row>
     <row r="40">
@@ -8537,35 +8309,29 @@
       <c r="C40" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="D40" s="13" t="n">
-        <v>48</v>
-      </c>
-      <c r="E40" s="13" t="n">
-        <v>35</v>
-      </c>
-      <c r="F40" s="13" t="n">
-        <v>50</v>
-      </c>
+      <c r="D40" s="13" t="n"/>
+      <c r="E40" s="13" t="n"/>
+      <c r="F40" s="13" t="n"/>
       <c r="G40" s="23" t="n">
-        <v>-16.27</v>
+        <v>2.64</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>-108.67</v>
+        <v>39.82</v>
       </c>
       <c r="I40" s="23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="J40" s="23" t="n">
-        <v>0.37</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K40" s="24" t="n">
-        <v>20.95</v>
+        <v>-7.86</v>
       </c>
       <c r="L40" s="23" t="n">
-        <v>-13</v>
+        <v>-0.12</v>
       </c>
       <c r="M40" s="24" t="n">
-        <v>-10.49</v>
+        <v>-13.23</v>
       </c>
     </row>
     <row r="41">
@@ -8578,35 +8344,29 @@
       <c r="C41" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="D41" s="13" t="n">
-        <v>48</v>
-      </c>
-      <c r="E41" s="13" t="n">
-        <v>35</v>
-      </c>
-      <c r="F41" s="13" t="n">
-        <v>50</v>
-      </c>
+      <c r="D41" s="13" t="n"/>
+      <c r="E41" s="13" t="n"/>
+      <c r="F41" s="13" t="n"/>
       <c r="G41" s="23" t="n">
-        <v>-18.54</v>
+        <v>2.59</v>
       </c>
       <c r="H41" s="24" t="n">
-        <v>-127.76</v>
+        <v>20.82</v>
       </c>
       <c r="I41" s="23" t="n">
-        <v>2.86</v>
+        <v>7.03</v>
       </c>
       <c r="J41" s="23" t="n">
-        <v>0.37</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="K41" s="24" t="n">
-        <v>21.53</v>
+        <v>-7.14</v>
       </c>
       <c r="L41" s="23" t="n">
-        <v>-13.79</v>
+        <v>0.11</v>
       </c>
       <c r="M41" s="24" t="n">
-        <v>-10.13</v>
+        <v>-12.78</v>
       </c>
     </row>
     <row r="42">
@@ -8619,35 +8379,29 @@
       <c r="C42" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="D42" s="13" t="n">
-        <v>37</v>
-      </c>
-      <c r="E42" s="13" t="n">
-        <v>35.01</v>
-      </c>
-      <c r="F42" s="13" t="n">
-        <v>50</v>
-      </c>
+      <c r="D42" s="13" t="n"/>
+      <c r="E42" s="13" t="n"/>
+      <c r="F42" s="13" t="n"/>
       <c r="G42" s="23" t="n">
-        <v>-20.73</v>
+        <v>0.28</v>
       </c>
       <c r="H42" s="24" t="n">
-        <v>-143.94</v>
+        <v>4.73</v>
       </c>
       <c r="I42" s="23" t="n">
-        <v>0</v>
+        <v>7.03</v>
       </c>
       <c r="J42" s="23" t="n">
-        <v>0.37</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="K42" s="24" t="n">
-        <v>25.01</v>
+        <v>-6.02</v>
       </c>
       <c r="L42" s="23" t="n">
-        <v>-14.11</v>
+        <v>-2.3</v>
       </c>
       <c r="M42" s="24" t="n">
-        <v>-9.210000000000001</v>
+        <v>-11.19</v>
       </c>
     </row>
     <row r="43">
@@ -8660,35 +8414,29 @@
       <c r="C43" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="D43" s="13" t="n">
-        <v>37</v>
-      </c>
-      <c r="E43" s="13" t="n">
-        <v>35.01</v>
-      </c>
-      <c r="F43" s="13" t="n">
-        <v>50</v>
-      </c>
+      <c r="D43" s="13" t="n"/>
+      <c r="E43" s="13" t="n"/>
+      <c r="F43" s="13" t="n"/>
       <c r="G43" s="23" t="n">
-        <v>-22.66</v>
+        <v>-2.21</v>
       </c>
       <c r="H43" s="24" t="n">
-        <v>-160.82</v>
+        <v>-12.1</v>
       </c>
       <c r="I43" s="23" t="n">
-        <v>0</v>
+        <v>7.03</v>
       </c>
       <c r="J43" s="23" t="n">
-        <v>0.2</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="K43" s="24" t="n">
-        <v>25.96</v>
+        <v>-5.43</v>
       </c>
       <c r="L43" s="23" t="n">
-        <v>-12.43</v>
+        <v>-1.79</v>
       </c>
       <c r="M43" s="24" t="n">
-        <v>-8.43</v>
+        <v>-12.39</v>
       </c>
     </row>
     <row r="44">
@@ -8701,35 +8449,29 @@
       <c r="C44" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="D44" s="13" t="n">
-        <v>37</v>
-      </c>
-      <c r="E44" s="13" t="n">
-        <v>35.01</v>
-      </c>
-      <c r="F44" s="13" t="n">
-        <v>50</v>
-      </c>
+      <c r="D44" s="13" t="n"/>
+      <c r="E44" s="13" t="n"/>
+      <c r="F44" s="13" t="n"/>
       <c r="G44" s="23" t="n">
-        <v>-23.06</v>
+        <v>-2.47</v>
       </c>
       <c r="H44" s="24" t="n">
-        <v>-167.7</v>
+        <v>-18.93</v>
       </c>
       <c r="I44" s="23" t="n">
-        <v>2.87</v>
+        <v>7.03</v>
       </c>
       <c r="J44" s="23" t="n">
-        <v>0.2</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="K44" s="24" t="n">
-        <v>25.61</v>
+        <v>-4.58</v>
       </c>
       <c r="L44" s="23" t="n">
-        <v>-11.87</v>
+        <v>1.26</v>
       </c>
       <c r="M44" s="24" t="n">
-        <v>-8.06</v>
+        <v>-11.36</v>
       </c>
     </row>
     <row r="45">
@@ -8742,35 +8484,29 @@
       <c r="C45" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="D45" s="13" t="n">
-        <v>37</v>
-      </c>
-      <c r="E45" s="13" t="n">
-        <v>35.01</v>
-      </c>
-      <c r="F45" s="13" t="n">
-        <v>50</v>
-      </c>
+      <c r="D45" s="13" t="n"/>
+      <c r="E45" s="13" t="n"/>
+      <c r="F45" s="13" t="n"/>
       <c r="G45" s="23" t="n">
-        <v>-20.02</v>
+        <v>-1.79</v>
       </c>
       <c r="H45" s="24" t="n">
-        <v>-162.05</v>
+        <v>-13.31</v>
       </c>
       <c r="I45" s="23" t="n">
-        <v>0</v>
+        <v>5.77</v>
       </c>
       <c r="J45" s="23" t="n">
-        <v>0.2</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="K45" s="24" t="n">
-        <v>27.86</v>
+        <v>-5.77</v>
       </c>
       <c r="L45" s="23" t="n">
-        <v>-1.69</v>
+        <v>1.53</v>
       </c>
       <c r="M45" s="24" t="n">
-        <v>-4.3</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="46">
@@ -8783,35 +8519,29 @@
       <c r="C46" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="D46" s="13" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="E46" s="13" t="n">
-        <v>37.11</v>
-      </c>
-      <c r="F46" s="13" t="n">
-        <v>50</v>
-      </c>
+      <c r="D46" s="13" t="n"/>
+      <c r="E46" s="13" t="n"/>
+      <c r="F46" s="13" t="n"/>
       <c r="G46" s="23" t="n">
-        <v>-13.84</v>
+        <v>0.42</v>
       </c>
       <c r="H46" s="24" t="n">
-        <v>-149.05</v>
+        <v>-0.23</v>
       </c>
       <c r="I46" s="23" t="n">
-        <v>3.51</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="J46" s="23" t="n">
-        <v>0.39</v>
+        <v>9</v>
       </c>
       <c r="K46" s="24" t="n">
-        <v>38.2</v>
+        <v>-1.91</v>
       </c>
       <c r="L46" s="23" t="n">
-        <v>6.83</v>
+        <v>-2.89</v>
       </c>
       <c r="M46" s="24" t="n">
-        <v>-1.58</v>
+        <v>-11.37</v>
       </c>
     </row>
     <row r="47">
@@ -8824,35 +8554,29 @@
       <c r="C47" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="D47" s="13" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="E47" s="13" t="n">
-        <v>37.11</v>
-      </c>
-      <c r="F47" s="13" t="n">
-        <v>50</v>
-      </c>
+      <c r="D47" s="13" t="n"/>
+      <c r="E47" s="13" t="n"/>
+      <c r="F47" s="13" t="n"/>
       <c r="G47" s="23" t="n">
-        <v>-15</v>
+        <v>1.65</v>
       </c>
       <c r="H47" s="24" t="n">
-        <v>-154.01</v>
+        <v>-5.22</v>
       </c>
       <c r="I47" s="23" t="n">
-        <v>1.41</v>
+        <v>5.77</v>
       </c>
       <c r="J47" s="23" t="n">
-        <v>0.2</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="K47" s="24" t="n">
-        <v>37.12</v>
+        <v>-2.52</v>
       </c>
       <c r="L47" s="23" t="n">
-        <v>0.52</v>
+        <v>5.05</v>
       </c>
       <c r="M47" s="24" t="n">
-        <v>5.54</v>
+        <v>-3.33</v>
       </c>
     </row>
     <row r="48">
@@ -8865,35 +8589,29 @@
       <c r="C48" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="D48" s="13" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="E48" s="13" t="n">
-        <v>37.11</v>
-      </c>
-      <c r="F48" s="13" t="n">
-        <v>50</v>
-      </c>
+      <c r="D48" s="13" t="n"/>
+      <c r="E48" s="13" t="n"/>
+      <c r="F48" s="13" t="n"/>
       <c r="G48" s="23" t="n">
-        <v>-15.24</v>
+        <v>5.17</v>
       </c>
       <c r="H48" s="24" t="n">
-        <v>-157.93</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="I48" s="23" t="n">
-        <v>0</v>
+        <v>10.31</v>
       </c>
       <c r="J48" s="23" t="n">
-        <v>0.2</v>
+        <v>16.16</v>
       </c>
       <c r="K48" s="24" t="n">
-        <v>41.52</v>
+        <v>0.41</v>
       </c>
       <c r="L48" s="23" t="n">
-        <v>1.09</v>
+        <v>11.31</v>
       </c>
       <c r="M48" s="24" t="n">
-        <v>4.07</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="49">
@@ -8906,35 +8624,29 @@
       <c r="C49" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="D49" s="13" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="E49" s="13" t="n">
-        <v>37.11</v>
-      </c>
-      <c r="F49" s="13" t="n">
-        <v>50</v>
-      </c>
+      <c r="D49" s="13" t="n"/>
+      <c r="E49" s="13" t="n"/>
+      <c r="F49" s="13" t="n"/>
       <c r="G49" s="23" t="n">
-        <v>-19.03</v>
+        <v>2.96</v>
       </c>
       <c r="H49" s="24" t="n">
-        <v>-189.17</v>
+        <v>-40.39</v>
       </c>
       <c r="I49" s="23" t="n">
-        <v>2.87</v>
+        <v>12.18</v>
       </c>
       <c r="J49" s="23" t="n">
-        <v>0.2</v>
+        <v>38.43</v>
       </c>
       <c r="K49" s="24" t="n">
-        <v>47</v>
+        <v>-2.58</v>
       </c>
       <c r="L49" s="23" t="n">
-        <v>-0.55</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="M49" s="24" t="n">
-        <v>1.88</v>
+        <v>-6.71</v>
       </c>
     </row>
     <row r="50">
@@ -8947,35 +8659,29 @@
       <c r="C50" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="D50" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="E50" s="13" t="n">
-        <v>36</v>
-      </c>
-      <c r="F50" s="13" t="n">
-        <v>50</v>
-      </c>
+      <c r="D50" s="13" t="n"/>
+      <c r="E50" s="13" t="n"/>
+      <c r="F50" s="13" t="n"/>
       <c r="G50" s="23" t="n">
-        <v>-19.71</v>
+        <v>3.93</v>
       </c>
       <c r="H50" s="24" t="n">
-        <v>-187</v>
+        <v>-38.15</v>
       </c>
       <c r="I50" s="23" t="n">
-        <v>0</v>
+        <v>10.31</v>
       </c>
       <c r="J50" s="23" t="n">
-        <v>0.2</v>
+        <v>38.21</v>
       </c>
       <c r="K50" s="24" t="n">
-        <v>41.49</v>
+        <v>-1.43</v>
       </c>
       <c r="L50" s="23" t="n">
-        <v>0.39</v>
+        <v>6.24</v>
       </c>
       <c r="M50" s="24" t="n">
-        <v>3.52</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="51">
@@ -8988,35 +8694,29 @@
       <c r="C51" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="D51" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="E51" s="13" t="n">
-        <v>36</v>
-      </c>
-      <c r="F51" s="13" t="n">
-        <v>50</v>
-      </c>
+      <c r="D51" s="13" t="n"/>
+      <c r="E51" s="13" t="n"/>
+      <c r="F51" s="13" t="n"/>
       <c r="G51" s="23" t="n">
-        <v>-20.84</v>
+        <v>6.95</v>
       </c>
       <c r="H51" s="24" t="n">
-        <v>-191.01</v>
+        <v>-42.15</v>
       </c>
       <c r="I51" s="23" t="n">
-        <v>0</v>
+        <v>16.69</v>
       </c>
       <c r="J51" s="23" t="n">
-        <v>0.2</v>
+        <v>45.32</v>
       </c>
       <c r="K51" s="24" t="n">
-        <v>41.46</v>
+        <v>-0.28</v>
       </c>
       <c r="L51" s="23" t="n">
-        <v>-3.43</v>
+        <v>11.87</v>
       </c>
       <c r="M51" s="24" t="n">
-        <v>4.13</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="52">
@@ -9029,35 +8729,29 @@
       <c r="C52" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="D52" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="E52" s="13" t="n">
-        <v>36</v>
-      </c>
-      <c r="F52" s="13" t="n">
-        <v>50</v>
-      </c>
+      <c r="D52" s="13" t="n"/>
+      <c r="E52" s="13" t="n"/>
+      <c r="F52" s="13" t="n"/>
       <c r="G52" s="23" t="n">
-        <v>-19.74</v>
+        <v>4.53</v>
       </c>
       <c r="H52" s="24" t="n">
-        <v>-187.3</v>
+        <v>-38.43</v>
       </c>
       <c r="I52" s="23" t="n">
-        <v>0</v>
+        <v>10.31</v>
       </c>
       <c r="J52" s="23" t="n">
-        <v>0.2</v>
+        <v>37.72</v>
       </c>
       <c r="K52" s="24" t="n">
-        <v>43.31</v>
+        <v>-1.31</v>
       </c>
       <c r="L52" s="23" t="n">
-        <v>-1.67</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="M52" s="24" t="n">
-        <v>3.86</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="53">
@@ -9070,35 +8764,29 @@
       <c r="C53" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="D53" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="E53" s="13" t="n">
-        <v>36</v>
-      </c>
-      <c r="F53" s="13" t="n">
-        <v>50</v>
-      </c>
+      <c r="D53" s="13" t="n"/>
+      <c r="E53" s="13" t="n"/>
+      <c r="F53" s="13" t="n"/>
       <c r="G53" s="23" t="n">
-        <v>-15.46</v>
+        <v>5.94</v>
       </c>
       <c r="H53" s="24" t="n">
-        <v>-171.4</v>
+        <v>-22.48</v>
       </c>
       <c r="I53" s="23" t="n">
-        <v>2.1</v>
+        <v>12.46</v>
       </c>
       <c r="J53" s="23" t="n">
-        <v>0.2</v>
+        <v>37.72</v>
       </c>
       <c r="K53" s="24" t="n">
-        <v>41.78</v>
+        <v>-3.5</v>
       </c>
       <c r="L53" s="23" t="n">
-        <v>9.529999999999999</v>
+        <v>6.67</v>
       </c>
       <c r="M53" s="24" t="n">
-        <v>3.62</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="54">
@@ -9111,35 +8799,29 @@
       <c r="C54" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="D54" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="E54" s="13" t="n">
-        <v>36</v>
-      </c>
-      <c r="F54" s="13" t="n">
-        <v>50</v>
-      </c>
+      <c r="D54" s="13" t="n"/>
+      <c r="E54" s="13" t="n"/>
+      <c r="F54" s="13" t="n"/>
       <c r="G54" s="23" t="n">
-        <v>-15.5</v>
+        <v>4.84</v>
       </c>
       <c r="H54" s="24" t="n">
-        <v>-163.56</v>
+        <v>-14.65</v>
       </c>
       <c r="I54" s="23" t="n">
-        <v>4.97</v>
+        <v>12.46</v>
       </c>
       <c r="J54" s="23" t="n">
-        <v>0.2</v>
+        <v>23.22</v>
       </c>
       <c r="K54" s="24" t="n">
-        <v>42.63</v>
+        <v>-2.88</v>
       </c>
       <c r="L54" s="23" t="n">
-        <v>0.34</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="M54" s="24" t="n">
-        <v>1.88</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="55">
@@ -9152,35 +8834,29 @@
       <c r="C55" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="D55" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="E55" s="13" t="n">
-        <v>36</v>
-      </c>
-      <c r="F55" s="13" t="n">
-        <v>50</v>
-      </c>
+      <c r="D55" s="13" t="n"/>
+      <c r="E55" s="13" t="n"/>
+      <c r="F55" s="13" t="n"/>
       <c r="G55" s="23" t="n">
-        <v>-11.68</v>
+        <v>4.89</v>
       </c>
       <c r="H55" s="24" t="n">
-        <v>-148.6</v>
+        <v>0.32</v>
       </c>
       <c r="I55" s="23" t="n">
-        <v>2.1</v>
+        <v>9.48</v>
       </c>
       <c r="J55" s="23" t="n">
-        <v>0.2</v>
+        <v>15.74</v>
       </c>
       <c r="K55" s="24" t="n">
-        <v>41.26</v>
+        <v>-3.99</v>
       </c>
       <c r="L55" s="23" t="n">
-        <v>13.04</v>
+        <v>6.94</v>
       </c>
       <c r="M55" s="24" t="n">
-        <v>3.28</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="56">
@@ -9193,35 +8869,29 @@
       <c r="C56" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="D56" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="E56" s="13" t="n">
-        <v>36</v>
-      </c>
-      <c r="F56" s="13" t="n">
-        <v>50</v>
-      </c>
+      <c r="D56" s="13" t="n"/>
+      <c r="E56" s="13" t="n"/>
+      <c r="F56" s="13" t="n"/>
       <c r="G56" s="23" t="n">
-        <v>-10.24</v>
+        <v>6.23</v>
       </c>
       <c r="H56" s="24" t="n">
-        <v>-132.06</v>
+        <v>16.81</v>
       </c>
       <c r="I56" s="23" t="n">
-        <v>2.1</v>
+        <v>9.48</v>
       </c>
       <c r="J56" s="23" t="n">
-        <v>0.39</v>
+        <v>15.8</v>
       </c>
       <c r="K56" s="24" t="n">
-        <v>41.04</v>
+        <v>-5.09</v>
       </c>
       <c r="L56" s="23" t="n">
-        <v>10.75</v>
+        <v>5.02</v>
       </c>
       <c r="M56" s="24" t="n">
-        <v>-0.26</v>
+        <v>-3.62</v>
       </c>
     </row>
     <row r="57">
@@ -9234,35 +8904,29 @@
       <c r="C57" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="D57" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="E57" s="13" t="n">
-        <v>36</v>
-      </c>
-      <c r="F57" s="13" t="n">
-        <v>50</v>
-      </c>
+      <c r="D57" s="13" t="n"/>
+      <c r="E57" s="13" t="n"/>
+      <c r="F57" s="13" t="n"/>
       <c r="G57" s="23" t="n">
-        <v>-7.74</v>
+        <v>8.27</v>
       </c>
       <c r="H57" s="24" t="n">
-        <v>-113.7</v>
+        <v>35.17</v>
       </c>
       <c r="I57" s="23" t="n">
-        <v>2.1</v>
+        <v>9.48</v>
       </c>
       <c r="J57" s="23" t="n">
-        <v>0.39</v>
+        <v>15.8</v>
       </c>
       <c r="K57" s="24" t="n">
-        <v>41.6</v>
+        <v>-4.02</v>
       </c>
       <c r="L57" s="23" t="n">
-        <v>10.15</v>
+        <v>3.05</v>
       </c>
       <c r="M57" s="24" t="n">
-        <v>-1.4</v>
+        <v>-6.61</v>
       </c>
     </row>
     <row r="58">
@@ -9276,34 +8940,34 @@
         <v>15</v>
       </c>
       <c r="D58" s="13" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E58" s="13" t="n">
-        <v>38.01</v>
+        <v>55</v>
       </c>
       <c r="F58" s="13" t="n">
         <v>55</v>
       </c>
       <c r="G58" s="23" t="n">
-        <v>-4.32</v>
+        <v>11.19</v>
       </c>
       <c r="H58" s="24" t="n">
-        <v>-91.56</v>
+        <v>57.29</v>
       </c>
       <c r="I58" s="23" t="n">
-        <v>4.21</v>
+        <v>12.77</v>
       </c>
       <c r="J58" s="23" t="n">
-        <v>0.39</v>
+        <v>15.8</v>
       </c>
       <c r="K58" s="24" t="n">
-        <v>41.69</v>
+        <v>-1.54</v>
       </c>
       <c r="L58" s="23" t="n">
-        <v>5.68</v>
+        <v>0.15</v>
       </c>
       <c r="M58" s="24" t="n">
-        <v>1.81</v>
+        <v>-11.59</v>
       </c>
     </row>
     <row r="59">
@@ -9317,34 +8981,34 @@
         <v>15</v>
       </c>
       <c r="D59" s="13" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E59" s="13" t="n">
-        <v>38.01</v>
+        <v>55</v>
       </c>
       <c r="F59" s="13" t="n">
         <v>55</v>
       </c>
       <c r="G59" s="23" t="n">
-        <v>-0.76</v>
+        <v>16.34</v>
       </c>
       <c r="H59" s="24" t="n">
-        <v>-66.58</v>
+        <v>82.3</v>
       </c>
       <c r="I59" s="23" t="n">
-        <v>6.81</v>
+        <v>15.58</v>
       </c>
       <c r="J59" s="23" t="n">
-        <v>0.39</v>
+        <v>15.8</v>
       </c>
       <c r="K59" s="24" t="n">
-        <v>41.09</v>
+        <v>-2.05</v>
       </c>
       <c r="L59" s="23" t="n">
-        <v>2.79</v>
+        <v>-2.48</v>
       </c>
       <c r="M59" s="24" t="n">
-        <v>1.94</v>
+        <v>-2.59</v>
       </c>
     </row>
     <row r="60">
@@ -9358,34 +9022,34 @@
         <v>15</v>
       </c>
       <c r="D60" s="13" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E60" s="13" t="n">
-        <v>38.01</v>
+        <v>55</v>
       </c>
       <c r="F60" s="13" t="n">
         <v>55</v>
       </c>
       <c r="G60" s="23" t="n">
-        <v>6.33</v>
+        <v>29.57</v>
       </c>
       <c r="H60" s="24" t="n">
-        <v>-39.98</v>
+        <v>108.89</v>
       </c>
       <c r="I60" s="23" t="n">
-        <v>12.54</v>
+        <v>19.61</v>
       </c>
       <c r="J60" s="23" t="n">
-        <v>1.58</v>
+        <v>21.54</v>
       </c>
       <c r="K60" s="24" t="n">
-        <v>40.77</v>
+        <v>-0.58</v>
       </c>
       <c r="L60" s="23" t="n">
-        <v>8.58</v>
+        <v>29.83</v>
       </c>
       <c r="M60" s="24" t="n">
-        <v>8.24</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="61">
@@ -9399,34 +9063,34 @@
         <v>15</v>
       </c>
       <c r="D61" s="13" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E61" s="13" t="n">
-        <v>38.01</v>
+        <v>55</v>
       </c>
       <c r="F61" s="13" t="n">
         <v>55</v>
       </c>
       <c r="G61" s="23" t="n">
-        <v>13.13</v>
+        <v>41.29</v>
       </c>
       <c r="H61" s="24" t="n">
-        <v>-12.22</v>
+        <v>136.72</v>
       </c>
       <c r="I61" s="23" t="n">
-        <v>19</v>
+        <v>23.68</v>
       </c>
       <c r="J61" s="23" t="n">
-        <v>2.7</v>
+        <v>38.77</v>
       </c>
       <c r="K61" s="24" t="n">
-        <v>49.13</v>
+        <v>4.38</v>
       </c>
       <c r="L61" s="23" t="n">
-        <v>5</v>
+        <v>37.63</v>
       </c>
       <c r="M61" s="24" t="n">
-        <v>11.72</v>
+        <v>19.84</v>
       </c>
     </row>
     <row r="62">
@@ -9439,35 +9103,29 @@
       <c r="C62" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="D62" s="13" t="n">
-        <v>205</v>
-      </c>
-      <c r="E62" s="13" t="n">
-        <v>199.99</v>
-      </c>
-      <c r="F62" s="13" t="n">
-        <v>211</v>
-      </c>
+      <c r="D62" s="13" t="n"/>
+      <c r="E62" s="13" t="n"/>
+      <c r="F62" s="13" t="n"/>
       <c r="G62" s="23" t="n">
-        <v>16.65</v>
+        <v>67.13</v>
       </c>
       <c r="H62" s="24" t="n">
-        <v>22.64</v>
+        <v>171.76</v>
       </c>
       <c r="I62" s="23" t="n">
-        <v>36.03</v>
+        <v>39.07</v>
       </c>
       <c r="J62" s="23" t="n">
-        <v>14.63</v>
+        <v>73.8</v>
       </c>
       <c r="K62" s="24" t="n">
-        <v>43.84</v>
+        <v>18.09</v>
       </c>
       <c r="L62" s="23" t="n">
-        <v>3.95</v>
+        <v>70.76000000000001</v>
       </c>
       <c r="M62" s="24" t="n">
-        <v>-21.38</v>
+        <v>44.15</v>
       </c>
     </row>
     <row r="63">
@@ -9480,35 +9138,29 @@
       <c r="C63" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="D63" s="13" t="n">
-        <v>205</v>
-      </c>
-      <c r="E63" s="13" t="n">
-        <v>199.99</v>
-      </c>
-      <c r="F63" s="13" t="n">
-        <v>211</v>
-      </c>
+      <c r="D63" s="13" t="n"/>
+      <c r="E63" s="13" t="n"/>
+      <c r="F63" s="13" t="n"/>
       <c r="G63" s="23" t="n">
-        <v>50.85</v>
+        <v>90.66</v>
       </c>
       <c r="H63" s="24" t="n">
-        <v>47.91</v>
+        <v>197.35</v>
       </c>
       <c r="I63" s="23" t="n">
-        <v>57.36</v>
+        <v>54.98</v>
       </c>
       <c r="J63" s="23" t="n">
-        <v>32.85</v>
+        <v>54.17</v>
       </c>
       <c r="K63" s="24" t="n">
-        <v>62.43</v>
+        <v>52.9</v>
       </c>
       <c r="L63" s="23" t="n">
-        <v>78.47</v>
+        <v>131.95</v>
       </c>
       <c r="M63" s="24" t="n">
-        <v>26.01</v>
+        <v>69.38</v>
       </c>
     </row>
     <row r="64">
@@ -9521,35 +9173,29 @@
       <c r="C64" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="D64" s="13" t="n">
-        <v>205</v>
-      </c>
-      <c r="E64" s="13" t="n">
-        <v>199.99</v>
-      </c>
-      <c r="F64" s="13" t="n">
-        <v>211</v>
-      </c>
+      <c r="D64" s="13" t="n"/>
+      <c r="E64" s="13" t="n"/>
+      <c r="F64" s="13" t="n"/>
       <c r="G64" s="23" t="n">
-        <v>118.12</v>
+        <v>136.64</v>
       </c>
       <c r="H64" s="24" t="n">
-        <v>74.69</v>
+        <v>224.45</v>
       </c>
       <c r="I64" s="23" t="n">
-        <v>130.57</v>
+        <v>107.55</v>
       </c>
       <c r="J64" s="23" t="n">
-        <v>128.6</v>
+        <v>153.75</v>
       </c>
       <c r="K64" s="24" t="n">
-        <v>101.26</v>
+        <v>109.38</v>
       </c>
       <c r="L64" s="23" t="n">
-        <v>142.21</v>
+        <v>129.54</v>
       </c>
       <c r="M64" s="24" t="n">
-        <v>125.17</v>
+        <v>107.47</v>
       </c>
     </row>
     <row r="65">
@@ -9562,35 +9208,29 @@
       <c r="C65" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="D65" s="13" t="n">
-        <v>205</v>
-      </c>
-      <c r="E65" s="13" t="n">
-        <v>199.99</v>
-      </c>
-      <c r="F65" s="13" t="n">
-        <v>211</v>
-      </c>
+      <c r="D65" s="13" t="n"/>
+      <c r="E65" s="13" t="n"/>
+      <c r="F65" s="13" t="n"/>
       <c r="G65" s="23" t="n">
-        <v>157.31</v>
+        <v>170.54</v>
       </c>
       <c r="H65" s="24" t="n">
-        <v>111.55</v>
+        <v>261.68</v>
       </c>
       <c r="I65" s="23" t="n">
-        <v>203.64</v>
+        <v>142.59</v>
       </c>
       <c r="J65" s="23" t="n">
-        <v>121.75</v>
+        <v>182.81</v>
       </c>
       <c r="K65" s="24" t="n">
-        <v>140.91</v>
+        <v>171.46</v>
       </c>
       <c r="L65" s="23" t="n">
-        <v>189.83</v>
+        <v>140.37</v>
       </c>
       <c r="M65" s="24" t="n">
-        <v>169.33</v>
+        <v>136.85</v>
       </c>
     </row>
     <row r="66">
@@ -9603,35 +9243,29 @@
       <c r="C66" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="D66" s="13" t="n">
-        <v>383</v>
-      </c>
-      <c r="E66" s="13" t="n">
-        <v>380</v>
-      </c>
-      <c r="F66" s="13" t="n">
-        <v>386</v>
-      </c>
+      <c r="D66" s="13" t="n"/>
+      <c r="E66" s="13" t="n"/>
+      <c r="F66" s="13" t="n"/>
       <c r="G66" s="23" t="n">
-        <v>147.16</v>
+        <v>300.09</v>
       </c>
       <c r="H66" s="24" t="n">
-        <v>127.42</v>
+        <v>278.22</v>
       </c>
       <c r="I66" s="23" t="n">
-        <v>234.53</v>
+        <v>278.64</v>
       </c>
       <c r="J66" s="23" t="n">
-        <v>28.85</v>
+        <v>301.8</v>
       </c>
       <c r="K66" s="24" t="n">
-        <v>189.52</v>
+        <v>291.97</v>
       </c>
       <c r="L66" s="23" t="n">
-        <v>177.87</v>
+        <v>333.7</v>
       </c>
       <c r="M66" s="24" t="n">
-        <v>121.41</v>
+        <v>314.52</v>
       </c>
     </row>
     <row r="67">
@@ -9644,35 +9278,29 @@
       <c r="C67" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="D67" s="13" t="n">
-        <v>383</v>
-      </c>
-      <c r="E67" s="13" t="n">
-        <v>380</v>
-      </c>
-      <c r="F67" s="13" t="n">
-        <v>386</v>
-      </c>
+      <c r="D67" s="13" t="n"/>
+      <c r="E67" s="13" t="n"/>
+      <c r="F67" s="13" t="n"/>
       <c r="G67" s="23" t="n">
-        <v>149.8</v>
+        <v>344.13</v>
       </c>
       <c r="H67" s="24" t="n">
-        <v>152.07</v>
+        <v>304.21</v>
       </c>
       <c r="I67" s="23" t="n">
-        <v>228.93</v>
+        <v>328.62</v>
       </c>
       <c r="J67" s="23" t="n">
-        <v>29.58</v>
+        <v>339.93</v>
       </c>
       <c r="K67" s="24" t="n">
-        <v>215.13</v>
+        <v>368.26</v>
       </c>
       <c r="L67" s="23" t="n">
-        <v>152.55</v>
+        <v>383.61</v>
       </c>
       <c r="M67" s="24" t="n">
-        <v>120.17</v>
+        <v>335.98</v>
       </c>
     </row>
     <row r="68">
@@ -9685,35 +9313,29 @@
       <c r="C68" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="D68" s="13" t="n">
-        <v>383</v>
-      </c>
-      <c r="E68" s="13" t="n">
-        <v>380</v>
-      </c>
-      <c r="F68" s="13" t="n">
-        <v>386</v>
-      </c>
+      <c r="D68" s="13" t="n"/>
+      <c r="E68" s="13" t="n"/>
+      <c r="F68" s="13" t="n"/>
       <c r="G68" s="23" t="n">
-        <v>142.95</v>
+        <v>362.13</v>
       </c>
       <c r="H68" s="24" t="n">
-        <v>180.5</v>
+        <v>333.86</v>
       </c>
       <c r="I68" s="23" t="n">
-        <v>188.32</v>
+        <v>332.53</v>
       </c>
       <c r="J68" s="23" t="n">
-        <v>58.75</v>
+        <v>358.92</v>
       </c>
       <c r="K68" s="24" t="n">
-        <v>205.63</v>
+        <v>384.54</v>
       </c>
       <c r="L68" s="23" t="n">
-        <v>124.94</v>
+        <v>403.15</v>
       </c>
       <c r="M68" s="24" t="n">
-        <v>104.22</v>
+        <v>357.74</v>
       </c>
     </row>
     <row r="69">
@@ -9726,35 +9348,29 @@
       <c r="C69" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="D69" s="13" t="n">
-        <v>383</v>
-      </c>
-      <c r="E69" s="13" t="n">
-        <v>380</v>
-      </c>
-      <c r="F69" s="13" t="n">
-        <v>386</v>
-      </c>
+      <c r="D69" s="13" t="n"/>
+      <c r="E69" s="13" t="n"/>
+      <c r="F69" s="13" t="n"/>
       <c r="G69" s="23" t="n">
-        <v>179.24</v>
+        <v>372.22</v>
       </c>
       <c r="H69" s="24" t="n">
-        <v>203.01</v>
+        <v>356.96</v>
       </c>
       <c r="I69" s="23" t="n">
-        <v>189.74</v>
+        <v>339</v>
       </c>
       <c r="J69" s="23" t="n">
-        <v>117.53</v>
+        <v>380.26</v>
       </c>
       <c r="K69" s="24" t="n">
-        <v>239.1</v>
+        <v>401.72</v>
       </c>
       <c r="L69" s="23" t="n">
-        <v>148.94</v>
+        <v>386.16</v>
       </c>
       <c r="M69" s="24" t="n">
-        <v>180.9</v>
+        <v>368.52</v>
       </c>
     </row>
     <row r="70">
@@ -9771,25 +9387,25 @@
       <c r="E70" s="13" t="n"/>
       <c r="F70" s="13" t="n"/>
       <c r="G70" s="23" t="n">
-        <v>181.86</v>
+        <v>373.43</v>
       </c>
       <c r="H70" s="24" t="n">
-        <v>219.33</v>
+        <v>373.82</v>
       </c>
       <c r="I70" s="23" t="n">
-        <v>181.75</v>
+        <v>342.75</v>
       </c>
       <c r="J70" s="23" t="n">
-        <v>136.04</v>
+        <v>388.4</v>
       </c>
       <c r="K70" s="24" t="n">
-        <v>232.39</v>
+        <v>389.02</v>
       </c>
       <c r="L70" s="23" t="n">
-        <v>151.1</v>
+        <v>385.36</v>
       </c>
       <c r="M70" s="24" t="n">
-        <v>176.24</v>
+        <v>362.29</v>
       </c>
     </row>
     <row r="71">
@@ -9806,25 +9422,25 @@
       <c r="E71" s="13" t="n"/>
       <c r="F71" s="13" t="n"/>
       <c r="G71" s="23" t="n">
-        <v>168.58</v>
+        <v>366.18</v>
       </c>
       <c r="H71" s="24" t="n">
-        <v>239.6</v>
+        <v>394.22</v>
       </c>
       <c r="I71" s="23" t="n">
-        <v>184.39</v>
+        <v>351.24</v>
       </c>
       <c r="J71" s="23" t="n">
-        <v>160.87</v>
+        <v>400.01</v>
       </c>
       <c r="K71" s="24" t="n">
-        <v>211.58</v>
+        <v>371.24</v>
       </c>
       <c r="L71" s="23" t="n">
-        <v>106.85</v>
+        <v>352.05</v>
       </c>
       <c r="M71" s="24" t="n">
-        <v>116.37</v>
+        <v>331.67</v>
       </c>
     </row>
     <row r="72">
@@ -9841,25 +9457,25 @@
       <c r="E72" s="13" t="n"/>
       <c r="F72" s="13" t="n"/>
       <c r="G72" s="23" t="n">
-        <v>171.74</v>
+        <v>363.98</v>
       </c>
       <c r="H72" s="24" t="n">
-        <v>251.07</v>
+        <v>406.35</v>
       </c>
       <c r="I72" s="23" t="n">
-        <v>172.12</v>
+        <v>356.87</v>
       </c>
       <c r="J72" s="23" t="n">
-        <v>173.65</v>
+        <v>409.14</v>
       </c>
       <c r="K72" s="24" t="n">
-        <v>197.85</v>
+        <v>356.63</v>
       </c>
       <c r="L72" s="23" t="n">
-        <v>130.59</v>
+        <v>347.88</v>
       </c>
       <c r="M72" s="24" t="n">
-        <v>115.06</v>
+        <v>311.62</v>
       </c>
     </row>
     <row r="73">
@@ -9876,25 +9492,25 @@
       <c r="E73" s="13" t="n"/>
       <c r="F73" s="13" t="n"/>
       <c r="G73" s="23" t="n">
-        <v>165.29</v>
+        <v>362.8</v>
       </c>
       <c r="H73" s="24" t="n">
-        <v>251.8</v>
+        <v>407.1</v>
       </c>
       <c r="I73" s="23" t="n">
-        <v>168.4</v>
+        <v>360.48</v>
       </c>
       <c r="J73" s="23" t="n">
-        <v>163.37</v>
+        <v>409.1</v>
       </c>
       <c r="K73" s="24" t="n">
-        <v>183.78</v>
+        <v>349.35</v>
       </c>
       <c r="L73" s="23" t="n">
-        <v>123.73</v>
+        <v>335.03</v>
       </c>
       <c r="M73" s="24" t="n">
-        <v>111.48</v>
+        <v>320.28</v>
       </c>
     </row>
     <row r="74">
@@ -9907,35 +9523,29 @@
       <c r="C74" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="D74" s="13" t="n">
-        <v>390</v>
-      </c>
-      <c r="E74" s="13" t="n">
-        <v>390</v>
-      </c>
-      <c r="F74" s="13" t="n">
-        <v>419.92</v>
-      </c>
+      <c r="D74" s="13" t="n"/>
+      <c r="E74" s="13" t="n"/>
+      <c r="F74" s="13" t="n"/>
       <c r="G74" s="23" t="n">
-        <v>144.8</v>
+        <v>357.16</v>
       </c>
       <c r="H74" s="24" t="n">
-        <v>245.98</v>
+        <v>401.3</v>
       </c>
       <c r="I74" s="23" t="n">
-        <v>163</v>
+        <v>354.62</v>
       </c>
       <c r="J74" s="23" t="n">
-        <v>119.43</v>
+        <v>402.37</v>
       </c>
       <c r="K74" s="24" t="n">
-        <v>170.8</v>
+        <v>343.16</v>
       </c>
       <c r="L74" s="23" t="n">
-        <v>87.14</v>
+        <v>333.82</v>
       </c>
       <c r="M74" s="24" t="n">
-        <v>94.93000000000001</v>
+        <v>312.28</v>
       </c>
     </row>
     <row r="75">
@@ -9948,35 +9558,29 @@
       <c r="C75" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="D75" s="13" t="n">
-        <v>390</v>
-      </c>
-      <c r="E75" s="13" t="n">
-        <v>390</v>
-      </c>
-      <c r="F75" s="13" t="n">
-        <v>419.92</v>
-      </c>
+      <c r="D75" s="13" t="n"/>
+      <c r="E75" s="13" t="n"/>
+      <c r="F75" s="13" t="n"/>
       <c r="G75" s="23" t="n">
-        <v>140.97</v>
+        <v>357.28</v>
       </c>
       <c r="H75" s="24" t="n">
-        <v>240.59</v>
+        <v>396.21</v>
       </c>
       <c r="I75" s="23" t="n">
-        <v>159.37</v>
+        <v>343.81</v>
       </c>
       <c r="J75" s="23" t="n">
-        <v>128.45</v>
+        <v>403.3</v>
       </c>
       <c r="K75" s="24" t="n">
-        <v>161.84</v>
+        <v>340.91</v>
       </c>
       <c r="L75" s="23" t="n">
-        <v>89.44</v>
+        <v>334.3</v>
       </c>
       <c r="M75" s="24" t="n">
-        <v>78.14</v>
+        <v>329.56</v>
       </c>
     </row>
     <row r="76">
@@ -9989,35 +9593,29 @@
       <c r="C76" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="D76" s="13" t="n">
-        <v>390</v>
-      </c>
-      <c r="E76" s="13" t="n">
-        <v>390</v>
-      </c>
-      <c r="F76" s="13" t="n">
-        <v>419.92</v>
-      </c>
+      <c r="D76" s="13" t="n"/>
+      <c r="E76" s="13" t="n"/>
+      <c r="F76" s="13" t="n"/>
       <c r="G76" s="23" t="n">
-        <v>139.02</v>
+        <v>354.62</v>
       </c>
       <c r="H76" s="24" t="n">
-        <v>236.23</v>
+        <v>392.29</v>
       </c>
       <c r="I76" s="23" t="n">
-        <v>156.92</v>
+        <v>341.31</v>
       </c>
       <c r="J76" s="23" t="n">
-        <v>133.24</v>
+        <v>410.49</v>
       </c>
       <c r="K76" s="24" t="n">
-        <v>159.11</v>
+        <v>339.85</v>
       </c>
       <c r="L76" s="23" t="n">
-        <v>79.26000000000001</v>
+        <v>320.02</v>
       </c>
       <c r="M76" s="24" t="n">
-        <v>80.88</v>
+        <v>327.61</v>
       </c>
     </row>
     <row r="77">
@@ -10030,35 +9628,29 @@
       <c r="C77" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="D77" s="13" t="n">
-        <v>390</v>
-      </c>
-      <c r="E77" s="13" t="n">
-        <v>390</v>
-      </c>
-      <c r="F77" s="13" t="n">
-        <v>419.92</v>
-      </c>
+      <c r="D77" s="13" t="n"/>
+      <c r="E77" s="13" t="n"/>
+      <c r="F77" s="13" t="n"/>
       <c r="G77" s="23" t="n">
-        <v>143.97</v>
+        <v>358.87</v>
       </c>
       <c r="H77" s="24" t="n">
-        <v>231.45</v>
+        <v>387.47</v>
       </c>
       <c r="I77" s="23" t="n">
-        <v>158.4</v>
+        <v>342.68</v>
       </c>
       <c r="J77" s="23" t="n">
-        <v>125.01</v>
+        <v>402.61</v>
       </c>
       <c r="K77" s="24" t="n">
-        <v>170.12</v>
+        <v>345.04</v>
       </c>
       <c r="L77" s="23" t="n">
-        <v>102.63</v>
+        <v>345.13</v>
       </c>
       <c r="M77" s="24" t="n">
-        <v>87.04000000000001</v>
+        <v>333.58</v>
       </c>
     </row>
     <row r="78">
@@ -10071,35 +9663,29 @@
       <c r="C78" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="D78" s="13" t="n">
-        <v>385</v>
-      </c>
-      <c r="E78" s="13" t="n">
-        <v>379.97</v>
-      </c>
-      <c r="F78" s="13" t="n">
-        <v>390.11</v>
-      </c>
+      <c r="D78" s="13" t="n"/>
+      <c r="E78" s="13" t="n"/>
+      <c r="F78" s="13" t="n"/>
       <c r="G78" s="23" t="n">
-        <v>139.02</v>
+        <v>357.76</v>
       </c>
       <c r="H78" s="24" t="n">
-        <v>224.4</v>
+        <v>380.57</v>
       </c>
       <c r="I78" s="23" t="n">
-        <v>155.84</v>
+        <v>335.09</v>
       </c>
       <c r="J78" s="23" t="n">
-        <v>104.01</v>
+        <v>401.68</v>
       </c>
       <c r="K78" s="24" t="n">
-        <v>166.42</v>
+        <v>348.4</v>
       </c>
       <c r="L78" s="23" t="n">
-        <v>96.83</v>
+        <v>342.38</v>
       </c>
       <c r="M78" s="24" t="n">
-        <v>97.5</v>
+        <v>341.2</v>
       </c>
     </row>
     <row r="79">
@@ -10112,35 +9698,29 @@
       <c r="C79" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="D79" s="13" t="n">
-        <v>385</v>
-      </c>
-      <c r="E79" s="13" t="n">
-        <v>379.97</v>
-      </c>
-      <c r="F79" s="13" t="n">
-        <v>390.11</v>
-      </c>
+      <c r="D79" s="13" t="n"/>
+      <c r="E79" s="13" t="n"/>
+      <c r="F79" s="13" t="n"/>
       <c r="G79" s="23" t="n">
-        <v>135.87</v>
+        <v>356.23</v>
       </c>
       <c r="H79" s="24" t="n">
-        <v>218.38</v>
+        <v>374.49</v>
       </c>
       <c r="I79" s="23" t="n">
-        <v>156.26</v>
+        <v>332.94</v>
       </c>
       <c r="J79" s="23" t="n">
-        <v>114.59</v>
+        <v>397.27</v>
       </c>
       <c r="K79" s="24" t="n">
-        <v>153.26</v>
+        <v>345.15</v>
       </c>
       <c r="L79" s="23" t="n">
-        <v>89.12</v>
+        <v>346.32</v>
       </c>
       <c r="M79" s="24" t="n">
-        <v>93.56999999999999</v>
+        <v>343.56</v>
       </c>
     </row>
     <row r="80">
@@ -10153,35 +9733,29 @@
       <c r="C80" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="D80" s="13" t="n">
-        <v>385</v>
-      </c>
-      <c r="E80" s="13" t="n">
-        <v>379.97</v>
-      </c>
-      <c r="F80" s="13" t="n">
-        <v>390.11</v>
-      </c>
+      <c r="D80" s="13" t="n"/>
+      <c r="E80" s="13" t="n"/>
+      <c r="F80" s="13" t="n"/>
       <c r="G80" s="23" t="n">
-        <v>130.04</v>
+        <v>352.11</v>
       </c>
       <c r="H80" s="24" t="n">
-        <v>211.69</v>
+        <v>367.73</v>
       </c>
       <c r="I80" s="23" t="n">
-        <v>150.46</v>
+        <v>331.11</v>
       </c>
       <c r="J80" s="23" t="n">
-        <v>122.88</v>
+        <v>403.77</v>
       </c>
       <c r="K80" s="24" t="n">
-        <v>146.47</v>
+        <v>343.47</v>
       </c>
       <c r="L80" s="23" t="n">
-        <v>78.73999999999999</v>
+        <v>331.48</v>
       </c>
       <c r="M80" s="24" t="n">
-        <v>79.5</v>
+        <v>336.64</v>
       </c>
     </row>
     <row r="81">
@@ -10194,35 +9768,29 @@
       <c r="C81" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="D81" s="13" t="n">
-        <v>385</v>
-      </c>
-      <c r="E81" s="13" t="n">
-        <v>379.97</v>
-      </c>
-      <c r="F81" s="13" t="n">
-        <v>390.11</v>
-      </c>
+      <c r="D81" s="13" t="n"/>
+      <c r="E81" s="13" t="n"/>
+      <c r="F81" s="13" t="n"/>
       <c r="G81" s="23" t="n">
-        <v>135.59</v>
+        <v>354.55</v>
       </c>
       <c r="H81" s="24" t="n">
-        <v>210.81</v>
+        <v>366.83</v>
       </c>
       <c r="I81" s="23" t="n">
-        <v>160.57</v>
+        <v>329.48</v>
       </c>
       <c r="J81" s="23" t="n">
-        <v>137.83</v>
+        <v>403.6</v>
       </c>
       <c r="K81" s="24" t="n">
-        <v>141.76</v>
+        <v>343.45</v>
       </c>
       <c r="L81" s="23" t="n">
-        <v>90.48999999999999</v>
+        <v>341.55</v>
       </c>
       <c r="M81" s="24" t="n">
-        <v>80.38</v>
+        <v>343.78</v>
       </c>
     </row>
     <row r="82">
@@ -10235,35 +9803,29 @@
       <c r="C82" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D82" s="13" t="n">
-        <v>384.73</v>
-      </c>
-      <c r="E82" s="13" t="n">
-        <v>379</v>
-      </c>
-      <c r="F82" s="13" t="n">
-        <v>390.11</v>
-      </c>
+      <c r="D82" s="13" t="n"/>
+      <c r="E82" s="13" t="n"/>
+      <c r="F82" s="13" t="n"/>
       <c r="G82" s="23" t="n">
-        <v>131.06</v>
+        <v>355.68</v>
       </c>
       <c r="H82" s="24" t="n">
-        <v>206.52</v>
+        <v>362.5</v>
       </c>
       <c r="I82" s="23" t="n">
-        <v>153.34</v>
+        <v>328.67</v>
       </c>
       <c r="J82" s="23" t="n">
-        <v>128.74</v>
+        <v>401.62</v>
       </c>
       <c r="K82" s="24" t="n">
-        <v>132.51</v>
+        <v>343.2</v>
       </c>
       <c r="L82" s="23" t="n">
-        <v>75.33</v>
+        <v>347.78</v>
       </c>
       <c r="M82" s="24" t="n">
-        <v>98.42</v>
+        <v>351.23</v>
       </c>
     </row>
     <row r="83">
@@ -10276,35 +9838,29 @@
       <c r="C83" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D83" s="13" t="n">
-        <v>384.73</v>
-      </c>
-      <c r="E83" s="13" t="n">
-        <v>379</v>
-      </c>
-      <c r="F83" s="13" t="n">
-        <v>390.11</v>
-      </c>
+      <c r="D83" s="13" t="n"/>
+      <c r="E83" s="13" t="n"/>
+      <c r="F83" s="13" t="n"/>
       <c r="G83" s="23" t="n">
-        <v>135.2</v>
+        <v>355.96</v>
       </c>
       <c r="H83" s="24" t="n">
-        <v>212.37</v>
+        <v>368.39</v>
       </c>
       <c r="I83" s="23" t="n">
-        <v>155.29</v>
+        <v>327.9</v>
       </c>
       <c r="J83" s="23" t="n">
-        <v>139.73</v>
+        <v>406.58</v>
       </c>
       <c r="K83" s="24" t="n">
-        <v>154.78</v>
+        <v>349.99</v>
       </c>
       <c r="L83" s="23" t="n">
-        <v>73.2</v>
+        <v>342.01</v>
       </c>
       <c r="M83" s="24" t="n">
-        <v>84.37</v>
+        <v>342.41</v>
       </c>
     </row>
     <row r="84">
@@ -10317,35 +9873,29 @@
       <c r="C84" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D84" s="13" t="n">
-        <v>384.73</v>
-      </c>
-      <c r="E84" s="13" t="n">
-        <v>379</v>
-      </c>
-      <c r="F84" s="13" t="n">
-        <v>390.11</v>
-      </c>
+      <c r="D84" s="13" t="n"/>
+      <c r="E84" s="13" t="n"/>
+      <c r="F84" s="13" t="n"/>
       <c r="G84" s="23" t="n">
-        <v>139.27</v>
+        <v>358.2</v>
       </c>
       <c r="H84" s="24" t="n">
-        <v>219.41</v>
+        <v>375.6</v>
       </c>
       <c r="I84" s="23" t="n">
-        <v>154.33</v>
+        <v>327.91</v>
       </c>
       <c r="J84" s="23" t="n">
-        <v>128.5</v>
+        <v>394.54</v>
       </c>
       <c r="K84" s="24" t="n">
-        <v>153.64</v>
+        <v>351.64</v>
       </c>
       <c r="L84" s="23" t="n">
-        <v>84.87</v>
+        <v>349.93</v>
       </c>
       <c r="M84" s="24" t="n">
-        <v>104.45</v>
+        <v>352.22</v>
       </c>
     </row>
     <row r="85">
@@ -10358,35 +9908,29 @@
       <c r="C85" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D85" s="13" t="n">
-        <v>384.73</v>
-      </c>
-      <c r="E85" s="13" t="n">
-        <v>379</v>
-      </c>
-      <c r="F85" s="13" t="n">
-        <v>390.11</v>
-      </c>
+      <c r="D85" s="13" t="n"/>
+      <c r="E85" s="13" t="n"/>
+      <c r="F85" s="13" t="n"/>
       <c r="G85" s="23" t="n">
-        <v>137.66</v>
+        <v>358.15</v>
       </c>
       <c r="H85" s="24" t="n">
-        <v>224.42</v>
+        <v>380.68</v>
       </c>
       <c r="I85" s="23" t="n">
-        <v>135.95</v>
+        <v>324.21</v>
       </c>
       <c r="J85" s="23" t="n">
-        <v>126.84</v>
+        <v>398.16</v>
       </c>
       <c r="K85" s="24" t="n">
-        <v>160.93</v>
+        <v>355.38</v>
       </c>
       <c r="L85" s="23" t="n">
-        <v>88.15000000000001</v>
+        <v>344.07</v>
       </c>
       <c r="M85" s="24" t="n">
-        <v>100.87</v>
+        <v>349.71</v>
       </c>
     </row>
     <row r="86">
@@ -10399,35 +9943,29 @@
       <c r="C86" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="D86" s="13" t="n">
-        <v>383.76</v>
-      </c>
-      <c r="E86" s="13" t="n">
-        <v>379</v>
-      </c>
-      <c r="F86" s="13" t="n">
-        <v>600</v>
-      </c>
+      <c r="D86" s="13" t="n"/>
+      <c r="E86" s="13" t="n"/>
+      <c r="F86" s="13" t="n"/>
       <c r="G86" s="23" t="n">
-        <v>140</v>
+        <v>351.12</v>
       </c>
       <c r="H86" s="24" t="n">
-        <v>230.05</v>
+        <v>386.48</v>
       </c>
       <c r="I86" s="23" t="n">
-        <v>139.44</v>
+        <v>332.24</v>
       </c>
       <c r="J86" s="23" t="n">
-        <v>156.49</v>
+        <v>406.3</v>
       </c>
       <c r="K86" s="24" t="n">
-        <v>158.38</v>
+        <v>342.42</v>
       </c>
       <c r="L86" s="23" t="n">
-        <v>102.62</v>
+        <v>333.65</v>
       </c>
       <c r="M86" s="24" t="n">
-        <v>64</v>
+        <v>309.56</v>
       </c>
     </row>
     <row r="87">
@@ -10440,35 +9978,29 @@
       <c r="C87" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="D87" s="13" t="n">
-        <v>383.76</v>
-      </c>
-      <c r="E87" s="13" t="n">
-        <v>379</v>
-      </c>
-      <c r="F87" s="13" t="n">
-        <v>600</v>
-      </c>
+      <c r="D87" s="13" t="n"/>
+      <c r="E87" s="13" t="n"/>
+      <c r="F87" s="13" t="n"/>
       <c r="G87" s="23" t="n">
-        <v>131.04</v>
+        <v>349.09</v>
       </c>
       <c r="H87" s="24" t="n">
-        <v>225.95</v>
+        <v>382.37</v>
       </c>
       <c r="I87" s="23" t="n">
-        <v>122.02</v>
+        <v>329.24</v>
       </c>
       <c r="J87" s="23" t="n">
-        <v>140.17</v>
+        <v>406.3</v>
       </c>
       <c r="K87" s="24" t="n">
-        <v>151.34</v>
+        <v>345.94</v>
       </c>
       <c r="L87" s="23" t="n">
-        <v>93.54000000000001</v>
+        <v>334.13</v>
       </c>
       <c r="M87" s="24" t="n">
-        <v>65.41</v>
+        <v>300.21</v>
       </c>
     </row>
     <row r="88">
@@ -10481,35 +10013,29 @@
       <c r="C88" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="D88" s="13" t="n">
-        <v>383.76</v>
-      </c>
-      <c r="E88" s="13" t="n">
-        <v>379</v>
-      </c>
-      <c r="F88" s="13" t="n">
-        <v>600</v>
-      </c>
+      <c r="D88" s="13" t="n"/>
+      <c r="E88" s="13" t="n"/>
+      <c r="F88" s="13" t="n"/>
       <c r="G88" s="23" t="n">
-        <v>127.53</v>
+        <v>348.27</v>
       </c>
       <c r="H88" s="24" t="n">
-        <v>228.08</v>
+        <v>384.57</v>
       </c>
       <c r="I88" s="23" t="n">
-        <v>120.44</v>
+        <v>326.94</v>
       </c>
       <c r="J88" s="23" t="n">
-        <v>129.81</v>
+        <v>411.19</v>
       </c>
       <c r="K88" s="24" t="n">
-        <v>156.76</v>
+        <v>349</v>
       </c>
       <c r="L88" s="23" t="n">
-        <v>92.11</v>
+        <v>330.72</v>
       </c>
       <c r="M88" s="24" t="n">
-        <v>50.96</v>
+        <v>291.18</v>
       </c>
     </row>
     <row r="89">
@@ -10522,35 +10048,29 @@
       <c r="C89" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="D89" s="13" t="n">
-        <v>383.76</v>
-      </c>
-      <c r="E89" s="13" t="n">
-        <v>379</v>
-      </c>
-      <c r="F89" s="13" t="n">
-        <v>600</v>
-      </c>
+      <c r="D89" s="13" t="n"/>
+      <c r="E89" s="13" t="n"/>
+      <c r="F89" s="13" t="n"/>
       <c r="G89" s="23" t="n">
-        <v>140.8</v>
+        <v>353.48</v>
       </c>
       <c r="H89" s="24" t="n">
-        <v>227.84</v>
+        <v>384.36</v>
       </c>
       <c r="I89" s="23" t="n">
-        <v>136.22</v>
+        <v>332.86</v>
       </c>
       <c r="J89" s="23" t="n">
-        <v>158.25</v>
+        <v>411.19</v>
       </c>
       <c r="K89" s="24" t="n">
-        <v>158.2</v>
+        <v>349.61</v>
       </c>
       <c r="L89" s="23" t="n">
-        <v>116.71</v>
+        <v>345.56</v>
       </c>
       <c r="M89" s="24" t="n">
-        <v>58.44</v>
+        <v>300.73</v>
       </c>
     </row>
     <row r="90">
@@ -10563,35 +10083,29 @@
       <c r="C90" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="D90" s="13" t="n">
-        <v>383.1</v>
-      </c>
-      <c r="E90" s="13" t="n">
-        <v>379</v>
-      </c>
-      <c r="F90" s="13" t="n">
-        <v>600</v>
-      </c>
+      <c r="D90" s="13" t="n"/>
+      <c r="E90" s="13" t="n"/>
+      <c r="F90" s="13" t="n"/>
       <c r="G90" s="23" t="n">
-        <v>150.31</v>
+        <v>358.92</v>
       </c>
       <c r="H90" s="24" t="n">
-        <v>224.24</v>
+        <v>380.64</v>
       </c>
       <c r="I90" s="23" t="n">
-        <v>148.16</v>
+        <v>337.33</v>
       </c>
       <c r="J90" s="23" t="n">
-        <v>156.22</v>
+        <v>411.19</v>
       </c>
       <c r="K90" s="24" t="n">
-        <v>176.58</v>
+        <v>353.7</v>
       </c>
       <c r="L90" s="23" t="n">
-        <v>136.83</v>
+        <v>360.31</v>
       </c>
       <c r="M90" s="24" t="n">
-        <v>69.23999999999999</v>
+        <v>312.82</v>
       </c>
     </row>
     <row r="91">
@@ -10604,35 +10118,29 @@
       <c r="C91" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="D91" s="13" t="n">
-        <v>383.1</v>
-      </c>
-      <c r="E91" s="13" t="n">
-        <v>379</v>
-      </c>
-      <c r="F91" s="13" t="n">
-        <v>600</v>
-      </c>
+      <c r="D91" s="13" t="n"/>
+      <c r="E91" s="13" t="n"/>
+      <c r="F91" s="13" t="n"/>
       <c r="G91" s="23" t="n">
-        <v>156.26</v>
+        <v>357.75</v>
       </c>
       <c r="H91" s="24" t="n">
-        <v>231.54</v>
+        <v>387.98</v>
       </c>
       <c r="I91" s="23" t="n">
-        <v>183.95</v>
+        <v>338.08</v>
       </c>
       <c r="J91" s="23" t="n">
-        <v>166.05</v>
+        <v>411.19</v>
       </c>
       <c r="K91" s="24" t="n">
-        <v>181.19</v>
+        <v>354.74</v>
       </c>
       <c r="L91" s="23" t="n">
-        <v>107.88</v>
+        <v>346.54</v>
       </c>
       <c r="M91" s="24" t="n">
-        <v>74.88</v>
+        <v>311.33</v>
       </c>
     </row>
     <row r="92">
@@ -10645,35 +10153,29 @@
       <c r="C92" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="D92" s="13" t="n">
-        <v>383.1</v>
-      </c>
-      <c r="E92" s="13" t="n">
-        <v>379</v>
-      </c>
-      <c r="F92" s="13" t="n">
-        <v>600</v>
-      </c>
+      <c r="D92" s="13" t="n"/>
+      <c r="E92" s="13" t="n"/>
+      <c r="F92" s="13" t="n"/>
       <c r="G92" s="23" t="n">
-        <v>171.12</v>
+        <v>355.35</v>
       </c>
       <c r="H92" s="24" t="n">
-        <v>238.4</v>
+        <v>394.21</v>
       </c>
       <c r="I92" s="23" t="n">
-        <v>174.84</v>
+        <v>334.23</v>
       </c>
       <c r="J92" s="23" t="n">
-        <v>200.08</v>
+        <v>412.37</v>
       </c>
       <c r="K92" s="24" t="n">
-        <v>192.21</v>
+        <v>360.22</v>
       </c>
       <c r="L92" s="23" t="n">
-        <v>138.59</v>
+        <v>329.47</v>
       </c>
       <c r="M92" s="24" t="n">
-        <v>90.14</v>
+        <v>305.97</v>
       </c>
     </row>
     <row r="93">
@@ -10686,35 +10188,29 @@
       <c r="C93" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="D93" s="13" t="n">
-        <v>383.1</v>
-      </c>
-      <c r="E93" s="13" t="n">
-        <v>379</v>
-      </c>
-      <c r="F93" s="13" t="n">
-        <v>600</v>
-      </c>
+      <c r="D93" s="13" t="n"/>
+      <c r="E93" s="13" t="n"/>
+      <c r="F93" s="13" t="n"/>
       <c r="G93" s="23" t="n">
-        <v>196.07</v>
+        <v>367.29</v>
       </c>
       <c r="H93" s="24" t="n">
-        <v>235.21</v>
+        <v>391.12</v>
       </c>
       <c r="I93" s="23" t="n">
-        <v>191.45</v>
+        <v>339.77</v>
       </c>
       <c r="J93" s="23" t="n">
-        <v>245.02</v>
+        <v>418.1</v>
       </c>
       <c r="K93" s="24" t="n">
-        <v>195.61</v>
+        <v>358.18</v>
       </c>
       <c r="L93" s="23" t="n">
-        <v>184.36</v>
+        <v>372.35</v>
       </c>
       <c r="M93" s="24" t="n">
-        <v>128.77</v>
+        <v>327.35</v>
       </c>
     </row>
     <row r="94">
@@ -10727,35 +10223,29 @@
       <c r="C94" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="D94" s="13" t="n">
-        <v>384.5</v>
-      </c>
-      <c r="E94" s="13" t="n">
-        <v>380</v>
-      </c>
-      <c r="F94" s="13" t="n">
-        <v>390.5</v>
-      </c>
+      <c r="D94" s="13" t="n"/>
+      <c r="E94" s="13" t="n"/>
+      <c r="F94" s="13" t="n"/>
       <c r="G94" s="23" t="n">
-        <v>226.33</v>
+        <v>378.46</v>
       </c>
       <c r="H94" s="24" t="n">
-        <v>227.78</v>
+        <v>384.34</v>
       </c>
       <c r="I94" s="23" t="n">
-        <v>221</v>
+        <v>339.84</v>
       </c>
       <c r="J94" s="23" t="n">
-        <v>265.36</v>
+        <v>417.03</v>
       </c>
       <c r="K94" s="24" t="n">
-        <v>208</v>
+        <v>366.15</v>
       </c>
       <c r="L94" s="23" t="n">
-        <v>240.54</v>
+        <v>389.43</v>
       </c>
       <c r="M94" s="24" t="n">
-        <v>194.91</v>
+        <v>375.6</v>
       </c>
     </row>
     <row r="95">
@@ -10768,35 +10258,29 @@
       <c r="C95" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="D95" s="13" t="n">
-        <v>384.5</v>
-      </c>
-      <c r="E95" s="13" t="n">
-        <v>380</v>
-      </c>
-      <c r="F95" s="13" t="n">
-        <v>390.5</v>
-      </c>
+      <c r="D95" s="13" t="n"/>
+      <c r="E95" s="13" t="n"/>
+      <c r="F95" s="13" t="n"/>
       <c r="G95" s="23" t="n">
-        <v>234.76</v>
+        <v>389.33</v>
       </c>
       <c r="H95" s="24" t="n">
-        <v>220.95</v>
+        <v>377.25</v>
       </c>
       <c r="I95" s="23" t="n">
-        <v>212.64</v>
+        <v>341.08</v>
       </c>
       <c r="J95" s="23" t="n">
-        <v>265.64</v>
+        <v>415.32</v>
       </c>
       <c r="K95" s="24" t="n">
-        <v>245.08</v>
+        <v>392.88</v>
       </c>
       <c r="L95" s="23" t="n">
-        <v>240.26</v>
+        <v>401.31</v>
       </c>
       <c r="M95" s="24" t="n">
-        <v>222.42</v>
+        <v>408.11</v>
       </c>
     </row>
     <row r="96">
@@ -10809,35 +10293,29 @@
       <c r="C96" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="D96" s="13" t="n">
-        <v>384.5</v>
-      </c>
-      <c r="E96" s="13" t="n">
-        <v>380</v>
-      </c>
-      <c r="F96" s="13" t="n">
-        <v>390.5</v>
-      </c>
+      <c r="D96" s="13" t="n"/>
+      <c r="E96" s="13" t="n"/>
+      <c r="F96" s="13" t="n"/>
       <c r="G96" s="23" t="n">
-        <v>219.97</v>
+        <v>380.11</v>
       </c>
       <c r="H96" s="24" t="n">
-        <v>204.79</v>
+        <v>360.91</v>
       </c>
       <c r="I96" s="23" t="n">
-        <v>216.98</v>
+        <v>337.62</v>
       </c>
       <c r="J96" s="23" t="n">
-        <v>249.99</v>
+        <v>413.95</v>
       </c>
       <c r="K96" s="24" t="n">
-        <v>231.41</v>
+        <v>389.79</v>
       </c>
       <c r="L96" s="23" t="n">
-        <v>206.07</v>
+        <v>390.52</v>
       </c>
       <c r="M96" s="24" t="n">
-        <v>207.86</v>
+        <v>386.43</v>
       </c>
     </row>
     <row r="97">
@@ -10852,35 +10330,29 @@
       <c r="C97" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="D97" s="13" t="n">
-        <v>384.5</v>
-      </c>
-      <c r="E97" s="13" t="n">
-        <v>380</v>
-      </c>
-      <c r="F97" s="13" t="n">
-        <v>390.5</v>
-      </c>
+      <c r="D97" s="13" t="n"/>
+      <c r="E97" s="13" t="n"/>
+      <c r="F97" s="13" t="n"/>
       <c r="G97" s="23" t="n">
-        <v>152.73</v>
+        <v>361.34</v>
       </c>
       <c r="H97" s="24" t="n">
-        <v>197.25</v>
+        <v>352.95</v>
       </c>
       <c r="I97" s="23" t="n">
-        <v>167.71</v>
+        <v>334.95</v>
       </c>
       <c r="J97" s="23" t="n">
-        <v>100.53</v>
+        <v>388.66</v>
       </c>
       <c r="K97" s="24" t="n">
-        <v>192.52</v>
+        <v>359.15</v>
       </c>
       <c r="L97" s="23" t="n">
-        <v>139</v>
+        <v>371.17</v>
       </c>
       <c r="M97" s="24" t="n">
-        <v>125.6</v>
+        <v>360.65</v>
       </c>
     </row>
   </sheetData>

--- a/forecast-results/河北电网披露及电价预估数据-20261003.xlsx
+++ b/forecast-results/河北电网披露及电价预估数据-20261003.xlsx
@@ -3764,25 +3764,25 @@
         <v>1</v>
       </c>
       <c r="D2" s="21" t="n">
-        <v>13236</v>
+        <v>13701</v>
       </c>
       <c r="E2" s="22" t="n">
-        <v>12015</v>
+        <v>14876</v>
       </c>
       <c r="F2" s="21" t="n">
-        <v>13746</v>
+        <v>13522</v>
       </c>
       <c r="G2" s="21" t="n">
-        <v>13176</v>
+        <v>12462</v>
       </c>
       <c r="H2" s="22" t="n">
-        <v>13662</v>
+        <v>13822</v>
       </c>
       <c r="I2" s="21" t="n">
-        <v>13464</v>
+        <v>13721</v>
       </c>
       <c r="J2" s="22" t="n">
-        <v>13435</v>
+        <v>13642</v>
       </c>
     </row>
     <row r="3">
@@ -3796,25 +3796,25 @@
         <v>1</v>
       </c>
       <c r="D3" s="21" t="n">
-        <v>13210</v>
+        <v>13681</v>
       </c>
       <c r="E3" s="22" t="n">
-        <v>11960</v>
+        <v>14821</v>
       </c>
       <c r="F3" s="21" t="n">
-        <v>13713</v>
+        <v>13497</v>
       </c>
       <c r="G3" s="21" t="n">
-        <v>13172</v>
+        <v>12455</v>
       </c>
       <c r="H3" s="22" t="n">
-        <v>13634</v>
+        <v>13816</v>
       </c>
       <c r="I3" s="21" t="n">
-        <v>13458</v>
+        <v>13697</v>
       </c>
       <c r="J3" s="22" t="n">
-        <v>13403</v>
+        <v>13642</v>
       </c>
     </row>
     <row r="4">
@@ -3828,25 +3828,25 @@
         <v>1</v>
       </c>
       <c r="D4" s="21" t="n">
-        <v>13123</v>
+        <v>13568</v>
       </c>
       <c r="E4" s="22" t="n">
-        <v>11884</v>
+        <v>14745</v>
       </c>
       <c r="F4" s="21" t="n">
-        <v>13578</v>
+        <v>13476</v>
       </c>
       <c r="G4" s="21" t="n">
-        <v>13234</v>
+        <v>12343</v>
       </c>
       <c r="H4" s="22" t="n">
-        <v>13427</v>
+        <v>13678</v>
       </c>
       <c r="I4" s="21" t="n">
-        <v>13308</v>
+        <v>13586</v>
       </c>
       <c r="J4" s="22" t="n">
-        <v>13396</v>
+        <v>13416</v>
       </c>
     </row>
     <row r="5">
@@ -3860,25 +3860,25 @@
         <v>1</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>12961</v>
+        <v>13373</v>
       </c>
       <c r="E5" s="22" t="n">
-        <v>11776</v>
+        <v>14637</v>
       </c>
       <c r="F5" s="21" t="n">
-        <v>13364</v>
+        <v>13380</v>
       </c>
       <c r="G5" s="21" t="n">
-        <v>13152</v>
+        <v>11934</v>
       </c>
       <c r="H5" s="22" t="n">
-        <v>13158</v>
+        <v>13542</v>
       </c>
       <c r="I5" s="21" t="n">
-        <v>13183</v>
+        <v>13258</v>
       </c>
       <c r="J5" s="22" t="n">
-        <v>13222</v>
+        <v>13303</v>
       </c>
     </row>
     <row r="6">
@@ -3892,25 +3892,25 @@
         <v>2</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>12901</v>
+        <v>13318</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>11751</v>
+        <v>14612</v>
       </c>
       <c r="F6" s="21" t="n">
-        <v>13295</v>
+        <v>13310</v>
       </c>
       <c r="G6" s="21" t="n">
-        <v>13134</v>
+        <v>11934</v>
       </c>
       <c r="H6" s="22" t="n">
-        <v>13056</v>
+        <v>13434</v>
       </c>
       <c r="I6" s="21" t="n">
-        <v>13100</v>
+        <v>13167</v>
       </c>
       <c r="J6" s="22" t="n">
-        <v>13159</v>
+        <v>13267</v>
       </c>
     </row>
     <row r="7">
@@ -3924,25 +3924,25 @@
         <v>2</v>
       </c>
       <c r="D7" s="21" t="n">
-        <v>12853</v>
+        <v>13280</v>
       </c>
       <c r="E7" s="22" t="n">
-        <v>11704</v>
+        <v>14564</v>
       </c>
       <c r="F7" s="21" t="n">
-        <v>13192</v>
+        <v>13304</v>
       </c>
       <c r="G7" s="21" t="n">
-        <v>13126</v>
+        <v>11934</v>
       </c>
       <c r="H7" s="22" t="n">
-        <v>12972</v>
+        <v>13376</v>
       </c>
       <c r="I7" s="21" t="n">
-        <v>13087</v>
+        <v>13110</v>
       </c>
       <c r="J7" s="22" t="n">
-        <v>13129</v>
+        <v>13206</v>
       </c>
     </row>
     <row r="8">
@@ -3956,25 +3956,25 @@
         <v>2</v>
       </c>
       <c r="D8" s="21" t="n">
-        <v>12687</v>
+        <v>13248</v>
       </c>
       <c r="E8" s="22" t="n">
-        <v>11591</v>
+        <v>14450</v>
       </c>
       <c r="F8" s="21" t="n">
-        <v>13207</v>
+        <v>13251</v>
       </c>
       <c r="G8" s="21" t="n">
-        <v>12931</v>
+        <v>11941</v>
       </c>
       <c r="H8" s="22" t="n">
-        <v>12540</v>
+        <v>13235</v>
       </c>
       <c r="I8" s="21" t="n">
-        <v>12989</v>
+        <v>13154</v>
       </c>
       <c r="J8" s="22" t="n">
-        <v>12944</v>
+        <v>13276</v>
       </c>
     </row>
     <row r="9">
@@ -3988,25 +3988,25 @@
         <v>2</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>12516</v>
+        <v>13138</v>
       </c>
       <c r="E9" s="22" t="n">
-        <v>11450</v>
+        <v>14309</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>13198</v>
+        <v>13169</v>
       </c>
       <c r="G9" s="21" t="n">
-        <v>12931</v>
+        <v>11941</v>
       </c>
       <c r="H9" s="22" t="n">
-        <v>12248</v>
+        <v>13158</v>
       </c>
       <c r="I9" s="21" t="n">
-        <v>12778</v>
+        <v>13004</v>
       </c>
       <c r="J9" s="22" t="n">
-        <v>12573</v>
+        <v>13074</v>
       </c>
     </row>
     <row r="10">
@@ -4020,25 +4020,25 @@
         <v>3</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>13215</v>
+        <v>14027</v>
       </c>
       <c r="E10" s="22" t="n">
-        <v>12407</v>
+        <v>15265</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>14033</v>
+        <v>14302</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>13310</v>
+        <v>12588</v>
       </c>
       <c r="H10" s="22" t="n">
-        <v>13492</v>
+        <v>13950</v>
       </c>
       <c r="I10" s="21" t="n">
-        <v>13180</v>
+        <v>13870</v>
       </c>
       <c r="J10" s="22" t="n">
-        <v>12914</v>
+        <v>13983</v>
       </c>
     </row>
     <row r="11">
@@ -4052,25 +4052,25 @@
         <v>3</v>
       </c>
       <c r="D11" s="21" t="n">
-        <v>13200</v>
+        <v>13969</v>
       </c>
       <c r="E11" s="22" t="n">
-        <v>12535</v>
+        <v>15391</v>
       </c>
       <c r="F11" s="21" t="n">
-        <v>13937</v>
+        <v>14201</v>
       </c>
       <c r="G11" s="21" t="n">
-        <v>13243</v>
+        <v>12457</v>
       </c>
       <c r="H11" s="22" t="n">
-        <v>13327</v>
+        <v>13825</v>
       </c>
       <c r="I11" s="21" t="n">
-        <v>13251</v>
+        <v>13750</v>
       </c>
       <c r="J11" s="22" t="n">
-        <v>12941</v>
+        <v>13964</v>
       </c>
     </row>
     <row r="12">
@@ -4084,25 +4084,25 @@
         <v>3</v>
       </c>
       <c r="D12" s="21" t="n">
-        <v>13114</v>
+        <v>13874</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>12444</v>
+        <v>15301</v>
       </c>
       <c r="F12" s="21" t="n">
-        <v>13860</v>
+        <v>13996</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>13222</v>
+        <v>12457</v>
       </c>
       <c r="H12" s="22" t="n">
-        <v>13190</v>
+        <v>13700</v>
       </c>
       <c r="I12" s="21" t="n">
-        <v>13138</v>
+        <v>13674</v>
       </c>
       <c r="J12" s="22" t="n">
-        <v>12867</v>
+        <v>13901</v>
       </c>
     </row>
     <row r="13">
@@ -4116,25 +4116,25 @@
         <v>3</v>
       </c>
       <c r="D13" s="21" t="n">
-        <v>13033</v>
+        <v>13826</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>12354</v>
+        <v>15211</v>
       </c>
       <c r="F13" s="21" t="n">
-        <v>13617</v>
+        <v>13776</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>13182</v>
+        <v>12435</v>
       </c>
       <c r="H13" s="22" t="n">
-        <v>13167</v>
+        <v>13725</v>
       </c>
       <c r="I13" s="21" t="n">
-        <v>13059</v>
+        <v>13646</v>
       </c>
       <c r="J13" s="22" t="n">
-        <v>12864</v>
+        <v>13961</v>
       </c>
     </row>
     <row r="14">
@@ -4148,25 +4148,25 @@
         <v>4</v>
       </c>
       <c r="D14" s="21" t="n">
-        <v>13043</v>
+        <v>13814</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>12368</v>
+        <v>15225</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>13455</v>
+        <v>13751</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>13182</v>
+        <v>12461</v>
       </c>
       <c r="H14" s="22" t="n">
-        <v>13124</v>
+        <v>13590</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>13079</v>
+        <v>13650</v>
       </c>
       <c r="J14" s="22" t="n">
-        <v>13096</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="15">
@@ -4180,25 +4180,25 @@
         <v>4</v>
       </c>
       <c r="D15" s="21" t="n">
-        <v>13102</v>
+        <v>13776</v>
       </c>
       <c r="E15" s="22" t="n">
-        <v>12346</v>
+        <v>15203</v>
       </c>
       <c r="F15" s="21" t="n">
-        <v>13601</v>
+        <v>13579</v>
       </c>
       <c r="G15" s="21" t="n">
-        <v>13133</v>
+        <v>12475</v>
       </c>
       <c r="H15" s="22" t="n">
-        <v>13202</v>
+        <v>13618</v>
       </c>
       <c r="I15" s="21" t="n">
-        <v>13221</v>
+        <v>13631</v>
       </c>
       <c r="J15" s="22" t="n">
-        <v>13153</v>
+        <v>13954</v>
       </c>
     </row>
     <row r="16">
@@ -4212,25 +4212,25 @@
         <v>4</v>
       </c>
       <c r="D16" s="21" t="n">
-        <v>13121</v>
+        <v>13704</v>
       </c>
       <c r="E16" s="22" t="n">
-        <v>12275</v>
+        <v>15132</v>
       </c>
       <c r="F16" s="21" t="n">
-        <v>13652</v>
+        <v>13476</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>13313</v>
+        <v>12380</v>
       </c>
       <c r="H16" s="22" t="n">
-        <v>13139</v>
+        <v>13604</v>
       </c>
       <c r="I16" s="21" t="n">
-        <v>13274</v>
+        <v>13604</v>
       </c>
       <c r="J16" s="22" t="n">
-        <v>13133</v>
+        <v>13832</v>
       </c>
     </row>
     <row r="17">
@@ -4244,25 +4244,25 @@
         <v>4</v>
       </c>
       <c r="D17" s="21" t="n">
-        <v>12979</v>
+        <v>13540</v>
       </c>
       <c r="E17" s="22" t="n">
-        <v>12179</v>
+        <v>15036</v>
       </c>
       <c r="F17" s="21" t="n">
-        <v>13441</v>
+        <v>13495</v>
       </c>
       <c r="G17" s="21" t="n">
-        <v>13111</v>
+        <v>11949</v>
       </c>
       <c r="H17" s="22" t="n">
-        <v>12955</v>
+        <v>13481</v>
       </c>
       <c r="I17" s="21" t="n">
-        <v>13202</v>
+        <v>13348</v>
       </c>
       <c r="J17" s="22" t="n">
-        <v>13038</v>
+        <v>13711</v>
       </c>
     </row>
     <row r="18">
@@ -4276,25 +4276,25 @@
         <v>5</v>
       </c>
       <c r="D18" s="21" t="n">
-        <v>12931</v>
+        <v>13465</v>
       </c>
       <c r="E18" s="22" t="n">
-        <v>12151</v>
+        <v>15008</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>13469</v>
+        <v>13337</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>13093</v>
+        <v>11949</v>
       </c>
       <c r="H18" s="22" t="n">
-        <v>12794</v>
+        <v>13361</v>
       </c>
       <c r="I18" s="21" t="n">
-        <v>13102</v>
+        <v>13253</v>
       </c>
       <c r="J18" s="22" t="n">
-        <v>13027</v>
+        <v>13658</v>
       </c>
     </row>
     <row r="19">
@@ -4308,25 +4308,25 @@
         <v>5</v>
       </c>
       <c r="D19" s="21" t="n">
-        <v>12866</v>
+        <v>13452</v>
       </c>
       <c r="E19" s="22" t="n">
-        <v>12076</v>
+        <v>14932</v>
       </c>
       <c r="F19" s="21" t="n">
-        <v>13461</v>
+        <v>13326</v>
       </c>
       <c r="G19" s="21" t="n">
-        <v>12972</v>
+        <v>11965</v>
       </c>
       <c r="H19" s="22" t="n">
-        <v>12715</v>
+        <v>13315</v>
       </c>
       <c r="I19" s="21" t="n">
-        <v>13042</v>
+        <v>13271</v>
       </c>
       <c r="J19" s="22" t="n">
-        <v>12975</v>
+        <v>13691</v>
       </c>
     </row>
     <row r="20">
@@ -4340,25 +4340,25 @@
         <v>5</v>
       </c>
       <c r="D20" s="21" t="n">
-        <v>12824</v>
+        <v>13400</v>
       </c>
       <c r="E20" s="22" t="n">
-        <v>12027</v>
+        <v>14884</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>13389</v>
+        <v>13294</v>
       </c>
       <c r="G20" s="21" t="n">
-        <v>12972</v>
+        <v>11932</v>
       </c>
       <c r="H20" s="22" t="n">
-        <v>12622</v>
+        <v>13185</v>
       </c>
       <c r="I20" s="21" t="n">
-        <v>13013</v>
+        <v>13243</v>
       </c>
       <c r="J20" s="22" t="n">
-        <v>12969</v>
+        <v>13646</v>
       </c>
     </row>
     <row r="21">
@@ -4372,25 +4372,25 @@
         <v>5</v>
       </c>
       <c r="D21" s="21" t="n">
-        <v>12777</v>
+        <v>13359</v>
       </c>
       <c r="E21" s="22" t="n">
-        <v>11983</v>
+        <v>14840</v>
       </c>
       <c r="F21" s="21" t="n">
-        <v>13384</v>
+        <v>13289</v>
       </c>
       <c r="G21" s="21" t="n">
-        <v>12891</v>
+        <v>11885</v>
       </c>
       <c r="H21" s="22" t="n">
-        <v>12549</v>
+        <v>13169</v>
       </c>
       <c r="I21" s="21" t="n">
-        <v>12978</v>
+        <v>13184</v>
       </c>
       <c r="J21" s="22" t="n">
-        <v>12919</v>
+        <v>13570</v>
       </c>
     </row>
     <row r="22">
@@ -4404,25 +4404,25 @@
         <v>6</v>
       </c>
       <c r="D22" s="21" t="n">
-        <v>12752</v>
+        <v>13358</v>
       </c>
       <c r="E22" s="22" t="n">
-        <v>12014</v>
+        <v>14871</v>
       </c>
       <c r="F22" s="21" t="n">
-        <v>13314</v>
+        <v>13309</v>
       </c>
       <c r="G22" s="21" t="n">
-        <v>12891</v>
+        <v>11885</v>
       </c>
       <c r="H22" s="22" t="n">
-        <v>12484</v>
+        <v>13109</v>
       </c>
       <c r="I22" s="21" t="n">
-        <v>12957</v>
+        <v>13194</v>
       </c>
       <c r="J22" s="22" t="n">
-        <v>12893</v>
+        <v>13558</v>
       </c>
     </row>
     <row r="23">
@@ -4436,25 +4436,25 @@
         <v>6</v>
       </c>
       <c r="D23" s="21" t="n">
-        <v>12727</v>
+        <v>13360</v>
       </c>
       <c r="E23" s="22" t="n">
-        <v>11984</v>
+        <v>14840</v>
       </c>
       <c r="F23" s="21" t="n">
-        <v>13319</v>
+        <v>13382</v>
       </c>
       <c r="G23" s="21" t="n">
-        <v>12859</v>
+        <v>11885</v>
       </c>
       <c r="H23" s="22" t="n">
-        <v>12335</v>
+        <v>13108</v>
       </c>
       <c r="I23" s="21" t="n">
-        <v>12986</v>
+        <v>13176</v>
       </c>
       <c r="J23" s="22" t="n">
-        <v>12918</v>
+        <v>13544</v>
       </c>
     </row>
     <row r="24">
@@ -4468,25 +4468,25 @@
         <v>6</v>
       </c>
       <c r="D24" s="21" t="n">
-        <v>12718</v>
+        <v>13347</v>
       </c>
       <c r="E24" s="22" t="n">
-        <v>11966</v>
+        <v>14823</v>
       </c>
       <c r="F24" s="21" t="n">
-        <v>13311</v>
+        <v>13348</v>
       </c>
       <c r="G24" s="21" t="n">
-        <v>12859</v>
+        <v>11885</v>
       </c>
       <c r="H24" s="22" t="n">
-        <v>12464</v>
+        <v>13107</v>
       </c>
       <c r="I24" s="21" t="n">
-        <v>12931</v>
+        <v>13171</v>
       </c>
       <c r="J24" s="22" t="n">
-        <v>12822</v>
+        <v>13526</v>
       </c>
     </row>
     <row r="25">
@@ -4500,25 +4500,25 @@
         <v>6</v>
       </c>
       <c r="D25" s="21" t="n">
-        <v>12721</v>
+        <v>13345</v>
       </c>
       <c r="E25" s="22" t="n">
-        <v>11950</v>
+        <v>14807</v>
       </c>
       <c r="F25" s="21" t="n">
-        <v>13316</v>
+        <v>13358</v>
       </c>
       <c r="G25" s="21" t="n">
-        <v>12859</v>
+        <v>11885</v>
       </c>
       <c r="H25" s="22" t="n">
-        <v>12470</v>
+        <v>13110</v>
       </c>
       <c r="I25" s="21" t="n">
-        <v>12930</v>
+        <v>13176</v>
       </c>
       <c r="J25" s="22" t="n">
-        <v>12844</v>
+        <v>13512</v>
       </c>
     </row>
     <row r="26">
@@ -4532,25 +4532,25 @@
         <v>7</v>
       </c>
       <c r="D26" s="21" t="n">
-        <v>12758</v>
+        <v>13267</v>
       </c>
       <c r="E26" s="22" t="n">
-        <v>11531</v>
+        <v>14392</v>
       </c>
       <c r="F26" s="21" t="n">
-        <v>13313</v>
+        <v>13367</v>
       </c>
       <c r="G26" s="21" t="n">
-        <v>12987</v>
+        <v>11943</v>
       </c>
       <c r="H26" s="22" t="n">
-        <v>12765</v>
+        <v>13219</v>
       </c>
       <c r="I26" s="21" t="n">
-        <v>13085</v>
+        <v>13095</v>
       </c>
       <c r="J26" s="22" t="n">
-        <v>12958</v>
+        <v>13407</v>
       </c>
     </row>
     <row r="27">
@@ -4564,25 +4564,25 @@
         <v>7</v>
       </c>
       <c r="D27" s="21" t="n">
-        <v>12660</v>
+        <v>13254</v>
       </c>
       <c r="E27" s="22" t="n">
-        <v>11493</v>
+        <v>14355</v>
       </c>
       <c r="F27" s="21" t="n">
-        <v>13209</v>
+        <v>13120</v>
       </c>
       <c r="G27" s="21" t="n">
-        <v>12624</v>
+        <v>12159</v>
       </c>
       <c r="H27" s="22" t="n">
-        <v>12782</v>
+        <v>13352</v>
       </c>
       <c r="I27" s="21" t="n">
-        <v>12913</v>
+        <v>13038</v>
       </c>
       <c r="J27" s="22" t="n">
-        <v>13007</v>
+        <v>13351</v>
       </c>
     </row>
     <row r="28">
@@ -4596,25 +4596,25 @@
         <v>7</v>
       </c>
       <c r="D28" s="21" t="n">
-        <v>12419</v>
+        <v>13045</v>
       </c>
       <c r="E28" s="22" t="n">
-        <v>11333</v>
+        <v>14195</v>
       </c>
       <c r="F28" s="21" t="n">
-        <v>12718</v>
+        <v>12823</v>
       </c>
       <c r="G28" s="21" t="n">
-        <v>12663</v>
+        <v>11863</v>
       </c>
       <c r="H28" s="22" t="n">
-        <v>12516</v>
+        <v>13139</v>
       </c>
       <c r="I28" s="21" t="n">
-        <v>12856</v>
+        <v>12844</v>
       </c>
       <c r="J28" s="22" t="n">
-        <v>12521</v>
+        <v>13249</v>
       </c>
     </row>
     <row r="29">
@@ -4628,25 +4628,25 @@
         <v>7</v>
       </c>
       <c r="D29" s="21" t="n">
-        <v>11883</v>
+        <v>12806</v>
       </c>
       <c r="E29" s="22" t="n">
-        <v>11005</v>
+        <v>13867</v>
       </c>
       <c r="F29" s="21" t="n">
-        <v>12254</v>
+        <v>12658</v>
       </c>
       <c r="G29" s="21" t="n">
-        <v>12009</v>
+        <v>11889</v>
       </c>
       <c r="H29" s="22" t="n">
-        <v>12054</v>
+        <v>12820</v>
       </c>
       <c r="I29" s="21" t="n">
-        <v>12111</v>
+        <v>12485</v>
       </c>
       <c r="J29" s="22" t="n">
-        <v>11931</v>
+        <v>12978</v>
       </c>
     </row>
     <row r="30">
@@ -4660,25 +4660,25 @@
         <v>8</v>
       </c>
       <c r="D30" s="21" t="n">
-        <v>11453</v>
+        <v>12565</v>
       </c>
       <c r="E30" s="22" t="n">
-        <v>10617</v>
+        <v>13480</v>
       </c>
       <c r="F30" s="21" t="n">
-        <v>11713</v>
+        <v>12515</v>
       </c>
       <c r="G30" s="21" t="n">
-        <v>11702</v>
+        <v>11837</v>
       </c>
       <c r="H30" s="22" t="n">
-        <v>11324</v>
+        <v>12450</v>
       </c>
       <c r="I30" s="21" t="n">
-        <v>11879</v>
+        <v>12242</v>
       </c>
       <c r="J30" s="22" t="n">
-        <v>11555</v>
+        <v>12737</v>
       </c>
     </row>
     <row r="31">
@@ -4692,25 +4692,25 @@
         <v>8</v>
       </c>
       <c r="D31" s="21" t="n">
-        <v>10635</v>
+        <v>12088</v>
       </c>
       <c r="E31" s="22" t="n">
-        <v>10075</v>
+        <v>12937</v>
       </c>
       <c r="F31" s="21" t="n">
-        <v>10883</v>
+        <v>11974</v>
       </c>
       <c r="G31" s="21" t="n">
-        <v>11273</v>
+        <v>11476</v>
       </c>
       <c r="H31" s="22" t="n">
-        <v>10334</v>
+        <v>12115</v>
       </c>
       <c r="I31" s="21" t="n">
-        <v>10688</v>
+        <v>11706</v>
       </c>
       <c r="J31" s="22" t="n">
-        <v>10621</v>
+        <v>12213</v>
       </c>
     </row>
     <row r="32">
@@ -4724,25 +4724,25 @@
         <v>8</v>
       </c>
       <c r="D32" s="21" t="n">
-        <v>9345</v>
+        <v>11150</v>
       </c>
       <c r="E32" s="22" t="n">
-        <v>9410</v>
+        <v>12270</v>
       </c>
       <c r="F32" s="21" t="n">
-        <v>9636</v>
+        <v>10912</v>
       </c>
       <c r="G32" s="21" t="n">
-        <v>9642</v>
+        <v>10839</v>
       </c>
       <c r="H32" s="22" t="n">
-        <v>9103</v>
+        <v>11193</v>
       </c>
       <c r="I32" s="21" t="n">
-        <v>9203</v>
+        <v>10603</v>
       </c>
       <c r="J32" s="22" t="n">
-        <v>9078</v>
+        <v>10967</v>
       </c>
     </row>
     <row r="33">
@@ -4756,25 +4756,25 @@
         <v>8</v>
       </c>
       <c r="D33" s="21" t="n">
-        <v>8569</v>
+        <v>10701</v>
       </c>
       <c r="E33" s="22" t="n">
-        <v>8650</v>
+        <v>11509</v>
       </c>
       <c r="F33" s="21" t="n">
-        <v>8767</v>
+        <v>10553</v>
       </c>
       <c r="G33" s="21" t="n">
-        <v>8997</v>
+        <v>10485</v>
       </c>
       <c r="H33" s="22" t="n">
-        <v>8242</v>
+        <v>10720</v>
       </c>
       <c r="I33" s="21" t="n">
-        <v>8346</v>
+        <v>10312</v>
       </c>
       <c r="J33" s="22" t="n">
-        <v>8420</v>
+        <v>10544</v>
       </c>
     </row>
     <row r="34">
@@ -4788,25 +4788,25 @@
         <v>9</v>
       </c>
       <c r="D34" s="21" t="n">
-        <v>7753</v>
+        <v>10295</v>
       </c>
       <c r="E34" s="22" t="n">
-        <v>8000</v>
+        <v>10857</v>
       </c>
       <c r="F34" s="21" t="n">
-        <v>8113</v>
+        <v>10443</v>
       </c>
       <c r="G34" s="21" t="n">
-        <v>7780</v>
+        <v>9816</v>
       </c>
       <c r="H34" s="22" t="n">
-        <v>7785</v>
+        <v>10485</v>
       </c>
       <c r="I34" s="21" t="n">
-        <v>7389</v>
+        <v>9892</v>
       </c>
       <c r="J34" s="22" t="n">
-        <v>7420</v>
+        <v>10200</v>
       </c>
     </row>
     <row r="35">
@@ -4820,25 +4820,25 @@
         <v>9</v>
       </c>
       <c r="D35" s="21" t="n">
-        <v>7418</v>
+        <v>10055</v>
       </c>
       <c r="E35" s="22" t="n">
-        <v>7359</v>
+        <v>10214</v>
       </c>
       <c r="F35" s="21" t="n">
-        <v>7860</v>
+        <v>10396</v>
       </c>
       <c r="G35" s="21" t="n">
-        <v>7754</v>
+        <v>9543</v>
       </c>
       <c r="H35" s="22" t="n">
-        <v>7401</v>
+        <v>10416</v>
       </c>
       <c r="I35" s="21" t="n">
-        <v>7062</v>
+        <v>9753</v>
       </c>
       <c r="J35" s="22" t="n">
-        <v>7080</v>
+        <v>9965</v>
       </c>
     </row>
     <row r="36">
@@ -4852,25 +4852,25 @@
         <v>9</v>
       </c>
       <c r="D36" s="21" t="n">
-        <v>7311</v>
+        <v>9884</v>
       </c>
       <c r="E36" s="22" t="n">
-        <v>6727</v>
+        <v>9582</v>
       </c>
       <c r="F36" s="21" t="n">
-        <v>7799</v>
+        <v>10233</v>
       </c>
       <c r="G36" s="21" t="n">
-        <v>7733</v>
+        <v>9478</v>
       </c>
       <c r="H36" s="22" t="n">
-        <v>7370</v>
+        <v>10379</v>
       </c>
       <c r="I36" s="21" t="n">
-        <v>7089</v>
+        <v>9706</v>
       </c>
       <c r="J36" s="22" t="n">
-        <v>7200</v>
+        <v>9940</v>
       </c>
     </row>
     <row r="37">
@@ -4884,25 +4884,25 @@
         <v>9</v>
       </c>
       <c r="D37" s="21" t="n">
-        <v>7052</v>
+        <v>9743</v>
       </c>
       <c r="E37" s="22" t="n">
-        <v>6131</v>
+        <v>8984</v>
       </c>
       <c r="F37" s="21" t="n">
-        <v>7730</v>
+        <v>10178</v>
       </c>
       <c r="G37" s="21" t="n">
-        <v>7725</v>
+        <v>9468</v>
       </c>
       <c r="H37" s="22" t="n">
-        <v>6797</v>
+        <v>10299</v>
       </c>
       <c r="I37" s="21" t="n">
-        <v>7031</v>
+        <v>9683</v>
       </c>
       <c r="J37" s="22" t="n">
-        <v>6979</v>
+        <v>9908</v>
       </c>
     </row>
     <row r="38">
@@ -4916,25 +4916,25 @@
         <v>10</v>
       </c>
       <c r="D38" s="21" t="n">
-        <v>6957</v>
+        <v>9631</v>
       </c>
       <c r="E38" s="22" t="n">
-        <v>5672</v>
+        <v>8524</v>
       </c>
       <c r="F38" s="21" t="n">
-        <v>7691</v>
+        <v>9986</v>
       </c>
       <c r="G38" s="21" t="n">
-        <v>7725</v>
+        <v>9468</v>
       </c>
       <c r="H38" s="22" t="n">
-        <v>6600</v>
+        <v>10256</v>
       </c>
       <c r="I38" s="21" t="n">
-        <v>7113</v>
+        <v>9742</v>
       </c>
       <c r="J38" s="22" t="n">
-        <v>7055</v>
+        <v>9919</v>
       </c>
     </row>
     <row r="39">
@@ -4948,25 +4948,25 @@
         <v>10</v>
       </c>
       <c r="D39" s="21" t="n">
-        <v>6840</v>
+        <v>9520</v>
       </c>
       <c r="E39" s="22" t="n">
-        <v>5209</v>
+        <v>8060</v>
       </c>
       <c r="F39" s="21" t="n">
-        <v>7641</v>
+        <v>9935</v>
       </c>
       <c r="G39" s="21" t="n">
-        <v>7718</v>
+        <v>9458</v>
       </c>
       <c r="H39" s="22" t="n">
-        <v>6596</v>
+        <v>10271</v>
       </c>
       <c r="I39" s="21" t="n">
-        <v>7046</v>
+        <v>9655</v>
       </c>
       <c r="J39" s="22" t="n">
-        <v>6974</v>
+        <v>9892</v>
       </c>
     </row>
     <row r="40">
@@ -4980,25 +4980,25 @@
         <v>10</v>
       </c>
       <c r="D40" s="21" t="n">
-        <v>6723</v>
+        <v>9425</v>
       </c>
       <c r="E40" s="22" t="n">
-        <v>4801</v>
+        <v>7653</v>
       </c>
       <c r="F40" s="21" t="n">
-        <v>7579</v>
+        <v>9923</v>
       </c>
       <c r="G40" s="21" t="n">
-        <v>7715</v>
+        <v>9458</v>
       </c>
       <c r="H40" s="22" t="n">
-        <v>6550</v>
+        <v>10249</v>
       </c>
       <c r="I40" s="21" t="n">
-        <v>6950</v>
+        <v>9629</v>
       </c>
       <c r="J40" s="22" t="n">
-        <v>6916</v>
+        <v>9820</v>
       </c>
     </row>
     <row r="41">
@@ -5012,25 +5012,25 @@
         <v>10</v>
       </c>
       <c r="D41" s="21" t="n">
-        <v>6673</v>
+        <v>9325</v>
       </c>
       <c r="E41" s="22" t="n">
-        <v>4459</v>
+        <v>7309</v>
       </c>
       <c r="F41" s="21" t="n">
-        <v>7658</v>
+        <v>9806</v>
       </c>
       <c r="G41" s="21" t="n">
-        <v>7715</v>
+        <v>9458</v>
       </c>
       <c r="H41" s="22" t="n">
-        <v>6555</v>
+        <v>10249</v>
       </c>
       <c r="I41" s="21" t="n">
-        <v>6935</v>
+        <v>9569</v>
       </c>
       <c r="J41" s="22" t="n">
-        <v>6912</v>
+        <v>9776</v>
       </c>
     </row>
     <row r="42">
@@ -5044,25 +5044,25 @@
         <v>11</v>
       </c>
       <c r="D42" s="21" t="n">
-        <v>6652</v>
+        <v>9270</v>
       </c>
       <c r="E42" s="22" t="n">
-        <v>4226</v>
+        <v>7076</v>
       </c>
       <c r="F42" s="21" t="n">
-        <v>7631</v>
+        <v>9741</v>
       </c>
       <c r="G42" s="21" t="n">
-        <v>7715</v>
+        <v>9458</v>
       </c>
       <c r="H42" s="22" t="n">
-        <v>6585</v>
+        <v>10270</v>
       </c>
       <c r="I42" s="21" t="n">
-        <v>7047</v>
+        <v>9579</v>
       </c>
       <c r="J42" s="22" t="n">
-        <v>6926</v>
+        <v>9733</v>
       </c>
     </row>
     <row r="43">
@@ -5076,25 +5076,25 @@
         <v>11</v>
       </c>
       <c r="D43" s="21" t="n">
-        <v>6605</v>
+        <v>9214</v>
       </c>
       <c r="E43" s="22" t="n">
-        <v>3931</v>
+        <v>6781</v>
       </c>
       <c r="F43" s="21" t="n">
-        <v>7640</v>
+        <v>9744</v>
       </c>
       <c r="G43" s="21" t="n">
-        <v>7716</v>
+        <v>9458</v>
       </c>
       <c r="H43" s="22" t="n">
-        <v>6590</v>
+        <v>10240</v>
       </c>
       <c r="I43" s="21" t="n">
-        <v>7050</v>
+        <v>9601</v>
       </c>
       <c r="J43" s="22" t="n">
-        <v>6939</v>
+        <v>9722</v>
       </c>
     </row>
     <row r="44">
@@ -5108,25 +5108,25 @@
         <v>11</v>
       </c>
       <c r="D44" s="21" t="n">
-        <v>6585</v>
+        <v>9163</v>
       </c>
       <c r="E44" s="22" t="n">
-        <v>3725</v>
+        <v>6575</v>
       </c>
       <c r="F44" s="21" t="n">
-        <v>7649</v>
+        <v>9717</v>
       </c>
       <c r="G44" s="21" t="n">
-        <v>7716</v>
+        <v>9458</v>
       </c>
       <c r="H44" s="22" t="n">
-        <v>6637</v>
+        <v>10250</v>
       </c>
       <c r="I44" s="21" t="n">
-        <v>7056</v>
+        <v>9601</v>
       </c>
       <c r="J44" s="22" t="n">
-        <v>6980</v>
+        <v>9662</v>
       </c>
     </row>
     <row r="45">
@@ -5140,25 +5140,25 @@
         <v>11</v>
       </c>
       <c r="D45" s="21" t="n">
-        <v>6560</v>
+        <v>9142</v>
       </c>
       <c r="E45" s="22" t="n">
-        <v>3694</v>
+        <v>6545</v>
       </c>
       <c r="F45" s="21" t="n">
-        <v>7621</v>
+        <v>9693</v>
       </c>
       <c r="G45" s="21" t="n">
-        <v>7716</v>
+        <v>9458</v>
       </c>
       <c r="H45" s="22" t="n">
-        <v>6644</v>
+        <v>10239</v>
       </c>
       <c r="I45" s="21" t="n">
-        <v>7015</v>
+        <v>9571</v>
       </c>
       <c r="J45" s="22" t="n">
-        <v>6925</v>
+        <v>9629</v>
       </c>
     </row>
     <row r="46">
@@ -5172,25 +5172,25 @@
         <v>12</v>
       </c>
       <c r="D46" s="21" t="n">
-        <v>6668</v>
+        <v>9245</v>
       </c>
       <c r="E46" s="22" t="n">
-        <v>4357</v>
+        <v>7206</v>
       </c>
       <c r="F46" s="21" t="n">
-        <v>7609</v>
+        <v>9641</v>
       </c>
       <c r="G46" s="21" t="n">
-        <v>7716</v>
+        <v>9465</v>
       </c>
       <c r="H46" s="22" t="n">
-        <v>6712</v>
+        <v>10295</v>
       </c>
       <c r="I46" s="21" t="n">
-        <v>6945</v>
+        <v>9498</v>
       </c>
       <c r="J46" s="22" t="n">
-        <v>6880</v>
+        <v>9598</v>
       </c>
     </row>
     <row r="47">
@@ -5204,25 +5204,25 @@
         <v>12</v>
       </c>
       <c r="D47" s="21" t="n">
-        <v>6653</v>
+        <v>9249</v>
       </c>
       <c r="E47" s="22" t="n">
-        <v>4369</v>
+        <v>7218</v>
       </c>
       <c r="F47" s="21" t="n">
-        <v>7629</v>
+        <v>9648</v>
       </c>
       <c r="G47" s="21" t="n">
-        <v>7716</v>
+        <v>9458</v>
       </c>
       <c r="H47" s="22" t="n">
-        <v>6524</v>
+        <v>10197</v>
       </c>
       <c r="I47" s="21" t="n">
-        <v>7008</v>
+        <v>9561</v>
       </c>
       <c r="J47" s="22" t="n">
-        <v>6878</v>
+        <v>9640</v>
       </c>
     </row>
     <row r="48">
@@ -5236,25 +5236,25 @@
         <v>12</v>
       </c>
       <c r="D48" s="21" t="n">
-        <v>6637</v>
+        <v>9255</v>
       </c>
       <c r="E48" s="22" t="n">
-        <v>4261</v>
+        <v>7110</v>
       </c>
       <c r="F48" s="21" t="n">
-        <v>7620</v>
+        <v>9680</v>
       </c>
       <c r="G48" s="21" t="n">
-        <v>7716</v>
+        <v>9458</v>
       </c>
       <c r="H48" s="22" t="n">
-        <v>6559</v>
+        <v>10241</v>
       </c>
       <c r="I48" s="21" t="n">
-        <v>7000</v>
+        <v>9587</v>
       </c>
       <c r="J48" s="22" t="n">
-        <v>6876</v>
+        <v>9693</v>
       </c>
     </row>
     <row r="49">
@@ -5268,25 +5268,25 @@
         <v>12</v>
       </c>
       <c r="D49" s="21" t="n">
-        <v>6606</v>
+        <v>9199</v>
       </c>
       <c r="E49" s="22" t="n">
-        <v>3892</v>
+        <v>6740</v>
       </c>
       <c r="F49" s="21" t="n">
-        <v>7613</v>
+        <v>9663</v>
       </c>
       <c r="G49" s="21" t="n">
-        <v>7716</v>
+        <v>9479</v>
       </c>
       <c r="H49" s="22" t="n">
-        <v>6558</v>
+        <v>10269</v>
       </c>
       <c r="I49" s="21" t="n">
-        <v>7158</v>
+        <v>9633</v>
       </c>
       <c r="J49" s="22" t="n">
-        <v>6940</v>
+        <v>9684</v>
       </c>
     </row>
     <row r="50">
@@ -5300,25 +5300,25 @@
         <v>13</v>
       </c>
       <c r="D50" s="21" t="n">
-        <v>6595</v>
+        <v>9179</v>
       </c>
       <c r="E50" s="22" t="n">
-        <v>3761</v>
+        <v>6610</v>
       </c>
       <c r="F50" s="21" t="n">
-        <v>7634</v>
+        <v>9688</v>
       </c>
       <c r="G50" s="21" t="n">
-        <v>7716</v>
+        <v>9508</v>
       </c>
       <c r="H50" s="22" t="n">
-        <v>6479</v>
+        <v>10157</v>
       </c>
       <c r="I50" s="21" t="n">
-        <v>7187</v>
+        <v>9635</v>
       </c>
       <c r="J50" s="22" t="n">
-        <v>7042</v>
+        <v>9756</v>
       </c>
     </row>
     <row r="51">
@@ -5332,25 +5332,25 @@
         <v>13</v>
       </c>
       <c r="D51" s="21" t="n">
-        <v>6602</v>
+        <v>9184</v>
       </c>
       <c r="E51" s="22" t="n">
-        <v>3699</v>
+        <v>6548</v>
       </c>
       <c r="F51" s="21" t="n">
-        <v>7640</v>
+        <v>9687</v>
       </c>
       <c r="G51" s="21" t="n">
-        <v>7716</v>
+        <v>9508</v>
       </c>
       <c r="H51" s="22" t="n">
-        <v>6550</v>
+        <v>10235</v>
       </c>
       <c r="I51" s="21" t="n">
-        <v>7175</v>
+        <v>9629</v>
       </c>
       <c r="J51" s="22" t="n">
-        <v>7085</v>
+        <v>9784</v>
       </c>
     </row>
     <row r="52">
@@ -5364,25 +5364,25 @@
         <v>13</v>
       </c>
       <c r="D52" s="21" t="n">
-        <v>6582</v>
+        <v>9159</v>
       </c>
       <c r="E52" s="22" t="n">
-        <v>3701</v>
+        <v>6550</v>
       </c>
       <c r="F52" s="21" t="n">
-        <v>7633</v>
+        <v>9697</v>
       </c>
       <c r="G52" s="21" t="n">
-        <v>7716</v>
+        <v>9508</v>
       </c>
       <c r="H52" s="22" t="n">
-        <v>6471</v>
+        <v>10147</v>
       </c>
       <c r="I52" s="21" t="n">
-        <v>7179</v>
+        <v>9603</v>
       </c>
       <c r="J52" s="22" t="n">
-        <v>7044</v>
+        <v>9733</v>
       </c>
     </row>
     <row r="53">
@@ -5396,25 +5396,25 @@
         <v>13</v>
       </c>
       <c r="D53" s="21" t="n">
-        <v>6594</v>
+        <v>9162</v>
       </c>
       <c r="E53" s="22" t="n">
-        <v>3854</v>
+        <v>6705</v>
       </c>
       <c r="F53" s="21" t="n">
-        <v>7616</v>
+        <v>9655</v>
       </c>
       <c r="G53" s="21" t="n">
-        <v>7716</v>
+        <v>9515</v>
       </c>
       <c r="H53" s="22" t="n">
-        <v>6459</v>
+        <v>10140</v>
       </c>
       <c r="I53" s="21" t="n">
-        <v>7116</v>
+        <v>9521</v>
       </c>
       <c r="J53" s="22" t="n">
-        <v>7041</v>
+        <v>9704</v>
       </c>
     </row>
     <row r="54">
@@ -5428,25 +5428,25 @@
         <v>14</v>
       </c>
       <c r="D54" s="21" t="n">
-        <v>6625</v>
+        <v>9218</v>
       </c>
       <c r="E54" s="22" t="n">
-        <v>4075</v>
+        <v>6925</v>
       </c>
       <c r="F54" s="21" t="n">
-        <v>7603</v>
+        <v>9751</v>
       </c>
       <c r="G54" s="21" t="n">
-        <v>7716</v>
+        <v>9508</v>
       </c>
       <c r="H54" s="22" t="n">
-        <v>6465</v>
+        <v>10128</v>
       </c>
       <c r="I54" s="21" t="n">
-        <v>7082</v>
+        <v>9550</v>
       </c>
       <c r="J54" s="22" t="n">
-        <v>7036</v>
+        <v>9696</v>
       </c>
     </row>
     <row r="55">
@@ -5460,25 +5460,25 @@
         <v>14</v>
       </c>
       <c r="D55" s="21" t="n">
-        <v>6656</v>
+        <v>9239</v>
       </c>
       <c r="E55" s="22" t="n">
-        <v>4269</v>
+        <v>7120</v>
       </c>
       <c r="F55" s="21" t="n">
-        <v>7584</v>
+        <v>9729</v>
       </c>
       <c r="G55" s="21" t="n">
-        <v>7716</v>
+        <v>9504</v>
       </c>
       <c r="H55" s="22" t="n">
-        <v>6459</v>
+        <v>10121</v>
       </c>
       <c r="I55" s="21" t="n">
-        <v>7062</v>
+        <v>9514</v>
       </c>
       <c r="J55" s="22" t="n">
-        <v>7057</v>
+        <v>9675</v>
       </c>
     </row>
     <row r="56">
@@ -5492,25 +5492,25 @@
         <v>14</v>
       </c>
       <c r="D56" s="21" t="n">
-        <v>6670</v>
+        <v>9274</v>
       </c>
       <c r="E56" s="22" t="n">
-        <v>4510</v>
+        <v>7361</v>
       </c>
       <c r="F56" s="21" t="n">
-        <v>7578</v>
+        <v>9745</v>
       </c>
       <c r="G56" s="21" t="n">
-        <v>7716</v>
+        <v>9504</v>
       </c>
       <c r="H56" s="22" t="n">
-        <v>6417</v>
+        <v>10107</v>
       </c>
       <c r="I56" s="21" t="n">
-        <v>7036</v>
+        <v>9485</v>
       </c>
       <c r="J56" s="22" t="n">
-        <v>6954</v>
+        <v>9650</v>
       </c>
     </row>
     <row r="57">
@@ -5524,25 +5524,25 @@
         <v>14</v>
       </c>
       <c r="D57" s="21" t="n">
-        <v>6720</v>
+        <v>9326</v>
       </c>
       <c r="E57" s="22" t="n">
-        <v>4786</v>
+        <v>7638</v>
       </c>
       <c r="F57" s="21" t="n">
-        <v>7580</v>
+        <v>9744</v>
       </c>
       <c r="G57" s="21" t="n">
-        <v>7716</v>
+        <v>9504</v>
       </c>
       <c r="H57" s="22" t="n">
-        <v>6409</v>
+        <v>10097</v>
       </c>
       <c r="I57" s="21" t="n">
-        <v>7023</v>
+        <v>9499</v>
       </c>
       <c r="J57" s="22" t="n">
-        <v>6981</v>
+        <v>9657</v>
       </c>
     </row>
     <row r="58">
@@ -5556,25 +5556,25 @@
         <v>15</v>
       </c>
       <c r="D58" s="21" t="n">
-        <v>6758</v>
+        <v>9371</v>
       </c>
       <c r="E58" s="22" t="n">
-        <v>5181</v>
+        <v>8033</v>
       </c>
       <c r="F58" s="21" t="n">
-        <v>7596</v>
+        <v>9761</v>
       </c>
       <c r="G58" s="21" t="n">
-        <v>7716</v>
+        <v>9487</v>
       </c>
       <c r="H58" s="22" t="n">
-        <v>6360</v>
+        <v>10047</v>
       </c>
       <c r="I58" s="21" t="n">
-        <v>6888</v>
+        <v>9423</v>
       </c>
       <c r="J58" s="22" t="n">
-        <v>6948</v>
+        <v>9621</v>
       </c>
     </row>
     <row r="59">
@@ -5588,25 +5588,25 @@
         <v>15</v>
       </c>
       <c r="D59" s="21" t="n">
-        <v>6821</v>
+        <v>9446</v>
       </c>
       <c r="E59" s="22" t="n">
-        <v>5571</v>
+        <v>8423</v>
       </c>
       <c r="F59" s="21" t="n">
-        <v>7602</v>
+        <v>9777</v>
       </c>
       <c r="G59" s="21" t="n">
-        <v>7716</v>
+        <v>9504</v>
       </c>
       <c r="H59" s="22" t="n">
-        <v>6372</v>
+        <v>10047</v>
       </c>
       <c r="I59" s="21" t="n">
-        <v>6890</v>
+        <v>9428</v>
       </c>
       <c r="J59" s="22" t="n">
-        <v>6891</v>
+        <v>9607</v>
       </c>
     </row>
     <row r="60">
@@ -5620,25 +5620,25 @@
         <v>15</v>
       </c>
       <c r="D60" s="21" t="n">
-        <v>6902</v>
+        <v>9515</v>
       </c>
       <c r="E60" s="22" t="n">
-        <v>5992</v>
+        <v>8846</v>
       </c>
       <c r="F60" s="21" t="n">
-        <v>7602</v>
+        <v>9765</v>
       </c>
       <c r="G60" s="21" t="n">
-        <v>7713</v>
+        <v>9504</v>
       </c>
       <c r="H60" s="22" t="n">
-        <v>6391</v>
+        <v>9997</v>
       </c>
       <c r="I60" s="21" t="n">
-        <v>6867</v>
+        <v>9432</v>
       </c>
       <c r="J60" s="22" t="n">
-        <v>6932</v>
+        <v>9621</v>
       </c>
     </row>
     <row r="61">
@@ -5652,25 +5652,25 @@
         <v>15</v>
       </c>
       <c r="D61" s="21" t="n">
-        <v>7001</v>
+        <v>9628</v>
       </c>
       <c r="E61" s="22" t="n">
-        <v>6426</v>
+        <v>9280</v>
       </c>
       <c r="F61" s="21" t="n">
-        <v>7653</v>
+        <v>9903</v>
       </c>
       <c r="G61" s="21" t="n">
-        <v>7711</v>
+        <v>9504</v>
       </c>
       <c r="H61" s="22" t="n">
-        <v>6411</v>
+        <v>9988</v>
       </c>
       <c r="I61" s="21" t="n">
-        <v>6897</v>
+        <v>9483</v>
       </c>
       <c r="J61" s="22" t="n">
-        <v>6962</v>
+        <v>9638</v>
       </c>
     </row>
     <row r="62">
@@ -5684,25 +5684,25 @@
         <v>16</v>
       </c>
       <c r="D62" s="21" t="n">
-        <v>7116</v>
+        <v>9671</v>
       </c>
       <c r="E62" s="22" t="n">
-        <v>6545</v>
+        <v>9403</v>
       </c>
       <c r="F62" s="21" t="n">
-        <v>7711</v>
+        <v>9968</v>
       </c>
       <c r="G62" s="21" t="n">
-        <v>7832</v>
+        <v>9504</v>
       </c>
       <c r="H62" s="22" t="n">
-        <v>6491</v>
+        <v>10009</v>
       </c>
       <c r="I62" s="21" t="n">
-        <v>7035</v>
+        <v>9547</v>
       </c>
       <c r="J62" s="22" t="n">
-        <v>7139</v>
+        <v>9612</v>
       </c>
     </row>
     <row r="63">
@@ -5716,25 +5716,25 @@
         <v>16</v>
       </c>
       <c r="D63" s="21" t="n">
-        <v>7392</v>
+        <v>9813</v>
       </c>
       <c r="E63" s="22" t="n">
-        <v>7098</v>
+        <v>9956</v>
       </c>
       <c r="F63" s="21" t="n">
-        <v>7958</v>
+        <v>9949</v>
       </c>
       <c r="G63" s="21" t="n">
-        <v>8014</v>
+        <v>9535</v>
       </c>
       <c r="H63" s="22" t="n">
-        <v>6765</v>
+        <v>10048</v>
       </c>
       <c r="I63" s="21" t="n">
-        <v>7333</v>
+        <v>9653</v>
       </c>
       <c r="J63" s="22" t="n">
-        <v>7215</v>
+        <v>9710</v>
       </c>
     </row>
     <row r="64">
@@ -5748,25 +5748,25 @@
         <v>16</v>
       </c>
       <c r="D64" s="21" t="n">
-        <v>7684</v>
+        <v>9995</v>
       </c>
       <c r="E64" s="22" t="n">
-        <v>7637</v>
+        <v>10495</v>
       </c>
       <c r="F64" s="21" t="n">
-        <v>8119</v>
+        <v>9935</v>
       </c>
       <c r="G64" s="21" t="n">
-        <v>8111</v>
+        <v>9878</v>
       </c>
       <c r="H64" s="22" t="n">
-        <v>7491</v>
+        <v>10154</v>
       </c>
       <c r="I64" s="21" t="n">
-        <v>7435</v>
+        <v>9720</v>
       </c>
       <c r="J64" s="22" t="n">
-        <v>7326</v>
+        <v>9740</v>
       </c>
     </row>
     <row r="65">
@@ -5780,25 +5780,25 @@
         <v>16</v>
       </c>
       <c r="D65" s="21" t="n">
-        <v>8250</v>
+        <v>10438</v>
       </c>
       <c r="E65" s="22" t="n">
-        <v>8169</v>
+        <v>11027</v>
       </c>
       <c r="F65" s="21" t="n">
-        <v>8689</v>
+        <v>10319</v>
       </c>
       <c r="G65" s="21" t="n">
-        <v>8897</v>
+        <v>10530</v>
       </c>
       <c r="H65" s="22" t="n">
-        <v>7963</v>
+        <v>10386</v>
       </c>
       <c r="I65" s="21" t="n">
-        <v>7951</v>
+        <v>10286</v>
       </c>
       <c r="J65" s="22" t="n">
-        <v>7859</v>
+        <v>10027</v>
       </c>
     </row>
     <row r="66">
@@ -5812,25 +5812,25 @@
         <v>17</v>
       </c>
       <c r="D66" s="21" t="n">
-        <v>9072</v>
+        <v>11104</v>
       </c>
       <c r="E66" s="22" t="n">
-        <v>8540</v>
+        <v>11404</v>
       </c>
       <c r="F66" s="21" t="n">
-        <v>9911</v>
+        <v>11094</v>
       </c>
       <c r="G66" s="21" t="n">
-        <v>9502</v>
+        <v>11138</v>
       </c>
       <c r="H66" s="22" t="n">
-        <v>9014</v>
+        <v>11038</v>
       </c>
       <c r="I66" s="21" t="n">
-        <v>8905</v>
+        <v>11194</v>
       </c>
       <c r="J66" s="22" t="n">
-        <v>8601</v>
+        <v>10727</v>
       </c>
     </row>
     <row r="67">
@@ -5844,25 +5844,25 @@
         <v>17</v>
       </c>
       <c r="D67" s="21" t="n">
-        <v>9932</v>
+        <v>11558</v>
       </c>
       <c r="E67" s="22" t="n">
-        <v>9139</v>
+        <v>12002</v>
       </c>
       <c r="F67" s="21" t="n">
-        <v>10738</v>
+        <v>11716</v>
       </c>
       <c r="G67" s="21" t="n">
-        <v>10443</v>
+        <v>11054</v>
       </c>
       <c r="H67" s="22" t="n">
-        <v>9721</v>
+        <v>11464</v>
       </c>
       <c r="I67" s="21" t="n">
-        <v>9900</v>
+        <v>11669</v>
       </c>
       <c r="J67" s="22" t="n">
-        <v>9711</v>
+        <v>11368</v>
       </c>
     </row>
     <row r="68">
@@ -5876,25 +5876,25 @@
         <v>17</v>
       </c>
       <c r="D68" s="21" t="n">
-        <v>10801</v>
+        <v>12111</v>
       </c>
       <c r="E68" s="22" t="n">
-        <v>9702</v>
+        <v>12564</v>
       </c>
       <c r="F68" s="21" t="n">
-        <v>11933</v>
+        <v>12161</v>
       </c>
       <c r="G68" s="21" t="n">
-        <v>11144</v>
+        <v>11460</v>
       </c>
       <c r="H68" s="22" t="n">
-        <v>10609</v>
+        <v>12207</v>
       </c>
       <c r="I68" s="21" t="n">
-        <v>10967</v>
+        <v>12248</v>
       </c>
       <c r="J68" s="22" t="n">
-        <v>10519</v>
+        <v>11956</v>
       </c>
     </row>
     <row r="69">
@@ -5908,25 +5908,25 @@
         <v>17</v>
       </c>
       <c r="D69" s="21" t="n">
-        <v>11376</v>
+        <v>12488</v>
       </c>
       <c r="E69" s="22" t="n">
-        <v>10218</v>
+        <v>13080</v>
       </c>
       <c r="F69" s="21" t="n">
-        <v>12378</v>
+        <v>12547</v>
       </c>
       <c r="G69" s="21" t="n">
-        <v>11337</v>
+        <v>11708</v>
       </c>
       <c r="H69" s="22" t="n">
-        <v>11353</v>
+        <v>12536</v>
       </c>
       <c r="I69" s="21" t="n">
-        <v>11675</v>
+        <v>12636</v>
       </c>
       <c r="J69" s="22" t="n">
-        <v>11351</v>
+        <v>12326</v>
       </c>
     </row>
     <row r="70">
@@ -5940,25 +5940,25 @@
         <v>18</v>
       </c>
       <c r="D70" s="21" t="n">
-        <v>11743</v>
+        <v>12620</v>
       </c>
       <c r="E70" s="22" t="n">
-        <v>10716</v>
+        <v>13577</v>
       </c>
       <c r="F70" s="21" t="n">
-        <v>12587</v>
+        <v>12544</v>
       </c>
       <c r="G70" s="21" t="n">
-        <v>11792</v>
+        <v>11852</v>
       </c>
       <c r="H70" s="22" t="n">
-        <v>11838</v>
+        <v>12658</v>
       </c>
       <c r="I70" s="21" t="n">
-        <v>11926</v>
+        <v>12481</v>
       </c>
       <c r="J70" s="22" t="n">
-        <v>11655</v>
+        <v>12482</v>
       </c>
     </row>
     <row r="71">
@@ -5972,25 +5972,25 @@
         <v>18</v>
       </c>
       <c r="D71" s="21" t="n">
-        <v>11983</v>
+        <v>12844</v>
       </c>
       <c r="E71" s="22" t="n">
-        <v>11117</v>
+        <v>13978</v>
       </c>
       <c r="F71" s="21" t="n">
-        <v>12762</v>
+        <v>12969</v>
       </c>
       <c r="G71" s="21" t="n">
-        <v>11869</v>
+        <v>11944</v>
       </c>
       <c r="H71" s="22" t="n">
-        <v>12323</v>
+        <v>12751</v>
       </c>
       <c r="I71" s="21" t="n">
-        <v>11989</v>
+        <v>12469</v>
       </c>
       <c r="J71" s="22" t="n">
-        <v>11880</v>
+        <v>12792</v>
       </c>
     </row>
     <row r="72">
@@ -6004,25 +6004,25 @@
         <v>18</v>
       </c>
       <c r="D72" s="21" t="n">
-        <v>12232</v>
+        <v>12954</v>
       </c>
       <c r="E72" s="22" t="n">
-        <v>11446</v>
+        <v>14307</v>
       </c>
       <c r="F72" s="21" t="n">
-        <v>13085</v>
+        <v>13162</v>
       </c>
       <c r="G72" s="21" t="n">
-        <v>11910</v>
+        <v>12007</v>
       </c>
       <c r="H72" s="22" t="n">
-        <v>12529</v>
+        <v>12845</v>
       </c>
       <c r="I72" s="21" t="n">
-        <v>12182</v>
+        <v>12541</v>
       </c>
       <c r="J72" s="22" t="n">
-        <v>12259</v>
+        <v>12672</v>
       </c>
     </row>
     <row r="73">
@@ -6036,25 +6036,25 @@
         <v>18</v>
       </c>
       <c r="D73" s="21" t="n">
-        <v>12223</v>
+        <v>12967</v>
       </c>
       <c r="E73" s="22" t="n">
-        <v>11622</v>
+        <v>14482</v>
       </c>
       <c r="F73" s="21" t="n">
-        <v>12968</v>
+        <v>13339</v>
       </c>
       <c r="G73" s="21" t="n">
-        <v>11916</v>
+        <v>11974</v>
       </c>
       <c r="H73" s="22" t="n">
-        <v>12507</v>
+        <v>12697</v>
       </c>
       <c r="I73" s="21" t="n">
-        <v>12214</v>
+        <v>12481</v>
       </c>
       <c r="J73" s="22" t="n">
-        <v>12122</v>
+        <v>12610</v>
       </c>
     </row>
     <row r="74">
@@ -6068,25 +6068,25 @@
         <v>19</v>
       </c>
       <c r="D74" s="21" t="n">
-        <v>12155</v>
+        <v>12869</v>
       </c>
       <c r="E74" s="22" t="n">
-        <v>11733</v>
+        <v>14592</v>
       </c>
       <c r="F74" s="21" t="n">
-        <v>13033</v>
+        <v>13297</v>
       </c>
       <c r="G74" s="21" t="n">
-        <v>11930</v>
+        <v>11922</v>
       </c>
       <c r="H74" s="22" t="n">
-        <v>12306</v>
+        <v>12446</v>
       </c>
       <c r="I74" s="21" t="n">
-        <v>12034</v>
+        <v>12206</v>
       </c>
       <c r="J74" s="22" t="n">
-        <v>11886</v>
+        <v>12506</v>
       </c>
     </row>
     <row r="75">
@@ -6100,25 +6100,25 @@
         <v>19</v>
       </c>
       <c r="D75" s="21" t="n">
-        <v>12167</v>
+        <v>12776</v>
       </c>
       <c r="E75" s="22" t="n">
-        <v>11712</v>
+        <v>14571</v>
       </c>
       <c r="F75" s="21" t="n">
-        <v>13076</v>
+        <v>13204</v>
       </c>
       <c r="G75" s="21" t="n">
-        <v>12125</v>
+        <v>11934</v>
       </c>
       <c r="H75" s="22" t="n">
-        <v>12226</v>
+        <v>12331</v>
       </c>
       <c r="I75" s="21" t="n">
-        <v>11994</v>
+        <v>12099</v>
       </c>
       <c r="J75" s="22" t="n">
-        <v>11873</v>
+        <v>12269</v>
       </c>
     </row>
     <row r="76">
@@ -6132,25 +6132,25 @@
         <v>19</v>
       </c>
       <c r="D76" s="21" t="n">
-        <v>12154</v>
+        <v>12652</v>
       </c>
       <c r="E76" s="22" t="n">
-        <v>11611</v>
+        <v>14469</v>
       </c>
       <c r="F76" s="21" t="n">
-        <v>12956</v>
+        <v>13171</v>
       </c>
       <c r="G76" s="21" t="n">
-        <v>12496</v>
+        <v>11778</v>
       </c>
       <c r="H76" s="22" t="n">
-        <v>12120</v>
+        <v>12235</v>
       </c>
       <c r="I76" s="21" t="n">
-        <v>11963</v>
+        <v>11846</v>
       </c>
       <c r="J76" s="22" t="n">
-        <v>11815</v>
+        <v>12157</v>
       </c>
     </row>
     <row r="77">
@@ -6164,25 +6164,25 @@
         <v>19</v>
       </c>
       <c r="D77" s="21" t="n">
-        <v>12092</v>
+        <v>12584</v>
       </c>
       <c r="E77" s="22" t="n">
-        <v>11517</v>
+        <v>14375</v>
       </c>
       <c r="F77" s="21" t="n">
-        <v>12799</v>
+        <v>13071</v>
       </c>
       <c r="G77" s="21" t="n">
-        <v>12576</v>
+        <v>11778</v>
       </c>
       <c r="H77" s="22" t="n">
-        <v>11977</v>
+        <v>12146</v>
       </c>
       <c r="I77" s="21" t="n">
-        <v>11953</v>
+        <v>11858</v>
       </c>
       <c r="J77" s="22" t="n">
-        <v>11783</v>
+        <v>12029</v>
       </c>
     </row>
     <row r="78">
@@ -6196,25 +6196,25 @@
         <v>20</v>
       </c>
       <c r="D78" s="21" t="n">
-        <v>12059</v>
+        <v>12496</v>
       </c>
       <c r="E78" s="22" t="n">
-        <v>11476</v>
+        <v>14334</v>
       </c>
       <c r="F78" s="21" t="n">
-        <v>12688</v>
+        <v>12861</v>
       </c>
       <c r="G78" s="21" t="n">
-        <v>12744</v>
+        <v>11916</v>
       </c>
       <c r="H78" s="22" t="n">
-        <v>11774</v>
+        <v>11951</v>
       </c>
       <c r="I78" s="21" t="n">
-        <v>11926</v>
+        <v>11793</v>
       </c>
       <c r="J78" s="22" t="n">
-        <v>11809</v>
+        <v>11882</v>
       </c>
     </row>
     <row r="79">
@@ -6228,25 +6228,25 @@
         <v>20</v>
       </c>
       <c r="D79" s="21" t="n">
-        <v>11998</v>
+        <v>12469</v>
       </c>
       <c r="E79" s="22" t="n">
-        <v>11367</v>
+        <v>14225</v>
       </c>
       <c r="F79" s="21" t="n">
-        <v>12672</v>
+        <v>12817</v>
       </c>
       <c r="G79" s="21" t="n">
-        <v>12663</v>
+        <v>11940</v>
       </c>
       <c r="H79" s="22" t="n">
-        <v>11572</v>
+        <v>11919</v>
       </c>
       <c r="I79" s="21" t="n">
-        <v>11931</v>
+        <v>11848</v>
       </c>
       <c r="J79" s="22" t="n">
-        <v>11839</v>
+        <v>11836</v>
       </c>
     </row>
     <row r="80">
@@ -6260,25 +6260,25 @@
         <v>20</v>
       </c>
       <c r="D80" s="21" t="n">
-        <v>11968</v>
+        <v>12452</v>
       </c>
       <c r="E80" s="22" t="n">
-        <v>11251</v>
+        <v>14108</v>
       </c>
       <c r="F80" s="21" t="n">
-        <v>12713</v>
+        <v>12784</v>
       </c>
       <c r="G80" s="21" t="n">
-        <v>12733</v>
+        <v>11947</v>
       </c>
       <c r="H80" s="22" t="n">
-        <v>11383</v>
+        <v>11852</v>
       </c>
       <c r="I80" s="21" t="n">
-        <v>11905</v>
+        <v>11915</v>
       </c>
       <c r="J80" s="22" t="n">
-        <v>11889</v>
+        <v>11882</v>
       </c>
     </row>
     <row r="81">
@@ -6292,25 +6292,25 @@
         <v>20</v>
       </c>
       <c r="D81" s="21" t="n">
-        <v>11940</v>
+        <v>12410</v>
       </c>
       <c r="E81" s="22" t="n">
-        <v>11183</v>
+        <v>14040</v>
       </c>
       <c r="F81" s="21" t="n">
-        <v>12736</v>
+        <v>12682</v>
       </c>
       <c r="G81" s="21" t="n">
-        <v>12733</v>
+        <v>11947</v>
       </c>
       <c r="H81" s="22" t="n">
-        <v>11323</v>
+        <v>11849</v>
       </c>
       <c r="I81" s="21" t="n">
-        <v>11893</v>
+        <v>11866</v>
       </c>
       <c r="J81" s="22" t="n">
-        <v>11839</v>
+        <v>11865</v>
       </c>
     </row>
     <row r="82">
@@ -6324,25 +6324,25 @@
         <v>21</v>
       </c>
       <c r="D82" s="21" t="n">
+        <v>12402</v>
+      </c>
+      <c r="E82" s="22" t="n">
+        <v>14048</v>
+      </c>
+      <c r="F82" s="21" t="n">
+        <v>12648</v>
+      </c>
+      <c r="G82" s="21" t="n">
+        <v>11947</v>
+      </c>
+      <c r="H82" s="22" t="n">
+        <v>11805</v>
+      </c>
+      <c r="I82" s="21" t="n">
         <v>11908</v>
       </c>
-      <c r="E82" s="22" t="n">
-        <v>11192</v>
-      </c>
-      <c r="F82" s="21" t="n">
-        <v>12708</v>
-      </c>
-      <c r="G82" s="21" t="n">
-        <v>12687</v>
-      </c>
-      <c r="H82" s="22" t="n">
-        <v>11197</v>
-      </c>
-      <c r="I82" s="21" t="n">
-        <v>11946</v>
-      </c>
       <c r="J82" s="22" t="n">
-        <v>11779</v>
+        <v>11838</v>
       </c>
     </row>
     <row r="83">
@@ -6356,25 +6356,25 @@
         <v>21</v>
       </c>
       <c r="D83" s="21" t="n">
-        <v>11945</v>
+        <v>12449</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>11182</v>
+        <v>14039</v>
       </c>
       <c r="F83" s="21" t="n">
-        <v>12806</v>
+        <v>12656</v>
       </c>
       <c r="G83" s="21" t="n">
-        <v>12706</v>
+        <v>11891</v>
       </c>
       <c r="H83" s="22" t="n">
-        <v>11235</v>
+        <v>11822</v>
       </c>
       <c r="I83" s="21" t="n">
-        <v>11949</v>
+        <v>12041</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>11853</v>
+        <v>12033</v>
       </c>
     </row>
     <row r="84">
@@ -6388,25 +6388,25 @@
         <v>21</v>
       </c>
       <c r="D84" s="21" t="n">
-        <v>11986</v>
+        <v>12443</v>
       </c>
       <c r="E84" s="22" t="n">
-        <v>11239</v>
+        <v>14097</v>
       </c>
       <c r="F84" s="21" t="n">
-        <v>12836</v>
+        <v>12586</v>
       </c>
       <c r="G84" s="21" t="n">
-        <v>12706</v>
+        <v>11891</v>
       </c>
       <c r="H84" s="22" t="n">
-        <v>11429</v>
+        <v>11795</v>
       </c>
       <c r="I84" s="21" t="n">
-        <v>11904</v>
+        <v>12019</v>
       </c>
       <c r="J84" s="22" t="n">
-        <v>11865</v>
+        <v>12050</v>
       </c>
     </row>
     <row r="85">
@@ -6420,25 +6420,25 @@
         <v>21</v>
       </c>
       <c r="D85" s="21" t="n">
-        <v>12033</v>
+        <v>12452</v>
       </c>
       <c r="E85" s="22" t="n">
-        <v>11288</v>
+        <v>14147</v>
       </c>
       <c r="F85" s="21" t="n">
-        <v>12877</v>
+        <v>12588</v>
       </c>
       <c r="G85" s="21" t="n">
-        <v>12716</v>
+        <v>11880</v>
       </c>
       <c r="H85" s="22" t="n">
-        <v>11621</v>
+        <v>11771</v>
       </c>
       <c r="I85" s="21" t="n">
-        <v>11958</v>
+        <v>12063</v>
       </c>
       <c r="J85" s="22" t="n">
-        <v>11799</v>
+        <v>12039</v>
       </c>
     </row>
     <row r="86">
@@ -6452,25 +6452,25 @@
         <v>22</v>
       </c>
       <c r="D86" s="21" t="n">
-        <v>12165</v>
+        <v>12492</v>
       </c>
       <c r="E86" s="22" t="n">
-        <v>11399</v>
+        <v>14258</v>
       </c>
       <c r="F86" s="21" t="n">
-        <v>12976</v>
+        <v>12534</v>
       </c>
       <c r="G86" s="21" t="n">
-        <v>12735</v>
+        <v>11779</v>
       </c>
       <c r="H86" s="22" t="n">
-        <v>12008</v>
+        <v>12055</v>
       </c>
       <c r="I86" s="21" t="n">
-        <v>12047</v>
+        <v>12070</v>
       </c>
       <c r="J86" s="22" t="n">
-        <v>11886</v>
+        <v>12030</v>
       </c>
     </row>
     <row r="87">
@@ -6484,25 +6484,25 @@
         <v>22</v>
       </c>
       <c r="D87" s="21" t="n">
-        <v>12142</v>
+        <v>12521</v>
       </c>
       <c r="E87" s="22" t="n">
-        <v>11375</v>
+        <v>14234</v>
       </c>
       <c r="F87" s="21" t="n">
-        <v>12962</v>
+        <v>12676</v>
       </c>
       <c r="G87" s="21" t="n">
-        <v>12696</v>
+        <v>11795</v>
       </c>
       <c r="H87" s="22" t="n">
-        <v>11962</v>
+        <v>12023</v>
       </c>
       <c r="I87" s="21" t="n">
-        <v>12053</v>
+        <v>12075</v>
       </c>
       <c r="J87" s="22" t="n">
-        <v>11870</v>
+        <v>12095</v>
       </c>
     </row>
     <row r="88">
@@ -6516,25 +6516,25 @@
         <v>22</v>
       </c>
       <c r="D88" s="21" t="n">
-        <v>12166</v>
+        <v>12508</v>
       </c>
       <c r="E88" s="22" t="n">
-        <v>11337</v>
+        <v>14197</v>
       </c>
       <c r="F88" s="21" t="n">
-        <v>12983</v>
+        <v>12617</v>
       </c>
       <c r="G88" s="21" t="n">
-        <v>12773</v>
+        <v>11779</v>
       </c>
       <c r="H88" s="22" t="n">
-        <v>12007</v>
+        <v>12074</v>
       </c>
       <c r="I88" s="21" t="n">
-        <v>12054</v>
+        <v>12089</v>
       </c>
       <c r="J88" s="22" t="n">
-        <v>11912</v>
+        <v>12072</v>
       </c>
     </row>
     <row r="89">
@@ -6548,25 +6548,25 @@
         <v>22</v>
       </c>
       <c r="D89" s="21" t="n">
-        <v>12160</v>
+        <v>12504</v>
       </c>
       <c r="E89" s="22" t="n">
-        <v>11305</v>
+        <v>14165</v>
       </c>
       <c r="F89" s="21" t="n">
-        <v>13038</v>
+        <v>12688</v>
       </c>
       <c r="G89" s="21" t="n">
-        <v>12791</v>
+        <v>11827</v>
       </c>
       <c r="H89" s="22" t="n">
-        <v>12031</v>
+        <v>12111</v>
       </c>
       <c r="I89" s="21" t="n">
-        <v>11979</v>
+        <v>11967</v>
       </c>
       <c r="J89" s="22" t="n">
-        <v>11886</v>
+        <v>12052</v>
       </c>
     </row>
     <row r="90">
@@ -6580,25 +6580,25 @@
         <v>23</v>
       </c>
       <c r="D90" s="21" t="n">
-        <v>12150</v>
+        <v>12549</v>
       </c>
       <c r="E90" s="22" t="n">
-        <v>11303</v>
+        <v>14163</v>
       </c>
       <c r="F90" s="21" t="n">
-        <v>13053</v>
+        <v>12765</v>
       </c>
       <c r="G90" s="21" t="n">
-        <v>12739</v>
+        <v>11873</v>
       </c>
       <c r="H90" s="22" t="n">
-        <v>12049</v>
+        <v>12175</v>
       </c>
       <c r="I90" s="21" t="n">
-        <v>11928</v>
+        <v>12018</v>
       </c>
       <c r="J90" s="22" t="n">
-        <v>11894</v>
+        <v>12088</v>
       </c>
     </row>
     <row r="91">
@@ -6612,25 +6612,25 @@
         <v>23</v>
       </c>
       <c r="D91" s="21" t="n">
-        <v>12250</v>
+        <v>12621</v>
       </c>
       <c r="E91" s="22" t="n">
-        <v>11285</v>
+        <v>14147</v>
       </c>
       <c r="F91" s="21" t="n">
-        <v>13079</v>
+        <v>12758</v>
       </c>
       <c r="G91" s="21" t="n">
-        <v>12723</v>
+        <v>11842</v>
       </c>
       <c r="H91" s="22" t="n">
-        <v>12283</v>
+        <v>12466</v>
       </c>
       <c r="I91" s="21" t="n">
-        <v>12161</v>
+        <v>12045</v>
       </c>
       <c r="J91" s="22" t="n">
-        <v>12045</v>
+        <v>12273</v>
       </c>
     </row>
     <row r="92">
@@ -6644,25 +6644,25 @@
         <v>23</v>
       </c>
       <c r="D92" s="21" t="n">
-        <v>12207</v>
+        <v>12757</v>
       </c>
       <c r="E92" s="22" t="n">
-        <v>11319</v>
+        <v>14182</v>
       </c>
       <c r="F92" s="21" t="n">
-        <v>13227</v>
+        <v>12807</v>
       </c>
       <c r="G92" s="21" t="n">
-        <v>11419</v>
+        <v>11536</v>
       </c>
       <c r="H92" s="22" t="n">
-        <v>12678</v>
+        <v>12707</v>
       </c>
       <c r="I92" s="21" t="n">
-        <v>12414</v>
+        <v>12447</v>
       </c>
       <c r="J92" s="22" t="n">
-        <v>12183</v>
+        <v>12660</v>
       </c>
     </row>
     <row r="93">
@@ -6676,25 +6676,25 @@
         <v>23</v>
       </c>
       <c r="D93" s="21" t="n">
-        <v>12283</v>
+        <v>12809</v>
       </c>
       <c r="E93" s="22" t="n">
-        <v>11282</v>
+        <v>14145</v>
       </c>
       <c r="F93" s="21" t="n">
-        <v>13124</v>
+        <v>12979</v>
       </c>
       <c r="G93" s="21" t="n">
-        <v>11951</v>
+        <v>11770</v>
       </c>
       <c r="H93" s="22" t="n">
-        <v>12675</v>
+        <v>12768</v>
       </c>
       <c r="I93" s="21" t="n">
-        <v>12456</v>
+        <v>12517</v>
       </c>
       <c r="J93" s="22" t="n">
-        <v>12247</v>
+        <v>12490</v>
       </c>
     </row>
     <row r="94">
@@ -6708,25 +6708,25 @@
         <v>24</v>
       </c>
       <c r="D94" s="21" t="n">
-        <v>12535</v>
+        <v>12852</v>
       </c>
       <c r="E94" s="22" t="n">
-        <v>11270</v>
+        <v>14133</v>
       </c>
       <c r="F94" s="21" t="n">
-        <v>13339</v>
+        <v>13103</v>
       </c>
       <c r="G94" s="21" t="n">
-        <v>12798</v>
+        <v>11871</v>
       </c>
       <c r="H94" s="22" t="n">
-        <v>12581</v>
+        <v>12635</v>
       </c>
       <c r="I94" s="21" t="n">
-        <v>12745</v>
+        <v>12553</v>
       </c>
       <c r="J94" s="22" t="n">
-        <v>12565</v>
+        <v>12628</v>
       </c>
     </row>
     <row r="95">
@@ -6740,25 +6740,25 @@
         <v>24</v>
       </c>
       <c r="D95" s="21" t="n">
-        <v>12435</v>
+        <v>12840</v>
       </c>
       <c r="E95" s="22" t="n">
-        <v>11192</v>
+        <v>14055</v>
       </c>
       <c r="F95" s="21" t="n">
-        <v>13194</v>
+        <v>13199</v>
       </c>
       <c r="G95" s="21" t="n">
-        <v>12811</v>
+        <v>11902</v>
       </c>
       <c r="H95" s="22" t="n">
-        <v>12430</v>
+        <v>12526</v>
       </c>
       <c r="I95" s="21" t="n">
-        <v>12610</v>
+        <v>12559</v>
       </c>
       <c r="J95" s="22" t="n">
-        <v>12466</v>
+        <v>12607</v>
       </c>
     </row>
     <row r="96">
@@ -6772,25 +6772,25 @@
         <v>24</v>
       </c>
       <c r="D96" s="21" t="n">
-        <v>12299</v>
+        <v>12786</v>
       </c>
       <c r="E96" s="22" t="n">
-        <v>11018</v>
+        <v>13880</v>
       </c>
       <c r="F96" s="21" t="n">
-        <v>13245</v>
+        <v>13066</v>
       </c>
       <c r="G96" s="21" t="n">
-        <v>12807</v>
+        <v>11916</v>
       </c>
       <c r="H96" s="22" t="n">
-        <v>11791</v>
+        <v>12345</v>
       </c>
       <c r="I96" s="21" t="n">
-        <v>12565</v>
+        <v>12644</v>
       </c>
       <c r="J96" s="22" t="n">
-        <v>12458</v>
+        <v>12691</v>
       </c>
     </row>
     <row r="97">
@@ -6806,25 +6806,25 @@
         <v>24</v>
       </c>
       <c r="D97" s="21" t="n">
-        <v>12004</v>
+        <v>12619</v>
       </c>
       <c r="E97" s="22" t="n">
-        <v>10873</v>
+        <v>13735</v>
       </c>
       <c r="F97" s="21" t="n">
-        <v>12848</v>
+        <v>12913</v>
       </c>
       <c r="G97" s="21" t="n">
-        <v>12544</v>
+        <v>11845</v>
       </c>
       <c r="H97" s="22" t="n">
-        <v>11423</v>
+        <v>12268</v>
       </c>
       <c r="I97" s="21" t="n">
-        <v>12304</v>
+        <v>12465</v>
       </c>
       <c r="J97" s="22" t="n">
-        <v>12115</v>
+        <v>12316</v>
       </c>
     </row>
   </sheetData>
@@ -6979,29 +6979,35 @@
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="13" t="n"/>
+      <c r="D2" s="13" t="n">
+        <v>385</v>
+      </c>
+      <c r="E2" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F2" s="13" t="n">
+        <v>385.1</v>
+      </c>
       <c r="G2" s="23" t="n">
-        <v>398.17</v>
+        <v>314.2</v>
       </c>
       <c r="H2" s="24" t="n">
-        <v>424.99</v>
+        <v>268.33</v>
       </c>
       <c r="I2" s="23" t="n">
-        <v>378.03</v>
+        <v>323.41</v>
       </c>
       <c r="J2" s="23" t="n">
-        <v>430.9</v>
+        <v>351.25</v>
       </c>
       <c r="K2" s="24" t="n">
-        <v>387.42</v>
+        <v>286.22</v>
       </c>
       <c r="L2" s="23" t="n">
-        <v>395.56</v>
+        <v>321.11</v>
       </c>
       <c r="M2" s="24" t="n">
-        <v>375.69</v>
+        <v>328.52</v>
       </c>
     </row>
     <row r="3">
@@ -7014,29 +7020,35 @@
       <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="13" t="n"/>
+      <c r="D3" s="13" t="n">
+        <v>385</v>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F3" s="13" t="n">
+        <v>385.1</v>
+      </c>
       <c r="G3" s="23" t="n">
-        <v>397.68</v>
+        <v>310</v>
       </c>
       <c r="H3" s="24" t="n">
-        <v>422.17</v>
+        <v>265.56</v>
       </c>
       <c r="I3" s="23" t="n">
-        <v>376.1</v>
+        <v>321.48</v>
       </c>
       <c r="J3" s="23" t="n">
-        <v>429.3</v>
+        <v>342.8</v>
       </c>
       <c r="K3" s="24" t="n">
-        <v>387.67</v>
+        <v>286.24</v>
       </c>
       <c r="L3" s="23" t="n">
-        <v>395.73</v>
+        <v>312.9</v>
       </c>
       <c r="M3" s="24" t="n">
-        <v>378.47</v>
+        <v>324.74</v>
       </c>
     </row>
     <row r="4">
@@ -7049,29 +7061,35 @@
       <c r="C4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="13" t="n"/>
+      <c r="D4" s="13" t="n">
+        <v>385</v>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F4" s="13" t="n">
+        <v>385.1</v>
+      </c>
       <c r="G4" s="23" t="n">
-        <v>392.36</v>
+        <v>305.81</v>
       </c>
       <c r="H4" s="24" t="n">
-        <v>417.76</v>
+        <v>261.08</v>
       </c>
       <c r="I4" s="23" t="n">
-        <v>373.02</v>
+        <v>327.27</v>
       </c>
       <c r="J4" s="23" t="n">
-        <v>434.37</v>
+        <v>347.75</v>
       </c>
       <c r="K4" s="24" t="n">
-        <v>380.04</v>
+        <v>276.84</v>
       </c>
       <c r="L4" s="23" t="n">
-        <v>381.25</v>
+        <v>300.14</v>
       </c>
       <c r="M4" s="24" t="n">
-        <v>370.77</v>
+        <v>314.73</v>
       </c>
     </row>
     <row r="5">
@@ -7084,29 +7102,35 @@
       <c r="C5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
+      <c r="D5" s="13" t="n">
+        <v>385</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>385.1</v>
+      </c>
       <c r="G5" s="23" t="n">
-        <v>387.37</v>
+        <v>297.45</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>410.75</v>
+        <v>253.98</v>
       </c>
       <c r="I5" s="23" t="n">
-        <v>368.3</v>
+        <v>325.84</v>
       </c>
       <c r="J5" s="23" t="n">
-        <v>437.13</v>
+        <v>351.54</v>
       </c>
       <c r="K5" s="24" t="n">
-        <v>377.67</v>
+        <v>263.5</v>
       </c>
       <c r="L5" s="23" t="n">
-        <v>367.11</v>
+        <v>280.8</v>
       </c>
       <c r="M5" s="24" t="n">
-        <v>365.76</v>
+        <v>301.44</v>
       </c>
     </row>
     <row r="6">
@@ -7119,29 +7143,35 @@
       <c r="C6" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
+      <c r="D6" s="13" t="n">
+        <v>385</v>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>390</v>
+      </c>
       <c r="G6" s="23" t="n">
-        <v>376.22</v>
+        <v>287.95</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>406.81</v>
+        <v>250.02</v>
       </c>
       <c r="I6" s="23" t="n">
-        <v>347.6</v>
+        <v>307.3</v>
       </c>
       <c r="J6" s="23" t="n">
-        <v>434.58</v>
+        <v>340.73</v>
       </c>
       <c r="K6" s="24" t="n">
-        <v>375.38</v>
+        <v>258.51</v>
       </c>
       <c r="L6" s="23" t="n">
-        <v>344.59</v>
+        <v>266.64</v>
       </c>
       <c r="M6" s="24" t="n">
-        <v>351.92</v>
+        <v>298.07</v>
       </c>
     </row>
     <row r="7">
@@ -7154,29 +7184,35 @@
       <c r="C7" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="13" t="n"/>
-      <c r="E7" s="13" t="n"/>
-      <c r="F7" s="13" t="n"/>
+      <c r="D7" s="13" t="n">
+        <v>385</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>390</v>
+      </c>
       <c r="G7" s="23" t="n">
-        <v>387.5</v>
+        <v>308.66</v>
       </c>
       <c r="H7" s="24" t="n">
-        <v>405.92</v>
+        <v>249.22</v>
       </c>
       <c r="I7" s="23" t="n">
-        <v>351.15</v>
+        <v>300.29</v>
       </c>
       <c r="J7" s="23" t="n">
-        <v>433.27</v>
+        <v>418.49</v>
       </c>
       <c r="K7" s="24" t="n">
-        <v>378.54</v>
+        <v>263.5</v>
       </c>
       <c r="L7" s="23" t="n">
-        <v>377.91</v>
+        <v>303.43</v>
       </c>
       <c r="M7" s="24" t="n">
-        <v>380.99</v>
+        <v>307.86</v>
       </c>
     </row>
     <row r="8">
@@ -7189,29 +7225,35 @@
       <c r="C8" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
+      <c r="D8" s="13" t="n">
+        <v>385</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>390</v>
+      </c>
       <c r="G8" s="23" t="n">
-        <v>376.6</v>
+        <v>282.87</v>
       </c>
       <c r="H8" s="24" t="n">
-        <v>394.24</v>
+        <v>237.96</v>
       </c>
       <c r="I8" s="23" t="n">
-        <v>345.35</v>
+        <v>310.8</v>
       </c>
       <c r="J8" s="23" t="n">
-        <v>414.38</v>
+        <v>330.28</v>
       </c>
       <c r="K8" s="24" t="n">
-        <v>372.59</v>
+        <v>253.37</v>
       </c>
       <c r="L8" s="23" t="n">
-        <v>364.95</v>
+        <v>275.01</v>
       </c>
       <c r="M8" s="24" t="n">
-        <v>370.76</v>
+        <v>282.13</v>
       </c>
     </row>
     <row r="9">
@@ -7224,29 +7266,35 @@
       <c r="C9" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="13" t="n"/>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="13" t="n"/>
+      <c r="D9" s="13" t="n">
+        <v>385</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>390</v>
+      </c>
       <c r="G9" s="23" t="n">
-        <v>366.91</v>
+        <v>266.28</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>386.18</v>
+        <v>230.16</v>
       </c>
       <c r="I9" s="23" t="n">
-        <v>342.81</v>
+        <v>307.47</v>
       </c>
       <c r="J9" s="23" t="n">
-        <v>402.96</v>
+        <v>272.43</v>
       </c>
       <c r="K9" s="24" t="n">
-        <v>371.03</v>
+        <v>247.12</v>
       </c>
       <c r="L9" s="23" t="n">
-        <v>348.88</v>
+        <v>266.23</v>
       </c>
       <c r="M9" s="24" t="n">
-        <v>352.14</v>
+        <v>268.02</v>
       </c>
     </row>
     <row r="10">
@@ -7259,29 +7307,35 @@
       <c r="C10" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
+      <c r="D10" s="13" t="n">
+        <v>390</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>385</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>395</v>
+      </c>
       <c r="G10" s="23" t="n">
-        <v>393.13</v>
+        <v>309.54</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>435.13</v>
+        <v>279.96</v>
       </c>
       <c r="I10" s="23" t="n">
-        <v>378.17</v>
+        <v>328.57</v>
       </c>
       <c r="J10" s="23" t="n">
-        <v>421.02</v>
+        <v>337.35</v>
       </c>
       <c r="K10" s="24" t="n">
-        <v>376.37</v>
+        <v>278.54</v>
       </c>
       <c r="L10" s="23" t="n">
-        <v>387.01</v>
+        <v>311.32</v>
       </c>
       <c r="M10" s="24" t="n">
-        <v>366.49</v>
+        <v>316.88</v>
       </c>
     </row>
     <row r="11">
@@ -7294,29 +7348,35 @@
       <c r="C11" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
+      <c r="D11" s="13" t="n">
+        <v>390</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>385</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>395</v>
+      </c>
       <c r="G11" s="23" t="n">
-        <v>401.21</v>
+        <v>314.98</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>419.46</v>
+        <v>263.7</v>
       </c>
       <c r="I11" s="23" t="n">
-        <v>388.67</v>
+        <v>335.75</v>
       </c>
       <c r="J11" s="23" t="n">
-        <v>419.71</v>
+        <v>357.34</v>
       </c>
       <c r="K11" s="24" t="n">
-        <v>385.51</v>
+        <v>276.13</v>
       </c>
       <c r="L11" s="23" t="n">
-        <v>406.51</v>
+        <v>321.02</v>
       </c>
       <c r="M11" s="24" t="n">
-        <v>389.92</v>
+        <v>328.43</v>
       </c>
     </row>
     <row r="12">
@@ -7329,29 +7389,35 @@
       <c r="C12" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
+      <c r="D12" s="13" t="n">
+        <v>390</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>385</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>395</v>
+      </c>
       <c r="G12" s="23" t="n">
-        <v>395.02</v>
+        <v>314.84</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>419.43</v>
+        <v>263.74</v>
       </c>
       <c r="I12" s="23" t="n">
-        <v>378.94</v>
+        <v>330.82</v>
       </c>
       <c r="J12" s="23" t="n">
-        <v>421.42</v>
+        <v>374.29</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>382.88</v>
+        <v>273.82</v>
       </c>
       <c r="L12" s="23" t="n">
-        <v>388.72</v>
+        <v>309.79</v>
       </c>
       <c r="M12" s="24" t="n">
-        <v>381.95</v>
+        <v>328.87</v>
       </c>
     </row>
     <row r="13">
@@ -7364,29 +7430,35 @@
       <c r="C13" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="13" t="n"/>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="13" t="n"/>
+      <c r="D13" s="13" t="n">
+        <v>390</v>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>385</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>395</v>
+      </c>
       <c r="G13" s="23" t="n">
-        <v>391.17</v>
+        <v>304.01</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>414.16</v>
+        <v>258.62</v>
       </c>
       <c r="I13" s="23" t="n">
-        <v>373.94</v>
+        <v>319.72</v>
       </c>
       <c r="J13" s="23" t="n">
-        <v>413.9</v>
+        <v>326.73</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>378.03</v>
+        <v>272.4</v>
       </c>
       <c r="L13" s="23" t="n">
-        <v>397.01</v>
+        <v>316.7</v>
       </c>
       <c r="M13" s="24" t="n">
-        <v>373.24</v>
+        <v>323.89</v>
       </c>
     </row>
     <row r="14">
@@ -7399,29 +7471,35 @@
       <c r="C14" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D14" s="13" t="n"/>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="13" t="n"/>
+      <c r="D14" s="13" t="n">
+        <v>384.82</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>381</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>385</v>
+      </c>
       <c r="G14" s="23" t="n">
-        <v>386.08</v>
+        <v>296.48</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>414.87</v>
+        <v>259.24</v>
       </c>
       <c r="I14" s="23" t="n">
-        <v>376.76</v>
+        <v>319.38</v>
       </c>
       <c r="J14" s="23" t="n">
-        <v>413.95</v>
+        <v>310.32</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>373.41</v>
+        <v>266.93</v>
       </c>
       <c r="L14" s="23" t="n">
-        <v>379.78</v>
+        <v>305.95</v>
       </c>
       <c r="M14" s="24" t="n">
-        <v>361.14</v>
+        <v>311.83</v>
       </c>
     </row>
     <row r="15">
@@ -7434,29 +7512,35 @@
       <c r="C15" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D15" s="13" t="n"/>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="13" t="n"/>
+      <c r="D15" s="13" t="n">
+        <v>384.82</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>381</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>385</v>
+      </c>
       <c r="G15" s="23" t="n">
-        <v>388.34</v>
+        <v>294.3</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>415.94</v>
+        <v>260.03</v>
       </c>
       <c r="I15" s="23" t="n">
-        <v>377.54</v>
+        <v>317.93</v>
       </c>
       <c r="J15" s="23" t="n">
-        <v>413.95</v>
+        <v>295.5</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>382.66</v>
+        <v>279.14</v>
       </c>
       <c r="L15" s="23" t="n">
-        <v>376.07</v>
+        <v>285.55</v>
       </c>
       <c r="M15" s="24" t="n">
-        <v>367.25</v>
+        <v>323.02</v>
       </c>
     </row>
     <row r="16">
@@ -7469,29 +7553,35 @@
       <c r="C16" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
+      <c r="D16" s="13" t="n">
+        <v>384.82</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>381</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>385</v>
+      </c>
       <c r="G16" s="23" t="n">
-        <v>391.46</v>
+        <v>294.44</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>409.89</v>
+        <v>253.67</v>
       </c>
       <c r="I16" s="23" t="n">
-        <v>369.7</v>
+        <v>322.84</v>
       </c>
       <c r="J16" s="23" t="n">
-        <v>414.73</v>
+        <v>300.36</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>385.3</v>
+        <v>279.68</v>
       </c>
       <c r="L16" s="23" t="n">
-        <v>391.54</v>
+        <v>290.25</v>
       </c>
       <c r="M16" s="24" t="n">
-        <v>380.39</v>
+        <v>313.86</v>
       </c>
     </row>
     <row r="17">
@@ -7504,29 +7594,35 @@
       <c r="C17" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
+      <c r="D17" s="13" t="n">
+        <v>384.82</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>381</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>385</v>
+      </c>
       <c r="G17" s="23" t="n">
-        <v>388.11</v>
+        <v>284.12</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>405.16</v>
+        <v>248.9</v>
       </c>
       <c r="I17" s="23" t="n">
-        <v>363.38</v>
+        <v>315.35</v>
       </c>
       <c r="J17" s="23" t="n">
-        <v>416.54</v>
+        <v>301.17</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>384.78</v>
+        <v>271.86</v>
       </c>
       <c r="L17" s="23" t="n">
-        <v>375.98</v>
+        <v>276.02</v>
       </c>
       <c r="M17" s="24" t="n">
-        <v>385.34</v>
+        <v>285.3</v>
       </c>
     </row>
     <row r="18">
@@ -7539,29 +7635,35 @@
       <c r="C18" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
+      <c r="D18" s="13" t="n">
+        <v>385</v>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>600</v>
+      </c>
       <c r="G18" s="23" t="n">
-        <v>390.98</v>
+        <v>276.7</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>399.03</v>
+        <v>242.62</v>
       </c>
       <c r="I18" s="23" t="n">
-        <v>358.96</v>
+        <v>313.36</v>
       </c>
       <c r="J18" s="23" t="n">
-        <v>427.63</v>
+        <v>250.08</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>378.37</v>
+        <v>271.29</v>
       </c>
       <c r="L18" s="23" t="n">
-        <v>393.84</v>
+        <v>276.46</v>
       </c>
       <c r="M18" s="24" t="n">
-        <v>389.69</v>
+        <v>301.68</v>
       </c>
     </row>
     <row r="19">
@@ -7574,29 +7676,35 @@
       <c r="C19" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
+      <c r="D19" s="13" t="n">
+        <v>385</v>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>600</v>
+      </c>
       <c r="G19" s="23" t="n">
-        <v>382.41</v>
+        <v>266.31</v>
       </c>
       <c r="H19" s="24" t="n">
-        <v>396.53</v>
+        <v>240.36</v>
       </c>
       <c r="I19" s="23" t="n">
-        <v>356.76</v>
+        <v>300.83</v>
       </c>
       <c r="J19" s="23" t="n">
-        <v>426.03</v>
+        <v>243.56</v>
       </c>
       <c r="K19" s="24" t="n">
-        <v>374.74</v>
+        <v>264.34</v>
       </c>
       <c r="L19" s="23" t="n">
-        <v>365.97</v>
+        <v>261.62</v>
       </c>
       <c r="M19" s="24" t="n">
-        <v>376.24</v>
+        <v>283.2</v>
       </c>
     </row>
     <row r="20">
@@ -7609,29 +7717,35 @@
       <c r="C20" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
+      <c r="D20" s="13" t="n">
+        <v>385</v>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>600</v>
+      </c>
       <c r="G20" s="23" t="n">
-        <v>380.97</v>
+        <v>263.64</v>
       </c>
       <c r="H20" s="24" t="n">
-        <v>395.42</v>
+        <v>239.26</v>
       </c>
       <c r="I20" s="23" t="n">
-        <v>361.13</v>
+        <v>303.29</v>
       </c>
       <c r="J20" s="23" t="n">
-        <v>421.28</v>
+        <v>241.14</v>
       </c>
       <c r="K20" s="24" t="n">
-        <v>374.44</v>
+        <v>264.14</v>
       </c>
       <c r="L20" s="23" t="n">
-        <v>363.47</v>
+        <v>246.52</v>
       </c>
       <c r="M20" s="24" t="n">
-        <v>371.71</v>
+        <v>283.47</v>
       </c>
     </row>
     <row r="21">
@@ -7644,29 +7758,35 @@
       <c r="C21" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
+      <c r="D21" s="13" t="n">
+        <v>385</v>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>600</v>
+      </c>
       <c r="G21" s="23" t="n">
-        <v>381.2</v>
+        <v>259.51</v>
       </c>
       <c r="H21" s="24" t="n">
-        <v>393.93</v>
+        <v>237.82</v>
       </c>
       <c r="I21" s="23" t="n">
-        <v>358.8</v>
+        <v>288.08</v>
       </c>
       <c r="J21" s="23" t="n">
-        <v>420.16</v>
+        <v>240.74</v>
       </c>
       <c r="K21" s="24" t="n">
-        <v>375.57</v>
+        <v>263.22</v>
       </c>
       <c r="L21" s="23" t="n">
-        <v>368.68</v>
+        <v>245.27</v>
       </c>
       <c r="M21" s="24" t="n">
-        <v>371.66</v>
+        <v>278.62</v>
       </c>
     </row>
     <row r="22">
@@ -7679,29 +7799,35 @@
       <c r="C22" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
+      <c r="D22" s="13" t="n">
+        <v>385</v>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>600</v>
+      </c>
       <c r="G22" s="23" t="n">
-        <v>386.28</v>
+        <v>260.08</v>
       </c>
       <c r="H22" s="24" t="n">
-        <v>392.51</v>
+        <v>236.42</v>
       </c>
       <c r="I22" s="23" t="n">
-        <v>363.51</v>
+        <v>279.55</v>
       </c>
       <c r="J22" s="23" t="n">
-        <v>424.87</v>
+        <v>233.66</v>
       </c>
       <c r="K22" s="24" t="n">
-        <v>373.54</v>
+        <v>261.95</v>
       </c>
       <c r="L22" s="23" t="n">
-        <v>381.84</v>
+        <v>257.55</v>
       </c>
       <c r="M22" s="24" t="n">
-        <v>382.23</v>
+        <v>288.68</v>
       </c>
     </row>
     <row r="23">
@@ -7714,29 +7840,35 @@
       <c r="C23" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
+      <c r="D23" s="13" t="n">
+        <v>385</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>600</v>
+      </c>
       <c r="G23" s="23" t="n">
-        <v>385.23</v>
+        <v>255.57</v>
       </c>
       <c r="H23" s="24" t="n">
-        <v>391.85</v>
+        <v>235.88</v>
       </c>
       <c r="I23" s="23" t="n">
-        <v>364.78</v>
+        <v>279.12</v>
       </c>
       <c r="J23" s="23" t="n">
-        <v>420</v>
+        <v>216.65</v>
       </c>
       <c r="K23" s="24" t="n">
-        <v>372.5</v>
+        <v>260.44</v>
       </c>
       <c r="L23" s="23" t="n">
-        <v>381.69</v>
+        <v>257.43</v>
       </c>
       <c r="M23" s="24" t="n">
-        <v>381.49</v>
+        <v>281.78</v>
       </c>
     </row>
     <row r="24">
@@ -7749,29 +7881,35 @@
       <c r="C24" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
+      <c r="D24" s="13" t="n">
+        <v>385</v>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>600</v>
+      </c>
       <c r="G24" s="23" t="n">
-        <v>379.08</v>
+        <v>240.61</v>
       </c>
       <c r="H24" s="24" t="n">
-        <v>392.56</v>
+        <v>236.6</v>
       </c>
       <c r="I24" s="23" t="n">
-        <v>362.46</v>
+        <v>277.33</v>
       </c>
       <c r="J24" s="23" t="n">
-        <v>419.94</v>
+        <v>208.64</v>
       </c>
       <c r="K24" s="24" t="n">
-        <v>370.51</v>
+        <v>254.84</v>
       </c>
       <c r="L24" s="23" t="n">
-        <v>365.49</v>
+        <v>218.1</v>
       </c>
       <c r="M24" s="24" t="n">
-        <v>364.9</v>
+        <v>246.51</v>
       </c>
     </row>
     <row r="25">
@@ -7784,29 +7922,35 @@
       <c r="C25" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D25" s="13" t="n"/>
-      <c r="E25" s="13" t="n"/>
-      <c r="F25" s="13" t="n"/>
+      <c r="D25" s="13" t="n">
+        <v>385</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>600</v>
+      </c>
       <c r="G25" s="23" t="n">
-        <v>372.45</v>
+        <v>236.22</v>
       </c>
       <c r="H25" s="24" t="n">
-        <v>392.85</v>
+        <v>236.9</v>
       </c>
       <c r="I25" s="23" t="n">
-        <v>362.3</v>
+        <v>275.55</v>
       </c>
       <c r="J25" s="23" t="n">
-        <v>418.77</v>
+        <v>208.64</v>
       </c>
       <c r="K25" s="24" t="n">
-        <v>366.01</v>
+        <v>254.94</v>
       </c>
       <c r="L25" s="23" t="n">
-        <v>350.48</v>
+        <v>201.47</v>
       </c>
       <c r="M25" s="24" t="n">
-        <v>346.1</v>
+        <v>238.31</v>
       </c>
     </row>
     <row r="26">
@@ -7819,29 +7963,35 @@
       <c r="C26" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="13" t="n"/>
+      <c r="D26" s="13" t="n">
+        <v>384.26</v>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>385</v>
+      </c>
       <c r="G26" s="23" t="n">
-        <v>369.03</v>
+        <v>227.73</v>
       </c>
       <c r="H26" s="24" t="n">
-        <v>402.32</v>
+        <v>245.99</v>
       </c>
       <c r="I26" s="23" t="n">
-        <v>351.51</v>
+        <v>254.19</v>
       </c>
       <c r="J26" s="23" t="n">
-        <v>418.22</v>
+        <v>213.05</v>
       </c>
       <c r="K26" s="24" t="n">
-        <v>355.62</v>
+        <v>241.56</v>
       </c>
       <c r="L26" s="23" t="n">
-        <v>358.85</v>
+        <v>195.76</v>
       </c>
       <c r="M26" s="24" t="n">
-        <v>331.52</v>
+        <v>216.67</v>
       </c>
     </row>
     <row r="27">
@@ -7854,29 +8004,35 @@
       <c r="C27" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="D27" s="13" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="13" t="n"/>
+      <c r="D27" s="13" t="n">
+        <v>384.26</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>385</v>
+      </c>
       <c r="G27" s="23" t="n">
-        <v>354.53</v>
+        <v>213.48</v>
       </c>
       <c r="H27" s="24" t="n">
-        <v>409.23</v>
+        <v>253.21</v>
       </c>
       <c r="I27" s="23" t="n">
-        <v>345.91</v>
+        <v>246.85</v>
       </c>
       <c r="J27" s="23" t="n">
-        <v>408.67</v>
+        <v>204.09</v>
       </c>
       <c r="K27" s="24" t="n">
-        <v>341.98</v>
+        <v>242.84</v>
       </c>
       <c r="L27" s="23" t="n">
-        <v>313.1</v>
+        <v>151.99</v>
       </c>
       <c r="M27" s="24" t="n">
-        <v>314.16</v>
+        <v>184.19</v>
       </c>
     </row>
     <row r="28">
@@ -7889,29 +8045,35 @@
       <c r="C28" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="D28" s="13" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="13" t="n"/>
+      <c r="D28" s="13" t="n">
+        <v>384.26</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>385</v>
+      </c>
       <c r="G28" s="23" t="n">
-        <v>337.93</v>
+        <v>194.8</v>
       </c>
       <c r="H28" s="24" t="n">
-        <v>401.77</v>
+        <v>245.77</v>
       </c>
       <c r="I28" s="23" t="n">
-        <v>328.77</v>
+        <v>235.79</v>
       </c>
       <c r="J28" s="23" t="n">
-        <v>416.13</v>
+        <v>185.05</v>
       </c>
       <c r="K28" s="24" t="n">
-        <v>316.56</v>
+        <v>215.13</v>
       </c>
       <c r="L28" s="23" t="n">
-        <v>317.46</v>
+        <v>151.31</v>
       </c>
       <c r="M28" s="24" t="n">
-        <v>253.52</v>
+        <v>138.86</v>
       </c>
     </row>
     <row r="29">
@@ -7924,29 +8086,35 @@
       <c r="C29" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="D29" s="13" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
+      <c r="D29" s="13" t="n">
+        <v>384.26</v>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>385</v>
+      </c>
       <c r="G29" s="23" t="n">
-        <v>319.1</v>
+        <v>177.07</v>
       </c>
       <c r="H29" s="24" t="n">
-        <v>394.72</v>
+        <v>239.73</v>
       </c>
       <c r="I29" s="23" t="n">
-        <v>292.85</v>
+        <v>209.51</v>
       </c>
       <c r="J29" s="23" t="n">
-        <v>399.9</v>
+        <v>181.38</v>
       </c>
       <c r="K29" s="24" t="n">
-        <v>322.44</v>
+        <v>216.79</v>
       </c>
       <c r="L29" s="23" t="n">
-        <v>270.57</v>
+        <v>104.73</v>
       </c>
       <c r="M29" s="24" t="n">
-        <v>242.75</v>
+        <v>114.24</v>
       </c>
     </row>
     <row r="30">
@@ -7959,29 +8127,35 @@
       <c r="C30" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
+      <c r="D30" s="13" t="n">
+        <v>370</v>
+      </c>
+      <c r="E30" s="13" t="n">
+        <v>354.36</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>370</v>
+      </c>
       <c r="G30" s="23" t="n">
-        <v>333.25</v>
+        <v>195.35</v>
       </c>
       <c r="H30" s="24" t="n">
-        <v>373.64</v>
+        <v>219.16</v>
       </c>
       <c r="I30" s="23" t="n">
-        <v>289.76</v>
+        <v>234.98</v>
       </c>
       <c r="J30" s="23" t="n">
-        <v>398</v>
+        <v>188.78</v>
       </c>
       <c r="K30" s="24" t="n">
-        <v>323.06</v>
+        <v>228.64</v>
       </c>
       <c r="L30" s="23" t="n">
-        <v>329.54</v>
+        <v>139.07</v>
       </c>
       <c r="M30" s="24" t="n">
-        <v>291.02</v>
+        <v>161.26</v>
       </c>
     </row>
     <row r="31">
@@ -7994,29 +8168,35 @@
       <c r="C31" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="D31" s="13" t="n"/>
-      <c r="E31" s="13" t="n"/>
-      <c r="F31" s="13" t="n"/>
+      <c r="D31" s="13" t="n">
+        <v>370</v>
+      </c>
+      <c r="E31" s="13" t="n">
+        <v>354.36</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>370</v>
+      </c>
       <c r="G31" s="23" t="n">
-        <v>285.69</v>
+        <v>123.95</v>
       </c>
       <c r="H31" s="24" t="n">
-        <v>338.46</v>
+        <v>185.07</v>
       </c>
       <c r="I31" s="23" t="n">
-        <v>267.79</v>
+        <v>210.28</v>
       </c>
       <c r="J31" s="23" t="n">
-        <v>296.5</v>
+        <v>77.87</v>
       </c>
       <c r="K31" s="24" t="n">
-        <v>278.54</v>
+        <v>175.42</v>
       </c>
       <c r="L31" s="23" t="n">
-        <v>308.72</v>
+        <v>58.23</v>
       </c>
       <c r="M31" s="24" t="n">
-        <v>231.72</v>
+        <v>38.78</v>
       </c>
     </row>
     <row r="32">
@@ -8029,29 +8209,35 @@
       <c r="C32" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="D32" s="13" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
+      <c r="D32" s="13" t="n">
+        <v>370</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <v>354.36</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>370</v>
+      </c>
       <c r="G32" s="23" t="n">
-        <v>203.33</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="H32" s="24" t="n">
-        <v>297.83</v>
+        <v>145.58</v>
       </c>
       <c r="I32" s="23" t="n">
-        <v>174.53</v>
+        <v>170.84</v>
       </c>
       <c r="J32" s="23" t="n">
-        <v>241.69</v>
+        <v>62.57</v>
       </c>
       <c r="K32" s="24" t="n">
-        <v>188.88</v>
+        <v>142.57</v>
       </c>
       <c r="L32" s="23" t="n">
-        <v>176.88</v>
+        <v>63.1</v>
       </c>
       <c r="M32" s="24" t="n">
-        <v>152.6</v>
+        <v>8.539999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -8064,29 +8250,35 @@
       <c r="C33" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="D33" s="13" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
+      <c r="D33" s="13" t="n">
+        <v>370</v>
+      </c>
+      <c r="E33" s="13" t="n">
+        <v>354.36</v>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>370</v>
+      </c>
       <c r="G33" s="23" t="n">
-        <v>93.33</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="H33" s="24" t="n">
-        <v>252.16</v>
+        <v>101.11</v>
       </c>
       <c r="I33" s="23" t="n">
-        <v>106.02</v>
+        <v>102.61</v>
       </c>
       <c r="J33" s="23" t="n">
-        <v>88.29000000000001</v>
+        <v>142.46</v>
       </c>
       <c r="K33" s="24" t="n">
-        <v>82.97</v>
+        <v>87.78</v>
       </c>
       <c r="L33" s="23" t="n">
-        <v>5.63</v>
+        <v>31.69</v>
       </c>
       <c r="M33" s="24" t="n">
-        <v>44.48</v>
+        <v>19.59</v>
       </c>
     </row>
     <row r="34">
@@ -8099,29 +8291,35 @@
       <c r="C34" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
+      <c r="D34" s="13" t="n">
+        <v>195</v>
+      </c>
+      <c r="E34" s="13" t="n">
+        <v>190</v>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>197</v>
+      </c>
       <c r="G34" s="23" t="n">
-        <v>59.63</v>
+        <v>46.2</v>
       </c>
       <c r="H34" s="24" t="n">
-        <v>212.8</v>
+        <v>63.22</v>
       </c>
       <c r="I34" s="23" t="n">
-        <v>30.38</v>
+        <v>56.66</v>
       </c>
       <c r="J34" s="23" t="n">
-        <v>62.26</v>
+        <v>36.83</v>
       </c>
       <c r="K34" s="24" t="n">
-        <v>38.03</v>
+        <v>51.12</v>
       </c>
       <c r="L34" s="23" t="n">
-        <v>23.49</v>
+        <v>37</v>
       </c>
       <c r="M34" s="24" t="n">
-        <v>11.75</v>
+        <v>33.89</v>
       </c>
     </row>
     <row r="35">
@@ -8134,29 +8332,35 @@
       <c r="C35" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="D35" s="13" t="n"/>
-      <c r="E35" s="13" t="n"/>
-      <c r="F35" s="13" t="n"/>
+      <c r="D35" s="13" t="n">
+        <v>195</v>
+      </c>
+      <c r="E35" s="13" t="n">
+        <v>190</v>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>197</v>
+      </c>
       <c r="G35" s="23" t="n">
-        <v>46.15</v>
+        <v>25.7</v>
       </c>
       <c r="H35" s="24" t="n">
-        <v>177.06</v>
+        <v>27.98</v>
       </c>
       <c r="I35" s="23" t="n">
-        <v>35.89</v>
+        <v>28.21</v>
       </c>
       <c r="J35" s="23" t="n">
-        <v>40.9</v>
+        <v>31.62</v>
       </c>
       <c r="K35" s="24" t="n">
-        <v>-3.68</v>
+        <v>18.91</v>
       </c>
       <c r="L35" s="23" t="n">
-        <v>28.63</v>
+        <v>32.54</v>
       </c>
       <c r="M35" s="24" t="n">
-        <v>15.72</v>
+        <v>14.87</v>
       </c>
     </row>
     <row r="36">
@@ -8169,29 +8373,35 @@
       <c r="C36" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="D36" s="13" t="n"/>
-      <c r="E36" s="13" t="n"/>
-      <c r="F36" s="13" t="n"/>
+      <c r="D36" s="13" t="n">
+        <v>195</v>
+      </c>
+      <c r="E36" s="13" t="n">
+        <v>190</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>197</v>
+      </c>
       <c r="G36" s="23" t="n">
-        <v>23.04</v>
+        <v>7.7</v>
       </c>
       <c r="H36" s="24" t="n">
-        <v>141.14</v>
+        <v>-7.95</v>
       </c>
       <c r="I36" s="23" t="n">
-        <v>19.22</v>
+        <v>24.25</v>
       </c>
       <c r="J36" s="23" t="n">
-        <v>9.630000000000001</v>
+        <v>16.83</v>
       </c>
       <c r="K36" s="24" t="n">
-        <v>-6.93</v>
+        <v>21.33</v>
       </c>
       <c r="L36" s="23" t="n">
-        <v>-2.21</v>
+        <v>-4.55</v>
       </c>
       <c r="M36" s="24" t="n">
-        <v>-6.85</v>
+        <v>-7.28</v>
       </c>
     </row>
     <row r="37">
@@ -8204,29 +8414,35 @@
       <c r="C37" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="D37" s="13" t="n"/>
-      <c r="E37" s="13" t="n"/>
-      <c r="F37" s="13" t="n"/>
+      <c r="D37" s="13" t="n">
+        <v>195</v>
+      </c>
+      <c r="E37" s="13" t="n">
+        <v>190</v>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>197</v>
+      </c>
       <c r="G37" s="23" t="n">
-        <v>10.13</v>
+        <v>-2.15</v>
       </c>
       <c r="H37" s="24" t="n">
-        <v>108.95</v>
+        <v>-39.53</v>
       </c>
       <c r="I37" s="23" t="n">
-        <v>5.55</v>
+        <v>17.1</v>
       </c>
       <c r="J37" s="23" t="n">
-        <v>6.4</v>
+        <v>11.63</v>
       </c>
       <c r="K37" s="24" t="n">
-        <v>-9.18</v>
+        <v>19.24</v>
       </c>
       <c r="L37" s="23" t="n">
-        <v>-17.67</v>
+        <v>-11.05</v>
       </c>
       <c r="M37" s="24" t="n">
-        <v>-20.27</v>
+        <v>-16.95</v>
       </c>
     </row>
     <row r="38">
@@ -8239,29 +8455,35 @@
       <c r="C38" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="D38" s="13" t="n"/>
-      <c r="E38" s="13" t="n"/>
-      <c r="F38" s="13" t="n"/>
+      <c r="D38" s="13" t="n">
+        <v>48</v>
+      </c>
+      <c r="E38" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>50</v>
+      </c>
       <c r="G38" s="23" t="n">
-        <v>5.79</v>
+        <v>-11.16</v>
       </c>
       <c r="H38" s="24" t="n">
-        <v>80.8</v>
+        <v>-67.63</v>
       </c>
       <c r="I38" s="23" t="n">
-        <v>1.87</v>
+        <v>6.67</v>
       </c>
       <c r="J38" s="23" t="n">
-        <v>0.99</v>
+        <v>0.38</v>
       </c>
       <c r="K38" s="24" t="n">
-        <v>-9.52</v>
+        <v>17.14</v>
       </c>
       <c r="L38" s="23" t="n">
-        <v>-11.73</v>
+        <v>-14.84</v>
       </c>
       <c r="M38" s="24" t="n">
-        <v>-17.71</v>
+        <v>-17.57</v>
       </c>
     </row>
     <row r="39">
@@ -8274,29 +8496,35 @@
       <c r="C39" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="D39" s="13" t="n"/>
-      <c r="E39" s="13" t="n"/>
-      <c r="F39" s="13" t="n"/>
+      <c r="D39" s="13" t="n">
+        <v>48</v>
+      </c>
+      <c r="E39" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>50</v>
+      </c>
       <c r="G39" s="23" t="n">
-        <v>4.53</v>
+        <v>-14.81</v>
       </c>
       <c r="H39" s="24" t="n">
-        <v>59.26</v>
+        <v>-88.94</v>
       </c>
       <c r="I39" s="23" t="n">
-        <v>1.25</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J39" s="23" t="n">
-        <v>0.99</v>
+        <v>0.38</v>
       </c>
       <c r="K39" s="24" t="n">
-        <v>-8.359999999999999</v>
+        <v>17.49</v>
       </c>
       <c r="L39" s="23" t="n">
-        <v>-1.42</v>
+        <v>-14.11</v>
       </c>
       <c r="M39" s="24" t="n">
-        <v>-17.19</v>
+        <v>-15.64</v>
       </c>
     </row>
     <row r="40">
@@ -8309,29 +8537,35 @@
       <c r="C40" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="D40" s="13" t="n"/>
-      <c r="E40" s="13" t="n"/>
-      <c r="F40" s="13" t="n"/>
+      <c r="D40" s="13" t="n">
+        <v>48</v>
+      </c>
+      <c r="E40" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>50</v>
+      </c>
       <c r="G40" s="23" t="n">
-        <v>2.64</v>
+        <v>-17.01</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>39.82</v>
+        <v>-108.15</v>
       </c>
       <c r="I40" s="23" t="n">
-        <v>1.25</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J40" s="23" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.38</v>
       </c>
       <c r="K40" s="24" t="n">
-        <v>-7.86</v>
+        <v>16.24</v>
       </c>
       <c r="L40" s="23" t="n">
-        <v>-0.12</v>
+        <v>-12.62</v>
       </c>
       <c r="M40" s="24" t="n">
-        <v>-13.23</v>
+        <v>-12.03</v>
       </c>
     </row>
     <row r="41">
@@ -8344,29 +8578,35 @@
       <c r="C41" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="D41" s="13" t="n"/>
-      <c r="E41" s="13" t="n"/>
-      <c r="F41" s="13" t="n"/>
+      <c r="D41" s="13" t="n">
+        <v>48</v>
+      </c>
+      <c r="E41" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>50</v>
+      </c>
       <c r="G41" s="23" t="n">
-        <v>2.59</v>
+        <v>-19.8</v>
       </c>
       <c r="H41" s="24" t="n">
-        <v>20.82</v>
+        <v>-127.17</v>
       </c>
       <c r="I41" s="23" t="n">
-        <v>7.03</v>
+        <v>0</v>
       </c>
       <c r="J41" s="23" t="n">
-        <v>9.470000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="K41" s="24" t="n">
-        <v>-7.14</v>
+        <v>16.82</v>
       </c>
       <c r="L41" s="23" t="n">
-        <v>0.11</v>
+        <v>-11.33</v>
       </c>
       <c r="M41" s="24" t="n">
-        <v>-12.78</v>
+        <v>-12.89</v>
       </c>
     </row>
     <row r="42">
@@ -8379,29 +8619,35 @@
       <c r="C42" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="D42" s="13" t="n"/>
-      <c r="E42" s="13" t="n"/>
-      <c r="F42" s="13" t="n"/>
+      <c r="D42" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="E42" s="13" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>50</v>
+      </c>
       <c r="G42" s="23" t="n">
-        <v>0.28</v>
+        <v>-21.93</v>
       </c>
       <c r="H42" s="24" t="n">
-        <v>4.73</v>
+        <v>-143.33</v>
       </c>
       <c r="I42" s="23" t="n">
-        <v>7.03</v>
+        <v>0</v>
       </c>
       <c r="J42" s="23" t="n">
-        <v>9.470000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="K42" s="24" t="n">
-        <v>-6.02</v>
+        <v>20.02</v>
       </c>
       <c r="L42" s="23" t="n">
-        <v>-2.3</v>
+        <v>-12.61</v>
       </c>
       <c r="M42" s="24" t="n">
-        <v>-11.19</v>
+        <v>-13.42</v>
       </c>
     </row>
     <row r="43">
@@ -8414,29 +8660,35 @@
       <c r="C43" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="D43" s="13" t="n"/>
-      <c r="E43" s="13" t="n"/>
-      <c r="F43" s="13" t="n"/>
+      <c r="D43" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="E43" s="13" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="F43" s="13" t="n">
+        <v>50</v>
+      </c>
       <c r="G43" s="23" t="n">
-        <v>-2.21</v>
+        <v>-23.67</v>
       </c>
       <c r="H43" s="24" t="n">
-        <v>-12.1</v>
+        <v>-160.08</v>
       </c>
       <c r="I43" s="23" t="n">
-        <v>7.03</v>
+        <v>0</v>
       </c>
       <c r="J43" s="23" t="n">
-        <v>9.470000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="K43" s="24" t="n">
-        <v>-5.43</v>
+        <v>22.91</v>
       </c>
       <c r="L43" s="23" t="n">
-        <v>-1.79</v>
+        <v>-9.51</v>
       </c>
       <c r="M43" s="24" t="n">
-        <v>-12.39</v>
+        <v>-14.97</v>
       </c>
     </row>
     <row r="44">
@@ -8449,29 +8701,35 @@
       <c r="C44" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="D44" s="13" t="n"/>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
+      <c r="D44" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="E44" s="13" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="F44" s="13" t="n">
+        <v>50</v>
+      </c>
       <c r="G44" s="23" t="n">
-        <v>-2.47</v>
+        <v>-24.28</v>
       </c>
       <c r="H44" s="24" t="n">
-        <v>-18.93</v>
+        <v>-166.85</v>
       </c>
       <c r="I44" s="23" t="n">
-        <v>7.03</v>
+        <v>3.57</v>
       </c>
       <c r="J44" s="23" t="n">
-        <v>8.949999999999999</v>
+        <v>0.21</v>
       </c>
       <c r="K44" s="24" t="n">
-        <v>-4.58</v>
+        <v>23.02</v>
       </c>
       <c r="L44" s="23" t="n">
-        <v>1.26</v>
+        <v>-10.11</v>
       </c>
       <c r="M44" s="24" t="n">
-        <v>-11.36</v>
+        <v>-15.98</v>
       </c>
     </row>
     <row r="45">
@@ -8484,29 +8742,35 @@
       <c r="C45" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="D45" s="13" t="n"/>
-      <c r="E45" s="13" t="n"/>
-      <c r="F45" s="13" t="n"/>
+      <c r="D45" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="E45" s="13" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>50</v>
+      </c>
       <c r="G45" s="23" t="n">
-        <v>-1.79</v>
+        <v>-23.34</v>
       </c>
       <c r="H45" s="24" t="n">
-        <v>-13.31</v>
+        <v>-161.12</v>
       </c>
       <c r="I45" s="23" t="n">
-        <v>5.77</v>
+        <v>0</v>
       </c>
       <c r="J45" s="23" t="n">
-        <v>8.949999999999999</v>
+        <v>0.21</v>
       </c>
       <c r="K45" s="24" t="n">
-        <v>-5.77</v>
+        <v>22.44</v>
       </c>
       <c r="L45" s="23" t="n">
-        <v>1.53</v>
+        <v>-5.03</v>
       </c>
       <c r="M45" s="24" t="n">
-        <v>-10</v>
+        <v>-16.09</v>
       </c>
     </row>
     <row r="46">
@@ -8519,29 +8783,35 @@
       <c r="C46" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="D46" s="13" t="n"/>
-      <c r="E46" s="13" t="n"/>
-      <c r="F46" s="13" t="n"/>
+      <c r="D46" s="13" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="E46" s="13" t="n">
+        <v>37.11</v>
+      </c>
+      <c r="F46" s="13" t="n">
+        <v>50</v>
+      </c>
       <c r="G46" s="23" t="n">
-        <v>0.42</v>
+        <v>-11.66</v>
       </c>
       <c r="H46" s="24" t="n">
-        <v>-0.23</v>
+        <v>-148.16</v>
       </c>
       <c r="I46" s="23" t="n">
-        <v>9.220000000000001</v>
+        <v>6.16</v>
       </c>
       <c r="J46" s="23" t="n">
-        <v>9</v>
+        <v>0.21</v>
       </c>
       <c r="K46" s="24" t="n">
-        <v>-1.91</v>
+        <v>44.77</v>
       </c>
       <c r="L46" s="23" t="n">
-        <v>-2.89</v>
+        <v>0.87</v>
       </c>
       <c r="M46" s="24" t="n">
-        <v>-11.37</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="47">
@@ -8554,29 +8824,35 @@
       <c r="C47" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="D47" s="13" t="n"/>
-      <c r="E47" s="13" t="n"/>
-      <c r="F47" s="13" t="n"/>
+      <c r="D47" s="13" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="E47" s="13" t="n">
+        <v>37.11</v>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>50</v>
+      </c>
       <c r="G47" s="23" t="n">
-        <v>1.65</v>
+        <v>-16.13</v>
       </c>
       <c r="H47" s="24" t="n">
-        <v>-5.22</v>
+        <v>-153.21</v>
       </c>
       <c r="I47" s="23" t="n">
-        <v>5.77</v>
+        <v>2.31</v>
       </c>
       <c r="J47" s="23" t="n">
-        <v>8.949999999999999</v>
+        <v>0.21</v>
       </c>
       <c r="K47" s="24" t="n">
-        <v>-2.52</v>
+        <v>37.28</v>
       </c>
       <c r="L47" s="23" t="n">
-        <v>5.05</v>
+        <v>-0.65</v>
       </c>
       <c r="M47" s="24" t="n">
-        <v>-3.33</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="48">
@@ -8589,29 +8865,35 @@
       <c r="C48" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="D48" s="13" t="n"/>
-      <c r="E48" s="13" t="n"/>
-      <c r="F48" s="13" t="n"/>
+      <c r="D48" s="13" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="E48" s="13" t="n">
+        <v>37.11</v>
+      </c>
+      <c r="F48" s="13" t="n">
+        <v>50</v>
+      </c>
       <c r="G48" s="23" t="n">
-        <v>5.17</v>
+        <v>-16.65</v>
       </c>
       <c r="H48" s="24" t="n">
-        <v>-9.220000000000001</v>
+        <v>-157.06</v>
       </c>
       <c r="I48" s="23" t="n">
-        <v>10.31</v>
+        <v>2.31</v>
       </c>
       <c r="J48" s="23" t="n">
-        <v>16.16</v>
+        <v>0.21</v>
       </c>
       <c r="K48" s="24" t="n">
-        <v>0.41</v>
+        <v>39.7</v>
       </c>
       <c r="L48" s="23" t="n">
-        <v>11.31</v>
+        <v>-1.77</v>
       </c>
       <c r="M48" s="24" t="n">
-        <v>-0.29</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="49">
@@ -8624,29 +8906,35 @@
       <c r="C49" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="D49" s="13" t="n"/>
-      <c r="E49" s="13" t="n"/>
-      <c r="F49" s="13" t="n"/>
+      <c r="D49" s="13" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="E49" s="13" t="n">
+        <v>37.11</v>
+      </c>
+      <c r="F49" s="13" t="n">
+        <v>50</v>
+      </c>
       <c r="G49" s="23" t="n">
-        <v>2.96</v>
+        <v>-21.35</v>
       </c>
       <c r="H49" s="24" t="n">
-        <v>-40.39</v>
+        <v>-188.3</v>
       </c>
       <c r="I49" s="23" t="n">
-        <v>12.18</v>
+        <v>4.09</v>
       </c>
       <c r="J49" s="23" t="n">
-        <v>38.43</v>
+        <v>0.21</v>
       </c>
       <c r="K49" s="24" t="n">
-        <v>-2.58</v>
+        <v>45.83</v>
       </c>
       <c r="L49" s="23" t="n">
-        <v>9.949999999999999</v>
+        <v>-3.48</v>
       </c>
       <c r="M49" s="24" t="n">
-        <v>-6.71</v>
+        <v>-10.04</v>
       </c>
     </row>
     <row r="50">
@@ -8659,29 +8947,35 @@
       <c r="C50" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="D50" s="13" t="n"/>
-      <c r="E50" s="13" t="n"/>
-      <c r="F50" s="13" t="n"/>
+      <c r="D50" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="E50" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>50</v>
+      </c>
       <c r="G50" s="23" t="n">
-        <v>3.93</v>
+        <v>-21.03</v>
       </c>
       <c r="H50" s="24" t="n">
-        <v>-38.15</v>
+        <v>-185.87</v>
       </c>
       <c r="I50" s="23" t="n">
-        <v>10.31</v>
+        <v>2.31</v>
       </c>
       <c r="J50" s="23" t="n">
-        <v>38.21</v>
+        <v>0.21</v>
       </c>
       <c r="K50" s="24" t="n">
-        <v>-1.43</v>
+        <v>40.5</v>
       </c>
       <c r="L50" s="23" t="n">
-        <v>6.24</v>
+        <v>1.19</v>
       </c>
       <c r="M50" s="24" t="n">
-        <v>1.8</v>
+        <v>-7.58</v>
       </c>
     </row>
     <row r="51">
@@ -8694,29 +8988,35 @@
       <c r="C51" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="D51" s="13" t="n"/>
-      <c r="E51" s="13" t="n"/>
-      <c r="F51" s="13" t="n"/>
+      <c r="D51" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="E51" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="F51" s="13" t="n">
+        <v>50</v>
+      </c>
       <c r="G51" s="23" t="n">
-        <v>6.95</v>
+        <v>-22.07</v>
       </c>
       <c r="H51" s="24" t="n">
-        <v>-42.15</v>
+        <v>-189.86</v>
       </c>
       <c r="I51" s="23" t="n">
-        <v>16.69</v>
+        <v>2.31</v>
       </c>
       <c r="J51" s="23" t="n">
-        <v>45.32</v>
+        <v>0.21</v>
       </c>
       <c r="K51" s="24" t="n">
-        <v>-0.28</v>
+        <v>40.95</v>
       </c>
       <c r="L51" s="23" t="n">
-        <v>11.87</v>
+        <v>-2.89</v>
       </c>
       <c r="M51" s="24" t="n">
-        <v>2.55</v>
+        <v>-6.62</v>
       </c>
     </row>
     <row r="52">
@@ -8729,29 +9029,35 @@
       <c r="C52" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="D52" s="13" t="n"/>
-      <c r="E52" s="13" t="n"/>
-      <c r="F52" s="13" t="n"/>
+      <c r="D52" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="E52" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="F52" s="13" t="n">
+        <v>50</v>
+      </c>
       <c r="G52" s="23" t="n">
-        <v>4.53</v>
+        <v>-20.74</v>
       </c>
       <c r="H52" s="24" t="n">
-        <v>-38.43</v>
+        <v>-186.09</v>
       </c>
       <c r="I52" s="23" t="n">
-        <v>10.31</v>
+        <v>5.88</v>
       </c>
       <c r="J52" s="23" t="n">
-        <v>37.72</v>
+        <v>0.21</v>
       </c>
       <c r="K52" s="24" t="n">
-        <v>-1.31</v>
+        <v>41.41</v>
       </c>
       <c r="L52" s="23" t="n">
-        <v>9.869999999999999</v>
+        <v>-1.15</v>
       </c>
       <c r="M52" s="24" t="n">
-        <v>2.41</v>
+        <v>-8.02</v>
       </c>
     </row>
     <row r="53">
@@ -8764,29 +9070,35 @@
       <c r="C53" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="D53" s="13" t="n"/>
-      <c r="E53" s="13" t="n"/>
-      <c r="F53" s="13" t="n"/>
+      <c r="D53" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="E53" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="F53" s="13" t="n">
+        <v>50</v>
+      </c>
       <c r="G53" s="23" t="n">
-        <v>5.94</v>
+        <v>-16.28</v>
       </c>
       <c r="H53" s="24" t="n">
-        <v>-22.48</v>
+        <v>-170.13</v>
       </c>
       <c r="I53" s="23" t="n">
-        <v>12.46</v>
+        <v>7.98</v>
       </c>
       <c r="J53" s="23" t="n">
-        <v>37.72</v>
+        <v>0.21</v>
       </c>
       <c r="K53" s="24" t="n">
-        <v>-3.5</v>
+        <v>41.9</v>
       </c>
       <c r="L53" s="23" t="n">
-        <v>6.67</v>
+        <v>4.46</v>
       </c>
       <c r="M53" s="24" t="n">
-        <v>0.01</v>
+        <v>-3.66</v>
       </c>
     </row>
     <row r="54">
@@ -8799,29 +9111,35 @@
       <c r="C54" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="D54" s="13" t="n"/>
-      <c r="E54" s="13" t="n"/>
-      <c r="F54" s="13" t="n"/>
+      <c r="D54" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="E54" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="F54" s="13" t="n">
+        <v>50</v>
+      </c>
       <c r="G54" s="23" t="n">
-        <v>4.84</v>
+        <v>-16.65</v>
       </c>
       <c r="H54" s="24" t="n">
-        <v>-14.65</v>
+        <v>-162.39</v>
       </c>
       <c r="I54" s="23" t="n">
-        <v>12.46</v>
+        <v>4.41</v>
       </c>
       <c r="J54" s="23" t="n">
-        <v>23.22</v>
+        <v>0.21</v>
       </c>
       <c r="K54" s="24" t="n">
-        <v>-2.88</v>
+        <v>40.8</v>
       </c>
       <c r="L54" s="23" t="n">
-        <v>8.279999999999999</v>
+        <v>2.01</v>
       </c>
       <c r="M54" s="24" t="n">
-        <v>-0.67</v>
+        <v>-5.34</v>
       </c>
     </row>
     <row r="55">
@@ -8834,29 +9152,35 @@
       <c r="C55" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="D55" s="13" t="n"/>
-      <c r="E55" s="13" t="n"/>
-      <c r="F55" s="13" t="n"/>
+      <c r="D55" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="E55" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="F55" s="13" t="n">
+        <v>50</v>
+      </c>
       <c r="G55" s="23" t="n">
-        <v>4.89</v>
+        <v>-12.01</v>
       </c>
       <c r="H55" s="24" t="n">
-        <v>0.32</v>
+        <v>-147.47</v>
       </c>
       <c r="I55" s="23" t="n">
-        <v>9.48</v>
+        <v>4.41</v>
       </c>
       <c r="J55" s="23" t="n">
-        <v>15.74</v>
+        <v>0.21</v>
       </c>
       <c r="K55" s="24" t="n">
-        <v>-3.99</v>
+        <v>42.34</v>
       </c>
       <c r="L55" s="23" t="n">
-        <v>6.94</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="M55" s="24" t="n">
-        <v>-0.18</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="56">
@@ -8869,29 +9193,35 @@
       <c r="C56" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="D56" s="13" t="n"/>
-      <c r="E56" s="13" t="n"/>
-      <c r="F56" s="13" t="n"/>
+      <c r="D56" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="E56" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="F56" s="13" t="n">
+        <v>50</v>
+      </c>
       <c r="G56" s="23" t="n">
-        <v>6.23</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="H56" s="24" t="n">
-        <v>16.81</v>
+        <v>-130.96</v>
       </c>
       <c r="I56" s="23" t="n">
-        <v>9.48</v>
+        <v>4.41</v>
       </c>
       <c r="J56" s="23" t="n">
-        <v>15.8</v>
+        <v>0.21</v>
       </c>
       <c r="K56" s="24" t="n">
-        <v>-5.09</v>
+        <v>42.79</v>
       </c>
       <c r="L56" s="23" t="n">
-        <v>5.02</v>
+        <v>11.67</v>
       </c>
       <c r="M56" s="24" t="n">
-        <v>-3.62</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="57">
@@ -8904,29 +9234,35 @@
       <c r="C57" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="D57" s="13" t="n"/>
-      <c r="E57" s="13" t="n"/>
-      <c r="F57" s="13" t="n"/>
+      <c r="D57" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="E57" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="F57" s="13" t="n">
+        <v>50</v>
+      </c>
       <c r="G57" s="23" t="n">
-        <v>8.27</v>
+        <v>-4.59</v>
       </c>
       <c r="H57" s="24" t="n">
-        <v>35.17</v>
+        <v>-112.66</v>
       </c>
       <c r="I57" s="23" t="n">
-        <v>9.48</v>
+        <v>6.42</v>
       </c>
       <c r="J57" s="23" t="n">
-        <v>15.8</v>
+        <v>0.21</v>
       </c>
       <c r="K57" s="24" t="n">
-        <v>-4.02</v>
+        <v>45.32</v>
       </c>
       <c r="L57" s="23" t="n">
-        <v>3.05</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M57" s="24" t="n">
-        <v>-6.61</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="58">
@@ -8940,34 +9276,34 @@
         <v>15</v>
       </c>
       <c r="D58" s="13" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="E58" s="13" t="n">
-        <v>55</v>
+        <v>38.01</v>
       </c>
       <c r="F58" s="13" t="n">
         <v>55</v>
       </c>
       <c r="G58" s="23" t="n">
-        <v>11.19</v>
+        <v>4.05</v>
       </c>
       <c r="H58" s="24" t="n">
-        <v>57.29</v>
+        <v>-90.69</v>
       </c>
       <c r="I58" s="23" t="n">
-        <v>12.77</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="J58" s="23" t="n">
-        <v>15.8</v>
+        <v>0.21</v>
       </c>
       <c r="K58" s="24" t="n">
-        <v>-1.54</v>
+        <v>50.99</v>
       </c>
       <c r="L58" s="23" t="n">
-        <v>0.15</v>
+        <v>22.86</v>
       </c>
       <c r="M58" s="24" t="n">
-        <v>-11.59</v>
+        <v>19.97</v>
       </c>
     </row>
     <row r="59">
@@ -8981,34 +9317,34 @@
         <v>15</v>
       </c>
       <c r="D59" s="13" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="E59" s="13" t="n">
-        <v>55</v>
+        <v>38.01</v>
       </c>
       <c r="F59" s="13" t="n">
         <v>55</v>
       </c>
       <c r="G59" s="23" t="n">
-        <v>16.34</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H59" s="24" t="n">
-        <v>82.3</v>
+        <v>-65.73999999999999</v>
       </c>
       <c r="I59" s="23" t="n">
-        <v>15.58</v>
+        <v>10.29</v>
       </c>
       <c r="J59" s="23" t="n">
-        <v>15.8</v>
+        <v>0.84</v>
       </c>
       <c r="K59" s="24" t="n">
-        <v>-2.05</v>
+        <v>51.75</v>
       </c>
       <c r="L59" s="23" t="n">
-        <v>-2.48</v>
+        <v>19.06</v>
       </c>
       <c r="M59" s="24" t="n">
-        <v>-2.59</v>
+        <v>32.45</v>
       </c>
     </row>
     <row r="60">
@@ -9022,34 +9358,34 @@
         <v>15</v>
       </c>
       <c r="D60" s="13" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="E60" s="13" t="n">
-        <v>55</v>
+        <v>38.01</v>
       </c>
       <c r="F60" s="13" t="n">
         <v>55</v>
       </c>
       <c r="G60" s="23" t="n">
-        <v>29.57</v>
+        <v>13.79</v>
       </c>
       <c r="H60" s="24" t="n">
-        <v>108.89</v>
+        <v>-39.31</v>
       </c>
       <c r="I60" s="23" t="n">
-        <v>19.61</v>
+        <v>7.46</v>
       </c>
       <c r="J60" s="23" t="n">
-        <v>21.54</v>
+        <v>2.24</v>
       </c>
       <c r="K60" s="24" t="n">
-        <v>-0.58</v>
+        <v>52.93</v>
       </c>
       <c r="L60" s="23" t="n">
-        <v>29.83</v>
+        <v>25.66</v>
       </c>
       <c r="M60" s="24" t="n">
-        <v>9.16</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="61">
@@ -9063,34 +9399,34 @@
         <v>15</v>
       </c>
       <c r="D61" s="13" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="E61" s="13" t="n">
-        <v>55</v>
+        <v>38.01</v>
       </c>
       <c r="F61" s="13" t="n">
         <v>55</v>
       </c>
       <c r="G61" s="23" t="n">
-        <v>41.29</v>
+        <v>19.56</v>
       </c>
       <c r="H61" s="24" t="n">
-        <v>136.72</v>
+        <v>-11.56</v>
       </c>
       <c r="I61" s="23" t="n">
-        <v>23.68</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="J61" s="23" t="n">
-        <v>38.77</v>
+        <v>2.74</v>
       </c>
       <c r="K61" s="24" t="n">
-        <v>4.38</v>
+        <v>56.31</v>
       </c>
       <c r="L61" s="23" t="n">
-        <v>37.63</v>
+        <v>27.71</v>
       </c>
       <c r="M61" s="24" t="n">
-        <v>19.84</v>
+        <v>30.04</v>
       </c>
     </row>
     <row r="62">
@@ -9103,29 +9439,35 @@
       <c r="C62" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="D62" s="13" t="n"/>
-      <c r="E62" s="13" t="n"/>
-      <c r="F62" s="13" t="n"/>
+      <c r="D62" s="13" t="n">
+        <v>205</v>
+      </c>
+      <c r="E62" s="13" t="n">
+        <v>199.99</v>
+      </c>
+      <c r="F62" s="13" t="n">
+        <v>211</v>
+      </c>
       <c r="G62" s="23" t="n">
-        <v>67.13</v>
+        <v>19.33</v>
       </c>
       <c r="H62" s="24" t="n">
-        <v>171.76</v>
+        <v>23.08</v>
       </c>
       <c r="I62" s="23" t="n">
-        <v>39.07</v>
+        <v>21.77</v>
       </c>
       <c r="J62" s="23" t="n">
-        <v>73.8</v>
+        <v>9.33</v>
       </c>
       <c r="K62" s="24" t="n">
-        <v>18.09</v>
+        <v>50.17</v>
       </c>
       <c r="L62" s="23" t="n">
-        <v>70.76000000000001</v>
+        <v>13.55</v>
       </c>
       <c r="M62" s="24" t="n">
-        <v>44.15</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="63">
@@ -9138,29 +9480,35 @@
       <c r="C63" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="D63" s="13" t="n"/>
-      <c r="E63" s="13" t="n"/>
-      <c r="F63" s="13" t="n"/>
+      <c r="D63" s="13" t="n">
+        <v>205</v>
+      </c>
+      <c r="E63" s="13" t="n">
+        <v>199.99</v>
+      </c>
+      <c r="F63" s="13" t="n">
+        <v>211</v>
+      </c>
       <c r="G63" s="23" t="n">
-        <v>90.66</v>
+        <v>51.31</v>
       </c>
       <c r="H63" s="24" t="n">
-        <v>197.35</v>
+        <v>48.06</v>
       </c>
       <c r="I63" s="23" t="n">
-        <v>54.98</v>
+        <v>51.53</v>
       </c>
       <c r="J63" s="23" t="n">
-        <v>54.17</v>
+        <v>18.13</v>
       </c>
       <c r="K63" s="24" t="n">
-        <v>52.9</v>
+        <v>72.55</v>
       </c>
       <c r="L63" s="23" t="n">
-        <v>131.95</v>
+        <v>68.52</v>
       </c>
       <c r="M63" s="24" t="n">
-        <v>69.38</v>
+        <v>49.16</v>
       </c>
     </row>
     <row r="64">
@@ -9173,29 +9521,35 @@
       <c r="C64" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="D64" s="13" t="n"/>
-      <c r="E64" s="13" t="n"/>
-      <c r="F64" s="13" t="n"/>
+      <c r="D64" s="13" t="n">
+        <v>205</v>
+      </c>
+      <c r="E64" s="13" t="n">
+        <v>199.99</v>
+      </c>
+      <c r="F64" s="13" t="n">
+        <v>211</v>
+      </c>
       <c r="G64" s="23" t="n">
-        <v>136.64</v>
+        <v>124.19</v>
       </c>
       <c r="H64" s="24" t="n">
-        <v>224.45</v>
+        <v>74.67</v>
       </c>
       <c r="I64" s="23" t="n">
-        <v>107.55</v>
+        <v>125.51</v>
       </c>
       <c r="J64" s="23" t="n">
-        <v>153.75</v>
+        <v>137.91</v>
       </c>
       <c r="K64" s="24" t="n">
-        <v>109.38</v>
+        <v>112.6</v>
       </c>
       <c r="L64" s="23" t="n">
-        <v>129.54</v>
+        <v>137.28</v>
       </c>
       <c r="M64" s="24" t="n">
-        <v>107.47</v>
+        <v>151.3</v>
       </c>
     </row>
     <row r="65">
@@ -9208,29 +9562,35 @@
       <c r="C65" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="D65" s="13" t="n"/>
-      <c r="E65" s="13" t="n"/>
-      <c r="F65" s="13" t="n"/>
+      <c r="D65" s="13" t="n">
+        <v>205</v>
+      </c>
+      <c r="E65" s="13" t="n">
+        <v>199.99</v>
+      </c>
+      <c r="F65" s="13" t="n">
+        <v>211</v>
+      </c>
       <c r="G65" s="23" t="n">
-        <v>170.54</v>
+        <v>164.79</v>
       </c>
       <c r="H65" s="24" t="n">
-        <v>261.68</v>
+        <v>111.47</v>
       </c>
       <c r="I65" s="23" t="n">
-        <v>142.59</v>
+        <v>175.78</v>
       </c>
       <c r="J65" s="23" t="n">
-        <v>182.81</v>
+        <v>156.3</v>
       </c>
       <c r="K65" s="24" t="n">
-        <v>171.46</v>
+        <v>162.78</v>
       </c>
       <c r="L65" s="23" t="n">
-        <v>140.37</v>
+        <v>191.43</v>
       </c>
       <c r="M65" s="24" t="n">
-        <v>136.85</v>
+        <v>184.49</v>
       </c>
     </row>
     <row r="66">
@@ -9243,29 +9603,35 @@
       <c r="C66" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="D66" s="13" t="n"/>
-      <c r="E66" s="13" t="n"/>
-      <c r="F66" s="13" t="n"/>
+      <c r="D66" s="13" t="n">
+        <v>383</v>
+      </c>
+      <c r="E66" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F66" s="13" t="n">
+        <v>386</v>
+      </c>
       <c r="G66" s="23" t="n">
-        <v>300.09</v>
+        <v>152.24</v>
       </c>
       <c r="H66" s="24" t="n">
-        <v>278.22</v>
+        <v>127.37</v>
       </c>
       <c r="I66" s="23" t="n">
-        <v>278.64</v>
+        <v>223.76</v>
       </c>
       <c r="J66" s="23" t="n">
-        <v>301.8</v>
+        <v>51.24</v>
       </c>
       <c r="K66" s="24" t="n">
-        <v>291.97</v>
+        <v>198.42</v>
       </c>
       <c r="L66" s="23" t="n">
-        <v>333.7</v>
+        <v>171.08</v>
       </c>
       <c r="M66" s="24" t="n">
-        <v>314.52</v>
+        <v>136.67</v>
       </c>
     </row>
     <row r="67">
@@ -9278,29 +9644,35 @@
       <c r="C67" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="D67" s="13" t="n"/>
-      <c r="E67" s="13" t="n"/>
-      <c r="F67" s="13" t="n"/>
+      <c r="D67" s="13" t="n">
+        <v>383</v>
+      </c>
+      <c r="E67" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F67" s="13" t="n">
+        <v>386</v>
+      </c>
       <c r="G67" s="23" t="n">
-        <v>344.13</v>
+        <v>150.3</v>
       </c>
       <c r="H67" s="24" t="n">
-        <v>304.21</v>
+        <v>151.84</v>
       </c>
       <c r="I67" s="23" t="n">
-        <v>328.62</v>
+        <v>238.78</v>
       </c>
       <c r="J67" s="23" t="n">
-        <v>339.93</v>
+        <v>48.29</v>
       </c>
       <c r="K67" s="24" t="n">
-        <v>368.26</v>
+        <v>215.02</v>
       </c>
       <c r="L67" s="23" t="n">
-        <v>383.61</v>
+        <v>133.7</v>
       </c>
       <c r="M67" s="24" t="n">
-        <v>335.98</v>
+        <v>110.86</v>
       </c>
     </row>
     <row r="68">
@@ -9313,29 +9685,35 @@
       <c r="C68" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="D68" s="13" t="n"/>
-      <c r="E68" s="13" t="n"/>
-      <c r="F68" s="13" t="n"/>
+      <c r="D68" s="13" t="n">
+        <v>383</v>
+      </c>
+      <c r="E68" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F68" s="13" t="n">
+        <v>386</v>
+      </c>
       <c r="G68" s="23" t="n">
-        <v>362.13</v>
+        <v>150.43</v>
       </c>
       <c r="H68" s="24" t="n">
-        <v>333.86</v>
+        <v>180.4</v>
       </c>
       <c r="I68" s="23" t="n">
-        <v>332.53</v>
+        <v>221.68</v>
       </c>
       <c r="J68" s="23" t="n">
-        <v>358.92</v>
+        <v>55.45</v>
       </c>
       <c r="K68" s="24" t="n">
-        <v>384.54</v>
+        <v>211.43</v>
       </c>
       <c r="L68" s="23" t="n">
-        <v>403.15</v>
+        <v>125.41</v>
       </c>
       <c r="M68" s="24" t="n">
-        <v>357.74</v>
+        <v>109.12</v>
       </c>
     </row>
     <row r="69">
@@ -9348,29 +9726,35 @@
       <c r="C69" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="D69" s="13" t="n"/>
-      <c r="E69" s="13" t="n"/>
-      <c r="F69" s="13" t="n"/>
+      <c r="D69" s="13" t="n">
+        <v>383</v>
+      </c>
+      <c r="E69" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F69" s="13" t="n">
+        <v>386</v>
+      </c>
       <c r="G69" s="23" t="n">
-        <v>372.22</v>
+        <v>179</v>
       </c>
       <c r="H69" s="24" t="n">
-        <v>356.96</v>
+        <v>202.74</v>
       </c>
       <c r="I69" s="23" t="n">
-        <v>339</v>
+        <v>197.86</v>
       </c>
       <c r="J69" s="23" t="n">
-        <v>380.26</v>
+        <v>106.78</v>
       </c>
       <c r="K69" s="24" t="n">
-        <v>401.72</v>
+        <v>234.83</v>
       </c>
       <c r="L69" s="23" t="n">
-        <v>386.16</v>
+        <v>156.61</v>
       </c>
       <c r="M69" s="24" t="n">
-        <v>368.52</v>
+        <v>178.01</v>
       </c>
     </row>
     <row r="70">
@@ -9387,25 +9771,25 @@
       <c r="E70" s="13" t="n"/>
       <c r="F70" s="13" t="n"/>
       <c r="G70" s="23" t="n">
-        <v>373.43</v>
+        <v>182.39</v>
       </c>
       <c r="H70" s="24" t="n">
-        <v>373.82</v>
+        <v>218.59</v>
       </c>
       <c r="I70" s="23" t="n">
-        <v>342.75</v>
+        <v>206.16</v>
       </c>
       <c r="J70" s="23" t="n">
-        <v>388.4</v>
+        <v>105.67</v>
       </c>
       <c r="K70" s="24" t="n">
-        <v>389.02</v>
+        <v>222.09</v>
       </c>
       <c r="L70" s="23" t="n">
-        <v>385.36</v>
+        <v>164.42</v>
       </c>
       <c r="M70" s="24" t="n">
-        <v>362.29</v>
+        <v>182.02</v>
       </c>
     </row>
     <row r="71">
@@ -9422,25 +9806,25 @@
       <c r="E71" s="13" t="n"/>
       <c r="F71" s="13" t="n"/>
       <c r="G71" s="23" t="n">
-        <v>366.18</v>
+        <v>171.27</v>
       </c>
       <c r="H71" s="24" t="n">
-        <v>394.22</v>
+        <v>238.9</v>
       </c>
       <c r="I71" s="23" t="n">
-        <v>351.24</v>
+        <v>202.08</v>
       </c>
       <c r="J71" s="23" t="n">
-        <v>400.01</v>
+        <v>129.28</v>
       </c>
       <c r="K71" s="24" t="n">
-        <v>371.24</v>
+        <v>208.78</v>
       </c>
       <c r="L71" s="23" t="n">
-        <v>352.05</v>
+        <v>130.07</v>
       </c>
       <c r="M71" s="24" t="n">
-        <v>331.67</v>
+        <v>124.91</v>
       </c>
     </row>
     <row r="72">
@@ -9457,25 +9841,25 @@
       <c r="E72" s="13" t="n"/>
       <c r="F72" s="13" t="n"/>
       <c r="G72" s="23" t="n">
-        <v>363.98</v>
+        <v>180.62</v>
       </c>
       <c r="H72" s="24" t="n">
-        <v>406.35</v>
+        <v>250.46</v>
       </c>
       <c r="I72" s="23" t="n">
-        <v>356.87</v>
+        <v>200.24</v>
       </c>
       <c r="J72" s="23" t="n">
-        <v>409.14</v>
+        <v>160.46</v>
       </c>
       <c r="K72" s="24" t="n">
-        <v>356.63</v>
+        <v>207.87</v>
       </c>
       <c r="L72" s="23" t="n">
-        <v>347.88</v>
+        <v>131.54</v>
       </c>
       <c r="M72" s="24" t="n">
-        <v>311.62</v>
+        <v>140.01</v>
       </c>
     </row>
     <row r="73">
@@ -9492,25 +9876,25 @@
       <c r="E73" s="13" t="n"/>
       <c r="F73" s="13" t="n"/>
       <c r="G73" s="23" t="n">
-        <v>362.8</v>
+        <v>171.98</v>
       </c>
       <c r="H73" s="24" t="n">
-        <v>407.1</v>
+        <v>251.19</v>
       </c>
       <c r="I73" s="23" t="n">
-        <v>360.48</v>
+        <v>206.45</v>
       </c>
       <c r="J73" s="23" t="n">
-        <v>409.1</v>
+        <v>139.7</v>
       </c>
       <c r="K73" s="24" t="n">
-        <v>349.35</v>
+        <v>201.43</v>
       </c>
       <c r="L73" s="23" t="n">
-        <v>335.03</v>
+        <v>114.53</v>
       </c>
       <c r="M73" s="24" t="n">
-        <v>320.28</v>
+        <v>126.07</v>
       </c>
     </row>
     <row r="74">
@@ -9523,29 +9907,35 @@
       <c r="C74" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="D74" s="13" t="n"/>
-      <c r="E74" s="13" t="n"/>
-      <c r="F74" s="13" t="n"/>
+      <c r="D74" s="13" t="n">
+        <v>390</v>
+      </c>
+      <c r="E74" s="13" t="n">
+        <v>390</v>
+      </c>
+      <c r="F74" s="13" t="n">
+        <v>419.92</v>
+      </c>
       <c r="G74" s="23" t="n">
-        <v>357.16</v>
+        <v>151.67</v>
       </c>
       <c r="H74" s="24" t="n">
-        <v>401.3</v>
+        <v>245.17</v>
       </c>
       <c r="I74" s="23" t="n">
-        <v>354.62</v>
+        <v>197.8</v>
       </c>
       <c r="J74" s="23" t="n">
-        <v>402.37</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="K74" s="24" t="n">
-        <v>343.16</v>
+        <v>189.86</v>
       </c>
       <c r="L74" s="23" t="n">
-        <v>333.82</v>
+        <v>82.05</v>
       </c>
       <c r="M74" s="24" t="n">
-        <v>312.28</v>
+        <v>114.25</v>
       </c>
     </row>
     <row r="75">
@@ -9558,29 +9948,35 @@
       <c r="C75" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="D75" s="13" t="n"/>
-      <c r="E75" s="13" t="n"/>
-      <c r="F75" s="13" t="n"/>
+      <c r="D75" s="13" t="n">
+        <v>390</v>
+      </c>
+      <c r="E75" s="13" t="n">
+        <v>390</v>
+      </c>
+      <c r="F75" s="13" t="n">
+        <v>419.92</v>
+      </c>
       <c r="G75" s="23" t="n">
-        <v>357.28</v>
+        <v>145.61</v>
       </c>
       <c r="H75" s="24" t="n">
-        <v>396.21</v>
+        <v>239.78</v>
       </c>
       <c r="I75" s="23" t="n">
-        <v>343.81</v>
+        <v>184.87</v>
       </c>
       <c r="J75" s="23" t="n">
-        <v>403.3</v>
+        <v>107.96</v>
       </c>
       <c r="K75" s="24" t="n">
-        <v>340.91</v>
+        <v>168.47</v>
       </c>
       <c r="L75" s="23" t="n">
-        <v>334.3</v>
+        <v>103.01</v>
       </c>
       <c r="M75" s="24" t="n">
-        <v>329.56</v>
+        <v>78.63</v>
       </c>
     </row>
     <row r="76">
@@ -9593,29 +9989,35 @@
       <c r="C76" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="D76" s="13" t="n"/>
-      <c r="E76" s="13" t="n"/>
-      <c r="F76" s="13" t="n"/>
+      <c r="D76" s="13" t="n">
+        <v>390</v>
+      </c>
+      <c r="E76" s="13" t="n">
+        <v>390</v>
+      </c>
+      <c r="F76" s="13" t="n">
+        <v>419.92</v>
+      </c>
       <c r="G76" s="23" t="n">
-        <v>354.62</v>
+        <v>145.67</v>
       </c>
       <c r="H76" s="24" t="n">
-        <v>392.29</v>
+        <v>235.55</v>
       </c>
       <c r="I76" s="23" t="n">
-        <v>341.31</v>
+        <v>188.39</v>
       </c>
       <c r="J76" s="23" t="n">
-        <v>410.49</v>
+        <v>112.22</v>
       </c>
       <c r="K76" s="24" t="n">
-        <v>339.85</v>
+        <v>163.1</v>
       </c>
       <c r="L76" s="23" t="n">
-        <v>320.02</v>
+        <v>100.39</v>
       </c>
       <c r="M76" s="24" t="n">
-        <v>327.61</v>
+        <v>82.79000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -9628,29 +10030,35 @@
       <c r="C77" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="D77" s="13" t="n"/>
-      <c r="E77" s="13" t="n"/>
-      <c r="F77" s="13" t="n"/>
+      <c r="D77" s="13" t="n">
+        <v>390</v>
+      </c>
+      <c r="E77" s="13" t="n">
+        <v>390</v>
+      </c>
+      <c r="F77" s="13" t="n">
+        <v>419.92</v>
+      </c>
       <c r="G77" s="23" t="n">
-        <v>358.87</v>
+        <v>145.09</v>
       </c>
       <c r="H77" s="24" t="n">
-        <v>387.47</v>
+        <v>230.75</v>
       </c>
       <c r="I77" s="23" t="n">
-        <v>342.68</v>
+        <v>187.87</v>
       </c>
       <c r="J77" s="23" t="n">
-        <v>402.61</v>
+        <v>107.39</v>
       </c>
       <c r="K77" s="24" t="n">
-        <v>345.04</v>
+        <v>159.03</v>
       </c>
       <c r="L77" s="23" t="n">
-        <v>345.13</v>
+        <v>98.06999999999999</v>
       </c>
       <c r="M77" s="24" t="n">
-        <v>333.58</v>
+        <v>95.73</v>
       </c>
     </row>
     <row r="78">
@@ -9663,29 +10071,35 @@
       <c r="C78" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="D78" s="13" t="n"/>
-      <c r="E78" s="13" t="n"/>
-      <c r="F78" s="13" t="n"/>
+      <c r="D78" s="13" t="n">
+        <v>385</v>
+      </c>
+      <c r="E78" s="13" t="n">
+        <v>379.97</v>
+      </c>
+      <c r="F78" s="13" t="n">
+        <v>390.11</v>
+      </c>
       <c r="G78" s="23" t="n">
-        <v>357.76</v>
+        <v>140.5</v>
       </c>
       <c r="H78" s="24" t="n">
-        <v>380.57</v>
+        <v>223.61</v>
       </c>
       <c r="I78" s="23" t="n">
-        <v>335.09</v>
+        <v>174.89</v>
       </c>
       <c r="J78" s="23" t="n">
-        <v>401.68</v>
+        <v>114.55</v>
       </c>
       <c r="K78" s="24" t="n">
-        <v>348.4</v>
+        <v>152.37</v>
       </c>
       <c r="L78" s="23" t="n">
-        <v>342.38</v>
+        <v>91.3</v>
       </c>
       <c r="M78" s="24" t="n">
-        <v>341.2</v>
+        <v>94.42</v>
       </c>
     </row>
     <row r="79">
@@ -9698,29 +10112,35 @@
       <c r="C79" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="D79" s="13" t="n"/>
-      <c r="E79" s="13" t="n"/>
-      <c r="F79" s="13" t="n"/>
+      <c r="D79" s="13" t="n">
+        <v>385</v>
+      </c>
+      <c r="E79" s="13" t="n">
+        <v>379.97</v>
+      </c>
+      <c r="F79" s="13" t="n">
+        <v>390.11</v>
+      </c>
       <c r="G79" s="23" t="n">
-        <v>356.23</v>
+        <v>134.31</v>
       </c>
       <c r="H79" s="24" t="n">
-        <v>374.49</v>
+        <v>217.71</v>
       </c>
       <c r="I79" s="23" t="n">
-        <v>332.94</v>
+        <v>177.43</v>
       </c>
       <c r="J79" s="23" t="n">
-        <v>397.27</v>
+        <v>116.26</v>
       </c>
       <c r="K79" s="24" t="n">
-        <v>345.15</v>
+        <v>137.71</v>
       </c>
       <c r="L79" s="23" t="n">
-        <v>346.32</v>
+        <v>80.91</v>
       </c>
       <c r="M79" s="24" t="n">
-        <v>343.56</v>
+        <v>83.48999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -9733,29 +10153,35 @@
       <c r="C80" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="D80" s="13" t="n"/>
-      <c r="E80" s="13" t="n"/>
-      <c r="F80" s="13" t="n"/>
+      <c r="D80" s="13" t="n">
+        <v>385</v>
+      </c>
+      <c r="E80" s="13" t="n">
+        <v>379.97</v>
+      </c>
+      <c r="F80" s="13" t="n">
+        <v>390.11</v>
+      </c>
       <c r="G80" s="23" t="n">
-        <v>352.11</v>
+        <v>128.83</v>
       </c>
       <c r="H80" s="24" t="n">
-        <v>367.73</v>
+        <v>211.05</v>
       </c>
       <c r="I80" s="23" t="n">
-        <v>331.11</v>
+        <v>170.68</v>
       </c>
       <c r="J80" s="23" t="n">
-        <v>403.77</v>
+        <v>130.29</v>
       </c>
       <c r="K80" s="24" t="n">
-        <v>343.47</v>
+        <v>131.41</v>
       </c>
       <c r="L80" s="23" t="n">
-        <v>331.48</v>
+        <v>64.63</v>
       </c>
       <c r="M80" s="24" t="n">
-        <v>336.64</v>
+        <v>71.81999999999999</v>
       </c>
     </row>
     <row r="81">
@@ -9768,29 +10194,35 @@
       <c r="C81" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="D81" s="13" t="n"/>
-      <c r="E81" s="13" t="n"/>
-      <c r="F81" s="13" t="n"/>
+      <c r="D81" s="13" t="n">
+        <v>385</v>
+      </c>
+      <c r="E81" s="13" t="n">
+        <v>379.97</v>
+      </c>
+      <c r="F81" s="13" t="n">
+        <v>390.11</v>
+      </c>
       <c r="G81" s="23" t="n">
-        <v>354.55</v>
+        <v>133.5</v>
       </c>
       <c r="H81" s="24" t="n">
-        <v>366.83</v>
+        <v>210.2</v>
       </c>
       <c r="I81" s="23" t="n">
-        <v>329.48</v>
+        <v>175.7</v>
       </c>
       <c r="J81" s="23" t="n">
-        <v>403.6</v>
+        <v>135.73</v>
       </c>
       <c r="K81" s="24" t="n">
-        <v>343.45</v>
+        <v>126.82</v>
       </c>
       <c r="L81" s="23" t="n">
-        <v>341.55</v>
+        <v>77.7</v>
       </c>
       <c r="M81" s="24" t="n">
-        <v>343.78</v>
+        <v>81.28</v>
       </c>
     </row>
     <row r="82">
@@ -9803,29 +10235,35 @@
       <c r="C82" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D82" s="13" t="n"/>
-      <c r="E82" s="13" t="n"/>
-      <c r="F82" s="13" t="n"/>
+      <c r="D82" s="13" t="n">
+        <v>384.73</v>
+      </c>
+      <c r="E82" s="13" t="n">
+        <v>379</v>
+      </c>
+      <c r="F82" s="13" t="n">
+        <v>390.11</v>
+      </c>
       <c r="G82" s="23" t="n">
-        <v>355.68</v>
+        <v>131.61</v>
       </c>
       <c r="H82" s="24" t="n">
-        <v>362.5</v>
+        <v>205.88</v>
       </c>
       <c r="I82" s="23" t="n">
-        <v>328.67</v>
+        <v>187.09</v>
       </c>
       <c r="J82" s="23" t="n">
-        <v>401.62</v>
+        <v>130.86</v>
       </c>
       <c r="K82" s="24" t="n">
-        <v>343.2</v>
+        <v>120</v>
       </c>
       <c r="L82" s="23" t="n">
-        <v>347.78</v>
+        <v>65.25</v>
       </c>
       <c r="M82" s="24" t="n">
-        <v>351.23</v>
+        <v>86.34999999999999</v>
       </c>
     </row>
     <row r="83">
@@ -9838,29 +10276,35 @@
       <c r="C83" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D83" s="13" t="n"/>
-      <c r="E83" s="13" t="n"/>
-      <c r="F83" s="13" t="n"/>
+      <c r="D83" s="13" t="n">
+        <v>384.73</v>
+      </c>
+      <c r="E83" s="13" t="n">
+        <v>379</v>
+      </c>
+      <c r="F83" s="13" t="n">
+        <v>390.11</v>
+      </c>
       <c r="G83" s="23" t="n">
-        <v>355.96</v>
+        <v>128.94</v>
       </c>
       <c r="H83" s="24" t="n">
-        <v>368.39</v>
+        <v>211.93</v>
       </c>
       <c r="I83" s="23" t="n">
-        <v>327.9</v>
+        <v>160.65</v>
       </c>
       <c r="J83" s="23" t="n">
-        <v>406.58</v>
+        <v>126.94</v>
       </c>
       <c r="K83" s="24" t="n">
-        <v>349.99</v>
+        <v>134.47</v>
       </c>
       <c r="L83" s="23" t="n">
-        <v>342.01</v>
+        <v>64.94</v>
       </c>
       <c r="M83" s="24" t="n">
-        <v>342.41</v>
+        <v>82.39</v>
       </c>
     </row>
     <row r="84">
@@ -9873,29 +10317,35 @@
       <c r="C84" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D84" s="13" t="n"/>
-      <c r="E84" s="13" t="n"/>
-      <c r="F84" s="13" t="n"/>
+      <c r="D84" s="13" t="n">
+        <v>384.73</v>
+      </c>
+      <c r="E84" s="13" t="n">
+        <v>379</v>
+      </c>
+      <c r="F84" s="13" t="n">
+        <v>390.11</v>
+      </c>
       <c r="G84" s="23" t="n">
-        <v>358.2</v>
+        <v>135.7</v>
       </c>
       <c r="H84" s="24" t="n">
-        <v>375.6</v>
+        <v>219</v>
       </c>
       <c r="I84" s="23" t="n">
-        <v>327.91</v>
+        <v>164.65</v>
       </c>
       <c r="J84" s="23" t="n">
-        <v>394.54</v>
+        <v>123.37</v>
       </c>
       <c r="K84" s="24" t="n">
-        <v>351.64</v>
+        <v>138.51</v>
       </c>
       <c r="L84" s="23" t="n">
-        <v>349.93</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="M84" s="24" t="n">
-        <v>352.22</v>
+        <v>91.97</v>
       </c>
     </row>
     <row r="85">
@@ -9908,29 +10358,35 @@
       <c r="C85" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D85" s="13" t="n"/>
-      <c r="E85" s="13" t="n"/>
-      <c r="F85" s="13" t="n"/>
+      <c r="D85" s="13" t="n">
+        <v>384.73</v>
+      </c>
+      <c r="E85" s="13" t="n">
+        <v>379</v>
+      </c>
+      <c r="F85" s="13" t="n">
+        <v>390.11</v>
+      </c>
       <c r="G85" s="23" t="n">
-        <v>358.15</v>
+        <v>136.56</v>
       </c>
       <c r="H85" s="24" t="n">
-        <v>380.68</v>
+        <v>223.97</v>
       </c>
       <c r="I85" s="23" t="n">
-        <v>324.21</v>
+        <v>133.37</v>
       </c>
       <c r="J85" s="23" t="n">
-        <v>398.16</v>
+        <v>133.85</v>
       </c>
       <c r="K85" s="24" t="n">
-        <v>355.38</v>
+        <v>145.36</v>
       </c>
       <c r="L85" s="23" t="n">
-        <v>344.07</v>
+        <v>99.88</v>
       </c>
       <c r="M85" s="24" t="n">
-        <v>349.71</v>
+        <v>92.94</v>
       </c>
     </row>
     <row r="86">
@@ -9943,29 +10399,35 @@
       <c r="C86" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="D86" s="13" t="n"/>
-      <c r="E86" s="13" t="n"/>
-      <c r="F86" s="13" t="n"/>
+      <c r="D86" s="13" t="n">
+        <v>383.76</v>
+      </c>
+      <c r="E86" s="13" t="n">
+        <v>379</v>
+      </c>
+      <c r="F86" s="13" t="n">
+        <v>600</v>
+      </c>
       <c r="G86" s="23" t="n">
-        <v>351.12</v>
+        <v>143.36</v>
       </c>
       <c r="H86" s="24" t="n">
-        <v>386.48</v>
+        <v>229.4</v>
       </c>
       <c r="I86" s="23" t="n">
-        <v>332.24</v>
+        <v>148.86</v>
       </c>
       <c r="J86" s="23" t="n">
-        <v>406.3</v>
+        <v>141.35</v>
       </c>
       <c r="K86" s="24" t="n">
-        <v>342.42</v>
+        <v>155.59</v>
       </c>
       <c r="L86" s="23" t="n">
-        <v>333.65</v>
+        <v>94.79000000000001</v>
       </c>
       <c r="M86" s="24" t="n">
-        <v>309.56</v>
+        <v>99.44</v>
       </c>
     </row>
     <row r="87">
@@ -9978,29 +10440,35 @@
       <c r="C87" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="D87" s="13" t="n"/>
-      <c r="E87" s="13" t="n"/>
-      <c r="F87" s="13" t="n"/>
+      <c r="D87" s="13" t="n">
+        <v>383.76</v>
+      </c>
+      <c r="E87" s="13" t="n">
+        <v>379</v>
+      </c>
+      <c r="F87" s="13" t="n">
+        <v>600</v>
+      </c>
       <c r="G87" s="23" t="n">
-        <v>349.09</v>
+        <v>139.19</v>
       </c>
       <c r="H87" s="24" t="n">
-        <v>382.37</v>
+        <v>225.43</v>
       </c>
       <c r="I87" s="23" t="n">
-        <v>329.24</v>
+        <v>145.33</v>
       </c>
       <c r="J87" s="23" t="n">
-        <v>406.3</v>
+        <v>139.9</v>
       </c>
       <c r="K87" s="24" t="n">
-        <v>345.94</v>
+        <v>149.01</v>
       </c>
       <c r="L87" s="23" t="n">
-        <v>334.13</v>
+        <v>80.87</v>
       </c>
       <c r="M87" s="24" t="n">
-        <v>300.21</v>
+        <v>104.03</v>
       </c>
     </row>
     <row r="88">
@@ -10013,29 +10481,35 @@
       <c r="C88" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="D88" s="13" t="n"/>
-      <c r="E88" s="13" t="n"/>
-      <c r="F88" s="13" t="n"/>
+      <c r="D88" s="13" t="n">
+        <v>383.76</v>
+      </c>
+      <c r="E88" s="13" t="n">
+        <v>379</v>
+      </c>
+      <c r="F88" s="13" t="n">
+        <v>600</v>
+      </c>
       <c r="G88" s="23" t="n">
-        <v>348.27</v>
+        <v>137.16</v>
       </c>
       <c r="H88" s="24" t="n">
-        <v>384.57</v>
+        <v>227.59</v>
       </c>
       <c r="I88" s="23" t="n">
-        <v>326.94</v>
+        <v>146.9</v>
       </c>
       <c r="J88" s="23" t="n">
-        <v>411.19</v>
+        <v>130.21</v>
       </c>
       <c r="K88" s="24" t="n">
-        <v>349</v>
+        <v>154.49</v>
       </c>
       <c r="L88" s="23" t="n">
-        <v>330.72</v>
+        <v>74.34</v>
       </c>
       <c r="M88" s="24" t="n">
-        <v>291.18</v>
+        <v>99.15000000000001</v>
       </c>
     </row>
     <row r="89">
@@ -10048,29 +10522,35 @@
       <c r="C89" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="D89" s="13" t="n"/>
-      <c r="E89" s="13" t="n"/>
-      <c r="F89" s="13" t="n"/>
+      <c r="D89" s="13" t="n">
+        <v>383.76</v>
+      </c>
+      <c r="E89" s="13" t="n">
+        <v>379</v>
+      </c>
+      <c r="F89" s="13" t="n">
+        <v>600</v>
+      </c>
       <c r="G89" s="23" t="n">
-        <v>353.48</v>
+        <v>151.27</v>
       </c>
       <c r="H89" s="24" t="n">
-        <v>384.36</v>
+        <v>227.43</v>
       </c>
       <c r="I89" s="23" t="n">
-        <v>332.86</v>
+        <v>162.99</v>
       </c>
       <c r="J89" s="23" t="n">
-        <v>411.19</v>
+        <v>150.46</v>
       </c>
       <c r="K89" s="24" t="n">
-        <v>349.61</v>
+        <v>155.8</v>
       </c>
       <c r="L89" s="23" t="n">
-        <v>345.56</v>
+        <v>112.33</v>
       </c>
       <c r="M89" s="24" t="n">
-        <v>300.73</v>
+        <v>106.51</v>
       </c>
     </row>
     <row r="90">
@@ -10083,29 +10563,35 @@
       <c r="C90" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="D90" s="13" t="n"/>
-      <c r="E90" s="13" t="n"/>
-      <c r="F90" s="13" t="n"/>
+      <c r="D90" s="13" t="n">
+        <v>383.1</v>
+      </c>
+      <c r="E90" s="13" t="n">
+        <v>379</v>
+      </c>
+      <c r="F90" s="13" t="n">
+        <v>600</v>
+      </c>
       <c r="G90" s="23" t="n">
-        <v>358.92</v>
+        <v>155.98</v>
       </c>
       <c r="H90" s="24" t="n">
-        <v>380.64</v>
+        <v>223.85</v>
       </c>
       <c r="I90" s="23" t="n">
-        <v>337.33</v>
+        <v>192.4</v>
       </c>
       <c r="J90" s="23" t="n">
-        <v>411.19</v>
+        <v>143.13</v>
       </c>
       <c r="K90" s="24" t="n">
-        <v>353.7</v>
+        <v>160.29</v>
       </c>
       <c r="L90" s="23" t="n">
-        <v>360.31</v>
+        <v>121.91</v>
       </c>
       <c r="M90" s="24" t="n">
-        <v>312.82</v>
+        <v>100.11</v>
       </c>
     </row>
     <row r="91">
@@ -10118,29 +10604,35 @@
       <c r="C91" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="D91" s="13" t="n"/>
-      <c r="E91" s="13" t="n"/>
-      <c r="F91" s="13" t="n"/>
+      <c r="D91" s="13" t="n">
+        <v>383.1</v>
+      </c>
+      <c r="E91" s="13" t="n">
+        <v>379</v>
+      </c>
+      <c r="F91" s="13" t="n">
+        <v>600</v>
+      </c>
       <c r="G91" s="23" t="n">
-        <v>357.75</v>
+        <v>161.85</v>
       </c>
       <c r="H91" s="24" t="n">
-        <v>387.98</v>
+        <v>231.23</v>
       </c>
       <c r="I91" s="23" t="n">
-        <v>338.08</v>
+        <v>193.6</v>
       </c>
       <c r="J91" s="23" t="n">
-        <v>411.19</v>
+        <v>158.54</v>
       </c>
       <c r="K91" s="24" t="n">
-        <v>354.74</v>
+        <v>186.05</v>
       </c>
       <c r="L91" s="23" t="n">
-        <v>346.54</v>
+        <v>107.51</v>
       </c>
       <c r="M91" s="24" t="n">
-        <v>311.33</v>
+        <v>99.61</v>
       </c>
     </row>
     <row r="92">
@@ -10153,29 +10645,35 @@
       <c r="C92" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="D92" s="13" t="n"/>
-      <c r="E92" s="13" t="n"/>
-      <c r="F92" s="13" t="n"/>
+      <c r="D92" s="13" t="n">
+        <v>383.1</v>
+      </c>
+      <c r="E92" s="13" t="n">
+        <v>379</v>
+      </c>
+      <c r="F92" s="13" t="n">
+        <v>600</v>
+      </c>
       <c r="G92" s="23" t="n">
-        <v>355.35</v>
+        <v>185.38</v>
       </c>
       <c r="H92" s="24" t="n">
-        <v>394.21</v>
+        <v>238.11</v>
       </c>
       <c r="I92" s="23" t="n">
-        <v>334.23</v>
+        <v>190.73</v>
       </c>
       <c r="J92" s="23" t="n">
-        <v>412.37</v>
+        <v>210.28</v>
       </c>
       <c r="K92" s="24" t="n">
-        <v>360.22</v>
+        <v>202.04</v>
       </c>
       <c r="L92" s="23" t="n">
-        <v>329.47</v>
+        <v>145.23</v>
       </c>
       <c r="M92" s="24" t="n">
-        <v>305.97</v>
+        <v>130.03</v>
       </c>
     </row>
     <row r="93">
@@ -10188,29 +10686,35 @@
       <c r="C93" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="D93" s="13" t="n"/>
-      <c r="E93" s="13" t="n"/>
-      <c r="F93" s="13" t="n"/>
+      <c r="D93" s="13" t="n">
+        <v>383.1</v>
+      </c>
+      <c r="E93" s="13" t="n">
+        <v>379</v>
+      </c>
+      <c r="F93" s="13" t="n">
+        <v>600</v>
+      </c>
       <c r="G93" s="23" t="n">
-        <v>367.29</v>
+        <v>206.67</v>
       </c>
       <c r="H93" s="24" t="n">
-        <v>391.12</v>
+        <v>234.94</v>
       </c>
       <c r="I93" s="23" t="n">
-        <v>339.77</v>
+        <v>209.69</v>
       </c>
       <c r="J93" s="23" t="n">
-        <v>418.1</v>
+        <v>247.31</v>
       </c>
       <c r="K93" s="24" t="n">
-        <v>358.18</v>
+        <v>202.19</v>
       </c>
       <c r="L93" s="23" t="n">
-        <v>372.35</v>
+        <v>190.87</v>
       </c>
       <c r="M93" s="24" t="n">
-        <v>327.35</v>
+        <v>156.37</v>
       </c>
     </row>
     <row r="94">
@@ -10223,29 +10727,35 @@
       <c r="C94" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="D94" s="13" t="n"/>
-      <c r="E94" s="13" t="n"/>
-      <c r="F94" s="13" t="n"/>
+      <c r="D94" s="13" t="n">
+        <v>384.5</v>
+      </c>
+      <c r="E94" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F94" s="13" t="n">
+        <v>390.5</v>
+      </c>
       <c r="G94" s="23" t="n">
-        <v>378.46</v>
+        <v>237.15</v>
       </c>
       <c r="H94" s="24" t="n">
-        <v>384.34</v>
+        <v>227.43</v>
       </c>
       <c r="I94" s="23" t="n">
-        <v>339.84</v>
+        <v>245.34</v>
       </c>
       <c r="J94" s="23" t="n">
-        <v>417.03</v>
+        <v>275.1</v>
       </c>
       <c r="K94" s="24" t="n">
-        <v>366.15</v>
+        <v>216.6</v>
       </c>
       <c r="L94" s="23" t="n">
-        <v>389.43</v>
+        <v>251.49</v>
       </c>
       <c r="M94" s="24" t="n">
-        <v>375.6</v>
+        <v>204.13</v>
       </c>
     </row>
     <row r="95">
@@ -10258,29 +10768,35 @@
       <c r="C95" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="D95" s="13" t="n"/>
-      <c r="E95" s="13" t="n"/>
-      <c r="F95" s="13" t="n"/>
+      <c r="D95" s="13" t="n">
+        <v>384.5</v>
+      </c>
+      <c r="E95" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F95" s="13" t="n">
+        <v>390.5</v>
+      </c>
       <c r="G95" s="23" t="n">
-        <v>389.33</v>
+        <v>243.8</v>
       </c>
       <c r="H95" s="24" t="n">
-        <v>377.25</v>
+        <v>220.7</v>
       </c>
       <c r="I95" s="23" t="n">
-        <v>341.08</v>
+        <v>250.69</v>
       </c>
       <c r="J95" s="23" t="n">
-        <v>415.32</v>
+        <v>276.97</v>
       </c>
       <c r="K95" s="24" t="n">
-        <v>392.88</v>
+        <v>231.98</v>
       </c>
       <c r="L95" s="23" t="n">
-        <v>401.31</v>
+        <v>258.71</v>
       </c>
       <c r="M95" s="24" t="n">
-        <v>408.11</v>
+        <v>219.5</v>
       </c>
     </row>
     <row r="96">
@@ -10293,29 +10809,35 @@
       <c r="C96" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="D96" s="13" t="n"/>
-      <c r="E96" s="13" t="n"/>
-      <c r="F96" s="13" t="n"/>
+      <c r="D96" s="13" t="n">
+        <v>384.5</v>
+      </c>
+      <c r="E96" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F96" s="13" t="n">
+        <v>390.5</v>
+      </c>
       <c r="G96" s="23" t="n">
-        <v>380.11</v>
+        <v>215.1</v>
       </c>
       <c r="H96" s="24" t="n">
-        <v>360.91</v>
+        <v>204.67</v>
       </c>
       <c r="I96" s="23" t="n">
-        <v>337.62</v>
+        <v>228.86</v>
       </c>
       <c r="J96" s="23" t="n">
-        <v>413.95</v>
+        <v>230.09</v>
       </c>
       <c r="K96" s="24" t="n">
-        <v>389.79</v>
+        <v>217.18</v>
       </c>
       <c r="L96" s="23" t="n">
-        <v>390.52</v>
+        <v>220.57</v>
       </c>
       <c r="M96" s="24" t="n">
-        <v>386.43</v>
+        <v>186.29</v>
       </c>
     </row>
     <row r="97">
@@ -10330,29 +10852,35 @@
       <c r="C97" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="D97" s="13" t="n"/>
-      <c r="E97" s="13" t="n"/>
-      <c r="F97" s="13" t="n"/>
+      <c r="D97" s="13" t="n">
+        <v>384.5</v>
+      </c>
+      <c r="E97" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F97" s="13" t="n">
+        <v>390.5</v>
+      </c>
       <c r="G97" s="23" t="n">
-        <v>361.34</v>
+        <v>159.1</v>
       </c>
       <c r="H97" s="24" t="n">
-        <v>352.95</v>
+        <v>197.25</v>
       </c>
       <c r="I97" s="23" t="n">
-        <v>334.95</v>
+        <v>208.17</v>
       </c>
       <c r="J97" s="23" t="n">
-        <v>388.66</v>
+        <v>99.52</v>
       </c>
       <c r="K97" s="24" t="n">
-        <v>359.15</v>
+        <v>189.62</v>
       </c>
       <c r="L97" s="23" t="n">
-        <v>371.17</v>
+        <v>131.26</v>
       </c>
       <c r="M97" s="24" t="n">
-        <v>360.65</v>
+        <v>131.6</v>
       </c>
     </row>
   </sheetData>

--- a/forecast-results/河北电网披露及电价预估数据-20261003.xlsx
+++ b/forecast-results/河北电网披露及电价预估数据-20261003.xlsx
@@ -3764,25 +3764,25 @@
         <v>1</v>
       </c>
       <c r="D2" s="21" t="n">
-        <v>13701</v>
+        <v>13368</v>
       </c>
       <c r="E2" s="22" t="n">
-        <v>14876</v>
+        <v>11995</v>
       </c>
       <c r="F2" s="21" t="n">
-        <v>13522</v>
+        <v>13851</v>
       </c>
       <c r="G2" s="21" t="n">
-        <v>12462</v>
+        <v>13205</v>
       </c>
       <c r="H2" s="22" t="n">
-        <v>13822</v>
+        <v>13350</v>
       </c>
       <c r="I2" s="21" t="n">
-        <v>13721</v>
+        <v>14182</v>
       </c>
       <c r="J2" s="22" t="n">
-        <v>13642</v>
+        <v>13731</v>
       </c>
     </row>
     <row r="3">
@@ -3796,25 +3796,25 @@
         <v>1</v>
       </c>
       <c r="D3" s="21" t="n">
-        <v>13681</v>
+        <v>13345</v>
       </c>
       <c r="E3" s="22" t="n">
-        <v>14821</v>
+        <v>11940</v>
       </c>
       <c r="F3" s="21" t="n">
-        <v>13497</v>
+        <v>13766</v>
       </c>
       <c r="G3" s="21" t="n">
-        <v>12455</v>
+        <v>13175</v>
       </c>
       <c r="H3" s="22" t="n">
-        <v>13816</v>
+        <v>13345</v>
       </c>
       <c r="I3" s="21" t="n">
-        <v>13697</v>
+        <v>14148</v>
       </c>
       <c r="J3" s="22" t="n">
-        <v>13642</v>
+        <v>13806</v>
       </c>
     </row>
     <row r="4">
@@ -3828,25 +3828,25 @@
         <v>1</v>
       </c>
       <c r="D4" s="21" t="n">
-        <v>13568</v>
+        <v>13196</v>
       </c>
       <c r="E4" s="22" t="n">
-        <v>14745</v>
+        <v>11864</v>
       </c>
       <c r="F4" s="21" t="n">
-        <v>13476</v>
+        <v>13666</v>
       </c>
       <c r="G4" s="21" t="n">
-        <v>12343</v>
+        <v>12876</v>
       </c>
       <c r="H4" s="22" t="n">
-        <v>13678</v>
+        <v>13125</v>
       </c>
       <c r="I4" s="21" t="n">
-        <v>13586</v>
+        <v>14094</v>
       </c>
       <c r="J4" s="22" t="n">
-        <v>13416</v>
+        <v>13645</v>
       </c>
     </row>
     <row r="5">
@@ -3860,25 +3860,25 @@
         <v>1</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>13373</v>
+        <v>13059</v>
       </c>
       <c r="E5" s="22" t="n">
-        <v>14637</v>
+        <v>11756</v>
       </c>
       <c r="F5" s="21" t="n">
-        <v>13380</v>
+        <v>13571</v>
       </c>
       <c r="G5" s="21" t="n">
-        <v>11934</v>
+        <v>12847</v>
       </c>
       <c r="H5" s="22" t="n">
-        <v>13542</v>
+        <v>12959</v>
       </c>
       <c r="I5" s="21" t="n">
-        <v>13258</v>
+        <v>13765</v>
       </c>
       <c r="J5" s="22" t="n">
-        <v>13303</v>
+        <v>13549</v>
       </c>
     </row>
     <row r="6">
@@ -3892,25 +3892,25 @@
         <v>2</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>13318</v>
+        <v>12968</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>14612</v>
+        <v>11731</v>
       </c>
       <c r="F6" s="21" t="n">
-        <v>13310</v>
+        <v>13398</v>
       </c>
       <c r="G6" s="21" t="n">
-        <v>11934</v>
+        <v>12895</v>
       </c>
       <c r="H6" s="22" t="n">
-        <v>13434</v>
+        <v>12786</v>
       </c>
       <c r="I6" s="21" t="n">
-        <v>13167</v>
+        <v>13614</v>
       </c>
       <c r="J6" s="22" t="n">
-        <v>13267</v>
+        <v>13476</v>
       </c>
     </row>
     <row r="7">
@@ -3924,25 +3924,25 @@
         <v>2</v>
       </c>
       <c r="D7" s="21" t="n">
-        <v>13280</v>
+        <v>12900</v>
       </c>
       <c r="E7" s="22" t="n">
-        <v>14564</v>
+        <v>11683</v>
       </c>
       <c r="F7" s="21" t="n">
-        <v>13304</v>
+        <v>13351</v>
       </c>
       <c r="G7" s="21" t="n">
-        <v>11934</v>
+        <v>12895</v>
       </c>
       <c r="H7" s="22" t="n">
-        <v>13376</v>
+        <v>12700</v>
       </c>
       <c r="I7" s="21" t="n">
-        <v>13110</v>
+        <v>13492</v>
       </c>
       <c r="J7" s="22" t="n">
-        <v>13206</v>
+        <v>13373</v>
       </c>
     </row>
     <row r="8">
@@ -3956,25 +3956,25 @@
         <v>2</v>
       </c>
       <c r="D8" s="21" t="n">
-        <v>13248</v>
+        <v>12584</v>
       </c>
       <c r="E8" s="22" t="n">
-        <v>14450</v>
+        <v>11569</v>
       </c>
       <c r="F8" s="21" t="n">
-        <v>13251</v>
+        <v>13139</v>
       </c>
       <c r="G8" s="21" t="n">
-        <v>11941</v>
+        <v>12639</v>
       </c>
       <c r="H8" s="22" t="n">
-        <v>13235</v>
+        <v>12140</v>
       </c>
       <c r="I8" s="21" t="n">
-        <v>13154</v>
+        <v>13039</v>
       </c>
       <c r="J8" s="22" t="n">
-        <v>13276</v>
+        <v>13041</v>
       </c>
     </row>
     <row r="9">
@@ -3988,25 +3988,25 @@
         <v>2</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>13138</v>
+        <v>12333</v>
       </c>
       <c r="E9" s="22" t="n">
-        <v>14309</v>
+        <v>11428</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>13169</v>
+        <v>13022</v>
       </c>
       <c r="G9" s="21" t="n">
-        <v>11941</v>
+        <v>12639</v>
       </c>
       <c r="H9" s="22" t="n">
-        <v>13158</v>
+        <v>11899</v>
       </c>
       <c r="I9" s="21" t="n">
-        <v>13004</v>
+        <v>12588</v>
       </c>
       <c r="J9" s="22" t="n">
-        <v>13074</v>
+        <v>12480</v>
       </c>
     </row>
     <row r="10">
@@ -4020,25 +4020,25 @@
         <v>3</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>14027</v>
+        <v>13092</v>
       </c>
       <c r="E10" s="22" t="n">
-        <v>15265</v>
+        <v>12384</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>14302</v>
+        <v>13958</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>12588</v>
+        <v>13428</v>
       </c>
       <c r="H10" s="22" t="n">
-        <v>13950</v>
+        <v>13001</v>
       </c>
       <c r="I10" s="21" t="n">
-        <v>13870</v>
+        <v>13108</v>
       </c>
       <c r="J10" s="22" t="n">
-        <v>13983</v>
+        <v>12718</v>
       </c>
     </row>
     <row r="11">
@@ -4052,25 +4052,25 @@
         <v>3</v>
       </c>
       <c r="D11" s="21" t="n">
-        <v>13969</v>
+        <v>13072</v>
       </c>
       <c r="E11" s="22" t="n">
-        <v>15391</v>
+        <v>12510</v>
       </c>
       <c r="F11" s="21" t="n">
-        <v>14201</v>
+        <v>14034</v>
       </c>
       <c r="G11" s="21" t="n">
-        <v>12457</v>
+        <v>13235</v>
       </c>
       <c r="H11" s="22" t="n">
-        <v>13825</v>
+        <v>12863</v>
       </c>
       <c r="I11" s="21" t="n">
-        <v>13750</v>
+        <v>13058</v>
       </c>
       <c r="J11" s="22" t="n">
-        <v>13964</v>
+        <v>12750</v>
       </c>
     </row>
     <row r="12">
@@ -4084,25 +4084,25 @@
         <v>3</v>
       </c>
       <c r="D12" s="21" t="n">
-        <v>13874</v>
+        <v>12964</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>15301</v>
+        <v>12419</v>
       </c>
       <c r="F12" s="21" t="n">
-        <v>13996</v>
+        <v>13852</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>12457</v>
+        <v>13235</v>
       </c>
       <c r="H12" s="22" t="n">
-        <v>13700</v>
+        <v>12714</v>
       </c>
       <c r="I12" s="21" t="n">
-        <v>13674</v>
+        <v>12950</v>
       </c>
       <c r="J12" s="22" t="n">
-        <v>13901</v>
+        <v>12636</v>
       </c>
     </row>
     <row r="13">
@@ -4116,25 +4116,25 @@
         <v>3</v>
       </c>
       <c r="D13" s="21" t="n">
-        <v>13826</v>
+        <v>12878</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>15211</v>
+        <v>12330</v>
       </c>
       <c r="F13" s="21" t="n">
-        <v>13776</v>
+        <v>13604</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>12435</v>
+        <v>13127</v>
       </c>
       <c r="H13" s="22" t="n">
-        <v>13725</v>
+        <v>12712</v>
       </c>
       <c r="I13" s="21" t="n">
-        <v>13646</v>
+        <v>12851</v>
       </c>
       <c r="J13" s="22" t="n">
-        <v>13961</v>
+        <v>12674</v>
       </c>
     </row>
     <row r="14">
@@ -4148,25 +4148,25 @@
         <v>4</v>
       </c>
       <c r="D14" s="21" t="n">
-        <v>13814</v>
+        <v>12878</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>15225</v>
+        <v>12344</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>13751</v>
+        <v>13639</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>12461</v>
+        <v>13127</v>
       </c>
       <c r="H14" s="22" t="n">
-        <v>13590</v>
+        <v>12622</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>13650</v>
+        <v>12865</v>
       </c>
       <c r="J14" s="22" t="n">
-        <v>14000</v>
+        <v>12694</v>
       </c>
     </row>
     <row r="15">
@@ -4180,25 +4180,25 @@
         <v>4</v>
       </c>
       <c r="D15" s="21" t="n">
-        <v>13776</v>
+        <v>12880</v>
       </c>
       <c r="E15" s="22" t="n">
-        <v>15203</v>
+        <v>12322</v>
       </c>
       <c r="F15" s="21" t="n">
-        <v>13579</v>
+        <v>13533</v>
       </c>
       <c r="G15" s="21" t="n">
-        <v>12475</v>
+        <v>13174</v>
       </c>
       <c r="H15" s="22" t="n">
-        <v>13618</v>
+        <v>12695</v>
       </c>
       <c r="I15" s="21" t="n">
-        <v>13631</v>
+        <v>12928</v>
       </c>
       <c r="J15" s="22" t="n">
-        <v>13954</v>
+        <v>12663</v>
       </c>
     </row>
     <row r="16">
@@ -4212,25 +4212,25 @@
         <v>4</v>
       </c>
       <c r="D16" s="21" t="n">
-        <v>13704</v>
+        <v>12820</v>
       </c>
       <c r="E16" s="22" t="n">
-        <v>15132</v>
+        <v>12251</v>
       </c>
       <c r="F16" s="21" t="n">
-        <v>13476</v>
+        <v>13558</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>12380</v>
+        <v>12895</v>
       </c>
       <c r="H16" s="22" t="n">
-        <v>13604</v>
+        <v>12650</v>
       </c>
       <c r="I16" s="21" t="n">
-        <v>13604</v>
+        <v>12842</v>
       </c>
       <c r="J16" s="22" t="n">
-        <v>13832</v>
+        <v>12745</v>
       </c>
     </row>
     <row r="17">
@@ -4244,25 +4244,25 @@
         <v>4</v>
       </c>
       <c r="D17" s="21" t="n">
-        <v>13540</v>
+        <v>12734</v>
       </c>
       <c r="E17" s="22" t="n">
-        <v>15036</v>
+        <v>12155</v>
       </c>
       <c r="F17" s="21" t="n">
-        <v>13495</v>
+        <v>13549</v>
       </c>
       <c r="G17" s="21" t="n">
-        <v>11949</v>
+        <v>12847</v>
       </c>
       <c r="H17" s="22" t="n">
-        <v>13481</v>
+        <v>12497</v>
       </c>
       <c r="I17" s="21" t="n">
-        <v>13348</v>
+        <v>12725</v>
       </c>
       <c r="J17" s="22" t="n">
-        <v>13711</v>
+        <v>12650</v>
       </c>
     </row>
     <row r="18">
@@ -4276,25 +4276,25 @@
         <v>5</v>
       </c>
       <c r="D18" s="21" t="n">
-        <v>13465</v>
+        <v>12659</v>
       </c>
       <c r="E18" s="22" t="n">
-        <v>15008</v>
+        <v>12127</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>13337</v>
+        <v>13442</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>11949</v>
+        <v>12895</v>
       </c>
       <c r="H18" s="22" t="n">
-        <v>13361</v>
+        <v>12352</v>
       </c>
       <c r="I18" s="21" t="n">
-        <v>13253</v>
+        <v>12615</v>
       </c>
       <c r="J18" s="22" t="n">
-        <v>13658</v>
+        <v>12542</v>
       </c>
     </row>
     <row r="19">
@@ -4308,25 +4308,25 @@
         <v>5</v>
       </c>
       <c r="D19" s="21" t="n">
-        <v>13452</v>
+        <v>12596</v>
       </c>
       <c r="E19" s="22" t="n">
-        <v>14932</v>
+        <v>12051</v>
       </c>
       <c r="F19" s="21" t="n">
-        <v>13326</v>
+        <v>13365</v>
       </c>
       <c r="G19" s="21" t="n">
-        <v>11965</v>
+        <v>12862</v>
       </c>
       <c r="H19" s="22" t="n">
-        <v>13315</v>
+        <v>12248</v>
       </c>
       <c r="I19" s="21" t="n">
-        <v>13271</v>
+        <v>12569</v>
       </c>
       <c r="J19" s="22" t="n">
-        <v>13691</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="20">
@@ -4340,25 +4340,25 @@
         <v>5</v>
       </c>
       <c r="D20" s="21" t="n">
-        <v>13400</v>
+        <v>12541</v>
       </c>
       <c r="E20" s="22" t="n">
-        <v>14884</v>
+        <v>12002</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>13294</v>
+        <v>13332</v>
       </c>
       <c r="G20" s="21" t="n">
-        <v>11932</v>
+        <v>12840</v>
       </c>
       <c r="H20" s="22" t="n">
-        <v>13185</v>
+        <v>12096</v>
       </c>
       <c r="I20" s="21" t="n">
-        <v>13243</v>
+        <v>12561</v>
       </c>
       <c r="J20" s="22" t="n">
-        <v>13646</v>
+        <v>12431</v>
       </c>
     </row>
     <row r="21">
@@ -4372,25 +4372,25 @@
         <v>5</v>
       </c>
       <c r="D21" s="21" t="n">
-        <v>13359</v>
+        <v>12481</v>
       </c>
       <c r="E21" s="22" t="n">
-        <v>14840</v>
+        <v>11959</v>
       </c>
       <c r="F21" s="21" t="n">
-        <v>13289</v>
+        <v>13275</v>
       </c>
       <c r="G21" s="21" t="n">
-        <v>11885</v>
+        <v>12642</v>
       </c>
       <c r="H21" s="22" t="n">
-        <v>13169</v>
+        <v>12014</v>
       </c>
       <c r="I21" s="21" t="n">
-        <v>13184</v>
+        <v>12545</v>
       </c>
       <c r="J21" s="22" t="n">
-        <v>13570</v>
+        <v>12459</v>
       </c>
     </row>
     <row r="22">
@@ -4404,25 +4404,25 @@
         <v>6</v>
       </c>
       <c r="D22" s="21" t="n">
-        <v>13358</v>
+        <v>12468</v>
       </c>
       <c r="E22" s="22" t="n">
-        <v>14871</v>
+        <v>11989</v>
       </c>
       <c r="F22" s="21" t="n">
-        <v>13309</v>
+        <v>13239</v>
       </c>
       <c r="G22" s="21" t="n">
-        <v>11885</v>
+        <v>12642</v>
       </c>
       <c r="H22" s="22" t="n">
-        <v>13109</v>
+        <v>11918</v>
       </c>
       <c r="I22" s="21" t="n">
-        <v>13194</v>
+        <v>12565</v>
       </c>
       <c r="J22" s="22" t="n">
-        <v>13558</v>
+        <v>12456</v>
       </c>
     </row>
     <row r="23">
@@ -4436,25 +4436,25 @@
         <v>6</v>
       </c>
       <c r="D23" s="21" t="n">
-        <v>13360</v>
+        <v>12456</v>
       </c>
       <c r="E23" s="22" t="n">
-        <v>14840</v>
+        <v>11959</v>
       </c>
       <c r="F23" s="21" t="n">
-        <v>13382</v>
+        <v>13270</v>
       </c>
       <c r="G23" s="21" t="n">
-        <v>11885</v>
+        <v>12642</v>
       </c>
       <c r="H23" s="22" t="n">
-        <v>13108</v>
+        <v>11819</v>
       </c>
       <c r="I23" s="21" t="n">
-        <v>13176</v>
+        <v>12583</v>
       </c>
       <c r="J23" s="22" t="n">
-        <v>13544</v>
+        <v>12464</v>
       </c>
     </row>
     <row r="24">
@@ -4468,25 +4468,25 @@
         <v>6</v>
       </c>
       <c r="D24" s="21" t="n">
-        <v>13347</v>
+        <v>12448</v>
       </c>
       <c r="E24" s="22" t="n">
-        <v>14823</v>
+        <v>11942</v>
       </c>
       <c r="F24" s="21" t="n">
-        <v>13348</v>
+        <v>13236</v>
       </c>
       <c r="G24" s="21" t="n">
-        <v>11885</v>
+        <v>12642</v>
       </c>
       <c r="H24" s="22" t="n">
-        <v>13107</v>
+        <v>11868</v>
       </c>
       <c r="I24" s="21" t="n">
-        <v>13171</v>
+        <v>12524</v>
       </c>
       <c r="J24" s="22" t="n">
-        <v>13526</v>
+        <v>12477</v>
       </c>
     </row>
     <row r="25">
@@ -4500,25 +4500,25 @@
         <v>6</v>
       </c>
       <c r="D25" s="21" t="n">
-        <v>13345</v>
+        <v>12437</v>
       </c>
       <c r="E25" s="22" t="n">
-        <v>14807</v>
+        <v>11926</v>
       </c>
       <c r="F25" s="21" t="n">
-        <v>13358</v>
+        <v>13202</v>
       </c>
       <c r="G25" s="21" t="n">
-        <v>11885</v>
+        <v>12642</v>
       </c>
       <c r="H25" s="22" t="n">
-        <v>13110</v>
+        <v>11860</v>
       </c>
       <c r="I25" s="21" t="n">
-        <v>13176</v>
+        <v>12545</v>
       </c>
       <c r="J25" s="22" t="n">
-        <v>13512</v>
+        <v>12453</v>
       </c>
     </row>
     <row r="26">
@@ -4532,25 +4532,25 @@
         <v>7</v>
       </c>
       <c r="D26" s="21" t="n">
-        <v>13267</v>
+        <v>12503</v>
       </c>
       <c r="E26" s="22" t="n">
-        <v>14392</v>
+        <v>11510</v>
       </c>
       <c r="F26" s="21" t="n">
-        <v>13367</v>
+        <v>13260</v>
       </c>
       <c r="G26" s="21" t="n">
-        <v>11943</v>
+        <v>12773</v>
       </c>
       <c r="H26" s="22" t="n">
-        <v>13219</v>
+        <v>12386</v>
       </c>
       <c r="I26" s="21" t="n">
-        <v>13095</v>
+        <v>12649</v>
       </c>
       <c r="J26" s="22" t="n">
-        <v>13407</v>
+        <v>12513</v>
       </c>
     </row>
     <row r="27">
@@ -4564,25 +4564,25 @@
         <v>7</v>
       </c>
       <c r="D27" s="21" t="n">
-        <v>13254</v>
+        <v>12468</v>
       </c>
       <c r="E27" s="22" t="n">
-        <v>14355</v>
+        <v>11474</v>
       </c>
       <c r="F27" s="21" t="n">
-        <v>13120</v>
+        <v>13156</v>
       </c>
       <c r="G27" s="21" t="n">
-        <v>12159</v>
+        <v>12644</v>
       </c>
       <c r="H27" s="22" t="n">
-        <v>13352</v>
+        <v>12557</v>
       </c>
       <c r="I27" s="21" t="n">
-        <v>13038</v>
+        <v>12505</v>
       </c>
       <c r="J27" s="22" t="n">
-        <v>13351</v>
+        <v>12553</v>
       </c>
     </row>
     <row r="28">
@@ -4596,25 +4596,25 @@
         <v>7</v>
       </c>
       <c r="D28" s="21" t="n">
-        <v>13045</v>
+        <v>12197</v>
       </c>
       <c r="E28" s="22" t="n">
-        <v>14195</v>
+        <v>11314</v>
       </c>
       <c r="F28" s="21" t="n">
-        <v>12823</v>
+        <v>12630</v>
       </c>
       <c r="G28" s="21" t="n">
-        <v>11863</v>
+        <v>12651</v>
       </c>
       <c r="H28" s="22" t="n">
-        <v>13139</v>
+        <v>12157</v>
       </c>
       <c r="I28" s="21" t="n">
-        <v>12844</v>
+        <v>12367</v>
       </c>
       <c r="J28" s="22" t="n">
-        <v>13249</v>
+        <v>12154</v>
       </c>
     </row>
     <row r="29">
@@ -4628,25 +4628,25 @@
         <v>7</v>
       </c>
       <c r="D29" s="21" t="n">
-        <v>12806</v>
+        <v>11612</v>
       </c>
       <c r="E29" s="22" t="n">
-        <v>13867</v>
+        <v>10986</v>
       </c>
       <c r="F29" s="21" t="n">
-        <v>12658</v>
+        <v>11968</v>
       </c>
       <c r="G29" s="21" t="n">
-        <v>11889</v>
+        <v>11813</v>
       </c>
       <c r="H29" s="22" t="n">
-        <v>12820</v>
+        <v>11668</v>
       </c>
       <c r="I29" s="21" t="n">
-        <v>12485</v>
+        <v>11736</v>
       </c>
       <c r="J29" s="22" t="n">
-        <v>12978</v>
+        <v>11559</v>
       </c>
     </row>
     <row r="30">
@@ -4660,25 +4660,25 @@
         <v>8</v>
       </c>
       <c r="D30" s="21" t="n">
-        <v>12565</v>
+        <v>11221</v>
       </c>
       <c r="E30" s="22" t="n">
-        <v>13480</v>
+        <v>10599</v>
       </c>
       <c r="F30" s="21" t="n">
-        <v>12515</v>
+        <v>11779</v>
       </c>
       <c r="G30" s="21" t="n">
-        <v>11837</v>
+        <v>11367</v>
       </c>
       <c r="H30" s="22" t="n">
-        <v>12450</v>
+        <v>11015</v>
       </c>
       <c r="I30" s="21" t="n">
-        <v>12242</v>
+        <v>11402</v>
       </c>
       <c r="J30" s="22" t="n">
-        <v>12737</v>
+        <v>11202</v>
       </c>
     </row>
     <row r="31">
@@ -4692,25 +4692,25 @@
         <v>8</v>
       </c>
       <c r="D31" s="21" t="n">
-        <v>12088</v>
+        <v>10416</v>
       </c>
       <c r="E31" s="22" t="n">
-        <v>12937</v>
+        <v>10056</v>
       </c>
       <c r="F31" s="21" t="n">
-        <v>11974</v>
+        <v>11137</v>
       </c>
       <c r="G31" s="21" t="n">
-        <v>11476</v>
+        <v>10768</v>
       </c>
       <c r="H31" s="22" t="n">
-        <v>12115</v>
+        <v>10131</v>
       </c>
       <c r="I31" s="21" t="n">
-        <v>11706</v>
+        <v>10189</v>
       </c>
       <c r="J31" s="22" t="n">
-        <v>12213</v>
+        <v>10226</v>
       </c>
     </row>
     <row r="32">
@@ -4724,25 +4724,25 @@
         <v>8</v>
       </c>
       <c r="D32" s="21" t="n">
-        <v>11150</v>
+        <v>9093</v>
       </c>
       <c r="E32" s="22" t="n">
-        <v>12270</v>
+        <v>9389</v>
       </c>
       <c r="F32" s="21" t="n">
-        <v>10912</v>
+        <v>9723</v>
       </c>
       <c r="G32" s="21" t="n">
-        <v>10839</v>
+        <v>9562</v>
       </c>
       <c r="H32" s="22" t="n">
-        <v>11193</v>
+        <v>8802</v>
       </c>
       <c r="I32" s="21" t="n">
-        <v>10603</v>
+        <v>8520</v>
       </c>
       <c r="J32" s="22" t="n">
-        <v>10967</v>
+        <v>8516</v>
       </c>
     </row>
     <row r="33">
@@ -4756,25 +4756,25 @@
         <v>8</v>
       </c>
       <c r="D33" s="21" t="n">
-        <v>10701</v>
+        <v>8306</v>
       </c>
       <c r="E33" s="22" t="n">
-        <v>11509</v>
+        <v>8627</v>
       </c>
       <c r="F33" s="21" t="n">
-        <v>10553</v>
+        <v>8786</v>
       </c>
       <c r="G33" s="21" t="n">
-        <v>10485</v>
+        <v>8944</v>
       </c>
       <c r="H33" s="22" t="n">
-        <v>10720</v>
+        <v>7912</v>
       </c>
       <c r="I33" s="21" t="n">
-        <v>10312</v>
+        <v>7715</v>
       </c>
       <c r="J33" s="22" t="n">
-        <v>10544</v>
+        <v>7812</v>
       </c>
     </row>
     <row r="34">
@@ -4788,25 +4788,25 @@
         <v>9</v>
       </c>
       <c r="D34" s="21" t="n">
-        <v>10295</v>
+        <v>7367</v>
       </c>
       <c r="E34" s="22" t="n">
-        <v>10857</v>
+        <v>7976</v>
       </c>
       <c r="F34" s="21" t="n">
-        <v>10443</v>
+        <v>7587</v>
       </c>
       <c r="G34" s="21" t="n">
-        <v>9816</v>
+        <v>7569</v>
       </c>
       <c r="H34" s="22" t="n">
-        <v>10485</v>
+        <v>7453</v>
       </c>
       <c r="I34" s="21" t="n">
-        <v>9892</v>
+        <v>6730</v>
       </c>
       <c r="J34" s="22" t="n">
-        <v>10200</v>
+        <v>6834</v>
       </c>
     </row>
     <row r="35">
@@ -4820,25 +4820,25 @@
         <v>9</v>
       </c>
       <c r="D35" s="21" t="n">
-        <v>10055</v>
+        <v>7068</v>
       </c>
       <c r="E35" s="22" t="n">
-        <v>10214</v>
+        <v>7333</v>
       </c>
       <c r="F35" s="21" t="n">
-        <v>10396</v>
+        <v>7467</v>
       </c>
       <c r="G35" s="21" t="n">
-        <v>9543</v>
+        <v>7407</v>
       </c>
       <c r="H35" s="22" t="n">
-        <v>10416</v>
+        <v>7039</v>
       </c>
       <c r="I35" s="21" t="n">
-        <v>9753</v>
+        <v>6486</v>
       </c>
       <c r="J35" s="22" t="n">
-        <v>9965</v>
+        <v>6647</v>
       </c>
     </row>
     <row r="36">
@@ -4852,25 +4852,25 @@
         <v>9</v>
       </c>
       <c r="D36" s="21" t="n">
-        <v>9884</v>
+        <v>6929</v>
       </c>
       <c r="E36" s="22" t="n">
-        <v>9582</v>
+        <v>6701</v>
       </c>
       <c r="F36" s="21" t="n">
-        <v>10233</v>
+        <v>7474</v>
       </c>
       <c r="G36" s="21" t="n">
-        <v>9478</v>
+        <v>7306</v>
       </c>
       <c r="H36" s="22" t="n">
-        <v>10379</v>
+        <v>6930</v>
       </c>
       <c r="I36" s="21" t="n">
-        <v>9706</v>
+        <v>6482</v>
       </c>
       <c r="J36" s="22" t="n">
-        <v>9940</v>
+        <v>6695</v>
       </c>
     </row>
     <row r="37">
@@ -4884,25 +4884,25 @@
         <v>9</v>
       </c>
       <c r="D37" s="21" t="n">
-        <v>9743</v>
+        <v>6689</v>
       </c>
       <c r="E37" s="22" t="n">
-        <v>8984</v>
+        <v>6103</v>
       </c>
       <c r="F37" s="21" t="n">
-        <v>10178</v>
+        <v>7310</v>
       </c>
       <c r="G37" s="21" t="n">
-        <v>9468</v>
+        <v>7276</v>
       </c>
       <c r="H37" s="22" t="n">
-        <v>10299</v>
+        <v>6361</v>
       </c>
       <c r="I37" s="21" t="n">
-        <v>9683</v>
+        <v>6506</v>
       </c>
       <c r="J37" s="22" t="n">
-        <v>9908</v>
+        <v>6625</v>
       </c>
     </row>
     <row r="38">
@@ -4916,25 +4916,25 @@
         <v>10</v>
       </c>
       <c r="D38" s="21" t="n">
-        <v>9631</v>
+        <v>6579</v>
       </c>
       <c r="E38" s="22" t="n">
-        <v>8524</v>
+        <v>5643</v>
       </c>
       <c r="F38" s="21" t="n">
-        <v>9986</v>
+        <v>7182</v>
       </c>
       <c r="G38" s="21" t="n">
-        <v>9468</v>
+        <v>7197</v>
       </c>
       <c r="H38" s="22" t="n">
-        <v>10256</v>
+        <v>6238</v>
       </c>
       <c r="I38" s="21" t="n">
-        <v>9742</v>
+        <v>6563</v>
       </c>
       <c r="J38" s="22" t="n">
-        <v>9919</v>
+        <v>6732</v>
       </c>
     </row>
     <row r="39">
@@ -4948,25 +4948,25 @@
         <v>10</v>
       </c>
       <c r="D39" s="21" t="n">
-        <v>9520</v>
+        <v>6493</v>
       </c>
       <c r="E39" s="22" t="n">
-        <v>8060</v>
+        <v>5179</v>
       </c>
       <c r="F39" s="21" t="n">
-        <v>9935</v>
+        <v>7192</v>
       </c>
       <c r="G39" s="21" t="n">
-        <v>9458</v>
+        <v>7180</v>
       </c>
       <c r="H39" s="22" t="n">
-        <v>10271</v>
+        <v>6235</v>
       </c>
       <c r="I39" s="21" t="n">
-        <v>9655</v>
+        <v>6556</v>
       </c>
       <c r="J39" s="22" t="n">
-        <v>9892</v>
+        <v>6740</v>
       </c>
     </row>
     <row r="40">
@@ -4980,25 +4980,25 @@
         <v>10</v>
       </c>
       <c r="D40" s="21" t="n">
-        <v>9425</v>
+        <v>6407</v>
       </c>
       <c r="E40" s="22" t="n">
-        <v>7653</v>
+        <v>4771</v>
       </c>
       <c r="F40" s="21" t="n">
-        <v>9923</v>
+        <v>7167</v>
       </c>
       <c r="G40" s="21" t="n">
-        <v>9458</v>
+        <v>7158</v>
       </c>
       <c r="H40" s="22" t="n">
-        <v>10249</v>
+        <v>6238</v>
       </c>
       <c r="I40" s="21" t="n">
-        <v>9629</v>
+        <v>6549</v>
       </c>
       <c r="J40" s="22" t="n">
-        <v>9820</v>
+        <v>6713</v>
       </c>
     </row>
     <row r="41">
@@ -5012,25 +5012,25 @@
         <v>10</v>
       </c>
       <c r="D41" s="21" t="n">
-        <v>9325</v>
+        <v>6341</v>
       </c>
       <c r="E41" s="22" t="n">
-        <v>7309</v>
+        <v>4428</v>
       </c>
       <c r="F41" s="21" t="n">
-        <v>9806</v>
+        <v>7163</v>
       </c>
       <c r="G41" s="21" t="n">
-        <v>9458</v>
+        <v>7133</v>
       </c>
       <c r="H41" s="22" t="n">
-        <v>10249</v>
+        <v>6248</v>
       </c>
       <c r="I41" s="21" t="n">
-        <v>9569</v>
+        <v>6544</v>
       </c>
       <c r="J41" s="22" t="n">
-        <v>9776</v>
+        <v>6714</v>
       </c>
     </row>
     <row r="42">
@@ -5044,25 +5044,25 @@
         <v>11</v>
       </c>
       <c r="D42" s="21" t="n">
-        <v>9270</v>
+        <v>6306</v>
       </c>
       <c r="E42" s="22" t="n">
-        <v>7076</v>
+        <v>4195</v>
       </c>
       <c r="F42" s="21" t="n">
-        <v>9741</v>
+        <v>7163</v>
       </c>
       <c r="G42" s="21" t="n">
-        <v>9458</v>
+        <v>7128</v>
       </c>
       <c r="H42" s="22" t="n">
-        <v>10270</v>
+        <v>6282</v>
       </c>
       <c r="I42" s="21" t="n">
-        <v>9579</v>
+        <v>6545</v>
       </c>
       <c r="J42" s="22" t="n">
-        <v>9733</v>
+        <v>6731</v>
       </c>
     </row>
     <row r="43">
@@ -5076,25 +5076,25 @@
         <v>11</v>
       </c>
       <c r="D43" s="21" t="n">
-        <v>9214</v>
+        <v>6257</v>
       </c>
       <c r="E43" s="22" t="n">
-        <v>6781</v>
+        <v>3900</v>
       </c>
       <c r="F43" s="21" t="n">
-        <v>9744</v>
+        <v>7160</v>
       </c>
       <c r="G43" s="21" t="n">
-        <v>9458</v>
+        <v>7128</v>
       </c>
       <c r="H43" s="22" t="n">
-        <v>10240</v>
+        <v>6285</v>
       </c>
       <c r="I43" s="21" t="n">
-        <v>9601</v>
+        <v>6571</v>
       </c>
       <c r="J43" s="22" t="n">
-        <v>9722</v>
+        <v>6733</v>
       </c>
     </row>
     <row r="44">
@@ -5108,25 +5108,25 @@
         <v>11</v>
       </c>
       <c r="D44" s="21" t="n">
-        <v>9163</v>
+        <v>6227</v>
       </c>
       <c r="E44" s="22" t="n">
-        <v>6575</v>
+        <v>3694</v>
       </c>
       <c r="F44" s="21" t="n">
-        <v>9717</v>
+        <v>7165</v>
       </c>
       <c r="G44" s="21" t="n">
-        <v>9458</v>
+        <v>7128</v>
       </c>
       <c r="H44" s="22" t="n">
-        <v>10250</v>
+        <v>6298</v>
       </c>
       <c r="I44" s="21" t="n">
-        <v>9601</v>
+        <v>6568</v>
       </c>
       <c r="J44" s="22" t="n">
-        <v>9662</v>
+        <v>6762</v>
       </c>
     </row>
     <row r="45">
@@ -5140,25 +5140,25 @@
         <v>11</v>
       </c>
       <c r="D45" s="21" t="n">
-        <v>9142</v>
+        <v>6209</v>
       </c>
       <c r="E45" s="22" t="n">
-        <v>6545</v>
+        <v>3664</v>
       </c>
       <c r="F45" s="21" t="n">
-        <v>9693</v>
+        <v>7131</v>
       </c>
       <c r="G45" s="21" t="n">
-        <v>9458</v>
+        <v>7122</v>
       </c>
       <c r="H45" s="22" t="n">
-        <v>10239</v>
+        <v>6297</v>
       </c>
       <c r="I45" s="21" t="n">
-        <v>9571</v>
+        <v>6561</v>
       </c>
       <c r="J45" s="22" t="n">
-        <v>9629</v>
+        <v>6731</v>
       </c>
     </row>
     <row r="46">
@@ -5172,25 +5172,25 @@
         <v>12</v>
       </c>
       <c r="D46" s="21" t="n">
-        <v>9245</v>
+        <v>6315</v>
       </c>
       <c r="E46" s="22" t="n">
-        <v>7206</v>
+        <v>4324</v>
       </c>
       <c r="F46" s="21" t="n">
-        <v>9641</v>
+        <v>7132</v>
       </c>
       <c r="G46" s="21" t="n">
-        <v>9465</v>
+        <v>7150</v>
       </c>
       <c r="H46" s="22" t="n">
-        <v>10295</v>
+        <v>6341</v>
       </c>
       <c r="I46" s="21" t="n">
-        <v>9498</v>
+        <v>6470</v>
       </c>
       <c r="J46" s="22" t="n">
-        <v>9598</v>
+        <v>6671</v>
       </c>
     </row>
     <row r="47">
@@ -5204,25 +5204,25 @@
         <v>12</v>
       </c>
       <c r="D47" s="21" t="n">
-        <v>9249</v>
+        <v>6321</v>
       </c>
       <c r="E47" s="22" t="n">
-        <v>7218</v>
+        <v>4337</v>
       </c>
       <c r="F47" s="21" t="n">
-        <v>9648</v>
+        <v>7144</v>
       </c>
       <c r="G47" s="21" t="n">
-        <v>9458</v>
+        <v>7133</v>
       </c>
       <c r="H47" s="22" t="n">
-        <v>10197</v>
+        <v>6269</v>
       </c>
       <c r="I47" s="21" t="n">
-        <v>9561</v>
+        <v>6570</v>
       </c>
       <c r="J47" s="22" t="n">
-        <v>9640</v>
+        <v>6670</v>
       </c>
     </row>
     <row r="48">
@@ -5236,25 +5236,25 @@
         <v>12</v>
       </c>
       <c r="D48" s="21" t="n">
-        <v>9255</v>
+        <v>6293</v>
       </c>
       <c r="E48" s="22" t="n">
-        <v>7110</v>
+        <v>4229</v>
       </c>
       <c r="F48" s="21" t="n">
-        <v>9680</v>
+        <v>7131</v>
       </c>
       <c r="G48" s="21" t="n">
-        <v>9458</v>
+        <v>7133</v>
       </c>
       <c r="H48" s="22" t="n">
-        <v>10241</v>
+        <v>6245</v>
       </c>
       <c r="I48" s="21" t="n">
-        <v>9587</v>
+        <v>6538</v>
       </c>
       <c r="J48" s="22" t="n">
-        <v>9693</v>
+        <v>6687</v>
       </c>
     </row>
     <row r="49">
@@ -5268,25 +5268,25 @@
         <v>12</v>
       </c>
       <c r="D49" s="21" t="n">
-        <v>9199</v>
+        <v>6218</v>
       </c>
       <c r="E49" s="22" t="n">
-        <v>6740</v>
+        <v>3859</v>
       </c>
       <c r="F49" s="21" t="n">
-        <v>9663</v>
+        <v>7064</v>
       </c>
       <c r="G49" s="21" t="n">
-        <v>9479</v>
+        <v>7130</v>
       </c>
       <c r="H49" s="22" t="n">
-        <v>10269</v>
+        <v>6277</v>
       </c>
       <c r="I49" s="21" t="n">
-        <v>9633</v>
+        <v>6545</v>
       </c>
       <c r="J49" s="22" t="n">
-        <v>9684</v>
+        <v>6675</v>
       </c>
     </row>
     <row r="50">
@@ -5300,25 +5300,25 @@
         <v>13</v>
       </c>
       <c r="D50" s="21" t="n">
-        <v>9179</v>
+        <v>6197</v>
       </c>
       <c r="E50" s="22" t="n">
-        <v>6610</v>
+        <v>3729</v>
       </c>
       <c r="F50" s="21" t="n">
-        <v>9688</v>
+        <v>6982</v>
       </c>
       <c r="G50" s="21" t="n">
-        <v>9508</v>
+        <v>7104</v>
       </c>
       <c r="H50" s="22" t="n">
-        <v>10157</v>
+        <v>6202</v>
       </c>
       <c r="I50" s="21" t="n">
-        <v>9635</v>
+        <v>6692</v>
       </c>
       <c r="J50" s="22" t="n">
-        <v>9756</v>
+        <v>6725</v>
       </c>
     </row>
     <row r="51">
@@ -5332,25 +5332,25 @@
         <v>13</v>
       </c>
       <c r="D51" s="21" t="n">
-        <v>9184</v>
+        <v>6199</v>
       </c>
       <c r="E51" s="22" t="n">
-        <v>6548</v>
+        <v>3667</v>
       </c>
       <c r="F51" s="21" t="n">
-        <v>9687</v>
+        <v>6959</v>
       </c>
       <c r="G51" s="21" t="n">
-        <v>9508</v>
+        <v>7104</v>
       </c>
       <c r="H51" s="22" t="n">
-        <v>10235</v>
+        <v>6287</v>
       </c>
       <c r="I51" s="21" t="n">
-        <v>9629</v>
+        <v>6691</v>
       </c>
       <c r="J51" s="22" t="n">
-        <v>9784</v>
+        <v>6748</v>
       </c>
     </row>
     <row r="52">
@@ -5364,25 +5364,25 @@
         <v>13</v>
       </c>
       <c r="D52" s="21" t="n">
-        <v>9159</v>
+        <v>6181</v>
       </c>
       <c r="E52" s="22" t="n">
-        <v>6550</v>
+        <v>3669</v>
       </c>
       <c r="F52" s="21" t="n">
-        <v>9697</v>
+        <v>6980</v>
       </c>
       <c r="G52" s="21" t="n">
-        <v>9508</v>
+        <v>7104</v>
       </c>
       <c r="H52" s="22" t="n">
-        <v>10147</v>
+        <v>6197</v>
       </c>
       <c r="I52" s="21" t="n">
-        <v>9603</v>
+        <v>6682</v>
       </c>
       <c r="J52" s="22" t="n">
-        <v>9733</v>
+        <v>6707</v>
       </c>
     </row>
     <row r="53">
@@ -5396,25 +5396,25 @@
         <v>13</v>
       </c>
       <c r="D53" s="21" t="n">
-        <v>9162</v>
+        <v>6193</v>
       </c>
       <c r="E53" s="22" t="n">
-        <v>6705</v>
+        <v>3823</v>
       </c>
       <c r="F53" s="21" t="n">
-        <v>9655</v>
+        <v>6997</v>
       </c>
       <c r="G53" s="21" t="n">
-        <v>9515</v>
+        <v>7104</v>
       </c>
       <c r="H53" s="22" t="n">
-        <v>10140</v>
+        <v>6190</v>
       </c>
       <c r="I53" s="21" t="n">
-        <v>9521</v>
+        <v>6580</v>
       </c>
       <c r="J53" s="22" t="n">
-        <v>9704</v>
+        <v>6703</v>
       </c>
     </row>
     <row r="54">
@@ -5428,25 +5428,25 @@
         <v>14</v>
       </c>
       <c r="D54" s="21" t="n">
-        <v>9218</v>
+        <v>6244</v>
       </c>
       <c r="E54" s="22" t="n">
-        <v>6925</v>
+        <v>4044</v>
       </c>
       <c r="F54" s="21" t="n">
-        <v>9751</v>
+        <v>7000</v>
       </c>
       <c r="G54" s="21" t="n">
-        <v>9508</v>
+        <v>7104</v>
       </c>
       <c r="H54" s="22" t="n">
-        <v>10128</v>
+        <v>6191</v>
       </c>
       <c r="I54" s="21" t="n">
-        <v>9550</v>
+        <v>6631</v>
       </c>
       <c r="J54" s="22" t="n">
-        <v>9696</v>
+        <v>6716</v>
       </c>
     </row>
     <row r="55">
@@ -5460,25 +5460,25 @@
         <v>14</v>
       </c>
       <c r="D55" s="21" t="n">
-        <v>9239</v>
+        <v>6275</v>
       </c>
       <c r="E55" s="22" t="n">
-        <v>7120</v>
+        <v>4239</v>
       </c>
       <c r="F55" s="21" t="n">
-        <v>9729</v>
+        <v>7022</v>
       </c>
       <c r="G55" s="21" t="n">
-        <v>9504</v>
+        <v>7104</v>
       </c>
       <c r="H55" s="22" t="n">
-        <v>10121</v>
+        <v>6187</v>
       </c>
       <c r="I55" s="21" t="n">
-        <v>9514</v>
+        <v>6600</v>
       </c>
       <c r="J55" s="22" t="n">
-        <v>9675</v>
+        <v>6703</v>
       </c>
     </row>
     <row r="56">
@@ -5492,25 +5492,25 @@
         <v>14</v>
       </c>
       <c r="D56" s="21" t="n">
-        <v>9274</v>
+        <v>6298</v>
       </c>
       <c r="E56" s="22" t="n">
-        <v>7361</v>
+        <v>4480</v>
       </c>
       <c r="F56" s="21" t="n">
-        <v>9745</v>
+        <v>7015</v>
       </c>
       <c r="G56" s="21" t="n">
-        <v>9504</v>
+        <v>7104</v>
       </c>
       <c r="H56" s="22" t="n">
-        <v>10107</v>
+        <v>6174</v>
       </c>
       <c r="I56" s="21" t="n">
-        <v>9485</v>
+        <v>6529</v>
       </c>
       <c r="J56" s="22" t="n">
-        <v>9650</v>
+        <v>6663</v>
       </c>
     </row>
     <row r="57">
@@ -5524,25 +5524,25 @@
         <v>14</v>
       </c>
       <c r="D57" s="21" t="n">
-        <v>9326</v>
+        <v>6337</v>
       </c>
       <c r="E57" s="22" t="n">
-        <v>7638</v>
+        <v>4757</v>
       </c>
       <c r="F57" s="21" t="n">
-        <v>9744</v>
+        <v>6994</v>
       </c>
       <c r="G57" s="21" t="n">
-        <v>9504</v>
+        <v>7135</v>
       </c>
       <c r="H57" s="22" t="n">
-        <v>10097</v>
+        <v>6164</v>
       </c>
       <c r="I57" s="21" t="n">
-        <v>9499</v>
+        <v>6501</v>
       </c>
       <c r="J57" s="22" t="n">
-        <v>9657</v>
+        <v>6630</v>
       </c>
     </row>
     <row r="58">
@@ -5556,25 +5556,25 @@
         <v>15</v>
       </c>
       <c r="D58" s="21" t="n">
-        <v>9371</v>
+        <v>6395</v>
       </c>
       <c r="E58" s="22" t="n">
-        <v>8033</v>
+        <v>5152</v>
       </c>
       <c r="F58" s="21" t="n">
-        <v>9761</v>
+        <v>7015</v>
       </c>
       <c r="G58" s="21" t="n">
-        <v>9487</v>
+        <v>7135</v>
       </c>
       <c r="H58" s="22" t="n">
-        <v>10047</v>
+        <v>6169</v>
       </c>
       <c r="I58" s="21" t="n">
-        <v>9423</v>
+        <v>6414</v>
       </c>
       <c r="J58" s="22" t="n">
-        <v>9621</v>
+        <v>6607</v>
       </c>
     </row>
     <row r="59">
@@ -5588,25 +5588,25 @@
         <v>15</v>
       </c>
       <c r="D59" s="21" t="n">
-        <v>9446</v>
+        <v>6462</v>
       </c>
       <c r="E59" s="22" t="n">
-        <v>8423</v>
+        <v>5542</v>
       </c>
       <c r="F59" s="21" t="n">
-        <v>9777</v>
+        <v>7048</v>
       </c>
       <c r="G59" s="21" t="n">
-        <v>9504</v>
+        <v>7180</v>
       </c>
       <c r="H59" s="22" t="n">
-        <v>10047</v>
+        <v>6171</v>
       </c>
       <c r="I59" s="21" t="n">
-        <v>9428</v>
+        <v>6360</v>
       </c>
       <c r="J59" s="22" t="n">
-        <v>9607</v>
+        <v>6557</v>
       </c>
     </row>
     <row r="60">
@@ -5620,25 +5620,25 @@
         <v>15</v>
       </c>
       <c r="D60" s="21" t="n">
-        <v>9515</v>
+        <v>6567</v>
       </c>
       <c r="E60" s="22" t="n">
-        <v>8846</v>
+        <v>5964</v>
       </c>
       <c r="F60" s="21" t="n">
-        <v>9765</v>
+        <v>7128</v>
       </c>
       <c r="G60" s="21" t="n">
-        <v>9504</v>
+        <v>7264</v>
       </c>
       <c r="H60" s="22" t="n">
-        <v>9997</v>
+        <v>6197</v>
       </c>
       <c r="I60" s="21" t="n">
-        <v>9432</v>
+        <v>6338</v>
       </c>
       <c r="J60" s="22" t="n">
-        <v>9621</v>
+        <v>6562</v>
       </c>
     </row>
     <row r="61">
@@ -5652,25 +5652,25 @@
         <v>15</v>
       </c>
       <c r="D61" s="21" t="n">
-        <v>9628</v>
+        <v>6680</v>
       </c>
       <c r="E61" s="22" t="n">
-        <v>9280</v>
+        <v>6399</v>
       </c>
       <c r="F61" s="21" t="n">
-        <v>9903</v>
+        <v>7079</v>
       </c>
       <c r="G61" s="21" t="n">
-        <v>9504</v>
+        <v>7405</v>
       </c>
       <c r="H61" s="22" t="n">
-        <v>9988</v>
+        <v>6214</v>
       </c>
       <c r="I61" s="21" t="n">
-        <v>9483</v>
+        <v>6425</v>
       </c>
       <c r="J61" s="22" t="n">
-        <v>9638</v>
+        <v>6587</v>
       </c>
     </row>
     <row r="62">
@@ -5684,25 +5684,25 @@
         <v>16</v>
       </c>
       <c r="D62" s="21" t="n">
-        <v>9671</v>
+        <v>6840</v>
       </c>
       <c r="E62" s="22" t="n">
-        <v>9403</v>
+        <v>6522</v>
       </c>
       <c r="F62" s="21" t="n">
-        <v>9968</v>
+        <v>7281</v>
       </c>
       <c r="G62" s="21" t="n">
-        <v>9504</v>
+        <v>7689</v>
       </c>
       <c r="H62" s="22" t="n">
-        <v>10009</v>
+        <v>6283</v>
       </c>
       <c r="I62" s="21" t="n">
-        <v>9547</v>
+        <v>6536</v>
       </c>
       <c r="J62" s="22" t="n">
-        <v>9612</v>
+        <v>6765</v>
       </c>
     </row>
     <row r="63">
@@ -5716,25 +5716,25 @@
         <v>16</v>
       </c>
       <c r="D63" s="21" t="n">
-        <v>9813</v>
+        <v>7122</v>
       </c>
       <c r="E63" s="22" t="n">
-        <v>9956</v>
+        <v>7075</v>
       </c>
       <c r="F63" s="21" t="n">
-        <v>9949</v>
+        <v>7567</v>
       </c>
       <c r="G63" s="21" t="n">
-        <v>9535</v>
+        <v>8004</v>
       </c>
       <c r="H63" s="22" t="n">
-        <v>10048</v>
+        <v>6488</v>
       </c>
       <c r="I63" s="21" t="n">
-        <v>9653</v>
+        <v>6732</v>
       </c>
       <c r="J63" s="22" t="n">
-        <v>9710</v>
+        <v>6872</v>
       </c>
     </row>
     <row r="64">
@@ -5748,25 +5748,25 @@
         <v>16</v>
       </c>
       <c r="D64" s="21" t="n">
-        <v>9995</v>
+        <v>7438</v>
       </c>
       <c r="E64" s="22" t="n">
-        <v>10495</v>
+        <v>7614</v>
       </c>
       <c r="F64" s="21" t="n">
-        <v>9935</v>
+        <v>7761</v>
       </c>
       <c r="G64" s="21" t="n">
-        <v>9878</v>
+        <v>8133</v>
       </c>
       <c r="H64" s="22" t="n">
-        <v>10154</v>
+        <v>7158</v>
       </c>
       <c r="I64" s="21" t="n">
-        <v>9720</v>
+        <v>6850</v>
       </c>
       <c r="J64" s="22" t="n">
-        <v>9740</v>
+        <v>7104</v>
       </c>
     </row>
     <row r="65">
@@ -5780,25 +5780,25 @@
         <v>16</v>
       </c>
       <c r="D65" s="21" t="n">
-        <v>10438</v>
+        <v>8125</v>
       </c>
       <c r="E65" s="22" t="n">
-        <v>11027</v>
+        <v>8146</v>
       </c>
       <c r="F65" s="21" t="n">
-        <v>10319</v>
+        <v>8554</v>
       </c>
       <c r="G65" s="21" t="n">
-        <v>10530</v>
+        <v>8929</v>
       </c>
       <c r="H65" s="22" t="n">
-        <v>10386</v>
+        <v>7561</v>
       </c>
       <c r="I65" s="21" t="n">
-        <v>10286</v>
+        <v>7763</v>
       </c>
       <c r="J65" s="22" t="n">
-        <v>10027</v>
+        <v>7791</v>
       </c>
     </row>
     <row r="66">
@@ -5812,25 +5812,25 @@
         <v>17</v>
       </c>
       <c r="D66" s="21" t="n">
-        <v>11104</v>
+        <v>8950</v>
       </c>
       <c r="E66" s="22" t="n">
-        <v>11404</v>
+        <v>8523</v>
       </c>
       <c r="F66" s="21" t="n">
-        <v>11094</v>
+        <v>9771</v>
       </c>
       <c r="G66" s="21" t="n">
-        <v>11138</v>
+        <v>9519</v>
       </c>
       <c r="H66" s="22" t="n">
-        <v>11038</v>
+        <v>8675</v>
       </c>
       <c r="I66" s="21" t="n">
-        <v>11194</v>
+        <v>8649</v>
       </c>
       <c r="J66" s="22" t="n">
-        <v>10727</v>
+        <v>8585</v>
       </c>
     </row>
     <row r="67">
@@ -5844,25 +5844,25 @@
         <v>17</v>
       </c>
       <c r="D67" s="21" t="n">
-        <v>11558</v>
+        <v>9747</v>
       </c>
       <c r="E67" s="22" t="n">
-        <v>12002</v>
+        <v>9121</v>
       </c>
       <c r="F67" s="21" t="n">
-        <v>11716</v>
+        <v>10423</v>
       </c>
       <c r="G67" s="21" t="n">
-        <v>11054</v>
+        <v>10438</v>
       </c>
       <c r="H67" s="22" t="n">
-        <v>11464</v>
+        <v>9337</v>
       </c>
       <c r="I67" s="21" t="n">
-        <v>11669</v>
+        <v>9684</v>
       </c>
       <c r="J67" s="22" t="n">
-        <v>11368</v>
+        <v>9529</v>
       </c>
     </row>
     <row r="68">
@@ -5876,25 +5876,25 @@
         <v>17</v>
       </c>
       <c r="D68" s="21" t="n">
-        <v>12111</v>
+        <v>10592</v>
       </c>
       <c r="E68" s="22" t="n">
-        <v>12564</v>
+        <v>9683</v>
       </c>
       <c r="F68" s="21" t="n">
-        <v>12161</v>
+        <v>11183</v>
       </c>
       <c r="G68" s="21" t="n">
-        <v>11460</v>
+        <v>10849</v>
       </c>
       <c r="H68" s="22" t="n">
-        <v>12207</v>
+        <v>10466</v>
       </c>
       <c r="I68" s="21" t="n">
-        <v>12248</v>
+        <v>10883</v>
       </c>
       <c r="J68" s="22" t="n">
-        <v>11956</v>
+        <v>10562</v>
       </c>
     </row>
     <row r="69">
@@ -5908,25 +5908,25 @@
         <v>17</v>
       </c>
       <c r="D69" s="21" t="n">
-        <v>12488</v>
+        <v>11201</v>
       </c>
       <c r="E69" s="22" t="n">
-        <v>13080</v>
+        <v>10199</v>
       </c>
       <c r="F69" s="21" t="n">
-        <v>12547</v>
+        <v>11711</v>
       </c>
       <c r="G69" s="21" t="n">
-        <v>11708</v>
+        <v>11133</v>
       </c>
       <c r="H69" s="22" t="n">
-        <v>12536</v>
+        <v>11275</v>
       </c>
       <c r="I69" s="21" t="n">
-        <v>12636</v>
+        <v>11599</v>
       </c>
       <c r="J69" s="22" t="n">
-        <v>12326</v>
+        <v>11364</v>
       </c>
     </row>
     <row r="70">
@@ -5940,25 +5940,25 @@
         <v>18</v>
       </c>
       <c r="D70" s="21" t="n">
-        <v>12620</v>
+        <v>11528</v>
       </c>
       <c r="E70" s="22" t="n">
-        <v>13577</v>
+        <v>10695</v>
       </c>
       <c r="F70" s="21" t="n">
-        <v>12544</v>
+        <v>11881</v>
       </c>
       <c r="G70" s="21" t="n">
-        <v>11852</v>
+        <v>11640</v>
       </c>
       <c r="H70" s="22" t="n">
-        <v>12658</v>
+        <v>11695</v>
       </c>
       <c r="I70" s="21" t="n">
-        <v>12481</v>
+        <v>11644</v>
       </c>
       <c r="J70" s="22" t="n">
-        <v>12482</v>
+        <v>11691</v>
       </c>
     </row>
     <row r="71">
@@ -5972,25 +5972,25 @@
         <v>18</v>
       </c>
       <c r="D71" s="21" t="n">
-        <v>12844</v>
+        <v>12016</v>
       </c>
       <c r="E71" s="22" t="n">
-        <v>13978</v>
+        <v>11097</v>
       </c>
       <c r="F71" s="21" t="n">
-        <v>12969</v>
+        <v>12516</v>
       </c>
       <c r="G71" s="21" t="n">
-        <v>11944</v>
+        <v>12519</v>
       </c>
       <c r="H71" s="22" t="n">
-        <v>12751</v>
+        <v>12152</v>
       </c>
       <c r="I71" s="21" t="n">
-        <v>12469</v>
+        <v>11803</v>
       </c>
       <c r="J71" s="22" t="n">
-        <v>12792</v>
+        <v>12106</v>
       </c>
     </row>
     <row r="72">
@@ -6004,25 +6004,25 @@
         <v>18</v>
       </c>
       <c r="D72" s="21" t="n">
-        <v>12954</v>
+        <v>12305</v>
       </c>
       <c r="E72" s="22" t="n">
-        <v>14307</v>
+        <v>11426</v>
       </c>
       <c r="F72" s="21" t="n">
-        <v>13162</v>
+        <v>12829</v>
       </c>
       <c r="G72" s="21" t="n">
-        <v>12007</v>
+        <v>12785</v>
       </c>
       <c r="H72" s="22" t="n">
-        <v>12845</v>
+        <v>12419</v>
       </c>
       <c r="I72" s="21" t="n">
-        <v>12541</v>
+        <v>12087</v>
       </c>
       <c r="J72" s="22" t="n">
-        <v>12672</v>
+        <v>12373</v>
       </c>
     </row>
     <row r="73">
@@ -6036,25 +6036,25 @@
         <v>18</v>
       </c>
       <c r="D73" s="21" t="n">
-        <v>12967</v>
+        <v>12326</v>
       </c>
       <c r="E73" s="22" t="n">
-        <v>14482</v>
+        <v>11601</v>
       </c>
       <c r="F73" s="21" t="n">
-        <v>13339</v>
+        <v>12922</v>
       </c>
       <c r="G73" s="21" t="n">
-        <v>11974</v>
+        <v>12809</v>
       </c>
       <c r="H73" s="22" t="n">
-        <v>12697</v>
+        <v>12390</v>
       </c>
       <c r="I73" s="21" t="n">
-        <v>12481</v>
+        <v>12046</v>
       </c>
       <c r="J73" s="22" t="n">
-        <v>12610</v>
+        <v>12258</v>
       </c>
     </row>
     <row r="74">
@@ -6068,25 +6068,25 @@
         <v>19</v>
       </c>
       <c r="D74" s="21" t="n">
-        <v>12869</v>
+        <v>12233</v>
       </c>
       <c r="E74" s="22" t="n">
-        <v>14592</v>
+        <v>11711</v>
       </c>
       <c r="F74" s="21" t="n">
-        <v>13297</v>
+        <v>12947</v>
       </c>
       <c r="G74" s="21" t="n">
-        <v>11922</v>
+        <v>12707</v>
       </c>
       <c r="H74" s="22" t="n">
-        <v>12446</v>
+        <v>12168</v>
       </c>
       <c r="I74" s="21" t="n">
-        <v>12206</v>
+        <v>11790</v>
       </c>
       <c r="J74" s="22" t="n">
-        <v>12506</v>
+        <v>12117</v>
       </c>
     </row>
     <row r="75">
@@ -6100,25 +6100,25 @@
         <v>19</v>
       </c>
       <c r="D75" s="21" t="n">
-        <v>12776</v>
+        <v>12116</v>
       </c>
       <c r="E75" s="22" t="n">
-        <v>14571</v>
+        <v>11690</v>
       </c>
       <c r="F75" s="21" t="n">
-        <v>13204</v>
+        <v>12895</v>
       </c>
       <c r="G75" s="21" t="n">
-        <v>11934</v>
+        <v>12360</v>
       </c>
       <c r="H75" s="22" t="n">
-        <v>12331</v>
+        <v>12073</v>
       </c>
       <c r="I75" s="21" t="n">
-        <v>12099</v>
+        <v>11672</v>
       </c>
       <c r="J75" s="22" t="n">
-        <v>12269</v>
+        <v>12024</v>
       </c>
     </row>
     <row r="76">
@@ -6132,25 +6132,25 @@
         <v>19</v>
       </c>
       <c r="D76" s="21" t="n">
-        <v>12652</v>
+        <v>12063</v>
       </c>
       <c r="E76" s="22" t="n">
-        <v>14469</v>
+        <v>11588</v>
       </c>
       <c r="F76" s="21" t="n">
-        <v>13171</v>
+        <v>12731</v>
       </c>
       <c r="G76" s="21" t="n">
-        <v>11778</v>
+        <v>12425</v>
       </c>
       <c r="H76" s="22" t="n">
-        <v>12235</v>
+        <v>12001</v>
       </c>
       <c r="I76" s="21" t="n">
-        <v>11846</v>
+        <v>11648</v>
       </c>
       <c r="J76" s="22" t="n">
-        <v>12157</v>
+        <v>12016</v>
       </c>
     </row>
     <row r="77">
@@ -6164,25 +6164,25 @@
         <v>19</v>
       </c>
       <c r="D77" s="21" t="n">
-        <v>12584</v>
+        <v>11987</v>
       </c>
       <c r="E77" s="22" t="n">
-        <v>14375</v>
+        <v>11494</v>
       </c>
       <c r="F77" s="21" t="n">
-        <v>13071</v>
+        <v>12634</v>
       </c>
       <c r="G77" s="21" t="n">
-        <v>11778</v>
+        <v>12425</v>
       </c>
       <c r="H77" s="22" t="n">
-        <v>12146</v>
+        <v>11885</v>
       </c>
       <c r="I77" s="21" t="n">
-        <v>11858</v>
+        <v>11564</v>
       </c>
       <c r="J77" s="22" t="n">
-        <v>12029</v>
+        <v>11956</v>
       </c>
     </row>
     <row r="78">
@@ -6196,25 +6196,25 @@
         <v>20</v>
       </c>
       <c r="D78" s="21" t="n">
-        <v>12496</v>
+        <v>11928</v>
       </c>
       <c r="E78" s="22" t="n">
-        <v>14334</v>
+        <v>11453</v>
       </c>
       <c r="F78" s="21" t="n">
-        <v>12861</v>
+        <v>12493</v>
       </c>
       <c r="G78" s="21" t="n">
-        <v>11916</v>
+        <v>12605</v>
       </c>
       <c r="H78" s="22" t="n">
-        <v>11951</v>
+        <v>11645</v>
       </c>
       <c r="I78" s="21" t="n">
-        <v>11793</v>
+        <v>11471</v>
       </c>
       <c r="J78" s="22" t="n">
-        <v>11882</v>
+        <v>11945</v>
       </c>
     </row>
     <row r="79">
@@ -6228,25 +6228,25 @@
         <v>20</v>
       </c>
       <c r="D79" s="21" t="n">
-        <v>12469</v>
+        <v>11890</v>
       </c>
       <c r="E79" s="22" t="n">
-        <v>14225</v>
+        <v>11343</v>
       </c>
       <c r="F79" s="21" t="n">
-        <v>12817</v>
+        <v>12483</v>
       </c>
       <c r="G79" s="21" t="n">
-        <v>11940</v>
+        <v>12570</v>
       </c>
       <c r="H79" s="22" t="n">
-        <v>11919</v>
+        <v>11490</v>
       </c>
       <c r="I79" s="21" t="n">
-        <v>11848</v>
+        <v>11576</v>
       </c>
       <c r="J79" s="22" t="n">
-        <v>11836</v>
+        <v>11924</v>
       </c>
     </row>
     <row r="80">
@@ -6260,25 +6260,25 @@
         <v>20</v>
       </c>
       <c r="D80" s="21" t="n">
-        <v>12452</v>
+        <v>11868</v>
       </c>
       <c r="E80" s="22" t="n">
-        <v>14108</v>
+        <v>11227</v>
       </c>
       <c r="F80" s="21" t="n">
-        <v>12784</v>
+        <v>12546</v>
       </c>
       <c r="G80" s="21" t="n">
-        <v>11947</v>
+        <v>12601</v>
       </c>
       <c r="H80" s="22" t="n">
-        <v>11852</v>
+        <v>11365</v>
       </c>
       <c r="I80" s="21" t="n">
-        <v>11915</v>
+        <v>11573</v>
       </c>
       <c r="J80" s="22" t="n">
-        <v>11882</v>
+        <v>11945</v>
       </c>
     </row>
     <row r="81">
@@ -6292,25 +6292,25 @@
         <v>20</v>
       </c>
       <c r="D81" s="21" t="n">
-        <v>12410</v>
+        <v>11817</v>
       </c>
       <c r="E81" s="22" t="n">
-        <v>14040</v>
+        <v>11159</v>
       </c>
       <c r="F81" s="21" t="n">
-        <v>12682</v>
+        <v>12469</v>
       </c>
       <c r="G81" s="21" t="n">
-        <v>11947</v>
+        <v>12601</v>
       </c>
       <c r="H81" s="22" t="n">
-        <v>11849</v>
+        <v>11339</v>
       </c>
       <c r="I81" s="21" t="n">
-        <v>11866</v>
+        <v>11506</v>
       </c>
       <c r="J81" s="22" t="n">
-        <v>11865</v>
+        <v>11883</v>
       </c>
     </row>
     <row r="82">
@@ -6324,25 +6324,25 @@
         <v>21</v>
       </c>
       <c r="D82" s="21" t="n">
-        <v>12402</v>
+        <v>11823</v>
       </c>
       <c r="E82" s="22" t="n">
-        <v>14048</v>
+        <v>11167</v>
       </c>
       <c r="F82" s="21" t="n">
-        <v>12648</v>
+        <v>12422</v>
       </c>
       <c r="G82" s="21" t="n">
-        <v>11947</v>
+        <v>12601</v>
       </c>
       <c r="H82" s="22" t="n">
-        <v>11805</v>
+        <v>11241</v>
       </c>
       <c r="I82" s="21" t="n">
-        <v>11908</v>
+        <v>11661</v>
       </c>
       <c r="J82" s="22" t="n">
-        <v>11838</v>
+        <v>11901</v>
       </c>
     </row>
     <row r="83">
@@ -6356,25 +6356,25 @@
         <v>21</v>
       </c>
       <c r="D83" s="21" t="n">
-        <v>12449</v>
+        <v>11892</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>14039</v>
+        <v>11158</v>
       </c>
       <c r="F83" s="21" t="n">
-        <v>12656</v>
+        <v>12515</v>
       </c>
       <c r="G83" s="21" t="n">
-        <v>11891</v>
+        <v>12545</v>
       </c>
       <c r="H83" s="22" t="n">
-        <v>11822</v>
+        <v>11359</v>
       </c>
       <c r="I83" s="21" t="n">
-        <v>12041</v>
+        <v>11823</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>12033</v>
+        <v>12006</v>
       </c>
     </row>
     <row r="84">
@@ -6388,25 +6388,25 @@
         <v>21</v>
       </c>
       <c r="D84" s="21" t="n">
-        <v>12443</v>
+        <v>11939</v>
       </c>
       <c r="E84" s="22" t="n">
-        <v>14097</v>
+        <v>11216</v>
       </c>
       <c r="F84" s="21" t="n">
-        <v>12586</v>
+        <v>12512</v>
       </c>
       <c r="G84" s="21" t="n">
-        <v>11891</v>
+        <v>12545</v>
       </c>
       <c r="H84" s="22" t="n">
-        <v>11795</v>
+        <v>11478</v>
       </c>
       <c r="I84" s="21" t="n">
-        <v>12019</v>
+        <v>11826</v>
       </c>
       <c r="J84" s="22" t="n">
-        <v>12050</v>
+        <v>12111</v>
       </c>
     </row>
     <row r="85">
@@ -6420,25 +6420,25 @@
         <v>21</v>
       </c>
       <c r="D85" s="21" t="n">
-        <v>12452</v>
+        <v>12017</v>
       </c>
       <c r="E85" s="22" t="n">
-        <v>14147</v>
+        <v>11266</v>
       </c>
       <c r="F85" s="21" t="n">
-        <v>12588</v>
+        <v>12663</v>
       </c>
       <c r="G85" s="21" t="n">
-        <v>11880</v>
+        <v>12593</v>
       </c>
       <c r="H85" s="22" t="n">
-        <v>11771</v>
+        <v>11578</v>
       </c>
       <c r="I85" s="21" t="n">
-        <v>12063</v>
+        <v>11921</v>
       </c>
       <c r="J85" s="22" t="n">
-        <v>12039</v>
+        <v>12139</v>
       </c>
     </row>
     <row r="86">
@@ -6452,25 +6452,25 @@
         <v>22</v>
       </c>
       <c r="D86" s="21" t="n">
-        <v>12492</v>
+        <v>12203</v>
       </c>
       <c r="E86" s="22" t="n">
-        <v>14258</v>
+        <v>11377</v>
       </c>
       <c r="F86" s="21" t="n">
-        <v>12534</v>
+        <v>12906</v>
       </c>
       <c r="G86" s="21" t="n">
-        <v>11779</v>
+        <v>12867</v>
       </c>
       <c r="H86" s="22" t="n">
-        <v>12055</v>
+        <v>11970</v>
       </c>
       <c r="I86" s="21" t="n">
-        <v>12070</v>
+        <v>12001</v>
       </c>
       <c r="J86" s="22" t="n">
-        <v>12030</v>
+        <v>12171</v>
       </c>
     </row>
     <row r="87">
@@ -6484,25 +6484,25 @@
         <v>22</v>
       </c>
       <c r="D87" s="21" t="n">
-        <v>12521</v>
+        <v>12192</v>
       </c>
       <c r="E87" s="22" t="n">
-        <v>14234</v>
+        <v>11353</v>
       </c>
       <c r="F87" s="21" t="n">
-        <v>12676</v>
+        <v>12926</v>
       </c>
       <c r="G87" s="21" t="n">
-        <v>11795</v>
+        <v>12835</v>
       </c>
       <c r="H87" s="22" t="n">
-        <v>12023</v>
+        <v>11886</v>
       </c>
       <c r="I87" s="21" t="n">
-        <v>12075</v>
+        <v>12001</v>
       </c>
       <c r="J87" s="22" t="n">
-        <v>12095</v>
+        <v>12217</v>
       </c>
     </row>
     <row r="88">
@@ -6516,25 +6516,25 @@
         <v>22</v>
       </c>
       <c r="D88" s="21" t="n">
-        <v>12508</v>
+        <v>12206</v>
       </c>
       <c r="E88" s="22" t="n">
-        <v>14197</v>
+        <v>11316</v>
       </c>
       <c r="F88" s="21" t="n">
-        <v>12617</v>
+        <v>12916</v>
       </c>
       <c r="G88" s="21" t="n">
-        <v>11779</v>
+        <v>12867</v>
       </c>
       <c r="H88" s="22" t="n">
-        <v>12074</v>
+        <v>12018</v>
       </c>
       <c r="I88" s="21" t="n">
-        <v>12089</v>
+        <v>12012</v>
       </c>
       <c r="J88" s="22" t="n">
-        <v>12072</v>
+        <v>12187</v>
       </c>
     </row>
     <row r="89">
@@ -6548,25 +6548,25 @@
         <v>22</v>
       </c>
       <c r="D89" s="21" t="n">
-        <v>12504</v>
+        <v>12201</v>
       </c>
       <c r="E89" s="22" t="n">
-        <v>14165</v>
+        <v>11284</v>
       </c>
       <c r="F89" s="21" t="n">
-        <v>12688</v>
+        <v>12958</v>
       </c>
       <c r="G89" s="21" t="n">
-        <v>11827</v>
+        <v>12867</v>
       </c>
       <c r="H89" s="22" t="n">
-        <v>12111</v>
+        <v>12059</v>
       </c>
       <c r="I89" s="21" t="n">
-        <v>11967</v>
+        <v>11951</v>
       </c>
       <c r="J89" s="22" t="n">
-        <v>12052</v>
+        <v>12166</v>
       </c>
     </row>
     <row r="90">
@@ -6580,25 +6580,25 @@
         <v>23</v>
       </c>
       <c r="D90" s="21" t="n">
-        <v>12549</v>
+        <v>12206</v>
       </c>
       <c r="E90" s="22" t="n">
-        <v>14163</v>
+        <v>11282</v>
       </c>
       <c r="F90" s="21" t="n">
-        <v>12765</v>
+        <v>13014</v>
       </c>
       <c r="G90" s="21" t="n">
-        <v>11873</v>
+        <v>12835</v>
       </c>
       <c r="H90" s="22" t="n">
-        <v>12175</v>
+        <v>12062</v>
       </c>
       <c r="I90" s="21" t="n">
-        <v>12018</v>
+        <v>11948</v>
       </c>
       <c r="J90" s="22" t="n">
-        <v>12088</v>
+        <v>12173</v>
       </c>
     </row>
     <row r="91">
@@ -6612,25 +6612,25 @@
         <v>23</v>
       </c>
       <c r="D91" s="21" t="n">
-        <v>12621</v>
+        <v>12312</v>
       </c>
       <c r="E91" s="22" t="n">
-        <v>14147</v>
+        <v>11266</v>
       </c>
       <c r="F91" s="21" t="n">
-        <v>12758</v>
+        <v>12984</v>
       </c>
       <c r="G91" s="21" t="n">
-        <v>11842</v>
+        <v>12820</v>
       </c>
       <c r="H91" s="22" t="n">
-        <v>12466</v>
+        <v>12406</v>
       </c>
       <c r="I91" s="21" t="n">
-        <v>12045</v>
+        <v>12072</v>
       </c>
       <c r="J91" s="22" t="n">
-        <v>12273</v>
+        <v>12423</v>
       </c>
     </row>
     <row r="92">
@@ -6644,25 +6644,25 @@
         <v>23</v>
       </c>
       <c r="D92" s="21" t="n">
-        <v>12757</v>
+        <v>12472</v>
       </c>
       <c r="E92" s="22" t="n">
-        <v>14182</v>
+        <v>11300</v>
       </c>
       <c r="F92" s="21" t="n">
-        <v>12807</v>
+        <v>13069</v>
       </c>
       <c r="G92" s="21" t="n">
-        <v>11536</v>
+        <v>12926</v>
       </c>
       <c r="H92" s="22" t="n">
-        <v>12707</v>
+        <v>12670</v>
       </c>
       <c r="I92" s="21" t="n">
-        <v>12447</v>
+        <v>12307</v>
       </c>
       <c r="J92" s="22" t="n">
-        <v>12660</v>
+        <v>12676</v>
       </c>
     </row>
     <row r="93">
@@ -6676,25 +6676,25 @@
         <v>23</v>
       </c>
       <c r="D93" s="21" t="n">
-        <v>12809</v>
+        <v>12467</v>
       </c>
       <c r="E93" s="22" t="n">
-        <v>14145</v>
+        <v>11264</v>
       </c>
       <c r="F93" s="21" t="n">
-        <v>12979</v>
+        <v>13120</v>
       </c>
       <c r="G93" s="21" t="n">
-        <v>11770</v>
+        <v>12799</v>
       </c>
       <c r="H93" s="22" t="n">
-        <v>12768</v>
+        <v>12701</v>
       </c>
       <c r="I93" s="21" t="n">
-        <v>12517</v>
+        <v>12413</v>
       </c>
       <c r="J93" s="22" t="n">
-        <v>12490</v>
+        <v>12618</v>
       </c>
     </row>
     <row r="94">
@@ -6708,25 +6708,25 @@
         <v>24</v>
       </c>
       <c r="D94" s="21" t="n">
-        <v>12852</v>
+        <v>12552</v>
       </c>
       <c r="E94" s="22" t="n">
-        <v>14133</v>
+        <v>11252</v>
       </c>
       <c r="F94" s="21" t="n">
-        <v>13103</v>
+        <v>13317</v>
       </c>
       <c r="G94" s="21" t="n">
-        <v>11871</v>
+        <v>12813</v>
       </c>
       <c r="H94" s="22" t="n">
-        <v>12635</v>
+        <v>12519</v>
       </c>
       <c r="I94" s="21" t="n">
-        <v>12553</v>
+        <v>12598</v>
       </c>
       <c r="J94" s="22" t="n">
-        <v>12628</v>
+        <v>12915</v>
       </c>
     </row>
     <row r="95">
@@ -6740,25 +6740,25 @@
         <v>24</v>
       </c>
       <c r="D95" s="21" t="n">
-        <v>12840</v>
+        <v>12447</v>
       </c>
       <c r="E95" s="22" t="n">
-        <v>14055</v>
+        <v>11174</v>
       </c>
       <c r="F95" s="21" t="n">
-        <v>13199</v>
+        <v>13297</v>
       </c>
       <c r="G95" s="21" t="n">
-        <v>11902</v>
+        <v>12768</v>
       </c>
       <c r="H95" s="22" t="n">
-        <v>12526</v>
+        <v>12337</v>
       </c>
       <c r="I95" s="21" t="n">
-        <v>12559</v>
+        <v>12399</v>
       </c>
       <c r="J95" s="22" t="n">
-        <v>12607</v>
+        <v>12805</v>
       </c>
     </row>
     <row r="96">
@@ -6772,25 +6772,25 @@
         <v>24</v>
       </c>
       <c r="D96" s="21" t="n">
-        <v>12786</v>
+        <v>12262</v>
       </c>
       <c r="E96" s="22" t="n">
-        <v>13880</v>
+        <v>10999</v>
       </c>
       <c r="F96" s="21" t="n">
-        <v>13066</v>
+        <v>13040</v>
       </c>
       <c r="G96" s="21" t="n">
-        <v>11916</v>
+        <v>12575</v>
       </c>
       <c r="H96" s="22" t="n">
-        <v>12345</v>
+        <v>11785</v>
       </c>
       <c r="I96" s="21" t="n">
-        <v>12644</v>
+        <v>12529</v>
       </c>
       <c r="J96" s="22" t="n">
-        <v>12691</v>
+        <v>12730</v>
       </c>
     </row>
     <row r="97">
@@ -6806,25 +6806,25 @@
         <v>24</v>
       </c>
       <c r="D97" s="21" t="n">
-        <v>12619</v>
+        <v>11973</v>
       </c>
       <c r="E97" s="22" t="n">
-        <v>13735</v>
+        <v>10854</v>
       </c>
       <c r="F97" s="21" t="n">
-        <v>12913</v>
+        <v>12890</v>
       </c>
       <c r="G97" s="21" t="n">
-        <v>11845</v>
+        <v>12316</v>
       </c>
       <c r="H97" s="22" t="n">
-        <v>12268</v>
+        <v>11447</v>
       </c>
       <c r="I97" s="21" t="n">
-        <v>12465</v>
+        <v>12191</v>
       </c>
       <c r="J97" s="22" t="n">
-        <v>12316</v>
+        <v>12210</v>
       </c>
     </row>
   </sheetData>
@@ -6989,25 +6989,25 @@
         <v>385.1</v>
       </c>
       <c r="G2" s="23" t="n">
-        <v>314.2</v>
+        <v>407.06</v>
       </c>
       <c r="H2" s="24" t="n">
-        <v>268.33</v>
+        <v>424.93</v>
       </c>
       <c r="I2" s="23" t="n">
-        <v>323.41</v>
+        <v>385.69</v>
       </c>
       <c r="J2" s="23" t="n">
-        <v>351.25</v>
+        <v>415.13</v>
       </c>
       <c r="K2" s="24" t="n">
-        <v>286.22</v>
+        <v>402.41</v>
       </c>
       <c r="L2" s="23" t="n">
-        <v>321.11</v>
+        <v>410.08</v>
       </c>
       <c r="M2" s="24" t="n">
-        <v>328.52</v>
+        <v>407.26</v>
       </c>
     </row>
     <row r="3">
@@ -7030,25 +7030,25 @@
         <v>385.1</v>
       </c>
       <c r="G3" s="23" t="n">
-        <v>310</v>
+        <v>407.76</v>
       </c>
       <c r="H3" s="24" t="n">
-        <v>265.56</v>
+        <v>422.15</v>
       </c>
       <c r="I3" s="23" t="n">
-        <v>321.48</v>
+        <v>386.32</v>
       </c>
       <c r="J3" s="23" t="n">
-        <v>342.8</v>
+        <v>416.88</v>
       </c>
       <c r="K3" s="24" t="n">
-        <v>286.24</v>
+        <v>402.69</v>
       </c>
       <c r="L3" s="23" t="n">
-        <v>312.9</v>
+        <v>412.82</v>
       </c>
       <c r="M3" s="24" t="n">
-        <v>324.74</v>
+        <v>408.38</v>
       </c>
     </row>
     <row r="4">
@@ -7071,25 +7071,25 @@
         <v>385.1</v>
       </c>
       <c r="G4" s="23" t="n">
-        <v>305.81</v>
+        <v>405.22</v>
       </c>
       <c r="H4" s="24" t="n">
-        <v>261.08</v>
+        <v>417.55</v>
       </c>
       <c r="I4" s="23" t="n">
-        <v>327.27</v>
+        <v>395.91</v>
       </c>
       <c r="J4" s="23" t="n">
-        <v>347.75</v>
+        <v>423.46</v>
       </c>
       <c r="K4" s="24" t="n">
-        <v>276.84</v>
+        <v>395.64</v>
       </c>
       <c r="L4" s="23" t="n">
-        <v>300.14</v>
+        <v>404.47</v>
       </c>
       <c r="M4" s="24" t="n">
-        <v>314.73</v>
+        <v>395.78</v>
       </c>
     </row>
     <row r="5">
@@ -7112,25 +7112,25 @@
         <v>385.1</v>
       </c>
       <c r="G5" s="23" t="n">
-        <v>297.45</v>
+        <v>399</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>253.98</v>
+        <v>410.65</v>
       </c>
       <c r="I5" s="23" t="n">
-        <v>325.84</v>
+        <v>391.64</v>
       </c>
       <c r="J5" s="23" t="n">
-        <v>351.54</v>
+        <v>426.35</v>
       </c>
       <c r="K5" s="24" t="n">
-        <v>263.5</v>
+        <v>390.51</v>
       </c>
       <c r="L5" s="23" t="n">
-        <v>280.8</v>
+        <v>387.95</v>
       </c>
       <c r="M5" s="24" t="n">
-        <v>301.44</v>
+        <v>387.91</v>
       </c>
     </row>
     <row r="6">
@@ -7153,25 +7153,25 @@
         <v>390</v>
       </c>
       <c r="G6" s="23" t="n">
-        <v>287.95</v>
+        <v>390.82</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>250.02</v>
+        <v>406.57</v>
       </c>
       <c r="I6" s="23" t="n">
-        <v>307.3</v>
+        <v>375.57</v>
       </c>
       <c r="J6" s="23" t="n">
-        <v>340.73</v>
+        <v>422.12</v>
       </c>
       <c r="K6" s="24" t="n">
-        <v>258.51</v>
+        <v>389.92</v>
       </c>
       <c r="L6" s="23" t="n">
-        <v>266.64</v>
+        <v>369.21</v>
       </c>
       <c r="M6" s="24" t="n">
-        <v>298.07</v>
+        <v>383.16</v>
       </c>
     </row>
     <row r="7">
@@ -7194,25 +7194,25 @@
         <v>390</v>
       </c>
       <c r="G7" s="23" t="n">
-        <v>308.66</v>
+        <v>397.56</v>
       </c>
       <c r="H7" s="24" t="n">
-        <v>249.22</v>
+        <v>405.66</v>
       </c>
       <c r="I7" s="23" t="n">
-        <v>300.29</v>
+        <v>389.15</v>
       </c>
       <c r="J7" s="23" t="n">
-        <v>418.49</v>
+        <v>418.3</v>
       </c>
       <c r="K7" s="24" t="n">
-        <v>263.5</v>
+        <v>392.94</v>
       </c>
       <c r="L7" s="23" t="n">
-        <v>303.43</v>
+        <v>390.14</v>
       </c>
       <c r="M7" s="24" t="n">
-        <v>307.86</v>
+        <v>389.97</v>
       </c>
     </row>
     <row r="8">
@@ -7235,25 +7235,25 @@
         <v>390</v>
       </c>
       <c r="G8" s="23" t="n">
-        <v>282.87</v>
+        <v>385.24</v>
       </c>
       <c r="H8" s="24" t="n">
-        <v>237.96</v>
+        <v>393.4</v>
       </c>
       <c r="I8" s="23" t="n">
-        <v>310.8</v>
+        <v>384.18</v>
       </c>
       <c r="J8" s="23" t="n">
-        <v>330.28</v>
+        <v>406.65</v>
       </c>
       <c r="K8" s="24" t="n">
-        <v>253.37</v>
+        <v>381.55</v>
       </c>
       <c r="L8" s="23" t="n">
-        <v>275.01</v>
+        <v>379.35</v>
       </c>
       <c r="M8" s="24" t="n">
-        <v>282.13</v>
+        <v>366.5</v>
       </c>
     </row>
     <row r="9">
@@ -7276,25 +7276,25 @@
         <v>390</v>
       </c>
       <c r="G9" s="23" t="n">
-        <v>266.28</v>
+        <v>379.98</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>230.16</v>
+        <v>385.11</v>
       </c>
       <c r="I9" s="23" t="n">
-        <v>307.47</v>
+        <v>387.33</v>
       </c>
       <c r="J9" s="23" t="n">
-        <v>272.43</v>
+        <v>395</v>
       </c>
       <c r="K9" s="24" t="n">
-        <v>247.12</v>
+        <v>377.28</v>
       </c>
       <c r="L9" s="23" t="n">
-        <v>266.23</v>
+        <v>373.65</v>
       </c>
       <c r="M9" s="24" t="n">
-        <v>268.02</v>
+        <v>361.1</v>
       </c>
     </row>
     <row r="10">
@@ -7317,25 +7317,25 @@
         <v>395</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>309.54</v>
+        <v>399.43</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>279.96</v>
+        <v>434.45</v>
       </c>
       <c r="I10" s="23" t="n">
-        <v>328.57</v>
+        <v>388.71</v>
       </c>
       <c r="J10" s="23" t="n">
-        <v>337.35</v>
+        <v>411.42</v>
       </c>
       <c r="K10" s="24" t="n">
-        <v>278.54</v>
+        <v>389.05</v>
       </c>
       <c r="L10" s="23" t="n">
-        <v>311.32</v>
+        <v>397.12</v>
       </c>
       <c r="M10" s="24" t="n">
-        <v>316.88</v>
+        <v>380.2</v>
       </c>
     </row>
     <row r="11">
@@ -7358,25 +7358,25 @@
         <v>395</v>
       </c>
       <c r="G11" s="23" t="n">
-        <v>314.98</v>
+        <v>399.49</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>263.7</v>
+        <v>418.33</v>
       </c>
       <c r="I11" s="23" t="n">
-        <v>335.75</v>
+        <v>396.23</v>
       </c>
       <c r="J11" s="23" t="n">
-        <v>357.34</v>
+        <v>408.55</v>
       </c>
       <c r="K11" s="24" t="n">
-        <v>276.13</v>
+        <v>385.97</v>
       </c>
       <c r="L11" s="23" t="n">
-        <v>321.02</v>
+        <v>402.14</v>
       </c>
       <c r="M11" s="24" t="n">
-        <v>328.43</v>
+        <v>388.04</v>
       </c>
     </row>
     <row r="12">
@@ -7399,25 +7399,25 @@
         <v>395</v>
       </c>
       <c r="G12" s="23" t="n">
-        <v>314.84</v>
+        <v>393.84</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>263.74</v>
+        <v>418.33</v>
       </c>
       <c r="I12" s="23" t="n">
-        <v>330.82</v>
+        <v>383.49</v>
       </c>
       <c r="J12" s="23" t="n">
-        <v>374.29</v>
+        <v>408.4</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>273.82</v>
+        <v>382.71</v>
       </c>
       <c r="L12" s="23" t="n">
-        <v>309.79</v>
+        <v>387.37</v>
       </c>
       <c r="M12" s="24" t="n">
-        <v>328.87</v>
+        <v>385.95</v>
       </c>
     </row>
     <row r="13">
@@ -7440,25 +7440,25 @@
         <v>395</v>
       </c>
       <c r="G13" s="23" t="n">
-        <v>304.01</v>
+        <v>394.17</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>258.62</v>
+        <v>413.06</v>
       </c>
       <c r="I13" s="23" t="n">
-        <v>319.72</v>
+        <v>392.38</v>
       </c>
       <c r="J13" s="23" t="n">
-        <v>326.73</v>
+        <v>408.9</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>272.4</v>
+        <v>381.1</v>
       </c>
       <c r="L13" s="23" t="n">
-        <v>316.7</v>
+        <v>392.1</v>
       </c>
       <c r="M13" s="24" t="n">
-        <v>323.89</v>
+        <v>379.5</v>
       </c>
     </row>
     <row r="14">
@@ -7481,25 +7481,25 @@
         <v>385</v>
       </c>
       <c r="G14" s="23" t="n">
-        <v>296.48</v>
+        <v>389.93</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>259.24</v>
+        <v>413.73</v>
       </c>
       <c r="I14" s="23" t="n">
-        <v>319.38</v>
+        <v>382.02</v>
       </c>
       <c r="J14" s="23" t="n">
-        <v>310.32</v>
+        <v>408.82</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>266.93</v>
+        <v>374.05</v>
       </c>
       <c r="L14" s="23" t="n">
-        <v>305.95</v>
+        <v>386.7</v>
       </c>
       <c r="M14" s="24" t="n">
-        <v>311.83</v>
+        <v>377.12</v>
       </c>
     </row>
     <row r="15">
@@ -7522,25 +7522,25 @@
         <v>385</v>
       </c>
       <c r="G15" s="23" t="n">
-        <v>294.3</v>
+        <v>393.94</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>260.03</v>
+        <v>414.66</v>
       </c>
       <c r="I15" s="23" t="n">
-        <v>317.93</v>
+        <v>377.85</v>
       </c>
       <c r="J15" s="23" t="n">
-        <v>295.5</v>
+        <v>408.82</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>279.14</v>
+        <v>384.76</v>
       </c>
       <c r="L15" s="23" t="n">
-        <v>285.55</v>
+        <v>389.96</v>
       </c>
       <c r="M15" s="24" t="n">
-        <v>323.02</v>
+        <v>390.64</v>
       </c>
     </row>
     <row r="16">
@@ -7563,25 +7563,25 @@
         <v>385</v>
       </c>
       <c r="G16" s="23" t="n">
-        <v>294.44</v>
+        <v>393.43</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>253.67</v>
+        <v>408.34</v>
       </c>
       <c r="I16" s="23" t="n">
-        <v>322.84</v>
+        <v>383.79</v>
       </c>
       <c r="J16" s="23" t="n">
-        <v>300.36</v>
+        <v>409.7</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>279.68</v>
+        <v>383.71</v>
       </c>
       <c r="L16" s="23" t="n">
-        <v>290.25</v>
+        <v>395.54</v>
       </c>
       <c r="M16" s="24" t="n">
-        <v>313.86</v>
+        <v>381.33</v>
       </c>
     </row>
     <row r="17">
@@ -7604,25 +7604,25 @@
         <v>385</v>
       </c>
       <c r="G17" s="23" t="n">
-        <v>284.12</v>
+        <v>386.26</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>248.9</v>
+        <v>403.84</v>
       </c>
       <c r="I17" s="23" t="n">
-        <v>315.35</v>
+        <v>379.73</v>
       </c>
       <c r="J17" s="23" t="n">
-        <v>301.17</v>
+        <v>411.42</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>271.86</v>
+        <v>380.77</v>
       </c>
       <c r="L17" s="23" t="n">
-        <v>276.02</v>
+        <v>377.81</v>
       </c>
       <c r="M17" s="24" t="n">
-        <v>285.3</v>
+        <v>365.52</v>
       </c>
     </row>
     <row r="18">
@@ -7645,25 +7645,25 @@
         <v>600</v>
       </c>
       <c r="G18" s="23" t="n">
-        <v>276.7</v>
+        <v>389.33</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>242.62</v>
+        <v>397.56</v>
       </c>
       <c r="I18" s="23" t="n">
-        <v>313.36</v>
+        <v>384.92</v>
       </c>
       <c r="J18" s="23" t="n">
-        <v>250.08</v>
+        <v>412.06</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>271.29</v>
+        <v>379.23</v>
       </c>
       <c r="L18" s="23" t="n">
-        <v>276.46</v>
+        <v>389.61</v>
       </c>
       <c r="M18" s="24" t="n">
-        <v>301.68</v>
+        <v>373.14</v>
       </c>
     </row>
     <row r="19">
@@ -7686,25 +7686,25 @@
         <v>600</v>
       </c>
       <c r="G19" s="23" t="n">
-        <v>266.31</v>
+        <v>384.43</v>
       </c>
       <c r="H19" s="24" t="n">
-        <v>240.36</v>
+        <v>395.13</v>
       </c>
       <c r="I19" s="23" t="n">
-        <v>300.83</v>
+        <v>375.46</v>
       </c>
       <c r="J19" s="23" t="n">
-        <v>243.56</v>
+        <v>414.75</v>
       </c>
       <c r="K19" s="24" t="n">
-        <v>264.34</v>
+        <v>378.05</v>
       </c>
       <c r="L19" s="23" t="n">
-        <v>261.62</v>
+        <v>375.88</v>
       </c>
       <c r="M19" s="24" t="n">
-        <v>283.2</v>
+        <v>368.02</v>
       </c>
     </row>
     <row r="20">
@@ -7727,25 +7727,25 @@
         <v>600</v>
       </c>
       <c r="G20" s="23" t="n">
-        <v>263.64</v>
+        <v>383.43</v>
       </c>
       <c r="H20" s="24" t="n">
-        <v>239.26</v>
+        <v>394.02</v>
       </c>
       <c r="I20" s="23" t="n">
-        <v>303.29</v>
+        <v>377.13</v>
       </c>
       <c r="J20" s="23" t="n">
-        <v>241.14</v>
+        <v>414.75</v>
       </c>
       <c r="K20" s="24" t="n">
-        <v>264.14</v>
+        <v>377.84</v>
       </c>
       <c r="L20" s="23" t="n">
-        <v>246.52</v>
+        <v>368.43</v>
       </c>
       <c r="M20" s="24" t="n">
-        <v>283.47</v>
+        <v>368.97</v>
       </c>
     </row>
     <row r="21">
@@ -7768,25 +7768,25 @@
         <v>600</v>
       </c>
       <c r="G21" s="23" t="n">
-        <v>259.51</v>
+        <v>382.92</v>
       </c>
       <c r="H21" s="24" t="n">
-        <v>237.82</v>
+        <v>392.51</v>
       </c>
       <c r="I21" s="23" t="n">
-        <v>288.08</v>
+        <v>374.88</v>
       </c>
       <c r="J21" s="23" t="n">
-        <v>240.74</v>
+        <v>414.75</v>
       </c>
       <c r="K21" s="24" t="n">
-        <v>263.22</v>
+        <v>377.72</v>
       </c>
       <c r="L21" s="23" t="n">
-        <v>245.27</v>
+        <v>369.36</v>
       </c>
       <c r="M21" s="24" t="n">
-        <v>278.62</v>
+        <v>368.84</v>
       </c>
     </row>
     <row r="22">
@@ -7809,25 +7809,25 @@
         <v>600</v>
       </c>
       <c r="G22" s="23" t="n">
-        <v>260.08</v>
+        <v>387.89</v>
       </c>
       <c r="H22" s="24" t="n">
-        <v>236.42</v>
+        <v>391.07</v>
       </c>
       <c r="I22" s="23" t="n">
-        <v>279.55</v>
+        <v>377.23</v>
       </c>
       <c r="J22" s="23" t="n">
-        <v>233.66</v>
+        <v>410.81</v>
       </c>
       <c r="K22" s="24" t="n">
-        <v>261.95</v>
+        <v>377.45</v>
       </c>
       <c r="L22" s="23" t="n">
-        <v>257.55</v>
+        <v>390.26</v>
       </c>
       <c r="M22" s="24" t="n">
-        <v>288.68</v>
+        <v>380.87</v>
       </c>
     </row>
     <row r="23">
@@ -7850,25 +7850,25 @@
         <v>600</v>
       </c>
       <c r="G23" s="23" t="n">
-        <v>255.57</v>
+        <v>387.96</v>
       </c>
       <c r="H23" s="24" t="n">
-        <v>235.88</v>
+        <v>390.48</v>
       </c>
       <c r="I23" s="23" t="n">
-        <v>279.12</v>
+        <v>376.06</v>
       </c>
       <c r="J23" s="23" t="n">
-        <v>216.65</v>
+        <v>410.81</v>
       </c>
       <c r="K23" s="24" t="n">
-        <v>260.44</v>
+        <v>376.66</v>
       </c>
       <c r="L23" s="23" t="n">
-        <v>257.43</v>
+        <v>394.7</v>
       </c>
       <c r="M23" s="24" t="n">
-        <v>281.78</v>
+        <v>379.4</v>
       </c>
     </row>
     <row r="24">
@@ -7891,25 +7891,25 @@
         <v>600</v>
       </c>
       <c r="G24" s="23" t="n">
-        <v>240.61</v>
+        <v>382.12</v>
       </c>
       <c r="H24" s="24" t="n">
-        <v>236.6</v>
+        <v>391.22</v>
       </c>
       <c r="I24" s="23" t="n">
-        <v>277.33</v>
+        <v>364.51</v>
       </c>
       <c r="J24" s="23" t="n">
-        <v>208.64</v>
+        <v>409.73</v>
       </c>
       <c r="K24" s="24" t="n">
-        <v>254.84</v>
+        <v>373.66</v>
       </c>
       <c r="L24" s="23" t="n">
-        <v>218.1</v>
+        <v>384.92</v>
       </c>
       <c r="M24" s="24" t="n">
-        <v>246.51</v>
+        <v>369.88</v>
       </c>
     </row>
     <row r="25">
@@ -7932,25 +7932,25 @@
         <v>600</v>
       </c>
       <c r="G25" s="23" t="n">
-        <v>236.22</v>
+        <v>379.87</v>
       </c>
       <c r="H25" s="24" t="n">
-        <v>236.9</v>
+        <v>391.49</v>
       </c>
       <c r="I25" s="23" t="n">
-        <v>275.55</v>
+        <v>363.15</v>
       </c>
       <c r="J25" s="23" t="n">
-        <v>208.64</v>
+        <v>409.73</v>
       </c>
       <c r="K25" s="24" t="n">
-        <v>254.94</v>
+        <v>372.06</v>
       </c>
       <c r="L25" s="23" t="n">
-        <v>201.47</v>
+        <v>373.81</v>
       </c>
       <c r="M25" s="24" t="n">
-        <v>238.31</v>
+        <v>370.4</v>
       </c>
     </row>
     <row r="26">
@@ -7973,25 +7973,25 @@
         <v>385</v>
       </c>
       <c r="G26" s="23" t="n">
-        <v>227.73</v>
+        <v>377.95</v>
       </c>
       <c r="H26" s="24" t="n">
-        <v>245.99</v>
+        <v>401.09</v>
       </c>
       <c r="I26" s="23" t="n">
-        <v>254.19</v>
+        <v>353.25</v>
       </c>
       <c r="J26" s="23" t="n">
-        <v>213.05</v>
+        <v>410.8</v>
       </c>
       <c r="K26" s="24" t="n">
-        <v>241.56</v>
+        <v>372.42</v>
       </c>
       <c r="L26" s="23" t="n">
-        <v>195.76</v>
+        <v>368.86</v>
       </c>
       <c r="M26" s="24" t="n">
-        <v>216.67</v>
+        <v>364.3</v>
       </c>
     </row>
     <row r="27">
@@ -8014,25 +8014,25 @@
         <v>385</v>
       </c>
       <c r="G27" s="23" t="n">
-        <v>213.48</v>
+        <v>372.24</v>
       </c>
       <c r="H27" s="24" t="n">
-        <v>253.21</v>
+        <v>408.23</v>
       </c>
       <c r="I27" s="23" t="n">
-        <v>246.85</v>
+        <v>355.69</v>
       </c>
       <c r="J27" s="23" t="n">
-        <v>204.09</v>
+        <v>411.62</v>
       </c>
       <c r="K27" s="24" t="n">
-        <v>242.84</v>
+        <v>369.35</v>
       </c>
       <c r="L27" s="23" t="n">
-        <v>151.99</v>
+        <v>343.77</v>
       </c>
       <c r="M27" s="24" t="n">
-        <v>184.19</v>
+        <v>348.54</v>
       </c>
     </row>
     <row r="28">
@@ -8055,25 +8055,25 @@
         <v>385</v>
       </c>
       <c r="G28" s="23" t="n">
-        <v>194.8</v>
+        <v>353.14</v>
       </c>
       <c r="H28" s="24" t="n">
-        <v>245.77</v>
+        <v>400.57</v>
       </c>
       <c r="I28" s="23" t="n">
-        <v>235.79</v>
+        <v>332.9</v>
       </c>
       <c r="J28" s="23" t="n">
-        <v>185.05</v>
+        <v>411.93</v>
       </c>
       <c r="K28" s="24" t="n">
-        <v>215.13</v>
+        <v>343.22</v>
       </c>
       <c r="L28" s="23" t="n">
-        <v>151.31</v>
+        <v>336.94</v>
       </c>
       <c r="M28" s="24" t="n">
-        <v>138.86</v>
+        <v>297.71</v>
       </c>
     </row>
     <row r="29">
@@ -8096,25 +8096,25 @@
         <v>385</v>
       </c>
       <c r="G29" s="23" t="n">
-        <v>177.07</v>
+        <v>343.7</v>
       </c>
       <c r="H29" s="24" t="n">
-        <v>239.73</v>
+        <v>393.32</v>
       </c>
       <c r="I29" s="23" t="n">
-        <v>209.51</v>
+        <v>291.25</v>
       </c>
       <c r="J29" s="23" t="n">
-        <v>181.38</v>
+        <v>397.94</v>
       </c>
       <c r="K29" s="24" t="n">
-        <v>216.79</v>
+        <v>367.03</v>
       </c>
       <c r="L29" s="23" t="n">
-        <v>104.73</v>
+        <v>312.96</v>
       </c>
       <c r="M29" s="24" t="n">
-        <v>114.24</v>
+        <v>305.69</v>
       </c>
     </row>
     <row r="30">
@@ -8137,25 +8137,25 @@
         <v>370</v>
       </c>
       <c r="G30" s="23" t="n">
-        <v>195.35</v>
+        <v>347</v>
       </c>
       <c r="H30" s="24" t="n">
-        <v>219.16</v>
+        <v>372.22</v>
       </c>
       <c r="I30" s="23" t="n">
-        <v>234.98</v>
+        <v>291.71</v>
       </c>
       <c r="J30" s="23" t="n">
-        <v>188.78</v>
+        <v>391.57</v>
       </c>
       <c r="K30" s="24" t="n">
-        <v>228.64</v>
+        <v>361.55</v>
       </c>
       <c r="L30" s="23" t="n">
-        <v>139.07</v>
+        <v>333.97</v>
       </c>
       <c r="M30" s="24" t="n">
-        <v>161.26</v>
+        <v>335.03</v>
       </c>
     </row>
     <row r="31">
@@ -8178,25 +8178,25 @@
         <v>370</v>
       </c>
       <c r="G31" s="23" t="n">
-        <v>123.95</v>
+        <v>302.56</v>
       </c>
       <c r="H31" s="24" t="n">
-        <v>185.07</v>
+        <v>336.98</v>
       </c>
       <c r="I31" s="23" t="n">
-        <v>210.28</v>
+        <v>273.72</v>
       </c>
       <c r="J31" s="23" t="n">
-        <v>77.87</v>
+        <v>300.37</v>
       </c>
       <c r="K31" s="24" t="n">
-        <v>175.42</v>
+        <v>325.83</v>
       </c>
       <c r="L31" s="23" t="n">
-        <v>58.23</v>
+        <v>300.89</v>
       </c>
       <c r="M31" s="24" t="n">
-        <v>38.78</v>
+        <v>282.52</v>
       </c>
     </row>
     <row r="32">
@@ -8219,25 +8219,25 @@
         <v>370</v>
       </c>
       <c r="G32" s="23" t="n">
-        <v>98.73999999999999</v>
+        <v>230.51</v>
       </c>
       <c r="H32" s="24" t="n">
-        <v>145.58</v>
+        <v>296.14</v>
       </c>
       <c r="I32" s="23" t="n">
-        <v>170.84</v>
+        <v>211.55</v>
       </c>
       <c r="J32" s="23" t="n">
-        <v>62.57</v>
+        <v>260.55</v>
       </c>
       <c r="K32" s="24" t="n">
-        <v>142.57</v>
+        <v>231.48</v>
       </c>
       <c r="L32" s="23" t="n">
-        <v>63.1</v>
+        <v>204.23</v>
       </c>
       <c r="M32" s="24" t="n">
-        <v>8.539999999999999</v>
+        <v>186.43</v>
       </c>
     </row>
     <row r="33">
@@ -8260,25 +8260,25 @@
         <v>370</v>
       </c>
       <c r="G33" s="23" t="n">
-        <v>81.15000000000001</v>
+        <v>105.49</v>
       </c>
       <c r="H33" s="24" t="n">
-        <v>101.11</v>
+        <v>250.49</v>
       </c>
       <c r="I33" s="23" t="n">
-        <v>102.61</v>
+        <v>117.33</v>
       </c>
       <c r="J33" s="23" t="n">
-        <v>142.46</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="K33" s="24" t="n">
-        <v>87.78</v>
+        <v>103.44</v>
       </c>
       <c r="L33" s="23" t="n">
-        <v>31.69</v>
+        <v>50.22</v>
       </c>
       <c r="M33" s="24" t="n">
-        <v>19.59</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="34">
@@ -8301,25 +8301,25 @@
         <v>197</v>
       </c>
       <c r="G34" s="23" t="n">
-        <v>46.2</v>
+        <v>77.41</v>
       </c>
       <c r="H34" s="24" t="n">
-        <v>63.22</v>
+        <v>210.73</v>
       </c>
       <c r="I34" s="23" t="n">
-        <v>56.66</v>
+        <v>73.62</v>
       </c>
       <c r="J34" s="23" t="n">
-        <v>36.83</v>
+        <v>77.53</v>
       </c>
       <c r="K34" s="24" t="n">
-        <v>51.12</v>
+        <v>46.9</v>
       </c>
       <c r="L34" s="23" t="n">
-        <v>37</v>
+        <v>34.18</v>
       </c>
       <c r="M34" s="24" t="n">
-        <v>33.89</v>
+        <v>37.97</v>
       </c>
     </row>
     <row r="35">
@@ -8342,25 +8342,25 @@
         <v>197</v>
       </c>
       <c r="G35" s="23" t="n">
-        <v>25.7</v>
+        <v>58.33</v>
       </c>
       <c r="H35" s="24" t="n">
-        <v>27.98</v>
+        <v>175.28</v>
       </c>
       <c r="I35" s="23" t="n">
-        <v>28.21</v>
+        <v>53.78</v>
       </c>
       <c r="J35" s="23" t="n">
-        <v>31.62</v>
+        <v>61.93</v>
       </c>
       <c r="K35" s="24" t="n">
-        <v>18.91</v>
+        <v>1.72</v>
       </c>
       <c r="L35" s="23" t="n">
-        <v>32.54</v>
+        <v>33.95</v>
       </c>
       <c r="M35" s="24" t="n">
-        <v>14.87</v>
+        <v>38.63</v>
       </c>
     </row>
     <row r="36">
@@ -8383,25 +8383,25 @@
         <v>197</v>
       </c>
       <c r="G36" s="23" t="n">
-        <v>7.7</v>
+        <v>27.5</v>
       </c>
       <c r="H36" s="24" t="n">
-        <v>-7.95</v>
+        <v>139.46</v>
       </c>
       <c r="I36" s="23" t="n">
-        <v>24.25</v>
+        <v>31.09</v>
       </c>
       <c r="J36" s="23" t="n">
-        <v>16.83</v>
+        <v>27.87</v>
       </c>
       <c r="K36" s="24" t="n">
-        <v>21.33</v>
+        <v>-7.88</v>
       </c>
       <c r="L36" s="23" t="n">
-        <v>-4.55</v>
+        <v>-5.92</v>
       </c>
       <c r="M36" s="24" t="n">
-        <v>-7.28</v>
+        <v>-5.92</v>
       </c>
     </row>
     <row r="37">
@@ -8424,25 +8424,25 @@
         <v>197</v>
       </c>
       <c r="G37" s="23" t="n">
-        <v>-2.15</v>
+        <v>13.07</v>
       </c>
       <c r="H37" s="24" t="n">
-        <v>-39.53</v>
+        <v>107.53</v>
       </c>
       <c r="I37" s="23" t="n">
-        <v>17.1</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="J37" s="23" t="n">
-        <v>11.63</v>
+        <v>31.99</v>
       </c>
       <c r="K37" s="24" t="n">
-        <v>19.24</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="L37" s="23" t="n">
-        <v>-11.05</v>
+        <v>-23.43</v>
       </c>
       <c r="M37" s="24" t="n">
-        <v>-16.95</v>
+        <v>-26.84</v>
       </c>
     </row>
     <row r="38">
@@ -8465,25 +8465,25 @@
         <v>50</v>
       </c>
       <c r="G38" s="23" t="n">
-        <v>-11.16</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="H38" s="24" t="n">
-        <v>-67.63</v>
+        <v>79.44</v>
       </c>
       <c r="I38" s="23" t="n">
-        <v>6.67</v>
+        <v>4.26</v>
       </c>
       <c r="J38" s="23" t="n">
-        <v>0.38</v>
+        <v>26.6</v>
       </c>
       <c r="K38" s="24" t="n">
-        <v>17.14</v>
+        <v>-10.73</v>
       </c>
       <c r="L38" s="23" t="n">
-        <v>-14.84</v>
+        <v>-15.24</v>
       </c>
       <c r="M38" s="24" t="n">
-        <v>-17.57</v>
+        <v>-19.82</v>
       </c>
     </row>
     <row r="39">
@@ -8506,25 +8506,25 @@
         <v>50</v>
       </c>
       <c r="G39" s="23" t="n">
-        <v>-14.81</v>
+        <v>6.15</v>
       </c>
       <c r="H39" s="24" t="n">
-        <v>-88.94</v>
+        <v>58.22</v>
       </c>
       <c r="I39" s="23" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.39</v>
       </c>
       <c r="J39" s="23" t="n">
-        <v>0.38</v>
+        <v>25.05</v>
       </c>
       <c r="K39" s="24" t="n">
-        <v>17.49</v>
+        <v>-15.17</v>
       </c>
       <c r="L39" s="23" t="n">
-        <v>-14.11</v>
+        <v>-8.73</v>
       </c>
       <c r="M39" s="24" t="n">
-        <v>-15.64</v>
+        <v>-18.82</v>
       </c>
     </row>
     <row r="40">
@@ -8547,25 +8547,25 @@
         <v>50</v>
       </c>
       <c r="G40" s="23" t="n">
-        <v>-17.01</v>
+        <v>3.98</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>-108.15</v>
+        <v>39.04</v>
       </c>
       <c r="I40" s="23" t="n">
-        <v>0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="J40" s="23" t="n">
-        <v>0.38</v>
+        <v>25.05</v>
       </c>
       <c r="K40" s="24" t="n">
-        <v>16.24</v>
+        <v>-15.4</v>
       </c>
       <c r="L40" s="23" t="n">
-        <v>-12.62</v>
+        <v>-7.86</v>
       </c>
       <c r="M40" s="24" t="n">
-        <v>-12.03</v>
+        <v>-12.95</v>
       </c>
     </row>
     <row r="41">
@@ -8588,25 +8588,25 @@
         <v>50</v>
       </c>
       <c r="G41" s="23" t="n">
-        <v>-19.8</v>
+        <v>4.27</v>
       </c>
       <c r="H41" s="24" t="n">
-        <v>-127.17</v>
+        <v>20.14</v>
       </c>
       <c r="I41" s="23" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="J41" s="23" t="n">
-        <v>0.38</v>
+        <v>33.58</v>
       </c>
       <c r="K41" s="24" t="n">
-        <v>16.82</v>
+        <v>-14.62</v>
       </c>
       <c r="L41" s="23" t="n">
-        <v>-11.33</v>
+        <v>-6.4</v>
       </c>
       <c r="M41" s="24" t="n">
-        <v>-12.89</v>
+        <v>-12.3</v>
       </c>
     </row>
     <row r="42">
@@ -8629,25 +8629,25 @@
         <v>50</v>
       </c>
       <c r="G42" s="23" t="n">
-        <v>-21.93</v>
+        <v>-0.48</v>
       </c>
       <c r="H42" s="24" t="n">
-        <v>-143.33</v>
+        <v>4.05</v>
       </c>
       <c r="I42" s="23" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="J42" s="23" t="n">
-        <v>0.38</v>
+        <v>25.33</v>
       </c>
       <c r="K42" s="24" t="n">
-        <v>20.02</v>
+        <v>-18.69</v>
       </c>
       <c r="L42" s="23" t="n">
-        <v>-12.61</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="M42" s="24" t="n">
-        <v>-13.42</v>
+        <v>-11.88</v>
       </c>
     </row>
     <row r="43">
@@ -8670,25 +8670,25 @@
         <v>50</v>
       </c>
       <c r="G43" s="23" t="n">
-        <v>-23.67</v>
+        <v>-4.62</v>
       </c>
       <c r="H43" s="24" t="n">
-        <v>-160.08</v>
+        <v>-12.67</v>
       </c>
       <c r="I43" s="23" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="J43" s="23" t="n">
-        <v>0.21</v>
+        <v>9.15</v>
       </c>
       <c r="K43" s="24" t="n">
-        <v>22.91</v>
+        <v>-15.59</v>
       </c>
       <c r="L43" s="23" t="n">
-        <v>-9.51</v>
+        <v>-4.37</v>
       </c>
       <c r="M43" s="24" t="n">
-        <v>-14.97</v>
+        <v>-12.44</v>
       </c>
     </row>
     <row r="44">
@@ -8711,25 +8711,25 @@
         <v>50</v>
       </c>
       <c r="G44" s="23" t="n">
-        <v>-24.28</v>
+        <v>-5.69</v>
       </c>
       <c r="H44" s="24" t="n">
-        <v>-166.85</v>
+        <v>-19.38</v>
       </c>
       <c r="I44" s="23" t="n">
-        <v>3.57</v>
+        <v>6.34</v>
       </c>
       <c r="J44" s="23" t="n">
-        <v>0.21</v>
+        <v>10.8</v>
       </c>
       <c r="K44" s="24" t="n">
-        <v>23.02</v>
+        <v>-15.66</v>
       </c>
       <c r="L44" s="23" t="n">
-        <v>-10.11</v>
+        <v>-7.98</v>
       </c>
       <c r="M44" s="24" t="n">
-        <v>-15.98</v>
+        <v>-10.88</v>
       </c>
     </row>
     <row r="45">
@@ -8752,25 +8752,25 @@
         <v>50</v>
       </c>
       <c r="G45" s="23" t="n">
-        <v>-23.34</v>
+        <v>-5.2</v>
       </c>
       <c r="H45" s="24" t="n">
-        <v>-161.12</v>
+        <v>-13.63</v>
       </c>
       <c r="I45" s="23" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="J45" s="23" t="n">
-        <v>0.21</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="K45" s="24" t="n">
-        <v>22.44</v>
+        <v>-15.94</v>
       </c>
       <c r="L45" s="23" t="n">
-        <v>-5.03</v>
+        <v>-7.27</v>
       </c>
       <c r="M45" s="24" t="n">
-        <v>-16.09</v>
+        <v>-11.45</v>
       </c>
     </row>
     <row r="46">
@@ -8793,25 +8793,25 @@
         <v>50</v>
       </c>
       <c r="G46" s="23" t="n">
-        <v>-11.66</v>
+        <v>0.25</v>
       </c>
       <c r="H46" s="24" t="n">
-        <v>-148.16</v>
+        <v>-0.66</v>
       </c>
       <c r="I46" s="23" t="n">
-        <v>6.16</v>
+        <v>10.15</v>
       </c>
       <c r="J46" s="23" t="n">
-        <v>0.21</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="K46" s="24" t="n">
-        <v>44.77</v>
+        <v>-1.42</v>
       </c>
       <c r="L46" s="23" t="n">
-        <v>0.87</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="M46" s="24" t="n">
-        <v>7.35</v>
+        <v>-6.82</v>
       </c>
     </row>
     <row r="47">
@@ -8834,25 +8834,25 @@
         <v>50</v>
       </c>
       <c r="G47" s="23" t="n">
-        <v>-16.13</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="H47" s="24" t="n">
-        <v>-153.21</v>
+        <v>-5.7</v>
       </c>
       <c r="I47" s="23" t="n">
-        <v>2.31</v>
+        <v>8.65</v>
       </c>
       <c r="J47" s="23" t="n">
-        <v>0.21</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="K47" s="24" t="n">
-        <v>37.28</v>
+        <v>-8.75</v>
       </c>
       <c r="L47" s="23" t="n">
-        <v>-0.65</v>
+        <v>-4.71</v>
       </c>
       <c r="M47" s="24" t="n">
-        <v>-1.83</v>
+        <v>-5.26</v>
       </c>
     </row>
     <row r="48">
@@ -8875,25 +8875,25 @@
         <v>50</v>
       </c>
       <c r="G48" s="23" t="n">
-        <v>-16.65</v>
+        <v>1.09</v>
       </c>
       <c r="H48" s="24" t="n">
-        <v>-157.06</v>
+        <v>-9.68</v>
       </c>
       <c r="I48" s="23" t="n">
-        <v>2.31</v>
+        <v>15.47</v>
       </c>
       <c r="J48" s="23" t="n">
-        <v>0.21</v>
+        <v>9.48</v>
       </c>
       <c r="K48" s="24" t="n">
-        <v>39.7</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="L48" s="23" t="n">
-        <v>-1.77</v>
+        <v>2.46</v>
       </c>
       <c r="M48" s="24" t="n">
-        <v>-2.9</v>
+        <v>-5.02</v>
       </c>
     </row>
     <row r="49">
@@ -8916,25 +8916,25 @@
         <v>50</v>
       </c>
       <c r="G49" s="23" t="n">
-        <v>-21.35</v>
+        <v>-3.34</v>
       </c>
       <c r="H49" s="24" t="n">
-        <v>-188.3</v>
+        <v>-40.98</v>
       </c>
       <c r="I49" s="23" t="n">
-        <v>4.09</v>
+        <v>17.96</v>
       </c>
       <c r="J49" s="23" t="n">
-        <v>0.21</v>
+        <v>16.94</v>
       </c>
       <c r="K49" s="24" t="n">
-        <v>45.83</v>
+        <v>-11.85</v>
       </c>
       <c r="L49" s="23" t="n">
-        <v>-3.48</v>
+        <v>0.4</v>
       </c>
       <c r="M49" s="24" t="n">
-        <v>-10.04</v>
+        <v>-8.710000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -8957,25 +8957,25 @@
         <v>50</v>
       </c>
       <c r="G50" s="23" t="n">
-        <v>-21.03</v>
+        <v>-3.59</v>
       </c>
       <c r="H50" s="24" t="n">
-        <v>-185.87</v>
+        <v>-38.55</v>
       </c>
       <c r="I50" s="23" t="n">
-        <v>2.31</v>
+        <v>13.7</v>
       </c>
       <c r="J50" s="23" t="n">
-        <v>0.21</v>
+        <v>9.48</v>
       </c>
       <c r="K50" s="24" t="n">
-        <v>40.5</v>
+        <v>-8.56</v>
       </c>
       <c r="L50" s="23" t="n">
-        <v>1.19</v>
+        <v>1.56</v>
       </c>
       <c r="M50" s="24" t="n">
-        <v>-7.58</v>
+        <v>-4.64</v>
       </c>
     </row>
     <row r="51">
@@ -8998,25 +8998,25 @@
         <v>50</v>
       </c>
       <c r="G51" s="23" t="n">
-        <v>-22.07</v>
+        <v>-3.16</v>
       </c>
       <c r="H51" s="24" t="n">
-        <v>-189.86</v>
+        <v>-42.55</v>
       </c>
       <c r="I51" s="23" t="n">
-        <v>2.31</v>
+        <v>13.7</v>
       </c>
       <c r="J51" s="23" t="n">
-        <v>0.21</v>
+        <v>9.48</v>
       </c>
       <c r="K51" s="24" t="n">
-        <v>40.95</v>
+        <v>-8.17</v>
       </c>
       <c r="L51" s="23" t="n">
-        <v>-2.89</v>
+        <v>3.97</v>
       </c>
       <c r="M51" s="24" t="n">
-        <v>-6.62</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="52">
@@ -9039,25 +9039,25 @@
         <v>50</v>
       </c>
       <c r="G52" s="23" t="n">
-        <v>-20.74</v>
+        <v>-2.42</v>
       </c>
       <c r="H52" s="24" t="n">
-        <v>-186.09</v>
+        <v>-38.76</v>
       </c>
       <c r="I52" s="23" t="n">
-        <v>5.88</v>
+        <v>13.7</v>
       </c>
       <c r="J52" s="23" t="n">
-        <v>0.21</v>
+        <v>9.48</v>
       </c>
       <c r="K52" s="24" t="n">
-        <v>41.41</v>
+        <v>-7.33</v>
       </c>
       <c r="L52" s="23" t="n">
-        <v>-1.15</v>
+        <v>6.33</v>
       </c>
       <c r="M52" s="24" t="n">
-        <v>-8.02</v>
+        <v>-3.48</v>
       </c>
     </row>
     <row r="53">
@@ -9080,25 +9080,25 @@
         <v>50</v>
       </c>
       <c r="G53" s="23" t="n">
-        <v>-16.28</v>
+        <v>0.71</v>
       </c>
       <c r="H53" s="24" t="n">
-        <v>-170.13</v>
+        <v>-22.77</v>
       </c>
       <c r="I53" s="23" t="n">
-        <v>7.98</v>
+        <v>15.28</v>
       </c>
       <c r="J53" s="23" t="n">
-        <v>0.21</v>
+        <v>15.51</v>
       </c>
       <c r="K53" s="24" t="n">
-        <v>41.9</v>
+        <v>-6.89</v>
       </c>
       <c r="L53" s="23" t="n">
-        <v>4.46</v>
+        <v>6.71</v>
       </c>
       <c r="M53" s="24" t="n">
-        <v>-3.66</v>
+        <v>-7.58</v>
       </c>
     </row>
     <row r="54">
@@ -9121,25 +9121,25 @@
         <v>50</v>
       </c>
       <c r="G54" s="23" t="n">
-        <v>-16.65</v>
+        <v>2.82</v>
       </c>
       <c r="H54" s="24" t="n">
-        <v>-162.39</v>
+        <v>-15.04</v>
       </c>
       <c r="I54" s="23" t="n">
-        <v>4.41</v>
+        <v>18.48</v>
       </c>
       <c r="J54" s="23" t="n">
-        <v>0.21</v>
+        <v>15.51</v>
       </c>
       <c r="K54" s="24" t="n">
-        <v>40.8</v>
+        <v>-7.18</v>
       </c>
       <c r="L54" s="23" t="n">
-        <v>2.01</v>
+        <v>8.35</v>
       </c>
       <c r="M54" s="24" t="n">
-        <v>-5.34</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="55">
@@ -9162,25 +9162,25 @@
         <v>50</v>
       </c>
       <c r="G55" s="23" t="n">
-        <v>-12.01</v>
+        <v>4.79</v>
       </c>
       <c r="H55" s="24" t="n">
-        <v>-147.47</v>
+        <v>-0.09</v>
       </c>
       <c r="I55" s="23" t="n">
-        <v>4.41</v>
+        <v>18.48</v>
       </c>
       <c r="J55" s="23" t="n">
-        <v>0.21</v>
+        <v>15.51</v>
       </c>
       <c r="K55" s="24" t="n">
-        <v>42.34</v>
+        <v>-5.94</v>
       </c>
       <c r="L55" s="23" t="n">
-        <v>9.279999999999999</v>
+        <v>7.24</v>
       </c>
       <c r="M55" s="24" t="n">
-        <v>0.45</v>
+        <v>-8.02</v>
       </c>
     </row>
     <row r="56">
@@ -9203,25 +9203,25 @@
         <v>50</v>
       </c>
       <c r="G56" s="23" t="n">
-        <v>-8.890000000000001</v>
+        <v>7.24</v>
       </c>
       <c r="H56" s="24" t="n">
-        <v>-130.96</v>
+        <v>16.37</v>
       </c>
       <c r="I56" s="23" t="n">
-        <v>4.41</v>
+        <v>18.48</v>
       </c>
       <c r="J56" s="23" t="n">
-        <v>0.21</v>
+        <v>15.51</v>
       </c>
       <c r="K56" s="24" t="n">
-        <v>42.79</v>
+        <v>-7.06</v>
       </c>
       <c r="L56" s="23" t="n">
-        <v>11.67</v>
+        <v>6.15</v>
       </c>
       <c r="M56" s="24" t="n">
-        <v>1.75</v>
+        <v>-5.61</v>
       </c>
     </row>
     <row r="57">
@@ -9244,25 +9244,25 @@
         <v>50</v>
       </c>
       <c r="G57" s="23" t="n">
-        <v>-4.59</v>
+        <v>11.93</v>
       </c>
       <c r="H57" s="24" t="n">
-        <v>-112.66</v>
+        <v>34.63</v>
       </c>
       <c r="I57" s="23" t="n">
-        <v>6.42</v>
+        <v>18.48</v>
       </c>
       <c r="J57" s="23" t="n">
-        <v>0.21</v>
+        <v>15.51</v>
       </c>
       <c r="K57" s="24" t="n">
-        <v>45.32</v>
+        <v>-3.72</v>
       </c>
       <c r="L57" s="23" t="n">
-        <v>8.140000000000001</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M57" s="24" t="n">
-        <v>10.31</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="58">
@@ -9285,25 +9285,25 @@
         <v>55</v>
       </c>
       <c r="G58" s="23" t="n">
-        <v>4.05</v>
+        <v>26.77</v>
       </c>
       <c r="H58" s="24" t="n">
-        <v>-90.69</v>
+        <v>56.65</v>
       </c>
       <c r="I58" s="23" t="n">
-        <v>8.529999999999999</v>
+        <v>26.82</v>
       </c>
       <c r="J58" s="23" t="n">
-        <v>0.21</v>
+        <v>22.14</v>
       </c>
       <c r="K58" s="24" t="n">
-        <v>50.99</v>
+        <v>1.72</v>
       </c>
       <c r="L58" s="23" t="n">
-        <v>22.86</v>
+        <v>34</v>
       </c>
       <c r="M58" s="24" t="n">
-        <v>19.97</v>
+        <v>23.53</v>
       </c>
     </row>
     <row r="59">
@@ -9326,25 +9326,25 @@
         <v>55</v>
       </c>
       <c r="G59" s="23" t="n">
-        <v>9.699999999999999</v>
+        <v>44.2</v>
       </c>
       <c r="H59" s="24" t="n">
-        <v>-65.73999999999999</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="I59" s="23" t="n">
-        <v>10.29</v>
+        <v>37.81</v>
       </c>
       <c r="J59" s="23" t="n">
-        <v>0.84</v>
+        <v>58.32</v>
       </c>
       <c r="K59" s="24" t="n">
-        <v>51.75</v>
+        <v>2.14</v>
       </c>
       <c r="L59" s="23" t="n">
-        <v>19.06</v>
+        <v>50.82</v>
       </c>
       <c r="M59" s="24" t="n">
-        <v>32.45</v>
+        <v>39.86</v>
       </c>
     </row>
     <row r="60">
@@ -9367,25 +9367,25 @@
         <v>55</v>
       </c>
       <c r="G60" s="23" t="n">
-        <v>13.79</v>
+        <v>58.06</v>
       </c>
       <c r="H60" s="24" t="n">
-        <v>-39.31</v>
+        <v>108.13</v>
       </c>
       <c r="I60" s="23" t="n">
-        <v>7.46</v>
+        <v>47.91</v>
       </c>
       <c r="J60" s="23" t="n">
-        <v>2.24</v>
+        <v>71.02</v>
       </c>
       <c r="K60" s="24" t="n">
-        <v>52.93</v>
+        <v>3.85</v>
       </c>
       <c r="L60" s="23" t="n">
-        <v>25.66</v>
+        <v>75.36</v>
       </c>
       <c r="M60" s="24" t="n">
-        <v>27.3</v>
+        <v>49.41</v>
       </c>
     </row>
     <row r="61">
@@ -9408,25 +9408,25 @@
         <v>55</v>
       </c>
       <c r="G61" s="23" t="n">
-        <v>19.56</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="H61" s="24" t="n">
-        <v>-11.56</v>
+        <v>135.88</v>
       </c>
       <c r="I61" s="23" t="n">
-        <v>8.779999999999999</v>
+        <v>47.37</v>
       </c>
       <c r="J61" s="23" t="n">
-        <v>2.74</v>
+        <v>90.03</v>
       </c>
       <c r="K61" s="24" t="n">
-        <v>56.31</v>
+        <v>6</v>
       </c>
       <c r="L61" s="23" t="n">
-        <v>27.71</v>
+        <v>94.19</v>
       </c>
       <c r="M61" s="24" t="n">
-        <v>30.04</v>
+        <v>62.13</v>
       </c>
     </row>
     <row r="62">
@@ -9449,25 +9449,25 @@
         <v>211</v>
       </c>
       <c r="G62" s="23" t="n">
-        <v>19.33</v>
+        <v>93.84</v>
       </c>
       <c r="H62" s="24" t="n">
-        <v>23.08</v>
+        <v>170.93</v>
       </c>
       <c r="I62" s="23" t="n">
-        <v>21.77</v>
+        <v>57.69</v>
       </c>
       <c r="J62" s="23" t="n">
-        <v>9.33</v>
+        <v>113.77</v>
       </c>
       <c r="K62" s="24" t="n">
-        <v>50.17</v>
+        <v>30.19</v>
       </c>
       <c r="L62" s="23" t="n">
-        <v>13.55</v>
+        <v>114.52</v>
       </c>
       <c r="M62" s="24" t="n">
-        <v>-2.32</v>
+        <v>87.88</v>
       </c>
     </row>
     <row r="63">
@@ -9490,25 +9490,25 @@
         <v>211</v>
       </c>
       <c r="G63" s="23" t="n">
-        <v>51.31</v>
+        <v>127.77</v>
       </c>
       <c r="H63" s="24" t="n">
-        <v>48.06</v>
+        <v>196.4</v>
       </c>
       <c r="I63" s="23" t="n">
-        <v>51.53</v>
+        <v>86.13</v>
       </c>
       <c r="J63" s="23" t="n">
-        <v>18.13</v>
+        <v>111.61</v>
       </c>
       <c r="K63" s="24" t="n">
-        <v>72.55</v>
+        <v>60.02</v>
       </c>
       <c r="L63" s="23" t="n">
-        <v>68.52</v>
+        <v>184.18</v>
       </c>
       <c r="M63" s="24" t="n">
-        <v>49.16</v>
+        <v>140.97</v>
       </c>
     </row>
     <row r="64">
@@ -9531,25 +9531,25 @@
         <v>211</v>
       </c>
       <c r="G64" s="23" t="n">
-        <v>124.19</v>
+        <v>152.73</v>
       </c>
       <c r="H64" s="24" t="n">
-        <v>74.67</v>
+        <v>223.48</v>
       </c>
       <c r="I64" s="23" t="n">
-        <v>125.51</v>
+        <v>98.63</v>
       </c>
       <c r="J64" s="23" t="n">
-        <v>137.91</v>
+        <v>153.62</v>
       </c>
       <c r="K64" s="24" t="n">
-        <v>112.6</v>
+        <v>129.21</v>
       </c>
       <c r="L64" s="23" t="n">
-        <v>137.28</v>
+        <v>162.75</v>
       </c>
       <c r="M64" s="24" t="n">
-        <v>151.3</v>
+        <v>160.71</v>
       </c>
     </row>
     <row r="65">
@@ -9572,25 +9572,25 @@
         <v>211</v>
       </c>
       <c r="G65" s="23" t="n">
-        <v>164.79</v>
+        <v>187.87</v>
       </c>
       <c r="H65" s="24" t="n">
-        <v>111.47</v>
+        <v>261.14</v>
       </c>
       <c r="I65" s="23" t="n">
-        <v>175.78</v>
+        <v>145.91</v>
       </c>
       <c r="J65" s="23" t="n">
-        <v>156.3</v>
+        <v>158.39</v>
       </c>
       <c r="K65" s="24" t="n">
-        <v>162.78</v>
+        <v>193.4</v>
       </c>
       <c r="L65" s="23" t="n">
-        <v>191.43</v>
+        <v>182.87</v>
       </c>
       <c r="M65" s="24" t="n">
-        <v>184.49</v>
+        <v>197.52</v>
       </c>
     </row>
     <row r="66">
@@ -9613,25 +9613,25 @@
         <v>386</v>
       </c>
       <c r="G66" s="23" t="n">
-        <v>152.24</v>
+        <v>302.48</v>
       </c>
       <c r="H66" s="24" t="n">
-        <v>127.37</v>
+        <v>277.59</v>
       </c>
       <c r="I66" s="23" t="n">
-        <v>223.76</v>
+        <v>247.25</v>
       </c>
       <c r="J66" s="23" t="n">
-        <v>51.24</v>
+        <v>312.41</v>
       </c>
       <c r="K66" s="24" t="n">
-        <v>198.42</v>
+        <v>320.97</v>
       </c>
       <c r="L66" s="23" t="n">
-        <v>171.08</v>
+        <v>332.38</v>
       </c>
       <c r="M66" s="24" t="n">
-        <v>136.67</v>
+        <v>323.72</v>
       </c>
     </row>
     <row r="67">
@@ -9654,25 +9654,25 @@
         <v>386</v>
       </c>
       <c r="G67" s="23" t="n">
-        <v>150.3</v>
+        <v>342.48</v>
       </c>
       <c r="H67" s="24" t="n">
-        <v>151.84</v>
+        <v>303.26</v>
       </c>
       <c r="I67" s="23" t="n">
-        <v>238.78</v>
+        <v>300.59</v>
       </c>
       <c r="J67" s="23" t="n">
-        <v>48.29</v>
+        <v>346.26</v>
       </c>
       <c r="K67" s="24" t="n">
-        <v>215.02</v>
+        <v>389.08</v>
       </c>
       <c r="L67" s="23" t="n">
-        <v>133.7</v>
+        <v>358.99</v>
       </c>
       <c r="M67" s="24" t="n">
-        <v>110.86</v>
+        <v>353.07</v>
       </c>
     </row>
     <row r="68">
@@ -9695,25 +9695,25 @@
         <v>386</v>
       </c>
       <c r="G68" s="23" t="n">
-        <v>150.43</v>
+        <v>370.89</v>
       </c>
       <c r="H68" s="24" t="n">
-        <v>180.4</v>
+        <v>332.85</v>
       </c>
       <c r="I68" s="23" t="n">
-        <v>221.68</v>
+        <v>348.87</v>
       </c>
       <c r="J68" s="23" t="n">
-        <v>55.45</v>
+        <v>367.38</v>
       </c>
       <c r="K68" s="24" t="n">
-        <v>211.43</v>
+        <v>407.5</v>
       </c>
       <c r="L68" s="23" t="n">
-        <v>125.41</v>
+        <v>397</v>
       </c>
       <c r="M68" s="24" t="n">
-        <v>109.12</v>
+        <v>367.52</v>
       </c>
     </row>
     <row r="69">
@@ -9736,25 +9736,25 @@
         <v>386</v>
       </c>
       <c r="G69" s="23" t="n">
-        <v>179</v>
+        <v>372.63</v>
       </c>
       <c r="H69" s="24" t="n">
-        <v>202.74</v>
+        <v>356</v>
       </c>
       <c r="I69" s="23" t="n">
-        <v>197.86</v>
+        <v>341.15</v>
       </c>
       <c r="J69" s="23" t="n">
-        <v>106.78</v>
+        <v>369.63</v>
       </c>
       <c r="K69" s="24" t="n">
-        <v>234.83</v>
+        <v>414.78</v>
       </c>
       <c r="L69" s="23" t="n">
-        <v>156.61</v>
+        <v>377.54</v>
       </c>
       <c r="M69" s="24" t="n">
-        <v>178.01</v>
+        <v>375.47</v>
       </c>
     </row>
     <row r="70">
@@ -9771,25 +9771,25 @@
       <c r="E70" s="13" t="n"/>
       <c r="F70" s="13" t="n"/>
       <c r="G70" s="23" t="n">
-        <v>182.39</v>
+        <v>380.15</v>
       </c>
       <c r="H70" s="24" t="n">
-        <v>218.59</v>
+        <v>372.53</v>
       </c>
       <c r="I70" s="23" t="n">
-        <v>206.16</v>
+        <v>345.5</v>
       </c>
       <c r="J70" s="23" t="n">
-        <v>105.67</v>
+        <v>395.88</v>
       </c>
       <c r="K70" s="24" t="n">
-        <v>222.09</v>
+        <v>410.02</v>
       </c>
       <c r="L70" s="23" t="n">
-        <v>164.42</v>
+        <v>378.73</v>
       </c>
       <c r="M70" s="24" t="n">
-        <v>182.02</v>
+        <v>377.91</v>
       </c>
     </row>
     <row r="71">
@@ -9806,25 +9806,25 @@
       <c r="E71" s="13" t="n"/>
       <c r="F71" s="13" t="n"/>
       <c r="G71" s="23" t="n">
-        <v>171.27</v>
+        <v>377.98</v>
       </c>
       <c r="H71" s="24" t="n">
-        <v>238.9</v>
+        <v>393.77</v>
       </c>
       <c r="I71" s="23" t="n">
-        <v>202.08</v>
+        <v>362.75</v>
       </c>
       <c r="J71" s="23" t="n">
-        <v>129.28</v>
+        <v>410.05</v>
       </c>
       <c r="K71" s="24" t="n">
-        <v>208.78</v>
+        <v>396.16</v>
       </c>
       <c r="L71" s="23" t="n">
-        <v>130.07</v>
+        <v>352.22</v>
       </c>
       <c r="M71" s="24" t="n">
-        <v>124.91</v>
+        <v>353.88</v>
       </c>
     </row>
     <row r="72">
@@ -9841,25 +9841,25 @@
       <c r="E72" s="13" t="n"/>
       <c r="F72" s="13" t="n"/>
       <c r="G72" s="23" t="n">
-        <v>180.62</v>
+        <v>374.58</v>
       </c>
       <c r="H72" s="24" t="n">
-        <v>250.46</v>
+        <v>405.96</v>
       </c>
       <c r="I72" s="23" t="n">
-        <v>200.24</v>
+        <v>363.28</v>
       </c>
       <c r="J72" s="23" t="n">
-        <v>160.46</v>
+        <v>404.19</v>
       </c>
       <c r="K72" s="24" t="n">
-        <v>207.87</v>
+        <v>382.91</v>
       </c>
       <c r="L72" s="23" t="n">
-        <v>131.54</v>
+        <v>344.38</v>
       </c>
       <c r="M72" s="24" t="n">
-        <v>140.01</v>
+        <v>349.67</v>
       </c>
     </row>
     <row r="73">
@@ -9876,25 +9876,25 @@
       <c r="E73" s="13" t="n"/>
       <c r="F73" s="13" t="n"/>
       <c r="G73" s="23" t="n">
-        <v>171.98</v>
+        <v>374.12</v>
       </c>
       <c r="H73" s="24" t="n">
-        <v>251.19</v>
+        <v>406.72</v>
       </c>
       <c r="I73" s="23" t="n">
-        <v>206.45</v>
+        <v>354.12</v>
       </c>
       <c r="J73" s="23" t="n">
-        <v>139.7</v>
+        <v>403.55</v>
       </c>
       <c r="K73" s="24" t="n">
-        <v>201.43</v>
+        <v>377.72</v>
       </c>
       <c r="L73" s="23" t="n">
-        <v>114.53</v>
+        <v>346.67</v>
       </c>
       <c r="M73" s="24" t="n">
-        <v>126.07</v>
+        <v>359.73</v>
       </c>
     </row>
     <row r="74">
@@ -9917,25 +9917,25 @@
         <v>419.92</v>
       </c>
       <c r="G74" s="23" t="n">
-        <v>151.67</v>
+        <v>363.14</v>
       </c>
       <c r="H74" s="24" t="n">
-        <v>245.17</v>
+        <v>400.71</v>
       </c>
       <c r="I74" s="23" t="n">
-        <v>197.8</v>
+        <v>332.14</v>
       </c>
       <c r="J74" s="23" t="n">
-        <v>90.31999999999999</v>
+        <v>403.13</v>
       </c>
       <c r="K74" s="24" t="n">
-        <v>189.86</v>
+        <v>370.73</v>
       </c>
       <c r="L74" s="23" t="n">
-        <v>82.05</v>
+        <v>329.39</v>
       </c>
       <c r="M74" s="24" t="n">
-        <v>114.25</v>
+        <v>347.28</v>
       </c>
     </row>
     <row r="75">
@@ -9958,25 +9958,25 @@
         <v>419.92</v>
       </c>
       <c r="G75" s="23" t="n">
-        <v>145.61</v>
+        <v>365.06</v>
       </c>
       <c r="H75" s="24" t="n">
-        <v>239.78</v>
+        <v>395.23</v>
       </c>
       <c r="I75" s="23" t="n">
-        <v>184.87</v>
+        <v>335.84</v>
       </c>
       <c r="J75" s="23" t="n">
-        <v>107.96</v>
+        <v>402.65</v>
       </c>
       <c r="K75" s="24" t="n">
-        <v>168.47</v>
+        <v>365.06</v>
       </c>
       <c r="L75" s="23" t="n">
-        <v>103.01</v>
+        <v>342.2</v>
       </c>
       <c r="M75" s="24" t="n">
-        <v>78.63</v>
+        <v>353.2</v>
       </c>
     </row>
     <row r="76">
@@ -9999,25 +9999,25 @@
         <v>419.92</v>
       </c>
       <c r="G76" s="23" t="n">
-        <v>145.67</v>
+        <v>364.76</v>
       </c>
       <c r="H76" s="24" t="n">
-        <v>235.55</v>
+        <v>391.25</v>
       </c>
       <c r="I76" s="23" t="n">
-        <v>188.39</v>
+        <v>338.94</v>
       </c>
       <c r="J76" s="23" t="n">
-        <v>112.22</v>
+        <v>403.73</v>
       </c>
       <c r="K76" s="24" t="n">
-        <v>163.1</v>
+        <v>369.02</v>
       </c>
       <c r="L76" s="23" t="n">
-        <v>100.39</v>
+        <v>339.05</v>
       </c>
       <c r="M76" s="24" t="n">
-        <v>82.79000000000001</v>
+        <v>349.62</v>
       </c>
     </row>
     <row r="77">
@@ -10040,25 +10040,25 @@
         <v>419.92</v>
       </c>
       <c r="G77" s="23" t="n">
-        <v>145.09</v>
+        <v>368.1</v>
       </c>
       <c r="H77" s="24" t="n">
-        <v>230.75</v>
+        <v>386.43</v>
       </c>
       <c r="I77" s="23" t="n">
-        <v>187.87</v>
+        <v>345.7</v>
       </c>
       <c r="J77" s="23" t="n">
-        <v>107.39</v>
+        <v>403.73</v>
       </c>
       <c r="K77" s="24" t="n">
-        <v>159.03</v>
+        <v>368.45</v>
       </c>
       <c r="L77" s="23" t="n">
-        <v>98.06999999999999</v>
+        <v>348.03</v>
       </c>
       <c r="M77" s="24" t="n">
-        <v>95.73</v>
+        <v>358.43</v>
       </c>
     </row>
     <row r="78">
@@ -10081,25 +10081,25 @@
         <v>390.11</v>
       </c>
       <c r="G78" s="23" t="n">
-        <v>140.5</v>
+        <v>365.23</v>
       </c>
       <c r="H78" s="24" t="n">
-        <v>223.61</v>
+        <v>379.39</v>
       </c>
       <c r="I78" s="23" t="n">
-        <v>174.89</v>
+        <v>340.17</v>
       </c>
       <c r="J78" s="23" t="n">
-        <v>114.55</v>
+        <v>402.19</v>
       </c>
       <c r="K78" s="24" t="n">
-        <v>152.37</v>
+        <v>366.77</v>
       </c>
       <c r="L78" s="23" t="n">
-        <v>91.3</v>
+        <v>346.71</v>
       </c>
       <c r="M78" s="24" t="n">
-        <v>94.42</v>
+        <v>357.89</v>
       </c>
     </row>
     <row r="79">
@@ -10122,25 +10122,25 @@
         <v>390.11</v>
       </c>
       <c r="G79" s="23" t="n">
-        <v>134.31</v>
+        <v>359.26</v>
       </c>
       <c r="H79" s="24" t="n">
-        <v>217.71</v>
+        <v>373.45</v>
       </c>
       <c r="I79" s="23" t="n">
-        <v>177.43</v>
+        <v>327.55</v>
       </c>
       <c r="J79" s="23" t="n">
-        <v>116.26</v>
+        <v>401.21</v>
       </c>
       <c r="K79" s="24" t="n">
-        <v>137.71</v>
+        <v>363.1</v>
       </c>
       <c r="L79" s="23" t="n">
-        <v>80.91</v>
+        <v>340</v>
       </c>
       <c r="M79" s="24" t="n">
-        <v>83.48999999999999</v>
+        <v>352.12</v>
       </c>
     </row>
     <row r="80">
@@ -10163,25 +10163,25 @@
         <v>390.11</v>
       </c>
       <c r="G80" s="23" t="n">
-        <v>128.83</v>
+        <v>353.39</v>
       </c>
       <c r="H80" s="24" t="n">
-        <v>211.05</v>
+        <v>366.78</v>
       </c>
       <c r="I80" s="23" t="n">
-        <v>170.68</v>
+        <v>328.87</v>
       </c>
       <c r="J80" s="23" t="n">
-        <v>130.29</v>
+        <v>386.48</v>
       </c>
       <c r="K80" s="24" t="n">
-        <v>131.41</v>
+        <v>362.86</v>
       </c>
       <c r="L80" s="23" t="n">
-        <v>64.63</v>
+        <v>330.3</v>
       </c>
       <c r="M80" s="24" t="n">
-        <v>71.81999999999999</v>
+        <v>346.65</v>
       </c>
     </row>
     <row r="81">
@@ -10204,25 +10204,25 @@
         <v>390.11</v>
       </c>
       <c r="G81" s="23" t="n">
-        <v>133.5</v>
+        <v>354.89</v>
       </c>
       <c r="H81" s="24" t="n">
-        <v>210.2</v>
+        <v>365.89</v>
       </c>
       <c r="I81" s="23" t="n">
-        <v>175.7</v>
+        <v>330.43</v>
       </c>
       <c r="J81" s="23" t="n">
-        <v>135.73</v>
+        <v>385.16</v>
       </c>
       <c r="K81" s="24" t="n">
-        <v>126.82</v>
+        <v>363.87</v>
       </c>
       <c r="L81" s="23" t="n">
-        <v>77.7</v>
+        <v>328.84</v>
       </c>
       <c r="M81" s="24" t="n">
-        <v>81.28</v>
+        <v>356.63</v>
       </c>
     </row>
     <row r="82">
@@ -10245,25 +10245,25 @@
         <v>390.11</v>
       </c>
       <c r="G82" s="23" t="n">
-        <v>131.61</v>
+        <v>352.78</v>
       </c>
       <c r="H82" s="24" t="n">
-        <v>205.88</v>
+        <v>361.62</v>
       </c>
       <c r="I82" s="23" t="n">
-        <v>187.09</v>
+        <v>322.41</v>
       </c>
       <c r="J82" s="23" t="n">
-        <v>130.86</v>
+        <v>383.31</v>
       </c>
       <c r="K82" s="24" t="n">
-        <v>120</v>
+        <v>363.63</v>
       </c>
       <c r="L82" s="23" t="n">
-        <v>65.25</v>
+        <v>328.48</v>
       </c>
       <c r="M82" s="24" t="n">
-        <v>86.34999999999999</v>
+        <v>358.81</v>
       </c>
     </row>
     <row r="83">
@@ -10286,25 +10286,25 @@
         <v>390.11</v>
       </c>
       <c r="G83" s="23" t="n">
-        <v>128.94</v>
+        <v>357.11</v>
       </c>
       <c r="H83" s="24" t="n">
-        <v>211.93</v>
+        <v>367.74</v>
       </c>
       <c r="I83" s="23" t="n">
-        <v>160.65</v>
+        <v>324.84</v>
       </c>
       <c r="J83" s="23" t="n">
-        <v>126.94</v>
+        <v>388.33</v>
       </c>
       <c r="K83" s="24" t="n">
-        <v>134.47</v>
+        <v>368.79</v>
       </c>
       <c r="L83" s="23" t="n">
-        <v>64.94</v>
+        <v>333.62</v>
       </c>
       <c r="M83" s="24" t="n">
-        <v>82.39</v>
+        <v>361.13</v>
       </c>
     </row>
     <row r="84">
@@ -10327,25 +10327,25 @@
         <v>390.11</v>
       </c>
       <c r="G84" s="23" t="n">
-        <v>135.7</v>
+        <v>364.75</v>
       </c>
       <c r="H84" s="24" t="n">
-        <v>219</v>
+        <v>375.01</v>
       </c>
       <c r="I84" s="23" t="n">
-        <v>164.65</v>
+        <v>332.02</v>
       </c>
       <c r="J84" s="23" t="n">
-        <v>123.37</v>
+        <v>407.04</v>
       </c>
       <c r="K84" s="24" t="n">
-        <v>138.51</v>
+        <v>370.03</v>
       </c>
       <c r="L84" s="23" t="n">
-        <v>84.95999999999999</v>
+        <v>341.57</v>
       </c>
       <c r="M84" s="24" t="n">
-        <v>91.97</v>
+        <v>364.34</v>
       </c>
     </row>
     <row r="85">
@@ -10368,25 +10368,25 @@
         <v>390.11</v>
       </c>
       <c r="G85" s="23" t="n">
-        <v>136.56</v>
+        <v>366.82</v>
       </c>
       <c r="H85" s="24" t="n">
-        <v>223.97</v>
+        <v>380.21</v>
       </c>
       <c r="I85" s="23" t="n">
-        <v>133.37</v>
+        <v>327.39</v>
       </c>
       <c r="J85" s="23" t="n">
-        <v>133.85</v>
+        <v>408.03</v>
       </c>
       <c r="K85" s="24" t="n">
-        <v>145.36</v>
+        <v>373.25</v>
       </c>
       <c r="L85" s="23" t="n">
-        <v>99.88</v>
+        <v>345.8</v>
       </c>
       <c r="M85" s="24" t="n">
-        <v>92.94</v>
+        <v>368.51</v>
       </c>
     </row>
     <row r="86">
@@ -10409,25 +10409,25 @@
         <v>600</v>
       </c>
       <c r="G86" s="23" t="n">
-        <v>143.36</v>
+        <v>365.46</v>
       </c>
       <c r="H86" s="24" t="n">
-        <v>229.4</v>
+        <v>386.16</v>
       </c>
       <c r="I86" s="23" t="n">
-        <v>148.86</v>
+        <v>335.28</v>
       </c>
       <c r="J86" s="23" t="n">
-        <v>141.35</v>
+        <v>411.75</v>
       </c>
       <c r="K86" s="24" t="n">
-        <v>155.59</v>
+        <v>371.23</v>
       </c>
       <c r="L86" s="23" t="n">
-        <v>94.79000000000001</v>
+        <v>332.71</v>
       </c>
       <c r="M86" s="24" t="n">
-        <v>99.44</v>
+        <v>358.04</v>
       </c>
     </row>
     <row r="87">
@@ -10450,25 +10450,25 @@
         <v>600</v>
       </c>
       <c r="G87" s="23" t="n">
-        <v>139.19</v>
+        <v>366.32</v>
       </c>
       <c r="H87" s="24" t="n">
-        <v>225.43</v>
+        <v>382.05</v>
       </c>
       <c r="I87" s="23" t="n">
-        <v>145.33</v>
+        <v>327.55</v>
       </c>
       <c r="J87" s="23" t="n">
-        <v>139.9</v>
+        <v>410.7</v>
       </c>
       <c r="K87" s="24" t="n">
-        <v>149.01</v>
+        <v>369.51</v>
       </c>
       <c r="L87" s="23" t="n">
-        <v>80.87</v>
+        <v>347.16</v>
       </c>
       <c r="M87" s="24" t="n">
-        <v>104.03</v>
+        <v>363.41</v>
       </c>
     </row>
     <row r="88">
@@ -10491,25 +10491,25 @@
         <v>600</v>
       </c>
       <c r="G88" s="23" t="n">
-        <v>137.16</v>
+        <v>363.01</v>
       </c>
       <c r="H88" s="24" t="n">
-        <v>227.59</v>
+        <v>384.31</v>
       </c>
       <c r="I88" s="23" t="n">
-        <v>146.9</v>
+        <v>332.56</v>
       </c>
       <c r="J88" s="23" t="n">
-        <v>130.21</v>
+        <v>412.39</v>
       </c>
       <c r="K88" s="24" t="n">
-        <v>154.49</v>
+        <v>369.41</v>
       </c>
       <c r="L88" s="23" t="n">
-        <v>74.34</v>
+        <v>327.09</v>
       </c>
       <c r="M88" s="24" t="n">
-        <v>99.15000000000001</v>
+        <v>354.72</v>
       </c>
     </row>
     <row r="89">
@@ -10532,25 +10532,25 @@
         <v>600</v>
       </c>
       <c r="G89" s="23" t="n">
-        <v>151.27</v>
+        <v>368.54</v>
       </c>
       <c r="H89" s="24" t="n">
-        <v>227.43</v>
+        <v>384.14</v>
       </c>
       <c r="I89" s="23" t="n">
-        <v>162.99</v>
+        <v>338.82</v>
       </c>
       <c r="J89" s="23" t="n">
-        <v>150.46</v>
+        <v>412.39</v>
       </c>
       <c r="K89" s="24" t="n">
-        <v>155.8</v>
+        <v>371.73</v>
       </c>
       <c r="L89" s="23" t="n">
-        <v>112.33</v>
+        <v>346.14</v>
       </c>
       <c r="M89" s="24" t="n">
-        <v>106.51</v>
+        <v>359.91</v>
       </c>
     </row>
     <row r="90">
@@ -10573,25 +10573,25 @@
         <v>600</v>
       </c>
       <c r="G90" s="23" t="n">
-        <v>155.98</v>
+        <v>369.48</v>
       </c>
       <c r="H90" s="24" t="n">
-        <v>223.85</v>
+        <v>380.42</v>
       </c>
       <c r="I90" s="23" t="n">
-        <v>192.4</v>
+        <v>343.33</v>
       </c>
       <c r="J90" s="23" t="n">
-        <v>143.13</v>
+        <v>412.39</v>
       </c>
       <c r="K90" s="24" t="n">
-        <v>160.29</v>
+        <v>372.05</v>
       </c>
       <c r="L90" s="23" t="n">
-        <v>121.91</v>
+        <v>354.78</v>
       </c>
       <c r="M90" s="24" t="n">
-        <v>100.11</v>
+        <v>355.01</v>
       </c>
     </row>
     <row r="91">
@@ -10614,25 +10614,25 @@
         <v>600</v>
       </c>
       <c r="G91" s="23" t="n">
-        <v>161.85</v>
+        <v>373.84</v>
       </c>
       <c r="H91" s="24" t="n">
-        <v>231.23</v>
+        <v>387.91</v>
       </c>
       <c r="I91" s="23" t="n">
-        <v>193.6</v>
+        <v>353.88</v>
       </c>
       <c r="J91" s="23" t="n">
-        <v>158.54</v>
+        <v>412.52</v>
       </c>
       <c r="K91" s="24" t="n">
-        <v>186.05</v>
+        <v>381.09</v>
       </c>
       <c r="L91" s="23" t="n">
-        <v>107.51</v>
+        <v>357.08</v>
       </c>
       <c r="M91" s="24" t="n">
-        <v>99.61</v>
+        <v>351.62</v>
       </c>
     </row>
     <row r="92">
@@ -10655,25 +10655,25 @@
         <v>600</v>
       </c>
       <c r="G92" s="23" t="n">
-        <v>185.38</v>
+        <v>374.92</v>
       </c>
       <c r="H92" s="24" t="n">
-        <v>238.11</v>
+        <v>394.88</v>
       </c>
       <c r="I92" s="23" t="n">
-        <v>190.73</v>
+        <v>355.82</v>
       </c>
       <c r="J92" s="23" t="n">
-        <v>210.28</v>
+        <v>411.65</v>
       </c>
       <c r="K92" s="24" t="n">
-        <v>202.04</v>
+        <v>389.18</v>
       </c>
       <c r="L92" s="23" t="n">
-        <v>145.23</v>
+        <v>343.55</v>
       </c>
       <c r="M92" s="24" t="n">
-        <v>130.03</v>
+        <v>356.11</v>
       </c>
     </row>
     <row r="93">
@@ -10696,25 +10696,25 @@
         <v>600</v>
       </c>
       <c r="G93" s="23" t="n">
-        <v>206.67</v>
+        <v>380.25</v>
       </c>
       <c r="H93" s="24" t="n">
-        <v>234.94</v>
+        <v>391.51</v>
       </c>
       <c r="I93" s="23" t="n">
-        <v>209.69</v>
+        <v>359.08</v>
       </c>
       <c r="J93" s="23" t="n">
-        <v>247.31</v>
+        <v>411.19</v>
       </c>
       <c r="K93" s="24" t="n">
-        <v>202.19</v>
+        <v>385.27</v>
       </c>
       <c r="L93" s="23" t="n">
-        <v>190.87</v>
+        <v>367.47</v>
       </c>
       <c r="M93" s="24" t="n">
-        <v>156.37</v>
+        <v>368.23</v>
       </c>
     </row>
     <row r="94">
@@ -10737,25 +10737,25 @@
         <v>390.5</v>
       </c>
       <c r="G94" s="23" t="n">
-        <v>237.15</v>
+        <v>392.1</v>
       </c>
       <c r="H94" s="24" t="n">
-        <v>227.43</v>
+        <v>384.15</v>
       </c>
       <c r="I94" s="23" t="n">
-        <v>245.34</v>
+        <v>370.81</v>
       </c>
       <c r="J94" s="23" t="n">
-        <v>275.1</v>
+        <v>411.19</v>
       </c>
       <c r="K94" s="24" t="n">
-        <v>216.6</v>
+        <v>389.1</v>
       </c>
       <c r="L94" s="23" t="n">
-        <v>251.49</v>
+        <v>407.2</v>
       </c>
       <c r="M94" s="24" t="n">
-        <v>204.13</v>
+        <v>389.73</v>
       </c>
     </row>
     <row r="95">
@@ -10778,25 +10778,25 @@
         <v>390.5</v>
       </c>
       <c r="G95" s="23" t="n">
-        <v>243.8</v>
+        <v>398.52</v>
       </c>
       <c r="H95" s="24" t="n">
-        <v>220.7</v>
+        <v>377.09</v>
       </c>
       <c r="I95" s="23" t="n">
-        <v>250.69</v>
+        <v>370.34</v>
       </c>
       <c r="J95" s="23" t="n">
-        <v>276.97</v>
+        <v>411.19</v>
       </c>
       <c r="K95" s="24" t="n">
-        <v>231.98</v>
+        <v>407.88</v>
       </c>
       <c r="L95" s="23" t="n">
-        <v>258.71</v>
+        <v>415.17</v>
       </c>
       <c r="M95" s="24" t="n">
-        <v>219.5</v>
+        <v>407.83</v>
       </c>
     </row>
     <row r="96">
@@ -10819,25 +10819,25 @@
         <v>390.5</v>
       </c>
       <c r="G96" s="23" t="n">
-        <v>215.1</v>
+        <v>386.29</v>
       </c>
       <c r="H96" s="24" t="n">
-        <v>204.67</v>
+        <v>360.61</v>
       </c>
       <c r="I96" s="23" t="n">
-        <v>228.86</v>
+        <v>367.8</v>
       </c>
       <c r="J96" s="23" t="n">
-        <v>230.09</v>
+        <v>404.22</v>
       </c>
       <c r="K96" s="24" t="n">
-        <v>217.18</v>
+        <v>399.27</v>
       </c>
       <c r="L96" s="23" t="n">
-        <v>220.57</v>
+        <v>398.33</v>
       </c>
       <c r="M96" s="24" t="n">
-        <v>186.29</v>
+        <v>384.48</v>
       </c>
     </row>
     <row r="97">
@@ -10862,25 +10862,25 @@
         <v>390.5</v>
       </c>
       <c r="G97" s="23" t="n">
-        <v>159.1</v>
+        <v>363.86</v>
       </c>
       <c r="H97" s="24" t="n">
-        <v>197.25</v>
+        <v>352.76</v>
       </c>
       <c r="I97" s="23" t="n">
-        <v>208.17</v>
+        <v>355.25</v>
       </c>
       <c r="J97" s="23" t="n">
-        <v>99.52</v>
+        <v>381.49</v>
       </c>
       <c r="K97" s="24" t="n">
-        <v>189.62</v>
+        <v>356.06</v>
       </c>
       <c r="L97" s="23" t="n">
-        <v>131.26</v>
+        <v>375.87</v>
       </c>
       <c r="M97" s="24" t="n">
-        <v>131.6</v>
+        <v>360.41</v>
       </c>
     </row>
   </sheetData>
